--- a/08-catalogo/catalogo_canal.xlsx
+++ b/08-catalogo/catalogo_canal.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Leyenda" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$S$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$T$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S41"/>
+  <dimension ref="A1:T41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -501,14 +501,15 @@
     <col width="30" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="62" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="62" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -569,40 +570,45 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>registro</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>semilla</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>duracion_min</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>comando_regeneracion</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>estado</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>fecha_publicacion</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>vistas</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>suscriptores</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>subs_por_1000</t>
         </is>
@@ -630,7 +636,7 @@
 Compuesta con raíz en 528 Hz, en entonación justa, modo hirajoshi.
 Para acompañar una práctica de respiración.
 Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Cuencos sintetizados cada 4 respiraciones.
+Cuencos y canto de ave sintetizados, sin grabaciones.
 Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
 — English —
 Composed with a root of 528 Hz in just intonation, hirajoshi mode.
@@ -665,27 +671,32 @@
           <t>hirajoshi</t>
         </is>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="n">
         <v>454078</v>
       </c>
-      <c r="M2" s="2" t="n">
+      <c r="N2" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 60 --raiz 528 --modo hirajoshi --semilla 454078</t>
         </is>
       </c>
-      <c r="O2" s="4" t="inlineStr">
+      <c r="P2" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="P2" s="4" t="inlineStr"/>
       <c r="Q2" s="4" t="inlineStr"/>
       <c r="R2" s="4" t="inlineStr"/>
-      <c r="S2" s="5">
-        <f>IFERROR(R2/Q2*1000,"")</f>
+      <c r="S2" s="4" t="inlineStr"/>
+      <c r="T2" s="5">
+        <f>IFERROR(S2/R2*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -711,7 +722,7 @@
 Compuesta con raíz en 432 Hz, en entonación justa, modo kumoi.
 Para acompañar una práctica de respiración.
 Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Cuencos sintetizados cada 4 respiraciones.
+Cuencos y canto de ave sintetizados, sin grabaciones.
 Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
 — English —
 Composed with a root of 432 Hz in just intonation, kumoi mode.
@@ -746,27 +757,32 @@
           <t>kumoi</t>
         </is>
       </c>
-      <c r="L3" s="2" t="n">
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="n">
         <v>146597</v>
       </c>
-      <c r="M3" s="2" t="n">
+      <c r="N3" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 60 --raiz 432 --modo kumoi --semilla 146597</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr"/>
       <c r="Q3" s="4" t="inlineStr"/>
       <c r="R3" s="4" t="inlineStr"/>
-      <c r="S3" s="5">
-        <f>IFERROR(R3/Q3*1000,"")</f>
+      <c r="S3" s="4" t="inlineStr"/>
+      <c r="T3" s="5">
+        <f>IFERROR(S3/R3*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -792,7 +808,7 @@
 Compuesta con raíz en 396 Hz, en entonación justa, modo kumoi.
 Para acompañar una práctica de respiración.
 Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Cuencos sintetizados cada 4 respiraciones.
+Cuencos y canto de ave sintetizados, sin grabaciones.
 Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
 — English —
 Composed with a root of 396 Hz in just intonation, kumoi mode.
@@ -827,27 +843,32 @@
           <t>kumoi</t>
         </is>
       </c>
-      <c r="L4" s="2" t="n">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
         <v>338018</v>
       </c>
-      <c r="M4" s="2" t="n">
+      <c r="N4" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 60 --raiz 396 --modo kumoi --semilla 338018</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="P4" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="P4" s="4" t="inlineStr"/>
       <c r="Q4" s="4" t="inlineStr"/>
       <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="5">
-        <f>IFERROR(R4/Q4*1000,"")</f>
+      <c r="S4" s="4" t="inlineStr"/>
+      <c r="T4" s="5">
+        <f>IFERROR(S4/R4*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -873,7 +894,7 @@
 Compuesta con raíz en 417 Hz, en entonación justa, modo hirajoshi.
 Para acompañar una práctica de respiración.
 Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Cuencos sintetizados cada 4 respiraciones.
+Cuencos y canto de ave sintetizados, sin grabaciones.
 Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
 — English —
 Composed with a root of 417 Hz in just intonation, hirajoshi mode.
@@ -908,27 +929,32 @@
           <t>hirajoshi</t>
         </is>
       </c>
-      <c r="L5" s="2" t="n">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
         <v>409966</v>
       </c>
-      <c r="M5" s="2" t="n">
+      <c r="N5" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 45 --raiz 417 --modo hirajoshi --semilla 409966</t>
         </is>
       </c>
-      <c r="O5" s="4" t="inlineStr">
+      <c r="P5" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="P5" s="4" t="inlineStr"/>
       <c r="Q5" s="4" t="inlineStr"/>
       <c r="R5" s="4" t="inlineStr"/>
-      <c r="S5" s="5">
-        <f>IFERROR(R5/Q5*1000,"")</f>
+      <c r="S5" s="4" t="inlineStr"/>
+      <c r="T5" s="5">
+        <f>IFERROR(S5/R5*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -954,7 +980,7 @@
 Compuesta con raíz en 639 Hz, en entonación justa, modo yo.
 Para acompañar una práctica de respiración.
 Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Cuencos sintetizados cada 4 respiraciones.
+Cuencos y canto de ave sintetizados, sin grabaciones.
 Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
 — English —
 Composed with a root of 639 Hz in just intonation, yo mode.
@@ -989,27 +1015,32 @@
           <t>yo</t>
         </is>
       </c>
-      <c r="L6" s="2" t="n">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
         <v>133046</v>
       </c>
-      <c r="M6" s="2" t="n">
+      <c r="N6" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="N6" s="3" t="inlineStr">
+      <c r="O6" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 60 --raiz 639 --modo yo --semilla 133046</t>
         </is>
       </c>
-      <c r="O6" s="4" t="inlineStr">
+      <c r="P6" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="P6" s="4" t="inlineStr"/>
       <c r="Q6" s="4" t="inlineStr"/>
       <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="5">
-        <f>IFERROR(R6/Q6*1000,"")</f>
+      <c r="S6" s="4" t="inlineStr"/>
+      <c r="T6" s="5">
+        <f>IFERROR(S6/R6*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -1035,7 +1066,7 @@
 Compuesta con raíz en 741 Hz, en entonación justa, modo yo.
 Para acompañar una práctica de respiración.
 Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Cuencos sintetizados cada 4 respiraciones.
+Cuencos y canto de ave sintetizados, sin grabaciones.
 Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
 — English —
 Composed with a root of 741 Hz in just intonation, yo mode.
@@ -1070,27 +1101,32 @@
           <t>yo</t>
         </is>
       </c>
-      <c r="L7" s="2" t="n">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
         <v>244487</v>
       </c>
-      <c r="M7" s="2" t="n">
+      <c r="N7" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="N7" s="3" t="inlineStr">
+      <c r="O7" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 45 --raiz 741 --modo yo --semilla 244487</t>
         </is>
       </c>
-      <c r="O7" s="4" t="inlineStr">
+      <c r="P7" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="P7" s="4" t="inlineStr"/>
       <c r="Q7" s="4" t="inlineStr"/>
       <c r="R7" s="4" t="inlineStr"/>
-      <c r="S7" s="5">
-        <f>IFERROR(R7/Q7*1000,"")</f>
+      <c r="S7" s="4" t="inlineStr"/>
+      <c r="T7" s="5">
+        <f>IFERROR(S7/R7*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -1116,7 +1152,7 @@
 Compuesta con raíz en 852 Hz, en entonación justa, modo hirajoshi.
 Para acompañar una práctica de respiración.
 Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Cuencos sintetizados cada 4 respiraciones.
+Cuencos y canto de ave sintetizados, sin grabaciones.
 Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
 — English —
 Composed with a root of 852 Hz in just intonation, hirajoshi mode.
@@ -1151,27 +1187,32 @@
           <t>hirajoshi</t>
         </is>
       </c>
-      <c r="L8" s="2" t="n">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
         <v>288169</v>
       </c>
-      <c r="M8" s="2" t="n">
+      <c r="N8" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="N8" s="3" t="inlineStr">
+      <c r="O8" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 45 --raiz 852 --modo hirajoshi --semilla 288169</t>
         </is>
       </c>
-      <c r="O8" s="4" t="inlineStr">
+      <c r="P8" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="P8" s="4" t="inlineStr"/>
       <c r="Q8" s="4" t="inlineStr"/>
       <c r="R8" s="4" t="inlineStr"/>
-      <c r="S8" s="5">
-        <f>IFERROR(R8/Q8*1000,"")</f>
+      <c r="S8" s="4" t="inlineStr"/>
+      <c r="T8" s="5">
+        <f>IFERROR(S8/R8*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -1197,7 +1238,7 @@
 Compuesta con raíz en 528 Hz, en entonación justa, modo hirajoshi.
 Para acompañar una práctica de respiración.
 Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Cuencos sintetizados cada 4 respiraciones.
+Cuencos y canto de ave sintetizados, sin grabaciones.
 Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
 — English —
 Composed with a root of 528 Hz in just intonation, hirajoshi mode.
@@ -1232,27 +1273,32 @@
           <t>hirajoshi</t>
         </is>
       </c>
-      <c r="L9" s="2" t="n">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
         <v>638156</v>
       </c>
-      <c r="M9" s="2" t="n">
+      <c r="N9" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="N9" s="3" t="inlineStr">
+      <c r="O9" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 180 --raiz 528 --modo hirajoshi --semilla 638156</t>
         </is>
       </c>
-      <c r="O9" s="4" t="inlineStr">
+      <c r="P9" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="P9" s="4" t="inlineStr"/>
       <c r="Q9" s="4" t="inlineStr"/>
       <c r="R9" s="4" t="inlineStr"/>
-      <c r="S9" s="5">
-        <f>IFERROR(R9/Q9*1000,"")</f>
+      <c r="S9" s="4" t="inlineStr"/>
+      <c r="T9" s="5">
+        <f>IFERROR(S9/R9*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -1275,91 +1321,1128 @@
       <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Noche sin fondo · 3 horas
-Compuesta con raíz en 432 Hz, en entonación justa, modo shin.
-Para acompañar una práctica de respiración.
+Compuesta con raíz en 216 Hz, la octava grave de 432 Hz, en entonación justa, modo shin.
+Para acompañar el sueño.
 Ciclo respiratorio: de 4.5 a 3.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Cuencos sintetizados cada 4 respiraciones.
+Cuencos y canto de ave sintetizados, sin grabaciones.
 Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
 — English —
 Composed with a root of 432 Hz in just intonation, shin mode.
+To accompany sleep.
+Original composition, synthesized from scratch. No third-party samples.
+Capítulos:
+00:00 [completar tras el montaje]</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3 HORAS</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>#MúsicaParaDormir #MúsicaRelajante #432Hz</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>432 hz, música 432 hz, música para dormir, sleep music, sueño, shin, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, singing bowls, just intonation</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" s="4" t="inlineStr"/>
+      <c r="J10" s="2" t="n">
+        <v>432</v>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>shin</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>grave</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>505716</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>python3 03-composicion/compositor.py --minutos 180 --raiz 432 --modo shin --semilla 505716 --registro grave</t>
+        </is>
+      </c>
+      <c r="P10" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="Q10" s="4" t="inlineStr"/>
+      <c r="R10" s="4" t="inlineStr"/>
+      <c r="S10" s="4" t="inlineStr"/>
+      <c r="T10" s="5">
+        <f>IFERROR(S10/R10*1000,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-010</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Música para dormir · 396 Hz · Cuarto oscuro · 2 horas</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Sueño</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Cuarto oscuro · 2 horas
+Compuesta con raíz en 198 Hz, la octava grave de 396 Hz, en entonación justa, modo kumoi.
+Para acompañar el sueño.
+Ciclo respiratorio: de 4.5 a 3.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
+Cuencos y canto de ave sintetizados, sin grabaciones.
+Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
+— English —
+Composed with a root of 396 Hz in just intonation, kumoi mode.
+To accompany sleep.
+Original composition, synthesized from scratch. No third-party samples.
+Capítulos:
+00:00 [completar tras el montaje]</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2 HORAS</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>#MúsicaParaDormir #MúsicaRelajante #396Hz</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>396 hz, música 396 hz, música para dormir, sleep music, sueño, kumoi, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, singing bowls, just intonation</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" s="4" t="inlineStr"/>
+      <c r="J11" s="2" t="n">
+        <v>396</v>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>kumoi</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>grave</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>692584</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>python3 03-composicion/compositor.py --minutos 120 --raiz 396 --modo kumoi --semilla 692584 --registro grave</t>
+        </is>
+      </c>
+      <c r="P11" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="Q11" s="4" t="inlineStr"/>
+      <c r="R11" s="4" t="inlineStr"/>
+      <c r="S11" s="4" t="inlineStr"/>
+      <c r="T11" s="5">
+        <f>IFERROR(S11/R11*1000,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-011</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Música para dormir · 432 Hz · Respiración de invierno · 2 horas</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Sueño</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Respiración de invierno · 2 horas
+Compuesta con raíz en 216 Hz, la octava grave de 432 Hz, en entonación justa, modo kumoi.
+Para acompañar el sueño.
+Ciclo respiratorio: de 4.5 a 3.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
+Cuencos y canto de ave sintetizados, sin grabaciones.
+Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
+— English —
+Composed with a root of 432 Hz in just intonation, kumoi mode.
+To accompany sleep.
+Original composition, synthesized from scratch. No third-party samples.
+Capítulos:
+00:00 [completar tras el montaje]</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2 HORAS</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>#MúsicaParaDormir #MúsicaRelajante #432Hz</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>432 hz, música 432 hz, música para dormir, sleep music, sueño, kumoi, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, singing bowls, just intonation</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr"/>
+      <c r="I12" s="4" t="inlineStr"/>
+      <c r="J12" s="2" t="n">
+        <v>432</v>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>kumoi</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>grave</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>531725</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>python3 03-composicion/compositor.py --minutos 120 --raiz 432 --modo kumoi --semilla 531725 --registro grave</t>
+        </is>
+      </c>
+      <c r="P12" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="Q12" s="4" t="inlineStr"/>
+      <c r="R12" s="4" t="inlineStr"/>
+      <c r="S12" s="4" t="inlineStr"/>
+      <c r="T12" s="5">
+        <f>IFERROR(S12/R12*1000,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-012</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Música para dormir · 528 Hz · Nadie despierto · 3 horas</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Sueño</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Nadie despierto · 3 horas
+Compuesta con raíz en 264 Hz, la octava grave de 528 Hz, en entonación justa, modo shin.
+Para acompañar el sueño.
+Ciclo respiratorio: de 4.5 a 3.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
+Cuencos y canto de ave sintetizados, sin grabaciones.
+Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
+— English —
+Composed with a root of 528 Hz in just intonation, shin mode.
+To accompany sleep.
+Original composition, synthesized from scratch. No third-party samples.
+Capítulos:
+00:00 [completar tras el montaje]</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3 HORAS</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>#MúsicaParaDormir #MúsicaRelajante #528Hz</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>528 hz, música 528 hz, música para dormir, sleep music, sueño, shin, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, singing bowls, just intonation</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr"/>
+      <c r="I13" s="4" t="inlineStr"/>
+      <c r="J13" s="2" t="n">
+        <v>528</v>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>shin</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>grave</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>751043</v>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>python3 03-composicion/compositor.py --minutos 180 --raiz 528 --modo shin --semilla 751043 --registro grave</t>
+        </is>
+      </c>
+      <c r="P13" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="Q13" s="4" t="inlineStr"/>
+      <c r="R13" s="4" t="inlineStr"/>
+      <c r="S13" s="4" t="inlineStr"/>
+      <c r="T13" s="5">
+        <f>IFERROR(S13/R13*1000,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-013</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Música para dormir · 417 Hz · Antes del alba · 90 minutos</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Sueño</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Antes del alba · 90 minutos
+Compuesta con raíz en 208.5 Hz, la octava grave de 417 Hz, en entonación justa, modo kumoi.
+Para acompañar el sueño.
+Ciclo respiratorio: de 4.5 a 3.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
+Cuencos y canto de ave sintetizados, sin grabaciones.
+Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
+— English —
+Composed with a root of 417 Hz in just intonation, kumoi mode.
+To accompany sleep.
+Original composition, synthesized from scratch. No third-party samples.
+Capítulos:
+00:00 [completar tras el montaje]</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>90 MIN</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>#MúsicaParaDormir #MúsicaRelajante #417Hz</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>417 hz, música 417 hz, música para dormir, sleep music, sueño, kumoi, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, singing bowls, just intonation</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr"/>
+      <c r="I14" s="4" t="inlineStr"/>
+      <c r="J14" s="2" t="n">
+        <v>417</v>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>kumoi</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>grave</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>813147</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>python3 03-composicion/compositor.py --minutos 90 --raiz 417 --modo kumoi --semilla 813147 --registro grave</t>
+        </is>
+      </c>
+      <c r="P14" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="Q14" s="4" t="inlineStr"/>
+      <c r="R14" s="4" t="inlineStr"/>
+      <c r="S14" s="4" t="inlineStr"/>
+      <c r="T14" s="5">
+        <f>IFERROR(S14/R14*1000,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-014</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Música para dormir · 396 Hz · Peso lento · 2 horas</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Sueño</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Peso lento · 2 horas
+Compuesta con raíz en 198 Hz, la octava grave de 396 Hz, en entonación justa, modo shin.
+Para acompañar el sueño.
+Ciclo respiratorio: de 4.5 a 3.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
+Cuencos y canto de ave sintetizados, sin grabaciones.
+Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
+— English —
+Composed with a root of 396 Hz in just intonation, shin mode.
+To accompany sleep.
+Original composition, synthesized from scratch. No third-party samples.
+Capítulos:
+00:00 [completar tras el montaje]</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2 HORAS</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>#MúsicaParaDormir #MúsicaRelajante #396Hz</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>396 hz, música 396 hz, música para dormir, sleep music, sueño, shin, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, singing bowls, just intonation</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" s="4" t="inlineStr"/>
+      <c r="J15" s="2" t="n">
+        <v>396</v>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>shin</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>grave</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>885916</v>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>python3 03-composicion/compositor.py --minutos 120 --raiz 396 --modo shin --semilla 885916 --registro grave</t>
+        </is>
+      </c>
+      <c r="P15" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="Q15" s="4" t="inlineStr"/>
+      <c r="R15" s="4" t="inlineStr"/>
+      <c r="S15" s="4" t="inlineStr"/>
+      <c r="T15" s="5">
+        <f>IFERROR(S15/R15*1000,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-015</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Música para dormir · 432 Hz · La casa dormida · 3 horas</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Sueño</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>La casa dormida · 3 horas
+Compuesta con raíz en 216 Hz, la octava grave de 432 Hz, en entonación justa, modo kumoi.
+Para acompañar el sueño.
+Ciclo respiratorio: de 4.5 a 3.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
+Cuencos y canto de ave sintetizados, sin grabaciones.
+Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
+— English —
+Composed with a root of 432 Hz in just intonation, kumoi mode.
+To accompany sleep.
+Original composition, synthesized from scratch. No third-party samples.
+Capítulos:
+00:00 [completar tras el montaje]</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3 HORAS</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>#MúsicaParaDormir #MúsicaRelajante #432Hz</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>432 hz, música 432 hz, música para dormir, sleep music, sueño, kumoi, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, singing bowls, just intonation</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr"/>
+      <c r="I16" s="4" t="inlineStr"/>
+      <c r="J16" s="2" t="n">
+        <v>432</v>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>kumoi</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>grave</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>295910</v>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>python3 03-composicion/compositor.py --minutos 180 --raiz 432 --modo kumoi --semilla 295910 --registro grave</t>
+        </is>
+      </c>
+      <c r="P16" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="Q16" s="4" t="inlineStr"/>
+      <c r="R16" s="4" t="inlineStr"/>
+      <c r="S16" s="4" t="inlineStr"/>
+      <c r="T16" s="5">
+        <f>IFERROR(S16/R16*1000,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-016</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Música para dormir · 528 Hz · Marea baja · 2 horas</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Sueño</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Marea baja · 2 horas
+Compuesta con raíz en 264 Hz, la octava grave de 528 Hz, en entonación justa, modo kumoi.
+Para acompañar el sueño.
+Ciclo respiratorio: de 4.5 a 3.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
+Cuencos y canto de ave sintetizados, sin grabaciones.
+Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
+— English —
+Composed with a root of 528 Hz in just intonation, kumoi mode.
+To accompany sleep.
+Original composition, synthesized from scratch. No third-party samples.
+Capítulos:
+00:00 [completar tras el montaje]</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2 HORAS</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>#MúsicaParaDormir #MúsicaRelajante #528Hz</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>528 hz, música 528 hz, música para dormir, sleep music, sueño, kumoi, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, singing bowls, just intonation</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" s="4" t="inlineStr"/>
+      <c r="J17" s="2" t="n">
+        <v>528</v>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>kumoi</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>grave</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>443547</v>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>python3 03-composicion/compositor.py --minutos 120 --raiz 528 --modo kumoi --semilla 443547 --registro grave</t>
+        </is>
+      </c>
+      <c r="P17" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="Q17" s="4" t="inlineStr"/>
+      <c r="R17" s="4" t="inlineStr"/>
+      <c r="S17" s="4" t="inlineStr"/>
+      <c r="T17" s="5">
+        <f>IFERROR(S17/R17*1000,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-017</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Música para meditar · 528 Hz · Cuatro y seis · 20 minutos</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Respiración</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Cuatro y seis · 20 minutos
+Compuesta con raíz en 528 Hz, en entonación justa, modo hirajoshi.
+Para acompañar una práctica de respiración.
+Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
+Cuencos y canto de ave sintetizados, sin grabaciones.
+Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
+— English —
+Composed with a root of 528 Hz in just intonation, hirajoshi mode.
 To accompany a breathing practice.
 Original composition, synthesized from scratch. No third-party samples.
 Capítulos:
 00:00 [completar tras el montaje]</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3 HORAS</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>#MúsicaParaDormir #MúsicaRelajante #432Hz</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>432 hz, música 432 hz, música para dormir, sleep music, sueño, shin, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, singing bowls, just intonation</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr"/>
-      <c r="I10" s="4" t="inlineStr"/>
-      <c r="J10" s="2" t="n">
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>20 MIN</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>#Respiración #MúsicaRelajante #528Hz</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>528 hz, música 528 hz, música para meditar, meditation music, respiración, hirajoshi, música relajante, meditación, relajación, entonación justa, composición original, relaxing music, sleep music, singing bowls, just intonation</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr"/>
+      <c r="I18" s="4" t="inlineStr"/>
+      <c r="J18" s="2" t="n">
+        <v>528</v>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>hirajoshi</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>913368</v>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>python3 03-composicion/compositor.py --minutos 20 --raiz 528 --modo hirajoshi --semilla 913368</t>
+        </is>
+      </c>
+      <c r="P18" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="Q18" s="4" t="inlineStr"/>
+      <c r="R18" s="4" t="inlineStr"/>
+      <c r="S18" s="4" t="inlineStr"/>
+      <c r="T18" s="5">
+        <f>IFERROR(S18/R18*1000,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-018</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Música para meditar · 432 Hz · Bajar el ritmo · 30 minutos</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Respiración</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Bajar el ritmo · 30 minutos
+Compuesta con raíz en 432 Hz, en entonación justa, modo hirajoshi.
+Para acompañar una práctica de respiración.
+Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
+Cuencos y canto de ave sintetizados, sin grabaciones.
+Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
+— English —
+Composed with a root of 432 Hz in just intonation, hirajoshi mode.
+To accompany a breathing practice.
+Original composition, synthesized from scratch. No third-party samples.
+Capítulos:
+00:00 [completar tras el montaje]</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>30 MIN</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>#Respiración #MúsicaRelajante #432Hz</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>432 hz, música 432 hz, música para meditar, meditation music, respiración, hirajoshi, música relajante, meditación, relajación, entonación justa, composición original, relaxing music, sleep music, singing bowls, just intonation</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr"/>
+      <c r="I19" s="4" t="inlineStr"/>
+      <c r="J19" s="2" t="n">
         <v>432</v>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>hirajoshi</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>739461</v>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>python3 03-composicion/compositor.py --minutos 30 --raiz 432 --modo hirajoshi --semilla 739461</t>
+        </is>
+      </c>
+      <c r="P19" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="Q19" s="4" t="inlineStr"/>
+      <c r="R19" s="4" t="inlineStr"/>
+      <c r="S19" s="4" t="inlineStr"/>
+      <c r="T19" s="5">
+        <f>IFERROR(S19/R19*1000,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-019</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Música para meditar · 528 Hz · Entrada y salida · 20 minutos</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Respiración</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Entrada y salida · 20 minutos
+Compuesta con raíz en 528 Hz, en entonación justa, modo yo.
+Para acompañar una práctica de respiración.
+Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
+Cuencos y canto de ave sintetizados, sin grabaciones.
+Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
+— English —
+Composed with a root of 528 Hz in just intonation, yo mode.
+To accompany a breathing practice.
+Original composition, synthesized from scratch. No third-party samples.
+Capítulos:
+00:00 [completar tras el montaje]</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>20 MIN</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>#Respiración #MúsicaRelajante #528Hz</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>528 hz, música 528 hz, música para meditar, meditation music, respiración, yo, música relajante, meditación, relajación, entonación justa, composición original, relaxing music, sleep music, singing bowls, just intonation</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr"/>
+      <c r="I20" s="4" t="inlineStr"/>
+      <c r="J20" s="2" t="n">
+        <v>528</v>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>yo</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>310137</v>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>python3 03-composicion/compositor.py --minutos 20 --raiz 528 --modo yo --semilla 310137</t>
+        </is>
+      </c>
+      <c r="P20" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="Q20" s="4" t="inlineStr"/>
+      <c r="R20" s="4" t="inlineStr"/>
+      <c r="S20" s="4" t="inlineStr"/>
+      <c r="T20" s="5">
+        <f>IFERROR(S20/R20*1000,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-020</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Música para meditar · 528 Hz · Diez minutos · 10 minutos</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Respiración</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Diez minutos · 10 minutos
+Compuesta con raíz en 528 Hz, en entonación justa, modo shin.
+Para acompañar una práctica de respiración.
+Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
+Cuencos y canto de ave sintetizados, sin grabaciones.
+Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
+— English —
+Composed with a root of 528 Hz in just intonation, shin mode.
+To accompany a breathing practice.
+Original composition, synthesized from scratch. No third-party samples.
+Capítulos:
+00:00 [completar tras el montaje]</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>10 MIN</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>#Respiración #MúsicaRelajante #528Hz</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>528 hz, música 528 hz, música para meditar, meditation music, respiración, shin, música relajante, meditación, relajación, entonación justa, composición original, relaxing music, sleep music, singing bowls, just intonation</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="4" t="inlineStr"/>
+      <c r="J21" s="2" t="n">
+        <v>528</v>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>shin</t>
         </is>
       </c>
-      <c r="L10" s="2" t="n">
-        <v>505716</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>180</v>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t>python3 03-composicion/compositor.py --minutos 180 --raiz 432 --modo shin --semilla 505716</t>
-        </is>
-      </c>
-      <c r="O10" s="4" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>207307</v>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>python3 03-composicion/compositor.py --minutos 10 --raiz 528 --modo shin --semilla 207307</t>
+        </is>
+      </c>
+      <c r="P21" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="P10" s="4" t="inlineStr"/>
-      <c r="Q10" s="4" t="inlineStr"/>
-      <c r="R10" s="4" t="inlineStr"/>
-      <c r="S10" s="5">
-        <f>IFERROR(R10/Q10*1000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>OBRA-010</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Música para dormir · 396 Hz · Cuarto oscuro · 2 horas</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Sueño</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Cuarto oscuro · 2 horas
+      <c r="Q21" s="4" t="inlineStr"/>
+      <c r="R21" s="4" t="inlineStr"/>
+      <c r="S21" s="4" t="inlineStr"/>
+      <c r="T21" s="5">
+        <f>IFERROR(S21/R21*1000,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-021</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Música para meditar · 639 Hz · Antes de empezar · 15 minutos</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Respiración</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Antes de empezar · 15 minutos
+Compuesta con raíz en 639 Hz, en entonación justa, modo yo.
+Para acompañar una práctica de respiración.
+Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
+Cuencos y canto de ave sintetizados, sin grabaciones.
+Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
+— English —
+Composed with a root of 639 Hz in just intonation, yo mode.
+To accompany a breathing practice.
+Original composition, synthesized from scratch. No third-party samples.
+Capítulos:
+00:00 [completar tras el montaje]</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>15 MIN</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>#Respiración #MúsicaRelajante #639Hz</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>639 hz, música 639 hz, música para meditar, meditation music, respiración, yo, música relajante, meditación, relajación, entonación justa, composición original, relaxing music, sleep music, singing bowls, just intonation</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr"/>
+      <c r="I22" s="4" t="inlineStr"/>
+      <c r="J22" s="2" t="n">
+        <v>639</v>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>yo</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>592463</v>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>python3 03-composicion/compositor.py --minutos 15 --raiz 639 --modo yo --semilla 592463</t>
+        </is>
+      </c>
+      <c r="P22" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="Q22" s="4" t="inlineStr"/>
+      <c r="R22" s="4" t="inlineStr"/>
+      <c r="S22" s="4" t="inlineStr"/>
+      <c r="T22" s="5">
+        <f>IFERROR(S22/R22*1000,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-022</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Música para meditar · 396 Hz · Solo exhalar · 25 minutos</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Respiración</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Solo exhalar · 25 minutos
 Compuesta con raíz en 396 Hz, en entonación justa, modo kumoi.
 Para acompañar una práctica de respiración.
-Ciclo respiratorio: de 4.5 a 3.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Cuencos sintetizados cada 4 respiraciones.
+Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
+Cuencos y canto de ave sintetizados, sin grabaciones.
 Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
 — English —
 Composed with a root of 396 Hz in just intonation, kumoi mode.
@@ -1369,240 +2452,169 @@
 00:00 [completar tras el montaje]</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2 HORAS</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>#MúsicaParaDormir #MúsicaRelajante #396Hz</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>396 hz, música 396 hz, música para dormir, sleep music, sueño, kumoi, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, singing bowls, just intonation</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr"/>
-      <c r="I11" s="4" t="inlineStr"/>
-      <c r="J11" s="2" t="n">
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>25 MIN</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>#Respiración #MúsicaRelajante #396Hz</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>396 hz, música 396 hz, música para meditar, meditation music, respiración, kumoi, música relajante, meditación, relajación, entonación justa, composición original, relaxing music, sleep music, singing bowls, just intonation</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" s="4" t="inlineStr"/>
+      <c r="J23" s="2" t="n">
         <v>396</v>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>kumoi</t>
         </is>
       </c>
-      <c r="L11" s="2" t="n">
-        <v>692584</v>
-      </c>
-      <c r="M11" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t>python3 03-composicion/compositor.py --minutos 120 --raiz 396 --modo kumoi --semilla 692584</t>
-        </is>
-      </c>
-      <c r="O11" s="4" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>555819</v>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>python3 03-composicion/compositor.py --minutos 25 --raiz 396 --modo kumoi --semilla 555819</t>
+        </is>
+      </c>
+      <c r="P23" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="P11" s="4" t="inlineStr"/>
-      <c r="Q11" s="4" t="inlineStr"/>
-      <c r="R11" s="4" t="inlineStr"/>
-      <c r="S11" s="5">
-        <f>IFERROR(R11/Q11*1000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>OBRA-011</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Música para dormir · 432 Hz · Respiración de invierno · 2 horas</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Sueño</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Respiración de invierno · 2 horas
-Compuesta con raíz en 432 Hz, en entonación justa, modo kumoi.
+      <c r="Q23" s="4" t="inlineStr"/>
+      <c r="R23" s="4" t="inlineStr"/>
+      <c r="S23" s="4" t="inlineStr"/>
+      <c r="T23" s="5">
+        <f>IFERROR(S23/R23*1000,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-023</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Música para meditar · 432 Hz · Contar hasta seis · 20 minutos</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Respiración</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Contar hasta seis · 20 minutos
+Compuesta con raíz en 432 Hz, en entonación justa, modo hirajoshi.
 Para acompañar una práctica de respiración.
-Ciclo respiratorio: de 4.5 a 3.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Cuencos sintetizados cada 4 respiraciones.
+Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
+Cuencos y canto de ave sintetizados, sin grabaciones.
 Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
 — English —
-Composed with a root of 432 Hz in just intonation, kumoi mode.
+Composed with a root of 432 Hz in just intonation, hirajoshi mode.
 To accompany a breathing practice.
 Original composition, synthesized from scratch. No third-party samples.
 Capítulos:
 00:00 [completar tras el montaje]</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2 HORAS</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>#MúsicaParaDormir #MúsicaRelajante #432Hz</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>432 hz, música 432 hz, música para dormir, sleep music, sueño, kumoi, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, singing bowls, just intonation</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr"/>
-      <c r="I12" s="4" t="inlineStr"/>
-      <c r="J12" s="2" t="n">
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>20 MIN</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>#Respiración #MúsicaRelajante #432Hz</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>432 hz, música 432 hz, música para meditar, meditation music, respiración, hirajoshi, música relajante, meditación, relajación, entonación justa, composición original, relaxing music, sleep music, singing bowls, just intonation</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr"/>
+      <c r="I24" s="4" t="inlineStr"/>
+      <c r="J24" s="2" t="n">
         <v>432</v>
       </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>kumoi</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>531725</v>
-      </c>
-      <c r="M12" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t>python3 03-composicion/compositor.py --minutos 120 --raiz 432 --modo kumoi --semilla 531725</t>
-        </is>
-      </c>
-      <c r="O12" s="4" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>hirajoshi</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>627771</v>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>python3 03-composicion/compositor.py --minutos 20 --raiz 432 --modo hirajoshi --semilla 627771</t>
+        </is>
+      </c>
+      <c r="P24" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="P12" s="4" t="inlineStr"/>
-      <c r="Q12" s="4" t="inlineStr"/>
-      <c r="R12" s="4" t="inlineStr"/>
-      <c r="S12" s="5">
-        <f>IFERROR(R12/Q12*1000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>OBRA-012</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Música para dormir · 528 Hz · Nadie despierto · 3 horas</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Sueño</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>Nadie despierto · 3 horas
-Compuesta con raíz en 528 Hz, en entonación justa, modo shin.
-Para acompañar una práctica de respiración.
-Ciclo respiratorio: de 4.5 a 3.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Cuencos sintetizados cada 4 respiraciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 528 Hz in just intonation, shin mode.
-To accompany a breathing practice.
-Original composition, synthesized from scratch. No third-party samples.
-Capítulos:
-00:00 [completar tras el montaje]</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3 HORAS</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>#MúsicaParaDormir #MúsicaRelajante #528Hz</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>528 hz, música 528 hz, música para dormir, sleep music, sueño, shin, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, singing bowls, just intonation</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr"/>
-      <c r="I13" s="4" t="inlineStr"/>
-      <c r="J13" s="2" t="n">
-        <v>528</v>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>shin</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>751043</v>
-      </c>
-      <c r="M13" s="2" t="n">
-        <v>180</v>
-      </c>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t>python3 03-composicion/compositor.py --minutos 180 --raiz 528 --modo shin --semilla 751043</t>
-        </is>
-      </c>
-      <c r="O13" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="P13" s="4" t="inlineStr"/>
-      <c r="Q13" s="4" t="inlineStr"/>
-      <c r="R13" s="4" t="inlineStr"/>
-      <c r="S13" s="5">
-        <f>IFERROR(R13/Q13*1000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>OBRA-013</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Música para dormir · 417 Hz · Antes del alba · 90 minutos</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Sueño</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Antes del alba · 90 minutos
+      <c r="Q24" s="4" t="inlineStr"/>
+      <c r="R24" s="4" t="inlineStr"/>
+      <c r="S24" s="4" t="inlineStr"/>
+      <c r="T24" s="5">
+        <f>IFERROR(S24/R24*1000,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-024</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Música para meditar · 417 Hz · El final del día · 30 minutos</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Respiración</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>El final del día · 30 minutos
 Compuesta con raíz en 417 Hz, en entonación justa, modo kumoi.
 Para acompañar una práctica de respiración.
-Ciclo respiratorio: de 4.5 a 3.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Cuencos sintetizados cada 4 respiraciones.
+Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
+Cuencos y canto de ave sintetizados, sin grabaciones.
 Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
 — English —
 Composed with a root of 417 Hz in just intonation, kumoi mode.
@@ -1612,897 +2624,6 @@
 00:00 [completar tras el montaje]</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>90 MIN</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>#MúsicaParaDormir #MúsicaRelajante #417Hz</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>417 hz, música 417 hz, música para dormir, sleep music, sueño, kumoi, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, singing bowls, just intonation</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr"/>
-      <c r="I14" s="4" t="inlineStr"/>
-      <c r="J14" s="2" t="n">
-        <v>417</v>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>kumoi</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>813147</v>
-      </c>
-      <c r="M14" s="2" t="n">
-        <v>90</v>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t>python3 03-composicion/compositor.py --minutos 90 --raiz 417 --modo kumoi --semilla 813147</t>
-        </is>
-      </c>
-      <c r="O14" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="P14" s="4" t="inlineStr"/>
-      <c r="Q14" s="4" t="inlineStr"/>
-      <c r="R14" s="4" t="inlineStr"/>
-      <c r="S14" s="5">
-        <f>IFERROR(R14/Q14*1000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>OBRA-014</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Música para dormir · 396 Hz · Peso lento · 2 horas</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Sueño</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Peso lento · 2 horas
-Compuesta con raíz en 396 Hz, en entonación justa, modo shin.
-Para acompañar una práctica de respiración.
-Ciclo respiratorio: de 4.5 a 3.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Cuencos sintetizados cada 4 respiraciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 396 Hz in just intonation, shin mode.
-To accompany a breathing practice.
-Original composition, synthesized from scratch. No third-party samples.
-Capítulos:
-00:00 [completar tras el montaje]</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>2 HORAS</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>#MúsicaParaDormir #MúsicaRelajante #396Hz</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>396 hz, música 396 hz, música para dormir, sleep music, sueño, shin, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, singing bowls, just intonation</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr"/>
-      <c r="I15" s="4" t="inlineStr"/>
-      <c r="J15" s="2" t="n">
-        <v>396</v>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>shin</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>885916</v>
-      </c>
-      <c r="M15" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t>python3 03-composicion/compositor.py --minutos 120 --raiz 396 --modo shin --semilla 885916</t>
-        </is>
-      </c>
-      <c r="O15" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="P15" s="4" t="inlineStr"/>
-      <c r="Q15" s="4" t="inlineStr"/>
-      <c r="R15" s="4" t="inlineStr"/>
-      <c r="S15" s="5">
-        <f>IFERROR(R15/Q15*1000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>OBRA-015</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Música para dormir · 432 Hz · La casa dormida · 3 horas</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Sueño</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>La casa dormida · 3 horas
-Compuesta con raíz en 432 Hz, en entonación justa, modo kumoi.
-Para acompañar una práctica de respiración.
-Ciclo respiratorio: de 4.5 a 3.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Cuencos sintetizados cada 4 respiraciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 432 Hz in just intonation, kumoi mode.
-To accompany a breathing practice.
-Original composition, synthesized from scratch. No third-party samples.
-Capítulos:
-00:00 [completar tras el montaje]</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>3 HORAS</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>#MúsicaParaDormir #MúsicaRelajante #432Hz</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>432 hz, música 432 hz, música para dormir, sleep music, sueño, kumoi, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, singing bowls, just intonation</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr"/>
-      <c r="I16" s="4" t="inlineStr"/>
-      <c r="J16" s="2" t="n">
-        <v>432</v>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>kumoi</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="n">
-        <v>295910</v>
-      </c>
-      <c r="M16" s="2" t="n">
-        <v>180</v>
-      </c>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t>python3 03-composicion/compositor.py --minutos 180 --raiz 432 --modo kumoi --semilla 295910</t>
-        </is>
-      </c>
-      <c r="O16" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="P16" s="4" t="inlineStr"/>
-      <c r="Q16" s="4" t="inlineStr"/>
-      <c r="R16" s="4" t="inlineStr"/>
-      <c r="S16" s="5">
-        <f>IFERROR(R16/Q16*1000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>OBRA-016</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Música para dormir · 528 Hz · Marea baja · 2 horas</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Sueño</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Marea baja · 2 horas
-Compuesta con raíz en 528 Hz, en entonación justa, modo kumoi.
-Para acompañar una práctica de respiración.
-Ciclo respiratorio: de 4.5 a 3.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Cuencos sintetizados cada 4 respiraciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 528 Hz in just intonation, kumoi mode.
-To accompany a breathing practice.
-Original composition, synthesized from scratch. No third-party samples.
-Capítulos:
-00:00 [completar tras el montaje]</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>2 HORAS</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>#MúsicaParaDormir #MúsicaRelajante #528Hz</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>528 hz, música 528 hz, música para dormir, sleep music, sueño, kumoi, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, singing bowls, just intonation</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr"/>
-      <c r="I17" s="4" t="inlineStr"/>
-      <c r="J17" s="2" t="n">
-        <v>528</v>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>kumoi</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="n">
-        <v>443547</v>
-      </c>
-      <c r="M17" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t>python3 03-composicion/compositor.py --minutos 120 --raiz 528 --modo kumoi --semilla 443547</t>
-        </is>
-      </c>
-      <c r="O17" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="P17" s="4" t="inlineStr"/>
-      <c r="Q17" s="4" t="inlineStr"/>
-      <c r="R17" s="4" t="inlineStr"/>
-      <c r="S17" s="5">
-        <f>IFERROR(R17/Q17*1000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>OBRA-017</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Música para meditar · 528 Hz · Cuatro y seis · 20 minutos</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Respiración</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>Cuatro y seis · 20 minutos
-Compuesta con raíz en 528 Hz, en entonación justa, modo hirajoshi.
-Para acompañar una práctica de respiración.
-Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Cuencos sintetizados cada 4 respiraciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 528 Hz in just intonation, hirajoshi mode.
-To accompany a breathing practice.
-Original composition, synthesized from scratch. No third-party samples.
-Capítulos:
-00:00 [completar tras el montaje]</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>20 MIN</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>#Respiración #MúsicaRelajante #528Hz</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>528 hz, música 528 hz, música para meditar, meditation music, respiración, hirajoshi, música relajante, meditación, relajación, entonación justa, composición original, relaxing music, sleep music, singing bowls, just intonation</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr"/>
-      <c r="I18" s="4" t="inlineStr"/>
-      <c r="J18" s="2" t="n">
-        <v>528</v>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>hirajoshi</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="n">
-        <v>913368</v>
-      </c>
-      <c r="M18" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t>python3 03-composicion/compositor.py --minutos 20 --raiz 528 --modo hirajoshi --semilla 913368</t>
-        </is>
-      </c>
-      <c r="O18" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="P18" s="4" t="inlineStr"/>
-      <c r="Q18" s="4" t="inlineStr"/>
-      <c r="R18" s="4" t="inlineStr"/>
-      <c r="S18" s="5">
-        <f>IFERROR(R18/Q18*1000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>OBRA-018</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Música para meditar · 432 Hz · Bajar el ritmo · 30 minutos</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Respiración</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Bajar el ritmo · 30 minutos
-Compuesta con raíz en 432 Hz, en entonación justa, modo hirajoshi.
-Para acompañar una práctica de respiración.
-Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Cuencos sintetizados cada 4 respiraciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 432 Hz in just intonation, hirajoshi mode.
-To accompany a breathing practice.
-Original composition, synthesized from scratch. No third-party samples.
-Capítulos:
-00:00 [completar tras el montaje]</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>30 MIN</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>#Respiración #MúsicaRelajante #432Hz</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>432 hz, música 432 hz, música para meditar, meditation music, respiración, hirajoshi, música relajante, meditación, relajación, entonación justa, composición original, relaxing music, sleep music, singing bowls, just intonation</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr"/>
-      <c r="I19" s="4" t="inlineStr"/>
-      <c r="J19" s="2" t="n">
-        <v>432</v>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>hirajoshi</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="n">
-        <v>739461</v>
-      </c>
-      <c r="M19" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
-          <t>python3 03-composicion/compositor.py --minutos 30 --raiz 432 --modo hirajoshi --semilla 739461</t>
-        </is>
-      </c>
-      <c r="O19" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="P19" s="4" t="inlineStr"/>
-      <c r="Q19" s="4" t="inlineStr"/>
-      <c r="R19" s="4" t="inlineStr"/>
-      <c r="S19" s="5">
-        <f>IFERROR(R19/Q19*1000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>OBRA-019</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Música para meditar · 528 Hz · Entrada y salida · 20 minutos</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Respiración</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>Entrada y salida · 20 minutos
-Compuesta con raíz en 528 Hz, en entonación justa, modo yo.
-Para acompañar una práctica de respiración.
-Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Cuencos sintetizados cada 4 respiraciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 528 Hz in just intonation, yo mode.
-To accompany a breathing practice.
-Original composition, synthesized from scratch. No third-party samples.
-Capítulos:
-00:00 [completar tras el montaje]</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>20 MIN</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>#Respiración #MúsicaRelajante #528Hz</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>528 hz, música 528 hz, música para meditar, meditation music, respiración, yo, música relajante, meditación, relajación, entonación justa, composición original, relaxing music, sleep music, singing bowls, just intonation</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr"/>
-      <c r="I20" s="4" t="inlineStr"/>
-      <c r="J20" s="2" t="n">
-        <v>528</v>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>yo</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="n">
-        <v>310137</v>
-      </c>
-      <c r="M20" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="N20" s="3" t="inlineStr">
-        <is>
-          <t>python3 03-composicion/compositor.py --minutos 20 --raiz 528 --modo yo --semilla 310137</t>
-        </is>
-      </c>
-      <c r="O20" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="P20" s="4" t="inlineStr"/>
-      <c r="Q20" s="4" t="inlineStr"/>
-      <c r="R20" s="4" t="inlineStr"/>
-      <c r="S20" s="5">
-        <f>IFERROR(R20/Q20*1000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>OBRA-020</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Música para meditar · 528 Hz · Diez minutos · 10 minutos</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Respiración</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>Diez minutos · 10 minutos
-Compuesta con raíz en 528 Hz, en entonación justa, modo shin.
-Para acompañar una práctica de respiración.
-Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Cuencos sintetizados cada 4 respiraciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 528 Hz in just intonation, shin mode.
-To accompany a breathing practice.
-Original composition, synthesized from scratch. No third-party samples.
-Capítulos:
-00:00 [completar tras el montaje]</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>10 MIN</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>#Respiración #MúsicaRelajante #528Hz</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>528 hz, música 528 hz, música para meditar, meditation music, respiración, shin, música relajante, meditación, relajación, entonación justa, composición original, relaxing music, sleep music, singing bowls, just intonation</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr"/>
-      <c r="I21" s="4" t="inlineStr"/>
-      <c r="J21" s="2" t="n">
-        <v>528</v>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>shin</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="n">
-        <v>207307</v>
-      </c>
-      <c r="M21" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t>python3 03-composicion/compositor.py --minutos 10 --raiz 528 --modo shin --semilla 207307</t>
-        </is>
-      </c>
-      <c r="O21" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="P21" s="4" t="inlineStr"/>
-      <c r="Q21" s="4" t="inlineStr"/>
-      <c r="R21" s="4" t="inlineStr"/>
-      <c r="S21" s="5">
-        <f>IFERROR(R21/Q21*1000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>OBRA-021</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Música para meditar · 639 Hz · Antes de empezar · 15 minutos</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Respiración</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Antes de empezar · 15 minutos
-Compuesta con raíz en 639 Hz, en entonación justa, modo yo.
-Para acompañar una práctica de respiración.
-Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Cuencos sintetizados cada 4 respiraciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 639 Hz in just intonation, yo mode.
-To accompany a breathing practice.
-Original composition, synthesized from scratch. No third-party samples.
-Capítulos:
-00:00 [completar tras el montaje]</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>15 MIN</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>#Respiración #MúsicaRelajante #639Hz</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>639 hz, música 639 hz, música para meditar, meditation music, respiración, yo, música relajante, meditación, relajación, entonación justa, composición original, relaxing music, sleep music, singing bowls, just intonation</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr"/>
-      <c r="I22" s="4" t="inlineStr"/>
-      <c r="J22" s="2" t="n">
-        <v>639</v>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>yo</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="n">
-        <v>592463</v>
-      </c>
-      <c r="M22" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t>python3 03-composicion/compositor.py --minutos 15 --raiz 639 --modo yo --semilla 592463</t>
-        </is>
-      </c>
-      <c r="O22" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="P22" s="4" t="inlineStr"/>
-      <c r="Q22" s="4" t="inlineStr"/>
-      <c r="R22" s="4" t="inlineStr"/>
-      <c r="S22" s="5">
-        <f>IFERROR(R22/Q22*1000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>OBRA-022</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Música para meditar · 396 Hz · Solo exhalar · 25 minutos</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Respiración</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>Solo exhalar · 25 minutos
-Compuesta con raíz en 396 Hz, en entonación justa, modo kumoi.
-Para acompañar una práctica de respiración.
-Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Cuencos sintetizados cada 4 respiraciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 396 Hz in just intonation, kumoi mode.
-To accompany a breathing practice.
-Original composition, synthesized from scratch. No third-party samples.
-Capítulos:
-00:00 [completar tras el montaje]</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>25 MIN</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>#Respiración #MúsicaRelajante #396Hz</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>396 hz, música 396 hz, música para meditar, meditation music, respiración, kumoi, música relajante, meditación, relajación, entonación justa, composición original, relaxing music, sleep music, singing bowls, just intonation</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr"/>
-      <c r="I23" s="4" t="inlineStr"/>
-      <c r="J23" s="2" t="n">
-        <v>396</v>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>kumoi</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="n">
-        <v>555819</v>
-      </c>
-      <c r="M23" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t>python3 03-composicion/compositor.py --minutos 25 --raiz 396 --modo kumoi --semilla 555819</t>
-        </is>
-      </c>
-      <c r="O23" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="P23" s="4" t="inlineStr"/>
-      <c r="Q23" s="4" t="inlineStr"/>
-      <c r="R23" s="4" t="inlineStr"/>
-      <c r="S23" s="5">
-        <f>IFERROR(R23/Q23*1000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>OBRA-023</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Música para meditar · 432 Hz · Contar hasta seis · 20 minutos</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Respiración</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Contar hasta seis · 20 minutos
-Compuesta con raíz en 432 Hz, en entonación justa, modo hirajoshi.
-Para acompañar una práctica de respiración.
-Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Cuencos sintetizados cada 4 respiraciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 432 Hz in just intonation, hirajoshi mode.
-To accompany a breathing practice.
-Original composition, synthesized from scratch. No third-party samples.
-Capítulos:
-00:00 [completar tras el montaje]</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>20 MIN</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>#Respiración #MúsicaRelajante #432Hz</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>432 hz, música 432 hz, música para meditar, meditation music, respiración, hirajoshi, música relajante, meditación, relajación, entonación justa, composición original, relaxing music, sleep music, singing bowls, just intonation</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr"/>
-      <c r="I24" s="4" t="inlineStr"/>
-      <c r="J24" s="2" t="n">
-        <v>432</v>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>hirajoshi</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="n">
-        <v>627771</v>
-      </c>
-      <c r="M24" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t>python3 03-composicion/compositor.py --minutos 20 --raiz 432 --modo hirajoshi --semilla 627771</t>
-        </is>
-      </c>
-      <c r="O24" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="P24" s="4" t="inlineStr"/>
-      <c r="Q24" s="4" t="inlineStr"/>
-      <c r="R24" s="4" t="inlineStr"/>
-      <c r="S24" s="5">
-        <f>IFERROR(R24/Q24*1000,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>OBRA-024</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Música para meditar · 417 Hz · El final del día · 30 minutos</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Respiración</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>El final del día · 30 minutos
-Compuesta con raíz en 417 Hz, en entonación justa, modo kumoi.
-Para acompañar una práctica de respiración.
-Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Cuencos sintetizados cada 4 respiraciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 417 Hz in just intonation, kumoi mode.
-To accompany a breathing practice.
-Original composition, synthesized from scratch. No third-party samples.
-Capítulos:
-00:00 [completar tras el montaje]</t>
-        </is>
-      </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
           <t>30 MIN</t>
@@ -2528,27 +2649,32 @@
           <t>kumoi</t>
         </is>
       </c>
-      <c r="L25" s="2" t="n">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
         <v>250697</v>
       </c>
-      <c r="M25" s="2" t="n">
+      <c r="N25" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="N25" s="3" t="inlineStr">
+      <c r="O25" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 30 --raiz 417 --modo kumoi --semilla 250697</t>
         </is>
       </c>
-      <c r="O25" s="4" t="inlineStr">
+      <c r="P25" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="P25" s="4" t="inlineStr"/>
       <c r="Q25" s="4" t="inlineStr"/>
       <c r="R25" s="4" t="inlineStr"/>
-      <c r="S25" s="5">
-        <f>IFERROR(R25/Q25*1000,"")</f>
+      <c r="S25" s="4" t="inlineStr"/>
+      <c r="T25" s="5">
+        <f>IFERROR(S25/R25*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -2572,13 +2698,13 @@
         <is>
           <t>Siete cuencos · 45 minutos
 Compuesta con raíz en 528 Hz, en entonación justa, modo hirajoshi.
-Para acompañar una práctica de respiración.
+Para acompañar una práctica de meditación.
 Ciclo respiratorio: de 5.5 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Cuencos sintetizados cada 4 respiraciones.
+Cuencos y canto de ave sintetizados, sin grabaciones.
 Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
 — English —
 Composed with a root of 528 Hz in just intonation, hirajoshi mode.
-To accompany a breathing practice.
+To accompany a meditation practice.
 Original composition, synthesized from scratch. No third-party samples.
 Capítulos:
 00:00 [completar tras el montaje]</t>
@@ -2609,27 +2735,32 @@
           <t>hirajoshi</t>
         </is>
       </c>
-      <c r="L26" s="2" t="n">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
         <v>1186</v>
       </c>
-      <c r="M26" s="2" t="n">
+      <c r="N26" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="N26" s="3" t="inlineStr">
+      <c r="O26" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 45 --raiz 528 --modo hirajoshi --semilla 1186</t>
         </is>
       </c>
-      <c r="O26" s="4" t="inlineStr">
+      <c r="P26" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="P26" s="4" t="inlineStr"/>
       <c r="Q26" s="4" t="inlineStr"/>
       <c r="R26" s="4" t="inlineStr"/>
-      <c r="S26" s="5">
-        <f>IFERROR(R26/Q26*1000,"")</f>
+      <c r="S26" s="4" t="inlineStr"/>
+      <c r="T26" s="5">
+        <f>IFERROR(S26/R26*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -2653,13 +2784,13 @@
         <is>
           <t>Metal y aire · 1 hora
 Compuesta con raíz en 432 Hz, en entonación justa, modo shin.
-Para acompañar una práctica de respiración.
+Para acompañar una práctica de meditación.
 Ciclo respiratorio: de 5.5 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Cuencos sintetizados cada 4 respiraciones.
+Cuencos y canto de ave sintetizados, sin grabaciones.
 Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
 — English —
 Composed with a root of 432 Hz in just intonation, shin mode.
-To accompany a breathing practice.
+To accompany a meditation practice.
 Original composition, synthesized from scratch. No third-party samples.
 Capítulos:
 00:00 [completar tras el montaje]</t>
@@ -2690,27 +2821,32 @@
           <t>shin</t>
         </is>
       </c>
-      <c r="L27" s="2" t="n">
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
         <v>627577</v>
       </c>
-      <c r="M27" s="2" t="n">
+      <c r="N27" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="N27" s="3" t="inlineStr">
+      <c r="O27" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 60 --raiz 432 --modo shin --semilla 627577</t>
         </is>
       </c>
-      <c r="O27" s="4" t="inlineStr">
+      <c r="P27" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="P27" s="4" t="inlineStr"/>
       <c r="Q27" s="4" t="inlineStr"/>
       <c r="R27" s="4" t="inlineStr"/>
-      <c r="S27" s="5">
-        <f>IFERROR(R27/Q27*1000,"")</f>
+      <c r="S27" s="4" t="inlineStr"/>
+      <c r="T27" s="5">
+        <f>IFERROR(S27/R27*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -2734,13 +2870,13 @@
         <is>
           <t>Golpe y silencio · 30 minutos
 Compuesta con raíz en 528 Hz, en entonación justa, modo shin.
-Para acompañar una práctica de respiración.
+Para acompañar una práctica de meditación.
 Ciclo respiratorio: de 5.5 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Cuencos sintetizados cada 4 respiraciones.
+Cuencos y canto de ave sintetizados, sin grabaciones.
 Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
 — English —
 Composed with a root of 528 Hz in just intonation, shin mode.
-To accompany a breathing practice.
+To accompany a meditation practice.
 Original composition, synthesized from scratch. No third-party samples.
 Capítulos:
 00:00 [completar tras el montaje]</t>
@@ -2771,27 +2907,32 @@
           <t>shin</t>
         </is>
       </c>
-      <c r="L28" s="2" t="n">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
         <v>632595</v>
       </c>
-      <c r="M28" s="2" t="n">
+      <c r="N28" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="N28" s="3" t="inlineStr">
+      <c r="O28" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 30 --raiz 528 --modo shin --semilla 632595</t>
         </is>
       </c>
-      <c r="O28" s="4" t="inlineStr">
+      <c r="P28" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="P28" s="4" t="inlineStr"/>
       <c r="Q28" s="4" t="inlineStr"/>
       <c r="R28" s="4" t="inlineStr"/>
-      <c r="S28" s="5">
-        <f>IFERROR(R28/Q28*1000,"")</f>
+      <c r="S28" s="4" t="inlineStr"/>
+      <c r="T28" s="5">
+        <f>IFERROR(S28/R28*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -2815,13 +2956,13 @@
         <is>
           <t>Cuenco de bronce · 45 minutos
 Compuesta con raíz en 396 Hz, en entonación justa, modo kumoi.
-Para acompañar una práctica de respiración.
+Para acompañar una práctica de meditación.
 Ciclo respiratorio: de 5.5 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Cuencos sintetizados cada 4 respiraciones.
+Cuencos y canto de ave sintetizados, sin grabaciones.
 Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
 — English —
 Composed with a root of 396 Hz in just intonation, kumoi mode.
-To accompany a breathing practice.
+To accompany a meditation practice.
 Original composition, synthesized from scratch. No third-party samples.
 Capítulos:
 00:00 [completar tras el montaje]</t>
@@ -2852,27 +2993,32 @@
           <t>kumoi</t>
         </is>
       </c>
-      <c r="L29" s="2" t="n">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="n">
         <v>894001</v>
       </c>
-      <c r="M29" s="2" t="n">
+      <c r="N29" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="N29" s="3" t="inlineStr">
+      <c r="O29" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 45 --raiz 396 --modo kumoi --semilla 894001</t>
         </is>
       </c>
-      <c r="O29" s="4" t="inlineStr">
+      <c r="P29" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="P29" s="4" t="inlineStr"/>
       <c r="Q29" s="4" t="inlineStr"/>
       <c r="R29" s="4" t="inlineStr"/>
-      <c r="S29" s="5">
-        <f>IFERROR(R29/Q29*1000,"")</f>
+      <c r="S29" s="4" t="inlineStr"/>
+      <c r="T29" s="5">
+        <f>IFERROR(S29/R29*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -2896,13 +3042,13 @@
         <is>
           <t>Resonancia larga · 1 hora
 Compuesta con raíz en 639 Hz, en entonación justa, modo yo.
-Para acompañar una práctica de respiración.
+Para acompañar una práctica de meditación.
 Ciclo respiratorio: de 5.5 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Cuencos sintetizados cada 4 respiraciones.
+Cuencos y canto de ave sintetizados, sin grabaciones.
 Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
 — English —
 Composed with a root of 639 Hz in just intonation, yo mode.
-To accompany a breathing practice.
+To accompany a meditation practice.
 Original composition, synthesized from scratch. No third-party samples.
 Capítulos:
 00:00 [completar tras el montaje]</t>
@@ -2933,27 +3079,32 @@
           <t>yo</t>
         </is>
       </c>
-      <c r="L30" s="2" t="n">
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
         <v>335798</v>
       </c>
-      <c r="M30" s="2" t="n">
+      <c r="N30" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="N30" s="3" t="inlineStr">
+      <c r="O30" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 60 --raiz 639 --modo yo --semilla 335798</t>
         </is>
       </c>
-      <c r="O30" s="4" t="inlineStr">
+      <c r="P30" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="P30" s="4" t="inlineStr"/>
       <c r="Q30" s="4" t="inlineStr"/>
       <c r="R30" s="4" t="inlineStr"/>
-      <c r="S30" s="5">
-        <f>IFERROR(R30/Q30*1000,"")</f>
+      <c r="S30" s="4" t="inlineStr"/>
+      <c r="T30" s="5">
+        <f>IFERROR(S30/R30*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -2977,13 +3128,13 @@
         <is>
           <t>Uno solo · 20 minutos
 Compuesta con raíz en 528 Hz, en entonación justa, modo shin.
-Para acompañar una práctica de respiración.
+Para acompañar una práctica de meditación.
 Ciclo respiratorio: de 5.5 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Cuencos sintetizados cada 4 respiraciones.
+Cuencos y canto de ave sintetizados, sin grabaciones.
 Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
 — English —
 Composed with a root of 528 Hz in just intonation, shin mode.
-To accompany a breathing practice.
+To accompany a meditation practice.
 Original composition, synthesized from scratch. No third-party samples.
 Capítulos:
 00:00 [completar tras el montaje]</t>
@@ -3014,27 +3165,32 @@
           <t>shin</t>
         </is>
       </c>
-      <c r="L31" s="2" t="n">
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
         <v>299306</v>
       </c>
-      <c r="M31" s="2" t="n">
+      <c r="N31" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="N31" s="3" t="inlineStr">
+      <c r="O31" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 20 --raiz 528 --modo shin --semilla 299306</t>
         </is>
       </c>
-      <c r="O31" s="4" t="inlineStr">
+      <c r="P31" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="P31" s="4" t="inlineStr"/>
       <c r="Q31" s="4" t="inlineStr"/>
       <c r="R31" s="4" t="inlineStr"/>
-      <c r="S31" s="5">
-        <f>IFERROR(R31/Q31*1000,"")</f>
+      <c r="S31" s="4" t="inlineStr"/>
+      <c r="T31" s="5">
+        <f>IFERROR(S31/R31*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -3058,13 +3214,13 @@
         <is>
           <t>Templo vacío · 45 minutos
 Compuesta con raíz en 417 Hz, en entonación justa, modo hirajoshi.
-Para acompañar una práctica de respiración.
+Para acompañar una práctica de meditación.
 Ciclo respiratorio: de 5.5 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Cuencos sintetizados cada 4 respiraciones.
+Cuencos y canto de ave sintetizados, sin grabaciones.
 Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
 — English —
 Composed with a root of 417 Hz in just intonation, hirajoshi mode.
-To accompany a breathing practice.
+To accompany a meditation practice.
 Original composition, synthesized from scratch. No third-party samples.
 Capítulos:
 00:00 [completar tras el montaje]</t>
@@ -3095,27 +3251,32 @@
           <t>hirajoshi</t>
         </is>
       </c>
-      <c r="L32" s="2" t="n">
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
         <v>714152</v>
       </c>
-      <c r="M32" s="2" t="n">
+      <c r="N32" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="N32" s="3" t="inlineStr">
+      <c r="O32" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 45 --raiz 417 --modo hirajoshi --semilla 714152</t>
         </is>
       </c>
-      <c r="O32" s="4" t="inlineStr">
+      <c r="P32" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="P32" s="4" t="inlineStr"/>
       <c r="Q32" s="4" t="inlineStr"/>
       <c r="R32" s="4" t="inlineStr"/>
-      <c r="S32" s="5">
-        <f>IFERROR(R32/Q32*1000,"")</f>
+      <c r="S32" s="4" t="inlineStr"/>
+      <c r="T32" s="5">
+        <f>IFERROR(S32/R32*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -3139,13 +3300,13 @@
         <is>
           <t>Lo que queda del sonido · 1 hora
 Compuesta con raíz en 432 Hz, en entonación justa, modo kumoi.
-Para acompañar una práctica de respiración.
+Para acompañar una práctica de meditación.
 Ciclo respiratorio: de 5.5 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Cuencos sintetizados cada 4 respiraciones.
+Cuencos y canto de ave sintetizados, sin grabaciones.
 Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
 — English —
 Composed with a root of 432 Hz in just intonation, kumoi mode.
-To accompany a breathing practice.
+To accompany a meditation practice.
 Original composition, synthesized from scratch. No third-party samples.
 Capítulos:
 00:00 [completar tras el montaje]</t>
@@ -3176,27 +3337,32 @@
           <t>kumoi</t>
         </is>
       </c>
-      <c r="L33" s="2" t="n">
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n">
         <v>926202</v>
       </c>
-      <c r="M33" s="2" t="n">
+      <c r="N33" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="N33" s="3" t="inlineStr">
+      <c r="O33" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 60 --raiz 432 --modo kumoi --semilla 926202</t>
         </is>
       </c>
-      <c r="O33" s="4" t="inlineStr">
+      <c r="P33" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="P33" s="4" t="inlineStr"/>
       <c r="Q33" s="4" t="inlineStr"/>
       <c r="R33" s="4" t="inlineStr"/>
-      <c r="S33" s="5">
-        <f>IFERROR(R33/Q33*1000,"")</f>
+      <c r="S33" s="4" t="inlineStr"/>
+      <c r="T33" s="5">
+        <f>IFERROR(S33/R33*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -3219,14 +3385,14 @@
       <c r="D34" s="3" t="inlineStr">
         <is>
           <t>Mesa limpia · 2 horas
-Compuesta con raíz en 639 Hz, en entonación justa, modo yo.
-Para acompañar una práctica de respiración.
+Compuesta con raíz en 319.5 Hz, la octava grave de 639 Hz, en entonación justa, modo yo.
+Para acompañar el trabajo o el estudio.
 Ciclo respiratorio: de 6.0 a 5.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Cuencos sintetizados cada 4 respiraciones.
+Cuencos y canto de ave sintetizados, sin grabaciones.
 Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
 — English —
 Composed with a root of 639 Hz in just intonation, yo mode.
-To accompany a breathing practice.
+To accompany work or study.
 Original composition, synthesized from scratch. No third-party samples.
 Capítulos:
 00:00 [completar tras el montaje]</t>
@@ -3257,27 +3423,32 @@
           <t>yo</t>
         </is>
       </c>
-      <c r="L34" s="2" t="n">
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>grave</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
         <v>112334</v>
       </c>
-      <c r="M34" s="2" t="n">
+      <c r="N34" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="N34" s="3" t="inlineStr">
-        <is>
-          <t>python3 03-composicion/compositor.py --minutos 120 --raiz 639 --modo yo --semilla 112334</t>
-        </is>
-      </c>
-      <c r="O34" s="4" t="inlineStr">
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>python3 03-composicion/compositor.py --minutos 120 --raiz 639 --modo yo --semilla 112334 --registro grave</t>
+        </is>
+      </c>
+      <c r="P34" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="P34" s="4" t="inlineStr"/>
       <c r="Q34" s="4" t="inlineStr"/>
       <c r="R34" s="4" t="inlineStr"/>
-      <c r="S34" s="5">
-        <f>IFERROR(R34/Q34*1000,"")</f>
+      <c r="S34" s="4" t="inlineStr"/>
+      <c r="T34" s="5">
+        <f>IFERROR(S34/R34*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -3300,14 +3471,14 @@
       <c r="D35" s="3" t="inlineStr">
         <is>
           <t>Tres horas · 3 horas
-Compuesta con raíz en 528 Hz, en entonación justa, modo yo.
-Para acompañar una práctica de respiración.
+Compuesta con raíz en 264 Hz, la octava grave de 528 Hz, en entonación justa, modo yo.
+Para acompañar el trabajo o el estudio.
 Ciclo respiratorio: de 6.0 a 5.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Cuencos sintetizados cada 4 respiraciones.
+Cuencos y canto de ave sintetizados, sin grabaciones.
 Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
 — English —
 Composed with a root of 528 Hz in just intonation, yo mode.
-To accompany a breathing practice.
+To accompany work or study.
 Original composition, synthesized from scratch. No third-party samples.
 Capítulos:
 00:00 [completar tras el montaje]</t>
@@ -3338,27 +3509,32 @@
           <t>yo</t>
         </is>
       </c>
-      <c r="L35" s="2" t="n">
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>grave</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
         <v>935486</v>
       </c>
-      <c r="M35" s="2" t="n">
+      <c r="N35" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="N35" s="3" t="inlineStr">
-        <is>
-          <t>python3 03-composicion/compositor.py --minutos 180 --raiz 528 --modo yo --semilla 935486</t>
-        </is>
-      </c>
-      <c r="O35" s="4" t="inlineStr">
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>python3 03-composicion/compositor.py --minutos 180 --raiz 528 --modo yo --semilla 935486 --registro grave</t>
+        </is>
+      </c>
+      <c r="P35" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="P35" s="4" t="inlineStr"/>
       <c r="Q35" s="4" t="inlineStr"/>
       <c r="R35" s="4" t="inlineStr"/>
-      <c r="S35" s="5">
-        <f>IFERROR(R35/Q35*1000,"")</f>
+      <c r="S35" s="4" t="inlineStr"/>
+      <c r="T35" s="5">
+        <f>IFERROR(S35/R35*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -3381,14 +3557,14 @@
       <c r="D36" s="3" t="inlineStr">
         <is>
           <t>Sin interrupciones · 2 horas
-Compuesta con raíz en 741 Hz, en entonación justa, modo yo.
-Para acompañar una práctica de respiración.
+Compuesta con raíz en 370.5 Hz, la octava grave de 741 Hz, en entonación justa, modo yo.
+Para acompañar el trabajo o el estudio.
 Ciclo respiratorio: de 6.0 a 5.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Cuencos sintetizados cada 4 respiraciones.
+Cuencos y canto de ave sintetizados, sin grabaciones.
 Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
 — English —
 Composed with a root of 741 Hz in just intonation, yo mode.
-To accompany a breathing practice.
+To accompany work or study.
 Original composition, synthesized from scratch. No third-party samples.
 Capítulos:
 00:00 [completar tras el montaje]</t>
@@ -3419,27 +3595,32 @@
           <t>yo</t>
         </is>
       </c>
-      <c r="L36" s="2" t="n">
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>grave</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
         <v>74636</v>
       </c>
-      <c r="M36" s="2" t="n">
+      <c r="N36" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="N36" s="3" t="inlineStr">
-        <is>
-          <t>python3 03-composicion/compositor.py --minutos 120 --raiz 741 --modo yo --semilla 74636</t>
-        </is>
-      </c>
-      <c r="O36" s="4" t="inlineStr">
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>python3 03-composicion/compositor.py --minutos 120 --raiz 741 --modo yo --semilla 74636 --registro grave</t>
+        </is>
+      </c>
+      <c r="P36" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="P36" s="4" t="inlineStr"/>
       <c r="Q36" s="4" t="inlineStr"/>
       <c r="R36" s="4" t="inlineStr"/>
-      <c r="S36" s="5">
-        <f>IFERROR(R36/Q36*1000,"")</f>
+      <c r="S36" s="4" t="inlineStr"/>
+      <c r="T36" s="5">
+        <f>IFERROR(S36/R36*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -3462,14 +3643,14 @@
       <c r="D37" s="3" t="inlineStr">
         <is>
           <t>Luz de mañana · 90 minutos
-Compuesta con raíz en 852 Hz, en entonación justa, modo yo.
-Para acompañar una práctica de respiración.
+Compuesta con raíz en 426 Hz, la octava grave de 852 Hz, en entonación justa, modo yo.
+Para acompañar el trabajo o el estudio.
 Ciclo respiratorio: de 6.0 a 5.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Cuencos sintetizados cada 4 respiraciones.
+Cuencos y canto de ave sintetizados, sin grabaciones.
 Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
 — English —
 Composed with a root of 852 Hz in just intonation, yo mode.
-To accompany a breathing practice.
+To accompany work or study.
 Original composition, synthesized from scratch. No third-party samples.
 Capítulos:
 00:00 [completar tras el montaje]</t>
@@ -3500,27 +3681,32 @@
           <t>yo</t>
         </is>
       </c>
-      <c r="L37" s="2" t="n">
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>grave</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
         <v>903477</v>
       </c>
-      <c r="M37" s="2" t="n">
+      <c r="N37" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="N37" s="3" t="inlineStr">
-        <is>
-          <t>python3 03-composicion/compositor.py --minutos 90 --raiz 852 --modo yo --semilla 903477</t>
-        </is>
-      </c>
-      <c r="O37" s="4" t="inlineStr">
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>python3 03-composicion/compositor.py --minutos 90 --raiz 852 --modo yo --semilla 903477 --registro grave</t>
+        </is>
+      </c>
+      <c r="P37" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="P37" s="4" t="inlineStr"/>
       <c r="Q37" s="4" t="inlineStr"/>
       <c r="R37" s="4" t="inlineStr"/>
-      <c r="S37" s="5">
-        <f>IFERROR(R37/Q37*1000,"")</f>
+      <c r="S37" s="4" t="inlineStr"/>
+      <c r="T37" s="5">
+        <f>IFERROR(S37/R37*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -3543,14 +3729,14 @@
       <c r="D38" s="3" t="inlineStr">
         <is>
           <t>Trabajo lento · 2 horas
-Compuesta con raíz en 432 Hz, en entonación justa, modo yo.
-Para acompañar una práctica de respiración.
+Compuesta con raíz en 216 Hz, la octava grave de 432 Hz, en entonación justa, modo yo.
+Para acompañar el trabajo o el estudio.
 Ciclo respiratorio: de 6.0 a 5.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Cuencos sintetizados cada 4 respiraciones.
+Cuencos y canto de ave sintetizados, sin grabaciones.
 Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
 — English —
 Composed with a root of 432 Hz in just intonation, yo mode.
-To accompany a breathing practice.
+To accompany work or study.
 Original composition, synthesized from scratch. No third-party samples.
 Capítulos:
 00:00 [completar tras el montaje]</t>
@@ -3581,27 +3767,32 @@
           <t>yo</t>
         </is>
       </c>
-      <c r="L38" s="2" t="n">
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>grave</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
         <v>718809</v>
       </c>
-      <c r="M38" s="2" t="n">
+      <c r="N38" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="N38" s="3" t="inlineStr">
-        <is>
-          <t>python3 03-composicion/compositor.py --minutos 120 --raiz 432 --modo yo --semilla 718809</t>
-        </is>
-      </c>
-      <c r="O38" s="4" t="inlineStr">
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>python3 03-composicion/compositor.py --minutos 120 --raiz 432 --modo yo --semilla 718809 --registro grave</t>
+        </is>
+      </c>
+      <c r="P38" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="P38" s="4" t="inlineStr"/>
       <c r="Q38" s="4" t="inlineStr"/>
       <c r="R38" s="4" t="inlineStr"/>
-      <c r="S38" s="5">
-        <f>IFERROR(R38/Q38*1000,"")</f>
+      <c r="S38" s="4" t="inlineStr"/>
+      <c r="T38" s="5">
+        <f>IFERROR(S38/R38*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -3624,14 +3815,14 @@
       <c r="D39" s="3" t="inlineStr">
         <is>
           <t>Una sola cosa · 2 horas
-Compuesta con raíz en 528 Hz, en entonación justa, modo shin.
-Para acompañar una práctica de respiración.
+Compuesta con raíz en 264 Hz, la octava grave de 528 Hz, en entonación justa, modo shin.
+Para acompañar el trabajo o el estudio.
 Ciclo respiratorio: de 6.0 a 5.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Cuencos sintetizados cada 4 respiraciones.
+Cuencos y canto de ave sintetizados, sin grabaciones.
 Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
 — English —
 Composed with a root of 528 Hz in just intonation, shin mode.
-To accompany a breathing practice.
+To accompany work or study.
 Original composition, synthesized from scratch. No third-party samples.
 Capítulos:
 00:00 [completar tras el montaje]</t>
@@ -3662,27 +3853,32 @@
           <t>shin</t>
         </is>
       </c>
-      <c r="L39" s="2" t="n">
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>grave</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
         <v>203246</v>
       </c>
-      <c r="M39" s="2" t="n">
+      <c r="N39" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="N39" s="3" t="inlineStr">
-        <is>
-          <t>python3 03-composicion/compositor.py --minutos 120 --raiz 528 --modo shin --semilla 203246</t>
-        </is>
-      </c>
-      <c r="O39" s="4" t="inlineStr">
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>python3 03-composicion/compositor.py --minutos 120 --raiz 528 --modo shin --semilla 203246 --registro grave</t>
+        </is>
+      </c>
+      <c r="P39" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="P39" s="4" t="inlineStr"/>
       <c r="Q39" s="4" t="inlineStr"/>
       <c r="R39" s="4" t="inlineStr"/>
-      <c r="S39" s="5">
-        <f>IFERROR(R39/Q39*1000,"")</f>
+      <c r="S39" s="4" t="inlineStr"/>
+      <c r="T39" s="5">
+        <f>IFERROR(S39/R39*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -3705,14 +3901,14 @@
       <c r="D40" s="3" t="inlineStr">
         <is>
           <t>Ventana abierta · 90 minutos
-Compuesta con raíz en 639 Hz, en entonación justa, modo yo.
-Para acompañar una práctica de respiración.
+Compuesta con raíz en 319.5 Hz, la octava grave de 639 Hz, en entonación justa, modo yo.
+Para acompañar el trabajo o el estudio.
 Ciclo respiratorio: de 6.0 a 5.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Cuencos sintetizados cada 4 respiraciones.
+Cuencos y canto de ave sintetizados, sin grabaciones.
 Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
 — English —
 Composed with a root of 639 Hz in just intonation, yo mode.
-To accompany a breathing practice.
+To accompany work or study.
 Original composition, synthesized from scratch. No third-party samples.
 Capítulos:
 00:00 [completar tras el montaje]</t>
@@ -3743,27 +3939,32 @@
           <t>yo</t>
         </is>
       </c>
-      <c r="L40" s="2" t="n">
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>grave</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n">
         <v>281608</v>
       </c>
-      <c r="M40" s="2" t="n">
+      <c r="N40" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="N40" s="3" t="inlineStr">
-        <is>
-          <t>python3 03-composicion/compositor.py --minutos 90 --raiz 639 --modo yo --semilla 281608</t>
-        </is>
-      </c>
-      <c r="O40" s="4" t="inlineStr">
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t>python3 03-composicion/compositor.py --minutos 90 --raiz 639 --modo yo --semilla 281608 --registro grave</t>
+        </is>
+      </c>
+      <c r="P40" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="P40" s="4" t="inlineStr"/>
       <c r="Q40" s="4" t="inlineStr"/>
       <c r="R40" s="4" t="inlineStr"/>
-      <c r="S40" s="5">
-        <f>IFERROR(R40/Q40*1000,"")</f>
+      <c r="S40" s="4" t="inlineStr"/>
+      <c r="T40" s="5">
+        <f>IFERROR(S40/R40*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -3786,14 +3987,14 @@
       <c r="D41" s="3" t="inlineStr">
         <is>
           <t>Hasta terminar · 3 horas
-Compuesta con raíz en 741 Hz, en entonación justa, modo yo.
-Para acompañar una práctica de respiración.
+Compuesta con raíz en 370.5 Hz, la octava grave de 741 Hz, en entonación justa, modo yo.
+Para acompañar el trabajo o el estudio.
 Ciclo respiratorio: de 6.0 a 5.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Cuencos sintetizados cada 4 respiraciones.
+Cuencos y canto de ave sintetizados, sin grabaciones.
 Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
 — English —
 Composed with a root of 741 Hz in just intonation, yo mode.
-To accompany a breathing practice.
+To accompany work or study.
 Original composition, synthesized from scratch. No third-party samples.
 Capítulos:
 00:00 [completar tras el montaje]</t>
@@ -3824,32 +4025,37 @@
           <t>yo</t>
         </is>
       </c>
-      <c r="L41" s="2" t="n">
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>grave</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="n">
         <v>883876</v>
       </c>
-      <c r="M41" s="2" t="n">
+      <c r="N41" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="N41" s="3" t="inlineStr">
-        <is>
-          <t>python3 03-composicion/compositor.py --minutos 180 --raiz 741 --modo yo --semilla 883876</t>
-        </is>
-      </c>
-      <c r="O41" s="4" t="inlineStr">
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>python3 03-composicion/compositor.py --minutos 180 --raiz 741 --modo yo --semilla 883876 --registro grave</t>
+        </is>
+      </c>
+      <c r="P41" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="P41" s="4" t="inlineStr"/>
       <c r="Q41" s="4" t="inlineStr"/>
       <c r="R41" s="4" t="inlineStr"/>
-      <c r="S41" s="5">
-        <f>IFERROR(R41/Q41*1000,"")</f>
+      <c r="S41" s="4" t="inlineStr"/>
+      <c r="T41" s="5">
+        <f>IFERROR(S41/R41*1000,"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S41"/>
+  <autoFilter ref="A1:T41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3895,7 +4101,7 @@
         </is>
       </c>
       <c r="B3" s="7">
-        <f>COUNTIF(Catálogo!O2:O41,"pendiente")</f>
+        <f>COUNTIF(Catálogo!P2:P41,"pendiente")</f>
         <v/>
       </c>
     </row>
@@ -3906,7 +4112,7 @@
         </is>
       </c>
       <c r="B4" s="7">
-        <f>COUNTIF(Catálogo!O2:O41,"compuesta")</f>
+        <f>COUNTIF(Catálogo!P2:P41,"compuesta")</f>
         <v/>
       </c>
     </row>
@@ -3917,7 +4123,7 @@
         </is>
       </c>
       <c r="B5" s="7">
-        <f>COUNTIF(Catálogo!O2:O41,"montada")</f>
+        <f>COUNTIF(Catálogo!P2:P41,"montada")</f>
         <v/>
       </c>
     </row>
@@ -3928,7 +4134,7 @@
         </is>
       </c>
       <c r="B6" s="7">
-        <f>COUNTIF(Catálogo!O2:O41,"publicada")</f>
+        <f>COUNTIF(Catálogo!P2:P41,"publicada")</f>
         <v/>
       </c>
     </row>
@@ -3972,11 +4178,11 @@
         <v/>
       </c>
       <c r="C10" s="7">
-        <f>COUNTIFS(Catálogo!C2:C41,A10,Catálogo!O2:O41,"publicada")</f>
+        <f>COUNTIFS(Catálogo!C2:C41,A10,Catálogo!P2:P41,"publicada")</f>
         <v/>
       </c>
       <c r="D10" s="7">
-        <f>SUMIF(Catálogo!C2:C41,A10,Catálogo!M2:M41)</f>
+        <f>SUMIF(Catálogo!C2:C41,A10,Catálogo!N2:N41)</f>
         <v/>
       </c>
     </row>
@@ -3991,11 +4197,11 @@
         <v/>
       </c>
       <c r="C11" s="7">
-        <f>COUNTIFS(Catálogo!C2:C41,A11,Catálogo!O2:O41,"publicada")</f>
+        <f>COUNTIFS(Catálogo!C2:C41,A11,Catálogo!P2:P41,"publicada")</f>
         <v/>
       </c>
       <c r="D11" s="7">
-        <f>SUMIF(Catálogo!C2:C41,A11,Catálogo!M2:M41)</f>
+        <f>SUMIF(Catálogo!C2:C41,A11,Catálogo!N2:N41)</f>
         <v/>
       </c>
     </row>
@@ -4010,11 +4216,11 @@
         <v/>
       </c>
       <c r="C12" s="7">
-        <f>COUNTIFS(Catálogo!C2:C41,A12,Catálogo!O2:O41,"publicada")</f>
+        <f>COUNTIFS(Catálogo!C2:C41,A12,Catálogo!P2:P41,"publicada")</f>
         <v/>
       </c>
       <c r="D12" s="7">
-        <f>SUMIF(Catálogo!C2:C41,A12,Catálogo!M2:M41)</f>
+        <f>SUMIF(Catálogo!C2:C41,A12,Catálogo!N2:N41)</f>
         <v/>
       </c>
     </row>
@@ -4029,11 +4235,11 @@
         <v/>
       </c>
       <c r="C13" s="7">
-        <f>COUNTIFS(Catálogo!C2:C41,A13,Catálogo!O2:O41,"publicada")</f>
+        <f>COUNTIFS(Catálogo!C2:C41,A13,Catálogo!P2:P41,"publicada")</f>
         <v/>
       </c>
       <c r="D13" s="7">
-        <f>SUMIF(Catálogo!C2:C41,A13,Catálogo!M2:M41)</f>
+        <f>SUMIF(Catálogo!C2:C41,A13,Catálogo!N2:N41)</f>
         <v/>
       </c>
     </row>
@@ -4048,11 +4254,11 @@
         <v/>
       </c>
       <c r="C14" s="7">
-        <f>COUNTIFS(Catálogo!C2:C41,A14,Catálogo!O2:O41,"publicada")</f>
+        <f>COUNTIFS(Catálogo!C2:C41,A14,Catálogo!P2:P41,"publicada")</f>
         <v/>
       </c>
       <c r="D14" s="7">
-        <f>SUMIF(Catálogo!C2:C41,A14,Catálogo!M2:M41)</f>
+        <f>SUMIF(Catálogo!C2:C41,A14,Catálogo!N2:N41)</f>
         <v/>
       </c>
     </row>
@@ -4089,7 +4295,7 @@
         </is>
       </c>
       <c r="B18" s="7">
-        <f>SUM(Catálogo!Q2:Q41)</f>
+        <f>SUM(Catálogo!R2:R41)</f>
         <v/>
       </c>
     </row>
@@ -4100,7 +4306,7 @@
         </is>
       </c>
       <c r="B19" s="7">
-        <f>SUM(Catálogo!R2:R41)</f>
+        <f>SUM(Catálogo!S2:S41)</f>
         <v/>
       </c>
     </row>
@@ -4286,12 +4492,12 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>raiz_hz / modo / semilla</t>
+          <t>raiz_hz / modo / registro / semilla</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Parámetros de composición. La semilla regenera la obra idéntica.</t>
+          <t>Parámetros de composición. El registro grave baja una octava (pilares Sueño y Foco). La semilla regenera la obra idéntica.</t>
         </is>
       </c>
     </row>

--- a/08-catalogo/catalogo_canal.xlsx
+++ b/08-catalogo/catalogo_canal.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Leyenda" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$V$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$X$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -487,31 +487,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V41"/>
+  <dimension ref="A1:X41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="70" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="62" customWidth="1" min="16" max="16"/>
-    <col width="62" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="18" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="62" customWidth="1" min="18" max="18"/>
+    <col width="62" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -527,100 +529,110 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>titulo_es</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>tema</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>ambiente</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>descripcion_optimizada</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>descripcion_es</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>titulo_miniatura</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>hashtags</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>etiquetas</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>imagen_miniatura</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>url_video</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>raiz_hz</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>modo</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>registro</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>semilla</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>duracion_min</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>comando_regeneracion</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>comando_ambiente</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>estado</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>fecha_publicacion</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>vistas</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>suscriptores</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>subs_por_1000</t>
         </is>
@@ -634,91 +646,104 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
+          <t>Sleep Music · Ocean Waves · 432 Hz · Bottomless Night · 3 Hours</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>Música para dormir · Olas del mar · 432 Hz · Noche sin fondo · 3 horas</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Dormir</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>mar</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Bottomless Night · 3 Hours
+To accompany sleep.
+Ambience: ocean waves.
+Composed around a root of 216 Hz, the low octave of 432 Hz, in just intonation, shin mode.
+Breathing cycle: from 4.5 down to 3.5 breaths per minute, 40 % inhale / 60 % exhale.
+Original composition, synthesized from scratch, ambience included. No third-party samples.
+Chapters:
+00:00 [fill in after editing]</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Noche sin fondo · 3 horas
+Para acompañar el sueño.
+Ambiente: olas del mar.
 Compuesta con raíz en 216 Hz, la octava grave de 432 Hz, en entonación justa, modo shin.
-Para acompañar el sueño.
 Ciclo respiratorio: de 4.5 a 3.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Ambiente: olas del mar, sintetizado, sin grabaciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 432 Hz in just intonation, shin mode.
-To accompany sleep.
-Original composition, synthesized from scratch. No third-party samples.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Capítulos:
 00:00 [completar tras el montaje]</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>3 HORAS</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>#MúsicaParaDormir #MúsicaRelajante #432Hz</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>3 HOURS</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>#SleepMusic #Meditation #432Hz</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>432 hz, música 432 hz, música para dormir, sleep music, dormir, shin, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, singing bowls, just intonation</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr"/>
-      <c r="J2" s="4" t="inlineStr"/>
-      <c r="K2" s="2" t="n">
+      <c r="K2" s="4" t="inlineStr"/>
+      <c r="L2" s="4" t="inlineStr"/>
+      <c r="M2" s="2" t="n">
         <v>432</v>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>shin</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>grave</t>
         </is>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="P2" s="2" t="n">
         <v>505716</v>
       </c>
-      <c r="O2" s="2" t="n">
+      <c r="Q2" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="P2" s="3" t="inlineStr">
+      <c r="R2" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 180 --raiz 432 --modo shin --semilla 505716 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/ambiente.py audio/OBRA-001_432_shin.wav audio/OBRA-001_final.wav --fondo mar</t>
         </is>
       </c>
-      <c r="R2" s="4" t="inlineStr">
+      <c r="T2" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="S2" s="4" t="inlineStr"/>
-      <c r="T2" s="4" t="inlineStr"/>
       <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="5">
-        <f>IFERROR(U2/T2*1000,"")</f>
+      <c r="V2" s="4" t="inlineStr"/>
+      <c r="W2" s="4" t="inlineStr"/>
+      <c r="X2" s="5">
+        <f>IFERROR(W2/V2*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -730,91 +755,104 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
+          <t>Sleep Music · Ocean Waves · 528 Hz · Low Tide · 2 Hours</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>Música para dormir · Olas del mar · 528 Hz · Marea baja · 2 horas</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Dormir</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>mar</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Low Tide · 2 Hours
+To accompany sleep.
+Ambience: ocean waves.
+Composed around a root of 264 Hz, the low octave of 528 Hz, in just intonation, kumoi mode.
+Breathing cycle: from 4.5 down to 3.5 breaths per minute, 40 % inhale / 60 % exhale.
+Original composition, synthesized from scratch, ambience included. No third-party samples.
+Chapters:
+00:00 [fill in after editing]</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Marea baja · 2 horas
+Para acompañar el sueño.
+Ambiente: olas del mar.
 Compuesta con raíz en 264 Hz, la octava grave de 528 Hz, en entonación justa, modo kumoi.
-Para acompañar el sueño.
 Ciclo respiratorio: de 4.5 a 3.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Ambiente: olas del mar, sintetizado, sin grabaciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 528 Hz in just intonation, kumoi mode.
-To accompany sleep.
-Original composition, synthesized from scratch. No third-party samples.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Capítulos:
 00:00 [completar tras el montaje]</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>2 HORAS</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>#MúsicaParaDormir #MúsicaRelajante #528Hz</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>2 HOURS</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>#SleepMusic #Meditation #528Hz</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>528 hz, música 528 hz, música para dormir, sleep music, dormir, kumoi, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, singing bowls, just intonation</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr"/>
-      <c r="J3" s="4" t="inlineStr"/>
-      <c r="K3" s="2" t="n">
+      <c r="K3" s="4" t="inlineStr"/>
+      <c r="L3" s="4" t="inlineStr"/>
+      <c r="M3" s="2" t="n">
         <v>528</v>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>kumoi</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>grave</t>
         </is>
       </c>
-      <c r="N3" s="2" t="n">
+      <c r="P3" s="2" t="n">
         <v>443547</v>
       </c>
-      <c r="O3" s="2" t="n">
+      <c r="Q3" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="P3" s="3" t="inlineStr">
+      <c r="R3" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 120 --raiz 528 --modo kumoi --semilla 443547 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="S3" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/ambiente.py audio/OBRA-002_528_kumoi.wav audio/OBRA-002_final.wav --fondo mar</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr">
+      <c r="T3" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="S3" s="4" t="inlineStr"/>
-      <c r="T3" s="4" t="inlineStr"/>
       <c r="U3" s="4" t="inlineStr"/>
-      <c r="V3" s="5">
-        <f>IFERROR(U3/T3*1000,"")</f>
+      <c r="V3" s="4" t="inlineStr"/>
+      <c r="W3" s="4" t="inlineStr"/>
+      <c r="X3" s="5">
+        <f>IFERROR(W3/V3*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -826,91 +864,104 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
+          <t>Sleep Music · Ocean Waves · 396 Hz · Dark Room · 2 Hours</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>Música para dormir · Olas del mar · 396 Hz · Cuarto oscuro · 2 horas</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Dormir</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>mar</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Dark Room · 2 Hours
+To accompany sleep.
+Ambience: ocean waves.
+Composed around a root of 198 Hz, the low octave of 396 Hz, in just intonation, kumoi mode.
+Breathing cycle: from 4.5 down to 3.5 breaths per minute, 40 % inhale / 60 % exhale.
+Original composition, synthesized from scratch, ambience included. No third-party samples.
+Chapters:
+00:00 [fill in after editing]</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Cuarto oscuro · 2 horas
+Para acompañar el sueño.
+Ambiente: olas del mar.
 Compuesta con raíz en 198 Hz, la octava grave de 396 Hz, en entonación justa, modo kumoi.
-Para acompañar el sueño.
 Ciclo respiratorio: de 4.5 a 3.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Ambiente: olas del mar, sintetizado, sin grabaciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 396 Hz in just intonation, kumoi mode.
-To accompany sleep.
-Original composition, synthesized from scratch. No third-party samples.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Capítulos:
 00:00 [completar tras el montaje]</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2 HORAS</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>#MúsicaParaDormir #MúsicaRelajante #396Hz</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2 HOURS</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>#SleepMusic #Meditation #396Hz</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>396 hz, música 396 hz, música para dormir, sleep music, dormir, kumoi, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, singing bowls, just intonation</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="2" t="n">
+      <c r="K4" s="4" t="inlineStr"/>
+      <c r="L4" s="4" t="inlineStr"/>
+      <c r="M4" s="2" t="n">
         <v>396</v>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>kumoi</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>grave</t>
         </is>
       </c>
-      <c r="N4" s="2" t="n">
+      <c r="P4" s="2" t="n">
         <v>692584</v>
       </c>
-      <c r="O4" s="2" t="n">
+      <c r="Q4" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="R4" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 120 --raiz 396 --modo kumoi --semilla 692584 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/ambiente.py audio/OBRA-003_396_kumoi.wav audio/OBRA-003_final.wav --fondo mar</t>
         </is>
       </c>
-      <c r="R4" s="4" t="inlineStr">
+      <c r="T4" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr"/>
       <c r="U4" s="4" t="inlineStr"/>
-      <c r="V4" s="5">
-        <f>IFERROR(U4/T4*1000,"")</f>
+      <c r="V4" s="4" t="inlineStr"/>
+      <c r="W4" s="4" t="inlineStr"/>
+      <c r="X4" s="5">
+        <f>IFERROR(W4/V4*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -922,91 +973,104 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
+          <t>Sleep Music · Ocean Waves · 528 Hz · No One Awake · 3 Hours</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>Música para dormir · Olas del mar · 528 Hz · Nadie despierto · 3 horas</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Dormir</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>mar</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>No One Awake · 3 Hours
+To accompany sleep.
+Ambience: ocean waves.
+Composed around a root of 264 Hz, the low octave of 528 Hz, in just intonation, shin mode.
+Breathing cycle: from 4.5 down to 3.5 breaths per minute, 40 % inhale / 60 % exhale.
+Original composition, synthesized from scratch, ambience included. No third-party samples.
+Chapters:
+00:00 [fill in after editing]</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Nadie despierto · 3 horas
+Para acompañar el sueño.
+Ambiente: olas del mar.
 Compuesta con raíz en 264 Hz, la octava grave de 528 Hz, en entonación justa, modo shin.
-Para acompañar el sueño.
 Ciclo respiratorio: de 4.5 a 3.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Ambiente: olas del mar, sintetizado, sin grabaciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 528 Hz in just intonation, shin mode.
-To accompany sleep.
-Original composition, synthesized from scratch. No third-party samples.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Capítulos:
 00:00 [completar tras el montaje]</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3 HORAS</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>#MúsicaParaDormir #MúsicaRelajante #528Hz</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>3 HOURS</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>#SleepMusic #Meditation #528Hz</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>528 hz, música 528 hz, música para dormir, sleep music, dormir, shin, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, singing bowls, just intonation</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr"/>
-      <c r="K5" s="2" t="n">
+      <c r="K5" s="4" t="inlineStr"/>
+      <c r="L5" s="4" t="inlineStr"/>
+      <c r="M5" s="2" t="n">
         <v>528</v>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>shin</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>grave</t>
         </is>
       </c>
-      <c r="N5" s="2" t="n">
+      <c r="P5" s="2" t="n">
         <v>751043</v>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="Q5" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="P5" s="3" t="inlineStr">
+      <c r="R5" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 180 --raiz 528 --modo shin --semilla 751043 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/ambiente.py audio/OBRA-004_528_shin.wav audio/OBRA-004_final.wav --fondo mar</t>
         </is>
       </c>
-      <c r="R5" s="4" t="inlineStr">
+      <c r="T5" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="S5" s="4" t="inlineStr"/>
-      <c r="T5" s="4" t="inlineStr"/>
       <c r="U5" s="4" t="inlineStr"/>
-      <c r="V5" s="5">
-        <f>IFERROR(U5/T5*1000,"")</f>
+      <c r="V5" s="4" t="inlineStr"/>
+      <c r="W5" s="4" t="inlineStr"/>
+      <c r="X5" s="5">
+        <f>IFERROR(W5/V5*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -1018,91 +1082,104 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
+          <t>Sleep Music · Ocean Waves · 432 Hz · Winter Breath · 2 Hours</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
           <t>Música para dormir · Olas del mar · 432 Hz · Respiración de invierno · 2 horas</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Dormir</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>mar</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Winter Breath · 2 Hours
+To accompany sleep.
+Ambience: ocean waves.
+Composed around a root of 216 Hz, the low octave of 432 Hz, in just intonation, kumoi mode.
+Breathing cycle: from 4.5 down to 3.5 breaths per minute, 40 % inhale / 60 % exhale.
+Original composition, synthesized from scratch, ambience included. No third-party samples.
+Chapters:
+00:00 [fill in after editing]</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Respiración de invierno · 2 horas
+Para acompañar el sueño.
+Ambiente: olas del mar.
 Compuesta con raíz en 216 Hz, la octava grave de 432 Hz, en entonación justa, modo kumoi.
-Para acompañar el sueño.
 Ciclo respiratorio: de 4.5 a 3.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Ambiente: olas del mar, sintetizado, sin grabaciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 432 Hz in just intonation, kumoi mode.
-To accompany sleep.
-Original composition, synthesized from scratch. No third-party samples.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Capítulos:
 00:00 [completar tras el montaje]</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2 HORAS</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>#MúsicaParaDormir #MúsicaRelajante #432Hz</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2 HOURS</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>#SleepMusic #Meditation #432Hz</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>432 hz, música 432 hz, música para dormir, sleep music, dormir, kumoi, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, singing bowls, just intonation</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="2" t="n">
+      <c r="K6" s="4" t="inlineStr"/>
+      <c r="L6" s="4" t="inlineStr"/>
+      <c r="M6" s="2" t="n">
         <v>432</v>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>kumoi</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>grave</t>
         </is>
       </c>
-      <c r="N6" s="2" t="n">
+      <c r="P6" s="2" t="n">
         <v>531725</v>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="Q6" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="P6" s="3" t="inlineStr">
+      <c r="R6" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 120 --raiz 432 --modo kumoi --semilla 531725 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/ambiente.py audio/OBRA-005_432_kumoi.wav audio/OBRA-005_final.wav --fondo mar</t>
         </is>
       </c>
-      <c r="R6" s="4" t="inlineStr">
+      <c r="T6" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr"/>
       <c r="U6" s="4" t="inlineStr"/>
-      <c r="V6" s="5">
-        <f>IFERROR(U6/T6*1000,"")</f>
+      <c r="V6" s="4" t="inlineStr"/>
+      <c r="W6" s="4" t="inlineStr"/>
+      <c r="X6" s="5">
+        <f>IFERROR(W6/V6*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -1114,91 +1191,104 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
+          <t>Sleep Music · Ocean Waves · 417 Hz · Before Dawn · 90 Minutes</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
           <t>Música para dormir · Olas del mar · 417 Hz · Antes del alba · 90 minutos</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Dormir</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>mar</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Before Dawn · 90 Minutes
+To accompany sleep.
+Ambience: ocean waves.
+Composed around a root of 208.5 Hz, the low octave of 417 Hz, in just intonation, kumoi mode.
+Breathing cycle: from 4.5 down to 3.5 breaths per minute, 40 % inhale / 60 % exhale.
+Original composition, synthesized from scratch, ambience included. No third-party samples.
+Chapters:
+00:00 [fill in after editing]</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Antes del alba · 90 minutos
+Para acompañar el sueño.
+Ambiente: olas del mar.
 Compuesta con raíz en 208.5 Hz, la octava grave de 417 Hz, en entonación justa, modo kumoi.
-Para acompañar el sueño.
 Ciclo respiratorio: de 4.5 a 3.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Ambiente: olas del mar, sintetizado, sin grabaciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 417 Hz in just intonation, kumoi mode.
-To accompany sleep.
-Original composition, synthesized from scratch. No third-party samples.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Capítulos:
 00:00 [completar tras el montaje]</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>90 MIN</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>#MúsicaParaDormir #MúsicaRelajante #417Hz</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>#SleepMusic #Meditation #417Hz</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>417 hz, música 417 hz, música para dormir, sleep music, dormir, kumoi, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, singing bowls, just intonation</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr"/>
-      <c r="J7" s="4" t="inlineStr"/>
-      <c r="K7" s="2" t="n">
+      <c r="K7" s="4" t="inlineStr"/>
+      <c r="L7" s="4" t="inlineStr"/>
+      <c r="M7" s="2" t="n">
         <v>417</v>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>kumoi</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>grave</t>
         </is>
       </c>
-      <c r="N7" s="2" t="n">
+      <c r="P7" s="2" t="n">
         <v>813147</v>
       </c>
-      <c r="O7" s="2" t="n">
+      <c r="Q7" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="P7" s="3" t="inlineStr">
+      <c r="R7" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 90 --raiz 417 --modo kumoi --semilla 813147 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="Q7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/ambiente.py audio/OBRA-006_417_kumoi.wav audio/OBRA-006_final.wav --fondo mar</t>
         </is>
       </c>
-      <c r="R7" s="4" t="inlineStr">
+      <c r="T7" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="S7" s="4" t="inlineStr"/>
-      <c r="T7" s="4" t="inlineStr"/>
       <c r="U7" s="4" t="inlineStr"/>
-      <c r="V7" s="5">
-        <f>IFERROR(U7/T7*1000,"")</f>
+      <c r="V7" s="4" t="inlineStr"/>
+      <c r="W7" s="4" t="inlineStr"/>
+      <c r="X7" s="5">
+        <f>IFERROR(W7/V7*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -1210,91 +1300,104 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
+          <t>Sleep Music · Ocean Waves · 396 Hz · Slow Weight · 2 Hours</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
           <t>Música para dormir · Olas del mar · 396 Hz · Peso lento · 2 horas</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Dormir</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>mar</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Slow Weight · 2 Hours
+To accompany sleep.
+Ambience: ocean waves.
+Composed around a root of 198 Hz, the low octave of 396 Hz, in just intonation, shin mode.
+Breathing cycle: from 4.5 down to 3.5 breaths per minute, 40 % inhale / 60 % exhale.
+Original composition, synthesized from scratch, ambience included. No third-party samples.
+Chapters:
+00:00 [fill in after editing]</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Peso lento · 2 horas
+Para acompañar el sueño.
+Ambiente: olas del mar.
 Compuesta con raíz en 198 Hz, la octava grave de 396 Hz, en entonación justa, modo shin.
-Para acompañar el sueño.
 Ciclo respiratorio: de 4.5 a 3.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Ambiente: olas del mar, sintetizado, sin grabaciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 396 Hz in just intonation, shin mode.
-To accompany sleep.
-Original composition, synthesized from scratch. No third-party samples.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Capítulos:
 00:00 [completar tras el montaje]</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2 HORAS</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>#MúsicaParaDormir #MúsicaRelajante #396Hz</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2 HOURS</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>#SleepMusic #Meditation #396Hz</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>396 hz, música 396 hz, música para dormir, sleep music, dormir, shin, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, singing bowls, just intonation</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr"/>
-      <c r="J8" s="4" t="inlineStr"/>
-      <c r="K8" s="2" t="n">
+      <c r="K8" s="4" t="inlineStr"/>
+      <c r="L8" s="4" t="inlineStr"/>
+      <c r="M8" s="2" t="n">
         <v>396</v>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>shin</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>grave</t>
         </is>
       </c>
-      <c r="N8" s="2" t="n">
+      <c r="P8" s="2" t="n">
         <v>885916</v>
       </c>
-      <c r="O8" s="2" t="n">
+      <c r="Q8" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="P8" s="3" t="inlineStr">
+      <c r="R8" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 120 --raiz 396 --modo shin --semilla 885916 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="Q8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/ambiente.py audio/OBRA-007_396_shin.wav audio/OBRA-007_final.wav --fondo mar</t>
         </is>
       </c>
-      <c r="R8" s="4" t="inlineStr">
+      <c r="T8" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="S8" s="4" t="inlineStr"/>
-      <c r="T8" s="4" t="inlineStr"/>
       <c r="U8" s="4" t="inlineStr"/>
-      <c r="V8" s="5">
-        <f>IFERROR(U8/T8*1000,"")</f>
+      <c r="V8" s="4" t="inlineStr"/>
+      <c r="W8" s="4" t="inlineStr"/>
+      <c r="X8" s="5">
+        <f>IFERROR(W8/V8*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -1306,91 +1409,104 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
+          <t>Sleep Music · Ocean Waves · 432 Hz · The Sleeping House · 3 Hours</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
           <t>Música para dormir · Olas del mar · 432 Hz · La casa dormida · 3 horas</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Dormir</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>mar</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>The Sleeping House · 3 Hours
+To accompany sleep.
+Ambience: ocean waves.
+Composed around a root of 216 Hz, the low octave of 432 Hz, in just intonation, kumoi mode.
+Breathing cycle: from 4.5 down to 3.5 breaths per minute, 40 % inhale / 60 % exhale.
+Original composition, synthesized from scratch, ambience included. No third-party samples.
+Chapters:
+00:00 [fill in after editing]</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>La casa dormida · 3 horas
+Para acompañar el sueño.
+Ambiente: olas del mar.
 Compuesta con raíz en 216 Hz, la octava grave de 432 Hz, en entonación justa, modo kumoi.
-Para acompañar el sueño.
 Ciclo respiratorio: de 4.5 a 3.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Ambiente: olas del mar, sintetizado, sin grabaciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 432 Hz in just intonation, kumoi mode.
-To accompany sleep.
-Original composition, synthesized from scratch. No third-party samples.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Capítulos:
 00:00 [completar tras el montaje]</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>3 HORAS</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>#MúsicaParaDormir #MúsicaRelajante #432Hz</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>3 HOURS</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>#SleepMusic #Meditation #432Hz</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>432 hz, música 432 hz, música para dormir, sleep music, dormir, kumoi, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, singing bowls, just intonation</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr"/>
-      <c r="J9" s="4" t="inlineStr"/>
-      <c r="K9" s="2" t="n">
+      <c r="K9" s="4" t="inlineStr"/>
+      <c r="L9" s="4" t="inlineStr"/>
+      <c r="M9" s="2" t="n">
         <v>432</v>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>kumoi</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>grave</t>
         </is>
       </c>
-      <c r="N9" s="2" t="n">
+      <c r="P9" s="2" t="n">
         <v>295910</v>
       </c>
-      <c r="O9" s="2" t="n">
+      <c r="Q9" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="P9" s="3" t="inlineStr">
+      <c r="R9" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 180 --raiz 432 --modo kumoi --semilla 295910 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="Q9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/ambiente.py audio/OBRA-008_432_kumoi.wav audio/OBRA-008_final.wav --fondo mar</t>
         </is>
       </c>
-      <c r="R9" s="4" t="inlineStr">
+      <c r="T9" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="S9" s="4" t="inlineStr"/>
-      <c r="T9" s="4" t="inlineStr"/>
       <c r="U9" s="4" t="inlineStr"/>
-      <c r="V9" s="5">
-        <f>IFERROR(U9/T9*1000,"")</f>
+      <c r="V9" s="4" t="inlineStr"/>
+      <c r="W9" s="4" t="inlineStr"/>
+      <c r="X9" s="5">
+        <f>IFERROR(W9/V9*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -1402,91 +1518,104 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
+          <t>Music for Anxiety · Ocean and Birds · 396 Hz · Just Exhale · 25 Minutes</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
           <t>Música para momentos de ansiedad · Mar y pájaros · 396 Hz · Solo exhalar · 25 minutos</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Ansiedad</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>mar-aves</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Just Exhale · 25 Minutes
+To accompany a pause when your mind won't stop.
+Ambience: ocean and birds.
+Composed around a root of 396 Hz, in just intonation, kumoi mode.
+Breathing cycle: from 6.0 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
+Original composition, synthesized from scratch, ambience included. No third-party samples.
+Chapters:
+00:00 [fill in after editing]</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Solo exhalar · 25 minutos
+Para acompañar un momento de pausa cuando la cabeza no para.
+Ambiente: mar y pájaros.
 Compuesta con raíz en 396 Hz, en entonación justa, modo kumoi.
-Para acompañar un momento de pausa cuando la cabeza no para.
 Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Ambiente: mar y pájaros, sintetizado, sin grabaciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 396 Hz in just intonation, kumoi mode.
-To accompany a pause when your mind won't stop.
-Original composition, synthesized from scratch. No third-party samples.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Capítulos:
 00:00 [completar tras el montaje]</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>25 MIN</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>#Relajación #MúsicaRelajante #396Hz</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>#RelaxingMusic #Meditation #396Hz</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>396 hz, música 396 hz, música para momentos de ansiedad, music for anxiety, ansiedad, kumoi, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr"/>
-      <c r="J10" s="4" t="inlineStr"/>
-      <c r="K10" s="2" t="n">
+      <c r="K10" s="4" t="inlineStr"/>
+      <c r="L10" s="4" t="inlineStr"/>
+      <c r="M10" s="2" t="n">
         <v>396</v>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>kumoi</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>medio</t>
         </is>
       </c>
-      <c r="N10" s="2" t="n">
+      <c r="P10" s="2" t="n">
         <v>555819</v>
       </c>
-      <c r="O10" s="2" t="n">
+      <c r="Q10" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="P10" s="3" t="inlineStr">
+      <c r="R10" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 25 --raiz 396 --modo kumoi --semilla 555819 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="Q10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py aves 1540 audio/OBRA-009_capa.wav --semilla 555819 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-009_396_kumoi.wav audio/OBRA-009_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-009_capa.wav</t>
         </is>
       </c>
-      <c r="R10" s="4" t="inlineStr">
+      <c r="T10" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="S10" s="4" t="inlineStr"/>
-      <c r="T10" s="4" t="inlineStr"/>
       <c r="U10" s="4" t="inlineStr"/>
-      <c r="V10" s="5">
-        <f>IFERROR(U10/T10*1000,"")</f>
+      <c r="V10" s="4" t="inlineStr"/>
+      <c r="W10" s="4" t="inlineStr"/>
+      <c r="X10" s="5">
+        <f>IFERROR(W10/V10*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -1498,91 +1627,104 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
+          <t>Music for Anxiety · Zen Temple · 432 Hz · Slowing Down · 30 Minutes</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>Música para momentos de ansiedad · Templo zen · 432 Hz · Bajar el ritmo · 30 minutos</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Ansiedad</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>zen</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Slowing Down · 30 Minutes
+To accompany a pause when your mind won't stop.
+Ambience: zen temple.
+Composed around a root of 432 Hz, in just intonation, hirajoshi mode.
+Breathing cycle: from 6.0 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
+Original composition, synthesized from scratch, ambience included. No third-party samples.
+Chapters:
+00:00 [fill in after editing]</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Bajar el ritmo · 30 minutos
+Para acompañar un momento de pausa cuando la cabeza no para.
+Ambiente: templo zen.
 Compuesta con raíz en 432 Hz, en entonación justa, modo hirajoshi.
-Para acompañar un momento de pausa cuando la cabeza no para.
 Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Ambiente: templo zen, sintetizado, sin grabaciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 432 Hz in just intonation, hirajoshi mode.
-To accompany a pause when your mind won't stop.
-Original composition, synthesized from scratch. No third-party samples.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Capítulos:
 00:00 [completar tras el montaje]</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>30 MIN</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>#Relajación #MúsicaRelajante #432Hz</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>#RelaxingMusic #Meditation #432Hz</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>432 hz, música 432 hz, música para momentos de ansiedad, music for anxiety, ansiedad, hirajoshi, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr"/>
-      <c r="J11" s="4" t="inlineStr"/>
-      <c r="K11" s="2" t="n">
+      <c r="K11" s="4" t="inlineStr"/>
+      <c r="L11" s="4" t="inlineStr"/>
+      <c r="M11" s="2" t="n">
         <v>432</v>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>hirajoshi</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>medio</t>
         </is>
       </c>
-      <c r="N11" s="2" t="n">
+      <c r="P11" s="2" t="n">
         <v>739461</v>
       </c>
-      <c r="O11" s="2" t="n">
+      <c r="Q11" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="P11" s="3" t="inlineStr">
+      <c r="R11" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 30 --raiz 432 --modo hirajoshi --semilla 739461 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="Q11" s="2" t="inlineStr">
+      <c r="S11" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py zen 1840 audio/OBRA-010_capa.wav --semilla 739461 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-010_432_hirajoshi.wav audio/OBRA-010_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-010_capa.wav</t>
         </is>
       </c>
-      <c r="R11" s="4" t="inlineStr">
+      <c r="T11" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="S11" s="4" t="inlineStr"/>
-      <c r="T11" s="4" t="inlineStr"/>
       <c r="U11" s="4" t="inlineStr"/>
-      <c r="V11" s="5">
-        <f>IFERROR(U11/T11*1000,"")</f>
+      <c r="V11" s="4" t="inlineStr"/>
+      <c r="W11" s="4" t="inlineStr"/>
+      <c r="X11" s="5">
+        <f>IFERROR(W11/V11*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -1594,91 +1736,104 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>Music for Anxiety · Ocean and Birds · 528 Hz · Four and Six · 20 Minutes</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
           <t>Música para momentos de ansiedad · Mar y pájaros · 528 Hz · Cuatro y seis · 20 minutos</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Ansiedad</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>mar-aves</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Four and Six · 20 Minutes
+To accompany a pause when your mind won't stop.
+Ambience: ocean and birds.
+Composed around a root of 528 Hz, in just intonation, hirajoshi mode.
+Breathing cycle: from 6.0 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
+Original composition, synthesized from scratch, ambience included. No third-party samples.
+Chapters:
+00:00 [fill in after editing]</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Cuatro y seis · 20 minutos
+Para acompañar un momento de pausa cuando la cabeza no para.
+Ambiente: mar y pájaros.
 Compuesta con raíz en 528 Hz, en entonación justa, modo hirajoshi.
-Para acompañar un momento de pausa cuando la cabeza no para.
 Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Ambiente: mar y pájaros, sintetizado, sin grabaciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 528 Hz in just intonation, hirajoshi mode.
-To accompany a pause when your mind won't stop.
-Original composition, synthesized from scratch. No third-party samples.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Capítulos:
 00:00 [completar tras el montaje]</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>20 MIN</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>#Relajación #MúsicaRelajante #528Hz</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>#RelaxingMusic #Meditation #528Hz</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>528 hz, música 528 hz, música para momentos de ansiedad, music for anxiety, ansiedad, hirajoshi, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr"/>
-      <c r="J12" s="4" t="inlineStr"/>
-      <c r="K12" s="2" t="n">
+      <c r="K12" s="4" t="inlineStr"/>
+      <c r="L12" s="4" t="inlineStr"/>
+      <c r="M12" s="2" t="n">
         <v>528</v>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>hirajoshi</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>medio</t>
         </is>
       </c>
-      <c r="N12" s="2" t="n">
+      <c r="P12" s="2" t="n">
         <v>913368</v>
       </c>
-      <c r="O12" s="2" t="n">
+      <c r="Q12" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="P12" s="3" t="inlineStr">
+      <c r="R12" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 20 --raiz 528 --modo hirajoshi --semilla 913368 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="Q12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py aves 1240 audio/OBRA-011_capa.wav --semilla 913368 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-011_528_hirajoshi.wav audio/OBRA-011_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-011_capa.wav</t>
         </is>
       </c>
-      <c r="R12" s="4" t="inlineStr">
+      <c r="T12" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="S12" s="4" t="inlineStr"/>
-      <c r="T12" s="4" t="inlineStr"/>
       <c r="U12" s="4" t="inlineStr"/>
-      <c r="V12" s="5">
-        <f>IFERROR(U12/T12*1000,"")</f>
+      <c r="V12" s="4" t="inlineStr"/>
+      <c r="W12" s="4" t="inlineStr"/>
+      <c r="X12" s="5">
+        <f>IFERROR(W12/V12*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -1690,91 +1845,104 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
+          <t>Music for Anxiety · Zen Temple · 528 Hz · Ten Minutes · 10 Minutes</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
           <t>Música para momentos de ansiedad · Templo zen · 528 Hz · Diez minutos · 10 minutos</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Ansiedad</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>zen</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Ten Minutes · 10 Minutes
+To accompany a pause when your mind won't stop.
+Ambience: zen temple.
+Composed around a root of 528 Hz, in just intonation, shin mode.
+Breathing cycle: from 6.0 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
+Original composition, synthesized from scratch, ambience included. No third-party samples.
+Chapters:
+00:00 [fill in after editing]</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>Diez minutos · 10 minutos
+Para acompañar un momento de pausa cuando la cabeza no para.
+Ambiente: templo zen.
 Compuesta con raíz en 528 Hz, en entonación justa, modo shin.
-Para acompañar un momento de pausa cuando la cabeza no para.
 Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Ambiente: templo zen, sintetizado, sin grabaciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 528 Hz in just intonation, shin mode.
-To accompany a pause when your mind won't stop.
-Original composition, synthesized from scratch. No third-party samples.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Capítulos:
 00:00 [completar tras el montaje]</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>10 MIN</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>#Relajación #MúsicaRelajante #528Hz</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>#RelaxingMusic #Meditation #528Hz</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>528 hz, música 528 hz, música para momentos de ansiedad, music for anxiety, ansiedad, shin, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr"/>
-      <c r="J13" s="4" t="inlineStr"/>
-      <c r="K13" s="2" t="n">
+      <c r="K13" s="4" t="inlineStr"/>
+      <c r="L13" s="4" t="inlineStr"/>
+      <c r="M13" s="2" t="n">
         <v>528</v>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>shin</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>medio</t>
         </is>
       </c>
-      <c r="N13" s="2" t="n">
+      <c r="P13" s="2" t="n">
         <v>207307</v>
       </c>
-      <c r="O13" s="2" t="n">
+      <c r="Q13" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="P13" s="3" t="inlineStr">
+      <c r="R13" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 10 --raiz 528 --modo shin --semilla 207307 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py zen 640 audio/OBRA-012_capa.wav --semilla 207307 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-012_528_shin.wav audio/OBRA-012_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-012_capa.wav</t>
         </is>
       </c>
-      <c r="R13" s="4" t="inlineStr">
+      <c r="T13" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="S13" s="4" t="inlineStr"/>
-      <c r="T13" s="4" t="inlineStr"/>
       <c r="U13" s="4" t="inlineStr"/>
-      <c r="V13" s="5">
-        <f>IFERROR(U13/T13*1000,"")</f>
+      <c r="V13" s="4" t="inlineStr"/>
+      <c r="W13" s="4" t="inlineStr"/>
+      <c r="X13" s="5">
+        <f>IFERROR(W13/V13*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -1786,91 +1954,104 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
+          <t>Music for Anxiety · Ocean and Birds · 432 Hz · Count to Six · 20 Minutes</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
           <t>Música para momentos de ansiedad · Mar y pájaros · 432 Hz · Contar hasta seis · 20 minutos</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Ansiedad</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>mar-aves</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Count to Six · 20 Minutes
+To accompany a pause when your mind won't stop.
+Ambience: ocean and birds.
+Composed around a root of 432 Hz, in just intonation, hirajoshi mode.
+Breathing cycle: from 6.0 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
+Original composition, synthesized from scratch, ambience included. No third-party samples.
+Chapters:
+00:00 [fill in after editing]</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Contar hasta seis · 20 minutos
+Para acompañar un momento de pausa cuando la cabeza no para.
+Ambiente: mar y pájaros.
 Compuesta con raíz en 432 Hz, en entonación justa, modo hirajoshi.
-Para acompañar un momento de pausa cuando la cabeza no para.
 Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Ambiente: mar y pájaros, sintetizado, sin grabaciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 432 Hz in just intonation, hirajoshi mode.
-To accompany a pause when your mind won't stop.
-Original composition, synthesized from scratch. No third-party samples.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Capítulos:
 00:00 [completar tras el montaje]</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>20 MIN</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>#Relajación #MúsicaRelajante #432Hz</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>#RelaxingMusic #Meditation #432Hz</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>432 hz, música 432 hz, música para momentos de ansiedad, music for anxiety, ansiedad, hirajoshi, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr"/>
-      <c r="J14" s="4" t="inlineStr"/>
-      <c r="K14" s="2" t="n">
+      <c r="K14" s="4" t="inlineStr"/>
+      <c r="L14" s="4" t="inlineStr"/>
+      <c r="M14" s="2" t="n">
         <v>432</v>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>hirajoshi</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>medio</t>
         </is>
       </c>
-      <c r="N14" s="2" t="n">
+      <c r="P14" s="2" t="n">
         <v>627771</v>
       </c>
-      <c r="O14" s="2" t="n">
+      <c r="Q14" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="P14" s="3" t="inlineStr">
+      <c r="R14" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 20 --raiz 432 --modo hirajoshi --semilla 627771 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py aves 1240 audio/OBRA-013_capa.wav --semilla 627771 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-013_432_hirajoshi.wav audio/OBRA-013_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-013_capa.wav</t>
         </is>
       </c>
-      <c r="R14" s="4" t="inlineStr">
+      <c r="T14" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="S14" s="4" t="inlineStr"/>
-      <c r="T14" s="4" t="inlineStr"/>
       <c r="U14" s="4" t="inlineStr"/>
-      <c r="V14" s="5">
-        <f>IFERROR(U14/T14*1000,"")</f>
+      <c r="V14" s="4" t="inlineStr"/>
+      <c r="W14" s="4" t="inlineStr"/>
+      <c r="X14" s="5">
+        <f>IFERROR(W14/V14*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -1882,91 +2063,104 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
+          <t>Music for Anxiety · Zen Temple · 528 Hz · In and Out · 20 Minutes</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
           <t>Música para momentos de ansiedad · Templo zen · 528 Hz · Entrada y salida · 20 minutos</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Ansiedad</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>zen</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>In and Out · 20 Minutes
+To accompany a pause when your mind won't stop.
+Ambience: zen temple.
+Composed around a root of 528 Hz, in just intonation, yo mode.
+Breathing cycle: from 6.0 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
+Original composition, synthesized from scratch, ambience included. No third-party samples.
+Chapters:
+00:00 [fill in after editing]</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>Entrada y salida · 20 minutos
+Para acompañar un momento de pausa cuando la cabeza no para.
+Ambiente: templo zen.
 Compuesta con raíz en 528 Hz, en entonación justa, modo yo.
-Para acompañar un momento de pausa cuando la cabeza no para.
 Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Ambiente: templo zen, sintetizado, sin grabaciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 528 Hz in just intonation, yo mode.
-To accompany a pause when your mind won't stop.
-Original composition, synthesized from scratch. No third-party samples.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Capítulos:
 00:00 [completar tras el montaje]</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>20 MIN</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>#Relajación #MúsicaRelajante #528Hz</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>#RelaxingMusic #Meditation #528Hz</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>528 hz, música 528 hz, música para momentos de ansiedad, music for anxiety, ansiedad, yo, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr"/>
-      <c r="J15" s="4" t="inlineStr"/>
-      <c r="K15" s="2" t="n">
+      <c r="K15" s="4" t="inlineStr"/>
+      <c r="L15" s="4" t="inlineStr"/>
+      <c r="M15" s="2" t="n">
         <v>528</v>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>yo</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>medio</t>
         </is>
       </c>
-      <c r="N15" s="2" t="n">
+      <c r="P15" s="2" t="n">
         <v>310137</v>
       </c>
-      <c r="O15" s="2" t="n">
+      <c r="Q15" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="P15" s="3" t="inlineStr">
+      <c r="R15" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 20 --raiz 528 --modo yo --semilla 310137 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="Q15" s="2" t="inlineStr">
+      <c r="S15" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py zen 1240 audio/OBRA-014_capa.wav --semilla 310137 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-014_528_yo.wav audio/OBRA-014_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-014_capa.wav</t>
         </is>
       </c>
-      <c r="R15" s="4" t="inlineStr">
+      <c r="T15" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="S15" s="4" t="inlineStr"/>
-      <c r="T15" s="4" t="inlineStr"/>
       <c r="U15" s="4" t="inlineStr"/>
-      <c r="V15" s="5">
-        <f>IFERROR(U15/T15*1000,"")</f>
+      <c r="V15" s="4" t="inlineStr"/>
+      <c r="W15" s="4" t="inlineStr"/>
+      <c r="X15" s="5">
+        <f>IFERROR(W15/V15*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -1978,91 +2172,104 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
+          <t>Music for Anxiety · Ocean and Birds · 639 Hz · Before You Begin · 15 Minutes</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
           <t>Música para momentos de ansiedad · Mar y pájaros · 639 Hz · Antes de empezar · 15 minutos</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Ansiedad</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>mar-aves</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Before You Begin · 15 Minutes
+To accompany a pause when your mind won't stop.
+Ambience: ocean and birds.
+Composed around a root of 639 Hz, in just intonation, yo mode.
+Breathing cycle: from 6.0 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
+Original composition, synthesized from scratch, ambience included. No third-party samples.
+Chapters:
+00:00 [fill in after editing]</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Antes de empezar · 15 minutos
+Para acompañar un momento de pausa cuando la cabeza no para.
+Ambiente: mar y pájaros.
 Compuesta con raíz en 639 Hz, en entonación justa, modo yo.
-Para acompañar un momento de pausa cuando la cabeza no para.
 Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Ambiente: mar y pájaros, sintetizado, sin grabaciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 639 Hz in just intonation, yo mode.
-To accompany a pause when your mind won't stop.
-Original composition, synthesized from scratch. No third-party samples.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Capítulos:
 00:00 [completar tras el montaje]</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>15 MIN</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>#Relajación #MúsicaRelajante #639Hz</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>#RelaxingMusic #Meditation #639Hz</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>639 hz, música 639 hz, música para momentos de ansiedad, music for anxiety, ansiedad, yo, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr"/>
-      <c r="J16" s="4" t="inlineStr"/>
-      <c r="K16" s="2" t="n">
+      <c r="K16" s="4" t="inlineStr"/>
+      <c r="L16" s="4" t="inlineStr"/>
+      <c r="M16" s="2" t="n">
         <v>639</v>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>yo</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>medio</t>
         </is>
       </c>
-      <c r="N16" s="2" t="n">
+      <c r="P16" s="2" t="n">
         <v>592463</v>
       </c>
-      <c r="O16" s="2" t="n">
+      <c r="Q16" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="P16" s="3" t="inlineStr">
+      <c r="R16" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 15 --raiz 639 --modo yo --semilla 592463 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py aves 940 audio/OBRA-015_capa.wav --semilla 592463 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-015_639_yo.wav audio/OBRA-015_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-015_capa.wav</t>
         </is>
       </c>
-      <c r="R16" s="4" t="inlineStr">
+      <c r="T16" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="S16" s="4" t="inlineStr"/>
-      <c r="T16" s="4" t="inlineStr"/>
       <c r="U16" s="4" t="inlineStr"/>
-      <c r="V16" s="5">
-        <f>IFERROR(U16/T16*1000,"")</f>
+      <c r="V16" s="4" t="inlineStr"/>
+      <c r="W16" s="4" t="inlineStr"/>
+      <c r="X16" s="5">
+        <f>IFERROR(W16/V16*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -2074,91 +2281,104 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
+          <t>Music for Anxiety · Rain on Leaves · 417 Hz · End of the Day · 30 Minutes</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
           <t>Música para momentos de ansiedad · Lluvia sobre hojas · 417 Hz · El final del día · 30 minutos</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Ansiedad</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>lluvia-tambor</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>End of the Day · 30 Minutes
+To accompany a pause when your mind won't stop.
+Ambience: rain on leaves.
+Composed around a root of 417 Hz, in just intonation, kumoi mode.
+Breathing cycle: from 6.0 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
+Original composition, synthesized from scratch, ambience included. No third-party samples.
+Chapters:
+00:00 [fill in after editing]</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>El final del día · 30 minutos
+Para acompañar un momento de pausa cuando la cabeza no para.
+Ambiente: lluvia sobre hojas.
 Compuesta con raíz en 417 Hz, en entonación justa, modo kumoi.
-Para acompañar un momento de pausa cuando la cabeza no para.
 Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Ambiente: lluvia sobre hojas, sintetizado, sin grabaciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 417 Hz in just intonation, kumoi mode.
-To accompany a pause when your mind won't stop.
-Original composition, synthesized from scratch. No third-party samples.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Capítulos:
 00:00 [completar tras el montaje]</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>30 MIN</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>#Relajación #MúsicaRelajante #417Hz</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>#RelaxingMusic #Meditation #417Hz</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>417 hz, música 417 hz, música para momentos de ansiedad, music for anxiety, ansiedad, kumoi, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr"/>
-      <c r="J17" s="4" t="inlineStr"/>
-      <c r="K17" s="2" t="n">
+      <c r="K17" s="4" t="inlineStr"/>
+      <c r="L17" s="4" t="inlineStr"/>
+      <c r="M17" s="2" t="n">
         <v>417</v>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>kumoi</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>medio</t>
         </is>
       </c>
-      <c r="N17" s="2" t="n">
+      <c r="P17" s="2" t="n">
         <v>250697</v>
       </c>
-      <c r="O17" s="2" t="n">
+      <c r="Q17" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="P17" s="3" t="inlineStr">
+      <c r="R17" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 30 --raiz 417 --modo kumoi --semilla 250697 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="Q17" s="2" t="inlineStr">
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py ancestral 1840 audio/OBRA-016_capa.wav --semilla 250697 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-016_417_kumoi.wav audio/OBRA-016_final.wav --fondo fuego --nivel-capa 0 --nivel-obra -20 --capa audio/OBRA-016_capa.wav</t>
         </is>
       </c>
-      <c r="R17" s="4" t="inlineStr">
+      <c r="T17" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="S17" s="4" t="inlineStr"/>
-      <c r="T17" s="4" t="inlineStr"/>
       <c r="U17" s="4" t="inlineStr"/>
-      <c r="V17" s="5">
-        <f>IFERROR(U17/T17*1000,"")</f>
+      <c r="V17" s="4" t="inlineStr"/>
+      <c r="W17" s="4" t="inlineStr"/>
+      <c r="X17" s="5">
+        <f>IFERROR(W17/V17*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -2170,91 +2390,104 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
+          <t>Meditation Music · Zen Temple · 417 Hz · Empty Temple · 45 Minutes</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
           <t>Música para meditar · Templo zen · 417 Hz · Templo vacío · 45 minutos</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Meditar</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>zen</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Empty Temple · 45 Minutes
+To accompany a meditation practice.
+Ambience: zen temple.
+Composed around a root of 417 Hz, in just intonation, hirajoshi mode.
+Breathing cycle: from 5.5 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
+Original composition, synthesized from scratch, ambience included. No third-party samples.
+Chapters:
+00:00 [fill in after editing]</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Templo vacío · 45 minutos
+Para acompañar una práctica de meditación.
+Ambiente: templo zen.
 Compuesta con raíz en 417 Hz, en entonación justa, modo hirajoshi.
-Para acompañar una práctica de meditación.
 Ciclo respiratorio: de 5.5 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Ambiente: templo zen, sintetizado, sin grabaciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 417 Hz in just intonation, hirajoshi mode.
-To accompany a meditation practice.
-Original composition, synthesized from scratch. No third-party samples.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Capítulos:
 00:00 [completar tras el montaje]</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>45 MIN</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>#Meditación #MúsicaRelajante #417Hz</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>#MeditationMusic #Meditation #417Hz</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>417 hz, música 417 hz, música para meditar, meditation music, meditar, hirajoshi, música relajante, meditación, relajación, entonación justa, composición original, relaxing music, sleep music, singing bowls, just intonation</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr"/>
-      <c r="J18" s="4" t="inlineStr"/>
-      <c r="K18" s="2" t="n">
+      <c r="K18" s="4" t="inlineStr"/>
+      <c r="L18" s="4" t="inlineStr"/>
+      <c r="M18" s="2" t="n">
         <v>417</v>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>hirajoshi</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>medio</t>
         </is>
       </c>
-      <c r="N18" s="2" t="n">
+      <c r="P18" s="2" t="n">
         <v>714152</v>
       </c>
-      <c r="O18" s="2" t="n">
+      <c r="Q18" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="P18" s="3" t="inlineStr">
+      <c r="R18" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 45 --raiz 417 --modo hirajoshi --semilla 714152 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="Q18" s="2" t="inlineStr">
+      <c r="S18" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py zen 2740 audio/OBRA-017_capa.wav --semilla 714152 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-017_417_hirajoshi.wav audio/OBRA-017_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-017_capa.wav</t>
         </is>
       </c>
-      <c r="R18" s="4" t="inlineStr">
+      <c r="T18" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="S18" s="4" t="inlineStr"/>
-      <c r="T18" s="4" t="inlineStr"/>
       <c r="U18" s="4" t="inlineStr"/>
-      <c r="V18" s="5">
-        <f>IFERROR(U18/T18*1000,"")</f>
+      <c r="V18" s="4" t="inlineStr"/>
+      <c r="W18" s="4" t="inlineStr"/>
+      <c r="X18" s="5">
+        <f>IFERROR(W18/V18*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -2266,91 +2499,104 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
+          <t>Meditation Music · Zen Temple · 528 Hz · Seven Bells · 45 Minutes</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
           <t>Música para meditar · Templo zen · 528 Hz · Siete campanas · 45 minutos</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Meditar</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>zen</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Seven Bells · 45 Minutes
+To accompany a meditation practice.
+Ambience: zen temple.
+Composed around a root of 528 Hz, in just intonation, hirajoshi mode.
+Breathing cycle: from 5.5 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
+Original composition, synthesized from scratch, ambience included. No third-party samples.
+Chapters:
+00:00 [fill in after editing]</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>Siete campanas · 45 minutos
+Para acompañar una práctica de meditación.
+Ambiente: templo zen.
 Compuesta con raíz en 528 Hz, en entonación justa, modo hirajoshi.
-Para acompañar una práctica de meditación.
 Ciclo respiratorio: de 5.5 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Ambiente: templo zen, sintetizado, sin grabaciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 528 Hz in just intonation, hirajoshi mode.
-To accompany a meditation practice.
-Original composition, synthesized from scratch. No third-party samples.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Capítulos:
 00:00 [completar tras el montaje]</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>45 MIN</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>#Meditación #MúsicaRelajante #528Hz</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>#MeditationMusic #Meditation #528Hz</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>528 hz, música 528 hz, música para meditar, meditation music, meditar, hirajoshi, música relajante, meditación, relajación, entonación justa, composición original, relaxing music, sleep music, singing bowls, just intonation</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr"/>
-      <c r="J19" s="4" t="inlineStr"/>
-      <c r="K19" s="2" t="n">
+      <c r="K19" s="4" t="inlineStr"/>
+      <c r="L19" s="4" t="inlineStr"/>
+      <c r="M19" s="2" t="n">
         <v>528</v>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>hirajoshi</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>medio</t>
         </is>
       </c>
-      <c r="N19" s="2" t="n">
+      <c r="P19" s="2" t="n">
         <v>735455</v>
       </c>
-      <c r="O19" s="2" t="n">
+      <c r="Q19" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="P19" s="3" t="inlineStr">
+      <c r="R19" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 45 --raiz 528 --modo hirajoshi --semilla 735455 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="Q19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py zen 2740 audio/OBRA-018_capa.wav --semilla 735455 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-018_528_hirajoshi.wav audio/OBRA-018_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-018_capa.wav</t>
         </is>
       </c>
-      <c r="R19" s="4" t="inlineStr">
+      <c r="T19" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="S19" s="4" t="inlineStr"/>
-      <c r="T19" s="4" t="inlineStr"/>
       <c r="U19" s="4" t="inlineStr"/>
-      <c r="V19" s="5">
-        <f>IFERROR(U19/T19*1000,"")</f>
+      <c r="V19" s="4" t="inlineStr"/>
+      <c r="W19" s="4" t="inlineStr"/>
+      <c r="X19" s="5">
+        <f>IFERROR(W19/V19*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -2362,91 +2608,104 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
+          <t>Meditation Music · Zen Temple · 432 Hz · Metal and Air · 1 Hour</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
           <t>Música para meditar · Templo zen · 432 Hz · Metal y aire · 1 hora</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Meditar</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>zen</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Metal and Air · 1 Hour
+To accompany a meditation practice.
+Ambience: zen temple.
+Composed around a root of 432 Hz, in just intonation, shin mode.
+Breathing cycle: from 5.5 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
+Original composition, synthesized from scratch, ambience included. No third-party samples.
+Chapters:
+00:00 [fill in after editing]</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>Metal y aire · 1 hora
+Para acompañar una práctica de meditación.
+Ambiente: templo zen.
 Compuesta con raíz en 432 Hz, en entonación justa, modo shin.
-Para acompañar una práctica de meditación.
 Ciclo respiratorio: de 5.5 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Ambiente: templo zen, sintetizado, sin grabaciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 432 Hz in just intonation, shin mode.
-To accompany a meditation practice.
-Original composition, synthesized from scratch. No third-party samples.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Capítulos:
 00:00 [completar tras el montaje]</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>60 MIN</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>#Meditación #MúsicaRelajante #432Hz</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>#MeditationMusic #Meditation #432Hz</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>432 hz, música 432 hz, música para meditar, meditation music, meditar, shin, música relajante, meditación, relajación, entonación justa, composición original, relaxing music, sleep music, singing bowls, just intonation</t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr"/>
-      <c r="J20" s="4" t="inlineStr"/>
-      <c r="K20" s="2" t="n">
+      <c r="K20" s="4" t="inlineStr"/>
+      <c r="L20" s="4" t="inlineStr"/>
+      <c r="M20" s="2" t="n">
         <v>432</v>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>shin</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>medio</t>
         </is>
       </c>
-      <c r="N20" s="2" t="n">
+      <c r="P20" s="2" t="n">
         <v>627577</v>
       </c>
-      <c r="O20" s="2" t="n">
+      <c r="Q20" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="P20" s="3" t="inlineStr">
+      <c r="R20" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 60 --raiz 432 --modo shin --semilla 627577 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="Q20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py zen 3640 audio/OBRA-019_capa.wav --semilla 627577 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-019_432_shin.wav audio/OBRA-019_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-019_capa.wav</t>
         </is>
       </c>
-      <c r="R20" s="4" t="inlineStr">
+      <c r="T20" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="S20" s="4" t="inlineStr"/>
-      <c r="T20" s="4" t="inlineStr"/>
       <c r="U20" s="4" t="inlineStr"/>
-      <c r="V20" s="5">
-        <f>IFERROR(U20/T20*1000,"")</f>
+      <c r="V20" s="4" t="inlineStr"/>
+      <c r="W20" s="4" t="inlineStr"/>
+      <c r="X20" s="5">
+        <f>IFERROR(W20/V20*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -2458,91 +2717,104 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
+          <t>Meditation Music · Rain on Leaves · 528 Hz · Strike and Silence · 30 Minutes</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
           <t>Música para meditar · Lluvia sobre hojas · 528 Hz · Golpe y silencio · 30 minutos</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Meditar</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>lluvia-tambor</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Strike and Silence · 30 Minutes
+To accompany a meditation practice.
+Ambience: rain on leaves.
+Composed around a root of 528 Hz, in just intonation, shin mode.
+Breathing cycle: from 5.5 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
+Original composition, synthesized from scratch, ambience included. No third-party samples.
+Chapters:
+00:00 [fill in after editing]</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>Golpe y silencio · 30 minutos
+Para acompañar una práctica de meditación.
+Ambiente: lluvia sobre hojas.
 Compuesta con raíz en 528 Hz, en entonación justa, modo shin.
-Para acompañar una práctica de meditación.
 Ciclo respiratorio: de 5.5 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Ambiente: lluvia sobre hojas, sintetizado, sin grabaciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 528 Hz in just intonation, shin mode.
-To accompany a meditation practice.
-Original composition, synthesized from scratch. No third-party samples.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Capítulos:
 00:00 [completar tras el montaje]</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>30 MIN</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>#Meditación #MúsicaRelajante #528Hz</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>#MeditationMusic #Meditation #528Hz</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>528 hz, música 528 hz, música para meditar, meditation music, meditar, shin, música relajante, meditación, relajación, entonación justa, composición original, relaxing music, sleep music, singing bowls, just intonation</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr"/>
-      <c r="J21" s="4" t="inlineStr"/>
-      <c r="K21" s="2" t="n">
+      <c r="K21" s="4" t="inlineStr"/>
+      <c r="L21" s="4" t="inlineStr"/>
+      <c r="M21" s="2" t="n">
         <v>528</v>
       </c>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>shin</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>medio</t>
         </is>
       </c>
-      <c r="N21" s="2" t="n">
+      <c r="P21" s="2" t="n">
         <v>632595</v>
       </c>
-      <c r="O21" s="2" t="n">
+      <c r="Q21" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="P21" s="3" t="inlineStr">
+      <c r="R21" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 30 --raiz 528 --modo shin --semilla 632595 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="Q21" s="2" t="inlineStr">
+      <c r="S21" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py ancestral 1840 audio/OBRA-020_capa.wav --semilla 632595 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-020_528_shin.wav audio/OBRA-020_final.wav --fondo fuego --nivel-capa 0 --nivel-obra -20 --capa audio/OBRA-020_capa.wav</t>
         </is>
       </c>
-      <c r="R21" s="4" t="inlineStr">
+      <c r="T21" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="S21" s="4" t="inlineStr"/>
-      <c r="T21" s="4" t="inlineStr"/>
       <c r="U21" s="4" t="inlineStr"/>
-      <c r="V21" s="5">
-        <f>IFERROR(U21/T21*1000,"")</f>
+      <c r="V21" s="4" t="inlineStr"/>
+      <c r="W21" s="4" t="inlineStr"/>
+      <c r="X21" s="5">
+        <f>IFERROR(W21/V21*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -2554,91 +2826,104 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
+          <t>Meditation Music · Zen Temple · 396 Hz · Bronze and Wood · 45 Minutes</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
           <t>Música para meditar · Templo zen · 396 Hz · Bronce y madera · 45 minutos</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Meditar</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>zen</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Bronze and Wood · 45 Minutes
+To accompany a meditation practice.
+Ambience: zen temple.
+Composed around a root of 396 Hz, in just intonation, kumoi mode.
+Breathing cycle: from 5.5 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
+Original composition, synthesized from scratch, ambience included. No third-party samples.
+Chapters:
+00:00 [fill in after editing]</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>Bronce y madera · 45 minutos
+Para acompañar una práctica de meditación.
+Ambiente: templo zen.
 Compuesta con raíz en 396 Hz, en entonación justa, modo kumoi.
-Para acompañar una práctica de meditación.
 Ciclo respiratorio: de 5.5 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Ambiente: templo zen, sintetizado, sin grabaciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 396 Hz in just intonation, kumoi mode.
-To accompany a meditation practice.
-Original composition, synthesized from scratch. No third-party samples.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Capítulos:
 00:00 [completar tras el montaje]</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>45 MIN</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>#Meditación #MúsicaRelajante #396Hz</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>#MeditationMusic #Meditation #396Hz</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>396 hz, música 396 hz, música para meditar, meditation music, meditar, kumoi, música relajante, meditación, relajación, entonación justa, composición original, relaxing music, sleep music, singing bowls, just intonation</t>
         </is>
       </c>
-      <c r="I22" s="4" t="inlineStr"/>
-      <c r="J22" s="4" t="inlineStr"/>
-      <c r="K22" s="2" t="n">
+      <c r="K22" s="4" t="inlineStr"/>
+      <c r="L22" s="4" t="inlineStr"/>
+      <c r="M22" s="2" t="n">
         <v>396</v>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>kumoi</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>medio</t>
         </is>
       </c>
-      <c r="N22" s="2" t="n">
+      <c r="P22" s="2" t="n">
         <v>864630</v>
       </c>
-      <c r="O22" s="2" t="n">
+      <c r="Q22" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="P22" s="3" t="inlineStr">
+      <c r="R22" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 45 --raiz 396 --modo kumoi --semilla 864630 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="Q22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py zen 2740 audio/OBRA-021_capa.wav --semilla 864630 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-021_396_kumoi.wav audio/OBRA-021_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-021_capa.wav</t>
         </is>
       </c>
-      <c r="R22" s="4" t="inlineStr">
+      <c r="T22" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="S22" s="4" t="inlineStr"/>
-      <c r="T22" s="4" t="inlineStr"/>
       <c r="U22" s="4" t="inlineStr"/>
-      <c r="V22" s="5">
-        <f>IFERROR(U22/T22*1000,"")</f>
+      <c r="V22" s="4" t="inlineStr"/>
+      <c r="W22" s="4" t="inlineStr"/>
+      <c r="X22" s="5">
+        <f>IFERROR(W22/V22*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -2650,91 +2935,104 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
+          <t>Meditation Music · Zen Temple · 639 Hz · Long Resonance · 1 Hour</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
           <t>Música para meditar · Templo zen · 639 Hz · Resonancia larga · 1 hora</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Meditar</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>zen</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Long Resonance · 1 Hour
+To accompany a meditation practice.
+Ambience: zen temple.
+Composed around a root of 639 Hz, in just intonation, yo mode.
+Breathing cycle: from 5.5 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
+Original composition, synthesized from scratch, ambience included. No third-party samples.
+Chapters:
+00:00 [fill in after editing]</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>Resonancia larga · 1 hora
+Para acompañar una práctica de meditación.
+Ambiente: templo zen.
 Compuesta con raíz en 639 Hz, en entonación justa, modo yo.
-Para acompañar una práctica de meditación.
 Ciclo respiratorio: de 5.5 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Ambiente: templo zen, sintetizado, sin grabaciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 639 Hz in just intonation, yo mode.
-To accompany a meditation practice.
-Original composition, synthesized from scratch. No third-party samples.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Capítulos:
 00:00 [completar tras el montaje]</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>60 MIN</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>#Meditación #MúsicaRelajante #639Hz</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>#MeditationMusic #Meditation #639Hz</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
         <is>
           <t>639 hz, música 639 hz, música para meditar, meditation music, meditar, yo, música relajante, meditación, relajación, entonación justa, composición original, relaxing music, sleep music, singing bowls, just intonation</t>
         </is>
       </c>
-      <c r="I23" s="4" t="inlineStr"/>
-      <c r="J23" s="4" t="inlineStr"/>
-      <c r="K23" s="2" t="n">
+      <c r="K23" s="4" t="inlineStr"/>
+      <c r="L23" s="4" t="inlineStr"/>
+      <c r="M23" s="2" t="n">
         <v>639</v>
       </c>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>yo</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>medio</t>
         </is>
       </c>
-      <c r="N23" s="2" t="n">
+      <c r="P23" s="2" t="n">
         <v>335798</v>
       </c>
-      <c r="O23" s="2" t="n">
+      <c r="Q23" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="P23" s="3" t="inlineStr">
+      <c r="R23" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 60 --raiz 639 --modo yo --semilla 335798 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="Q23" s="2" t="inlineStr">
+      <c r="S23" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py zen 3640 audio/OBRA-022_capa.wav --semilla 335798 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-022_639_yo.wav audio/OBRA-022_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-022_capa.wav</t>
         </is>
       </c>
-      <c r="R23" s="4" t="inlineStr">
+      <c r="T23" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="S23" s="4" t="inlineStr"/>
-      <c r="T23" s="4" t="inlineStr"/>
       <c r="U23" s="4" t="inlineStr"/>
-      <c r="V23" s="5">
-        <f>IFERROR(U23/T23*1000,"")</f>
+      <c r="V23" s="4" t="inlineStr"/>
+      <c r="W23" s="4" t="inlineStr"/>
+      <c r="X23" s="5">
+        <f>IFERROR(W23/V23*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -2746,91 +3044,104 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
+          <t>Meditation Music · Zen Temple · 528 Hz · Just One · 20 Minutes</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
           <t>Música para meditar · Templo zen · 528 Hz · Uno solo · 20 minutos</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Meditar</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>zen</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Just One · 20 Minutes
+To accompany a meditation practice.
+Ambience: zen temple.
+Composed around a root of 528 Hz, in just intonation, shin mode.
+Breathing cycle: from 5.5 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
+Original composition, synthesized from scratch, ambience included. No third-party samples.
+Chapters:
+00:00 [fill in after editing]</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>Uno solo · 20 minutos
+Para acompañar una práctica de meditación.
+Ambiente: templo zen.
 Compuesta con raíz en 528 Hz, en entonación justa, modo shin.
-Para acompañar una práctica de meditación.
 Ciclo respiratorio: de 5.5 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Ambiente: templo zen, sintetizado, sin grabaciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 528 Hz in just intonation, shin mode.
-To accompany a meditation practice.
-Original composition, synthesized from scratch. No third-party samples.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Capítulos:
 00:00 [completar tras el montaje]</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>20 MIN</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>#Meditación #MúsicaRelajante #528Hz</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>#MeditationMusic #Meditation #528Hz</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
         <is>
           <t>528 hz, música 528 hz, música para meditar, meditation music, meditar, shin, música relajante, meditación, relajación, entonación justa, composición original, relaxing music, sleep music, singing bowls, just intonation</t>
         </is>
       </c>
-      <c r="I24" s="4" t="inlineStr"/>
-      <c r="J24" s="4" t="inlineStr"/>
-      <c r="K24" s="2" t="n">
+      <c r="K24" s="4" t="inlineStr"/>
+      <c r="L24" s="4" t="inlineStr"/>
+      <c r="M24" s="2" t="n">
         <v>528</v>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>shin</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>medio</t>
         </is>
       </c>
-      <c r="N24" s="2" t="n">
+      <c r="P24" s="2" t="n">
         <v>299306</v>
       </c>
-      <c r="O24" s="2" t="n">
+      <c r="Q24" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="P24" s="3" t="inlineStr">
+      <c r="R24" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 20 --raiz 528 --modo shin --semilla 299306 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="Q24" s="2" t="inlineStr">
+      <c r="S24" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py zen 1240 audio/OBRA-023_capa.wav --semilla 299306 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-023_528_shin.wav audio/OBRA-023_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-023_capa.wav</t>
         </is>
       </c>
-      <c r="R24" s="4" t="inlineStr">
+      <c r="T24" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="S24" s="4" t="inlineStr"/>
-      <c r="T24" s="4" t="inlineStr"/>
       <c r="U24" s="4" t="inlineStr"/>
-      <c r="V24" s="5">
-        <f>IFERROR(U24/T24*1000,"")</f>
+      <c r="V24" s="4" t="inlineStr"/>
+      <c r="W24" s="4" t="inlineStr"/>
+      <c r="X24" s="5">
+        <f>IFERROR(W24/V24*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -2842,91 +3153,104 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
+          <t>Meditation Music · Rain on Leaves · 432 Hz · What Remains of Sound · 1 Hour</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
           <t>Música para meditar · Lluvia sobre hojas · 432 Hz · Lo que queda del sonido · 1 hora</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Meditar</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>lluvia-tambor</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>What Remains of Sound · 1 Hour
+To accompany a meditation practice.
+Ambience: rain on leaves.
+Composed around a root of 432 Hz, in just intonation, kumoi mode.
+Breathing cycle: from 5.5 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
+Original composition, synthesized from scratch, ambience included. No third-party samples.
+Chapters:
+00:00 [fill in after editing]</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>Lo que queda del sonido · 1 hora
+Para acompañar una práctica de meditación.
+Ambiente: lluvia sobre hojas.
 Compuesta con raíz en 432 Hz, en entonación justa, modo kumoi.
-Para acompañar una práctica de meditación.
 Ciclo respiratorio: de 5.5 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Ambiente: lluvia sobre hojas, sintetizado, sin grabaciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 432 Hz in just intonation, kumoi mode.
-To accompany a meditation practice.
-Original composition, synthesized from scratch. No third-party samples.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Capítulos:
 00:00 [completar tras el montaje]</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>60 MIN</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>#Meditación #MúsicaRelajante #432Hz</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>#MeditationMusic #Meditation #432Hz</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
         <is>
           <t>432 hz, música 432 hz, música para meditar, meditation music, meditar, kumoi, música relajante, meditación, relajación, entonación justa, composición original, relaxing music, sleep music, singing bowls, just intonation</t>
         </is>
       </c>
-      <c r="I25" s="4" t="inlineStr"/>
-      <c r="J25" s="4" t="inlineStr"/>
-      <c r="K25" s="2" t="n">
+      <c r="K25" s="4" t="inlineStr"/>
+      <c r="L25" s="4" t="inlineStr"/>
+      <c r="M25" s="2" t="n">
         <v>432</v>
       </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>kumoi</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>medio</t>
         </is>
       </c>
-      <c r="N25" s="2" t="n">
+      <c r="P25" s="2" t="n">
         <v>926202</v>
       </c>
-      <c r="O25" s="2" t="n">
+      <c r="Q25" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="P25" s="3" t="inlineStr">
+      <c r="R25" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 60 --raiz 432 --modo kumoi --semilla 926202 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="Q25" s="2" t="inlineStr">
+      <c r="S25" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py ancestral 3640 audio/OBRA-024_capa.wav --semilla 926202 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-024_432_kumoi.wav audio/OBRA-024_final.wav --fondo fuego --nivel-capa 0 --nivel-obra -20 --capa audio/OBRA-024_capa.wav</t>
         </is>
       </c>
-      <c r="R25" s="4" t="inlineStr">
+      <c r="T25" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="S25" s="4" t="inlineStr"/>
-      <c r="T25" s="4" t="inlineStr"/>
       <c r="U25" s="4" t="inlineStr"/>
-      <c r="V25" s="5">
-        <f>IFERROR(U25/T25*1000,"")</f>
+      <c r="V25" s="4" t="inlineStr"/>
+      <c r="W25" s="4" t="inlineStr"/>
+      <c r="X25" s="5">
+        <f>IFERROR(W25/V25*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -2938,91 +3262,104 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
+          <t>Music to Release Tension · Ocean and Birds · 528 Hz · Salt Root · 1 Hour</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
           <t>Música para soltar tensión · Mar y pájaros · 528 Hz · Raíz de sal · 1 hora</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Soltar</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>mar-aves</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Salt Root · 1 Hour
+To accompany some time to let go of the day's tension.
+Ambience: ocean and birds.
+Composed around a root of 528 Hz, in just intonation, hirajoshi mode.
+Breathing cycle: from 6.0 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
+Original composition, synthesized from scratch, ambience included. No third-party samples.
+Chapters:
+00:00 [fill in after editing]</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>Raíz de sal · 1 hora
+Para acompañar un rato de soltar la tensión del día.
+Ambiente: mar y pájaros.
 Compuesta con raíz en 528 Hz, en entonación justa, modo hirajoshi.
-Para acompañar un rato de soltar la tensión del día.
 Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Ambiente: mar y pájaros, sintetizado, sin grabaciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 528 Hz in just intonation, hirajoshi mode.
-To accompany some time to let go of the day's tension.
-Original composition, synthesized from scratch. No third-party samples.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Capítulos:
 00:00 [completar tras el montaje]</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>528 HZ</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>#MúsicaRelajante #528Hz</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>#RelaxingMusic #Meditation #528Hz</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
         <is>
           <t>528 hz, música 528 hz, música para soltar tensión, music to release tension, soltar, hirajoshi, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
         </is>
       </c>
-      <c r="I26" s="4" t="inlineStr"/>
-      <c r="J26" s="4" t="inlineStr"/>
-      <c r="K26" s="2" t="n">
+      <c r="K26" s="4" t="inlineStr"/>
+      <c r="L26" s="4" t="inlineStr"/>
+      <c r="M26" s="2" t="n">
         <v>528</v>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>hirajoshi</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>medio</t>
         </is>
       </c>
-      <c r="N26" s="2" t="n">
+      <c r="P26" s="2" t="n">
         <v>454078</v>
       </c>
-      <c r="O26" s="2" t="n">
+      <c r="Q26" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="P26" s="3" t="inlineStr">
+      <c r="R26" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 60 --raiz 528 --modo hirajoshi --semilla 454078 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="Q26" s="2" t="inlineStr">
+      <c r="S26" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py aves 3640 audio/OBRA-025_capa.wav --semilla 454078 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-025_528_hirajoshi.wav audio/OBRA-025_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-025_capa.wav</t>
         </is>
       </c>
-      <c r="R26" s="4" t="inlineStr">
+      <c r="T26" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="S26" s="4" t="inlineStr"/>
-      <c r="T26" s="4" t="inlineStr"/>
       <c r="U26" s="4" t="inlineStr"/>
-      <c r="V26" s="5">
-        <f>IFERROR(U26/T26*1000,"")</f>
+      <c r="V26" s="4" t="inlineStr"/>
+      <c r="W26" s="4" t="inlineStr"/>
+      <c r="X26" s="5">
+        <f>IFERROR(W26/V26*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -3034,91 +3371,104 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
+          <t>Music to Release Tension · Ocean Waves · 432 Hz · Still Water · 1 Hour</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
           <t>Música para soltar tensión · Olas del mar · 432 Hz · Agua quieta · 1 hora</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Soltar</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>mar</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Still Water · 1 Hour
+To accompany some time to let go of the day's tension.
+Ambience: ocean waves.
+Composed around a root of 432 Hz, in just intonation, kumoi mode.
+Breathing cycle: from 6.0 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
+Original composition, synthesized from scratch, ambience included. No third-party samples.
+Chapters:
+00:00 [fill in after editing]</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>Agua quieta · 1 hora
+Para acompañar un rato de soltar la tensión del día.
+Ambiente: olas del mar.
 Compuesta con raíz en 432 Hz, en entonación justa, modo kumoi.
-Para acompañar un rato de soltar la tensión del día.
 Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Ambiente: olas del mar, sintetizado, sin grabaciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 432 Hz in just intonation, kumoi mode.
-To accompany some time to let go of the day's tension.
-Original composition, synthesized from scratch. No third-party samples.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Capítulos:
 00:00 [completar tras el montaje]</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>432 HZ</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>#MúsicaRelajante #432Hz</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>#RelaxingMusic #Meditation #432Hz</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
         <is>
           <t>432 hz, música 432 hz, música para soltar tensión, music to release tension, soltar, kumoi, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
         </is>
       </c>
-      <c r="I27" s="4" t="inlineStr"/>
-      <c r="J27" s="4" t="inlineStr"/>
-      <c r="K27" s="2" t="n">
+      <c r="K27" s="4" t="inlineStr"/>
+      <c r="L27" s="4" t="inlineStr"/>
+      <c r="M27" s="2" t="n">
         <v>432</v>
       </c>
-      <c r="L27" s="2" t="inlineStr">
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t>kumoi</t>
         </is>
       </c>
-      <c r="M27" s="2" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>medio</t>
         </is>
       </c>
-      <c r="N27" s="2" t="n">
+      <c r="P27" s="2" t="n">
         <v>146597</v>
       </c>
-      <c r="O27" s="2" t="n">
+      <c r="Q27" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="P27" s="3" t="inlineStr">
+      <c r="R27" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 60 --raiz 432 --modo kumoi --semilla 146597 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="Q27" s="2" t="inlineStr">
+      <c r="S27" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/ambiente.py audio/OBRA-026_432_kumoi.wav audio/OBRA-026_final.wav --fondo mar</t>
         </is>
       </c>
-      <c r="R27" s="4" t="inlineStr">
+      <c r="T27" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="S27" s="4" t="inlineStr"/>
-      <c r="T27" s="4" t="inlineStr"/>
       <c r="U27" s="4" t="inlineStr"/>
-      <c r="V27" s="5">
-        <f>IFERROR(U27/T27*1000,"")</f>
+      <c r="V27" s="4" t="inlineStr"/>
+      <c r="W27" s="4" t="inlineStr"/>
+      <c r="X27" s="5">
+        <f>IFERROR(W27/V27*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -3130,91 +3480,104 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
+          <t>Music to Release Tension · Rain on Leaves · 396 Hz · Warm Ash · 1 Hour</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
           <t>Música para soltar tensión · Lluvia sobre hojas · 396 Hz · Ceniza tibia · 1 hora</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Soltar</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>lluvia-tambor</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Warm Ash · 1 Hour
+To accompany some time to let go of the day's tension.
+Ambience: rain on leaves.
+Composed around a root of 396 Hz, in just intonation, kumoi mode.
+Breathing cycle: from 6.0 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
+Original composition, synthesized from scratch, ambience included. No third-party samples.
+Chapters:
+00:00 [fill in after editing]</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>Ceniza tibia · 1 hora
+Para acompañar un rato de soltar la tensión del día.
+Ambiente: lluvia sobre hojas.
 Compuesta con raíz en 396 Hz, en entonación justa, modo kumoi.
-Para acompañar un rato de soltar la tensión del día.
 Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Ambiente: lluvia sobre hojas, sintetizado, sin grabaciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 396 Hz in just intonation, kumoi mode.
-To accompany some time to let go of the day's tension.
-Original composition, synthesized from scratch. No third-party samples.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Capítulos:
 00:00 [completar tras el montaje]</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>396 HZ</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>#MúsicaRelajante #396Hz</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>#RelaxingMusic #Meditation #396Hz</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
         <is>
           <t>396 hz, música 396 hz, música para soltar tensión, music to release tension, soltar, kumoi, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
         </is>
       </c>
-      <c r="I28" s="4" t="inlineStr"/>
-      <c r="J28" s="4" t="inlineStr"/>
-      <c r="K28" s="2" t="n">
+      <c r="K28" s="4" t="inlineStr"/>
+      <c r="L28" s="4" t="inlineStr"/>
+      <c r="M28" s="2" t="n">
         <v>396</v>
       </c>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>kumoi</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>medio</t>
         </is>
       </c>
-      <c r="N28" s="2" t="n">
+      <c r="P28" s="2" t="n">
         <v>338018</v>
       </c>
-      <c r="O28" s="2" t="n">
+      <c r="Q28" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="P28" s="3" t="inlineStr">
+      <c r="R28" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 60 --raiz 396 --modo kumoi --semilla 338018 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="Q28" s="2" t="inlineStr">
+      <c r="S28" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py ancestral 3640 audio/OBRA-027_capa.wav --semilla 338018 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-027_396_kumoi.wav audio/OBRA-027_final.wav --fondo fuego --nivel-capa 0 --nivel-obra -20 --capa audio/OBRA-027_capa.wav</t>
         </is>
       </c>
-      <c r="R28" s="4" t="inlineStr">
+      <c r="T28" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="S28" s="4" t="inlineStr"/>
-      <c r="T28" s="4" t="inlineStr"/>
       <c r="U28" s="4" t="inlineStr"/>
-      <c r="V28" s="5">
-        <f>IFERROR(U28/T28*1000,"")</f>
+      <c r="V28" s="4" t="inlineStr"/>
+      <c r="W28" s="4" t="inlineStr"/>
+      <c r="X28" s="5">
+        <f>IFERROR(W28/V28*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -3226,91 +3589,104 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
+          <t>Music to Release Tension · Zen Temple · 417 Hz · Low Door · 45 Minutes</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
           <t>Música para soltar tensión · Templo zen · 417 Hz · Puerta baja · 45 minutos</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Soltar</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>zen</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Low Door · 45 Minutes
+To accompany some time to let go of the day's tension.
+Ambience: zen temple.
+Composed around a root of 417 Hz, in just intonation, hirajoshi mode.
+Breathing cycle: from 6.0 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
+Original composition, synthesized from scratch, ambience included. No third-party samples.
+Chapters:
+00:00 [fill in after editing]</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>Puerta baja · 45 minutos
+Para acompañar un rato de soltar la tensión del día.
+Ambiente: templo zen.
 Compuesta con raíz en 417 Hz, en entonación justa, modo hirajoshi.
-Para acompañar un rato de soltar la tensión del día.
 Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Ambiente: templo zen, sintetizado, sin grabaciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 417 Hz in just intonation, hirajoshi mode.
-To accompany some time to let go of the day's tension.
-Original composition, synthesized from scratch. No third-party samples.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Capítulos:
 00:00 [completar tras el montaje]</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>417 HZ</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>#MúsicaRelajante #417Hz</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>#RelaxingMusic #Meditation #417Hz</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
         <is>
           <t>417 hz, música 417 hz, música para soltar tensión, music to release tension, soltar, hirajoshi, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
         </is>
       </c>
-      <c r="I29" s="4" t="inlineStr"/>
-      <c r="J29" s="4" t="inlineStr"/>
-      <c r="K29" s="2" t="n">
+      <c r="K29" s="4" t="inlineStr"/>
+      <c r="L29" s="4" t="inlineStr"/>
+      <c r="M29" s="2" t="n">
         <v>417</v>
       </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>hirajoshi</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>medio</t>
         </is>
       </c>
-      <c r="N29" s="2" t="n">
+      <c r="P29" s="2" t="n">
         <v>409966</v>
       </c>
-      <c r="O29" s="2" t="n">
+      <c r="Q29" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="P29" s="3" t="inlineStr">
+      <c r="R29" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 45 --raiz 417 --modo hirajoshi --semilla 409966 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="Q29" s="2" t="inlineStr">
+      <c r="S29" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py zen 2740 audio/OBRA-028_capa.wav --semilla 409966 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-028_417_hirajoshi.wav audio/OBRA-028_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-028_capa.wav</t>
         </is>
       </c>
-      <c r="R29" s="4" t="inlineStr">
+      <c r="T29" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="S29" s="4" t="inlineStr"/>
-      <c r="T29" s="4" t="inlineStr"/>
       <c r="U29" s="4" t="inlineStr"/>
-      <c r="V29" s="5">
-        <f>IFERROR(U29/T29*1000,"")</f>
+      <c r="V29" s="4" t="inlineStr"/>
+      <c r="W29" s="4" t="inlineStr"/>
+      <c r="X29" s="5">
+        <f>IFERROR(W29/V29*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -3322,91 +3698,104 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
+          <t>Music to Release Tension · Tropical Rainforest · 639 Hz · Open Field · 1 Hour</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
           <t>Música para soltar tensión · Selva tropical · 639 Hz · Campo abierto · 1 hora</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Soltar</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>selva</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Open Field · 1 Hour
+To accompany some time to let go of the day's tension.
+Ambience: tropical rainforest.
+Composed around a root of 639 Hz, in just intonation, yo mode.
+Breathing cycle: from 6.0 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
+Original composition, synthesized from scratch, ambience included. No third-party samples.
+Chapters:
+00:00 [fill in after editing]</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>Campo abierto · 1 hora
+Para acompañar un rato de soltar la tensión del día.
+Ambiente: selva tropical.
 Compuesta con raíz en 639 Hz, en entonación justa, modo yo.
-Para acompañar un rato de soltar la tensión del día.
 Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Ambiente: selva tropical, sintetizado, sin grabaciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 639 Hz in just intonation, yo mode.
-To accompany some time to let go of the day's tension.
-Original composition, synthesized from scratch. No third-party samples.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Capítulos:
 00:00 [completar tras el montaje]</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>639 HZ</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>#MúsicaRelajante #639Hz</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>#RelaxingMusic #Meditation #639Hz</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
         <is>
           <t>639 hz, música 639 hz, música para soltar tensión, music to release tension, soltar, yo, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
         </is>
       </c>
-      <c r="I30" s="4" t="inlineStr"/>
-      <c r="J30" s="4" t="inlineStr"/>
-      <c r="K30" s="2" t="n">
+      <c r="K30" s="4" t="inlineStr"/>
+      <c r="L30" s="4" t="inlineStr"/>
+      <c r="M30" s="2" t="n">
         <v>639</v>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t>yo</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>medio</t>
         </is>
       </c>
-      <c r="N30" s="2" t="n">
+      <c r="P30" s="2" t="n">
         <v>133046</v>
       </c>
-      <c r="O30" s="2" t="n">
+      <c r="Q30" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="P30" s="3" t="inlineStr">
+      <c r="R30" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 60 --raiz 639 --modo yo --semilla 133046 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="Q30" s="2" t="inlineStr">
+      <c r="S30" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py aves 3640 audio/OBRA-029_capa.wav --semilla 133046 --densidad 2 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-029_639_yo.wav audio/OBRA-029_final.wav --fondo selva --nivel-capa -2 --capa audio/OBRA-029_capa.wav</t>
         </is>
       </c>
-      <c r="R30" s="4" t="inlineStr">
+      <c r="T30" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="S30" s="4" t="inlineStr"/>
-      <c r="T30" s="4" t="inlineStr"/>
       <c r="U30" s="4" t="inlineStr"/>
-      <c r="V30" s="5">
-        <f>IFERROR(U30/T30*1000,"")</f>
+      <c r="V30" s="4" t="inlineStr"/>
+      <c r="W30" s="4" t="inlineStr"/>
+      <c r="X30" s="5">
+        <f>IFERROR(W30/V30*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -3418,91 +3807,104 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
+          <t>Music to Release Tension · Ocean and Birds · 741 Hz · Thin Air · 45 Minutes</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
           <t>Música para soltar tensión · Mar y pájaros · 741 Hz · Aire delgado · 45 minutos</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Soltar</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>mar-aves</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Thin Air · 45 Minutes
+To accompany some time to let go of the day's tension.
+Ambience: ocean and birds.
+Composed around a root of 741 Hz, in just intonation, yo mode.
+Breathing cycle: from 6.0 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
+Original composition, synthesized from scratch, ambience included. No third-party samples.
+Chapters:
+00:00 [fill in after editing]</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>Aire delgado · 45 minutos
+Para acompañar un rato de soltar la tensión del día.
+Ambiente: mar y pájaros.
 Compuesta con raíz en 741 Hz, en entonación justa, modo yo.
-Para acompañar un rato de soltar la tensión del día.
 Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Ambiente: mar y pájaros, sintetizado, sin grabaciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 741 Hz in just intonation, yo mode.
-To accompany some time to let go of the day's tension.
-Original composition, synthesized from scratch. No third-party samples.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Capítulos:
 00:00 [completar tras el montaje]</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>741 HZ</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>#MúsicaRelajante #741Hz</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>#RelaxingMusic #Meditation #741Hz</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
         <is>
           <t>741 hz, música 741 hz, música para soltar tensión, music to release tension, soltar, yo, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
         </is>
       </c>
-      <c r="I31" s="4" t="inlineStr"/>
-      <c r="J31" s="4" t="inlineStr"/>
-      <c r="K31" s="2" t="n">
+      <c r="K31" s="4" t="inlineStr"/>
+      <c r="L31" s="4" t="inlineStr"/>
+      <c r="M31" s="2" t="n">
         <v>741</v>
       </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t>yo</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>medio</t>
         </is>
       </c>
-      <c r="N31" s="2" t="n">
+      <c r="P31" s="2" t="n">
         <v>244487</v>
       </c>
-      <c r="O31" s="2" t="n">
+      <c r="Q31" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="P31" s="3" t="inlineStr">
+      <c r="R31" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 45 --raiz 741 --modo yo --semilla 244487 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="Q31" s="2" t="inlineStr">
+      <c r="S31" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py aves 2740 audio/OBRA-030_capa.wav --semilla 244487 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-030_741_yo.wav audio/OBRA-030_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-030_capa.wav</t>
         </is>
       </c>
-      <c r="R31" s="4" t="inlineStr">
+      <c r="T31" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="S31" s="4" t="inlineStr"/>
-      <c r="T31" s="4" t="inlineStr"/>
       <c r="U31" s="4" t="inlineStr"/>
-      <c r="V31" s="5">
-        <f>IFERROR(U31/T31*1000,"")</f>
+      <c r="V31" s="4" t="inlineStr"/>
+      <c r="W31" s="4" t="inlineStr"/>
+      <c r="X31" s="5">
+        <f>IFERROR(W31/V31*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -3514,91 +3916,104 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
+          <t>Music to Release Tension · Zen Temple · 852 Hz · Last Light · 45 Minutes</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
           <t>Música para soltar tensión · Templo zen · 852 Hz · Última luz · 45 minutos</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Soltar</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>zen</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Last Light · 45 Minutes
+To accompany some time to let go of the day's tension.
+Ambience: zen temple.
+Composed around a root of 852 Hz, in just intonation, hirajoshi mode.
+Breathing cycle: from 6.0 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
+Original composition, synthesized from scratch, ambience included. No third-party samples.
+Chapters:
+00:00 [fill in after editing]</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>Última luz · 45 minutos
+Para acompañar un rato de soltar la tensión del día.
+Ambiente: templo zen.
 Compuesta con raíz en 852 Hz, en entonación justa, modo hirajoshi.
-Para acompañar un rato de soltar la tensión del día.
 Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Ambiente: templo zen, sintetizado, sin grabaciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 852 Hz in just intonation, hirajoshi mode.
-To accompany some time to let go of the day's tension.
-Original composition, synthesized from scratch. No third-party samples.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Capítulos:
 00:00 [completar tras el montaje]</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>852 HZ</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>#MúsicaRelajante #852Hz</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>#RelaxingMusic #Meditation #852Hz</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
         <is>
           <t>852 hz, música 852 hz, música para soltar tensión, music to release tension, soltar, hirajoshi, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
         </is>
       </c>
-      <c r="I32" s="4" t="inlineStr"/>
-      <c r="J32" s="4" t="inlineStr"/>
-      <c r="K32" s="2" t="n">
+      <c r="K32" s="4" t="inlineStr"/>
+      <c r="L32" s="4" t="inlineStr"/>
+      <c r="M32" s="2" t="n">
         <v>852</v>
       </c>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>hirajoshi</t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>medio</t>
         </is>
       </c>
-      <c r="N32" s="2" t="n">
+      <c r="P32" s="2" t="n">
         <v>288169</v>
       </c>
-      <c r="O32" s="2" t="n">
+      <c r="Q32" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="P32" s="3" t="inlineStr">
+      <c r="R32" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 45 --raiz 852 --modo hirajoshi --semilla 288169 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="Q32" s="2" t="inlineStr">
+      <c r="S32" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py zen 2740 audio/OBRA-031_capa.wav --semilla 288169 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-031_852_hirajoshi.wav audio/OBRA-031_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-031_capa.wav</t>
         </is>
       </c>
-      <c r="R32" s="4" t="inlineStr">
+      <c r="T32" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="S32" s="4" t="inlineStr"/>
-      <c r="T32" s="4" t="inlineStr"/>
       <c r="U32" s="4" t="inlineStr"/>
-      <c r="V32" s="5">
-        <f>IFERROR(U32/T32*1000,"")</f>
+      <c r="V32" s="4" t="inlineStr"/>
+      <c r="W32" s="4" t="inlineStr"/>
+      <c r="X32" s="5">
+        <f>IFERROR(W32/V32*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -3610,91 +4025,104 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
+          <t>Music to Release Tension · Ocean and Birds · 528 Hz · Salt Root, Long · 3 Hours</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
           <t>Música para soltar tensión · Mar y pájaros · 528 Hz · Raíz de sal, larga · 3 horas</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Soltar</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>mar-aves</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Salt Root, Long · 3 Hours
+To accompany some time to let go of the day's tension.
+Ambience: ocean and birds.
+Composed around a root of 528 Hz, in just intonation, hirajoshi mode.
+Breathing cycle: from 6.0 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
+Original composition, synthesized from scratch, ambience included. No third-party samples.
+Chapters:
+00:00 [fill in after editing]</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>Raíz de sal, larga · 3 horas
+Para acompañar un rato de soltar la tensión del día.
+Ambiente: mar y pájaros.
 Compuesta con raíz en 528 Hz, en entonación justa, modo hirajoshi.
-Para acompañar un rato de soltar la tensión del día.
 Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Ambiente: mar y pájaros, sintetizado, sin grabaciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 528 Hz in just intonation, hirajoshi mode.
-To accompany some time to let go of the day's tension.
-Original composition, synthesized from scratch. No third-party samples.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Capítulos:
 00:00 [completar tras el montaje]</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>528 HZ</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>#MúsicaRelajante #528Hz</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>#RelaxingMusic #Meditation #528Hz</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
         <is>
           <t>528 hz, música 528 hz, música para soltar tensión, music to release tension, soltar, hirajoshi, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
         </is>
       </c>
-      <c r="I33" s="4" t="inlineStr"/>
-      <c r="J33" s="4" t="inlineStr"/>
-      <c r="K33" s="2" t="n">
+      <c r="K33" s="4" t="inlineStr"/>
+      <c r="L33" s="4" t="inlineStr"/>
+      <c r="M33" s="2" t="n">
         <v>528</v>
       </c>
-      <c r="L33" s="2" t="inlineStr">
+      <c r="N33" s="2" t="inlineStr">
         <is>
           <t>hirajoshi</t>
         </is>
       </c>
-      <c r="M33" s="2" t="inlineStr">
+      <c r="O33" s="2" t="inlineStr">
         <is>
           <t>medio</t>
         </is>
       </c>
-      <c r="N33" s="2" t="n">
+      <c r="P33" s="2" t="n">
         <v>638156</v>
       </c>
-      <c r="O33" s="2" t="n">
+      <c r="Q33" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="P33" s="3" t="inlineStr">
+      <c r="R33" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 180 --raiz 528 --modo hirajoshi --semilla 638156 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="Q33" s="2" t="inlineStr">
+      <c r="S33" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py aves 10840 audio/OBRA-032_capa.wav --semilla 638156 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-032_528_hirajoshi.wav audio/OBRA-032_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-032_capa.wav</t>
         </is>
       </c>
-      <c r="R33" s="4" t="inlineStr">
+      <c r="T33" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="S33" s="4" t="inlineStr"/>
-      <c r="T33" s="4" t="inlineStr"/>
       <c r="U33" s="4" t="inlineStr"/>
-      <c r="V33" s="5">
-        <f>IFERROR(U33/T33*1000,"")</f>
+      <c r="V33" s="4" t="inlineStr"/>
+      <c r="W33" s="4" t="inlineStr"/>
+      <c r="X33" s="5">
+        <f>IFERROR(W33/V33*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -3706,91 +4134,104 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
+          <t>Focus Music · Tropical Rainforest · 639 Hz · Clean Desk · 2 Hours</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
           <t>Música para concentrarse · Selva tropical · 639 Hz · Mesa limpia · 2 horas</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Concentración</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>selva</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Clean Desk · 2 Hours
+To accompany work or study.
+Ambience: tropical rainforest.
+Composed around a root of 319.5 Hz, the low octave of 639 Hz, in just intonation, yo mode.
+Breathing cycle: from 6.0 down to 5.5 breaths per minute, 40 % inhale / 60 % exhale.
+Original composition, synthesized from scratch, ambience included. No third-party samples.
+Chapters:
+00:00 [fill in after editing]</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>Mesa limpia · 2 horas
+Para acompañar el trabajo o el estudio.
+Ambiente: selva tropical.
 Compuesta con raíz en 319.5 Hz, la octava grave de 639 Hz, en entonación justa, modo yo.
-Para acompañar el trabajo o el estudio.
 Ciclo respiratorio: de 6.0 a 5.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Ambiente: selva tropical, sintetizado, sin grabaciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 639 Hz in just intonation, yo mode.
-To accompany work or study.
-Original composition, synthesized from scratch. No third-party samples.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Capítulos:
 00:00 [completar tras el montaje]</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>2 HORAS</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>#Concentración #MúsicaRelajante #639Hz</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>2 HOURS</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>#FocusMusic #Meditation #639Hz</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
         <is>
           <t>639 hz, música 639 hz, música para concentrarse, focus music, concentración, yo, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
         </is>
       </c>
-      <c r="I34" s="4" t="inlineStr"/>
-      <c r="J34" s="4" t="inlineStr"/>
-      <c r="K34" s="2" t="n">
+      <c r="K34" s="4" t="inlineStr"/>
+      <c r="L34" s="4" t="inlineStr"/>
+      <c r="M34" s="2" t="n">
         <v>639</v>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>yo</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>grave</t>
         </is>
       </c>
-      <c r="N34" s="2" t="n">
+      <c r="P34" s="2" t="n">
         <v>112334</v>
       </c>
-      <c r="O34" s="2" t="n">
+      <c r="Q34" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="P34" s="3" t="inlineStr">
+      <c r="R34" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 120 --raiz 639 --modo yo --semilla 112334 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="Q34" s="2" t="inlineStr">
+      <c r="S34" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py aves 7240 audio/OBRA-033_capa.wav --semilla 112334 --densidad 2 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-033_639_yo.wav audio/OBRA-033_final.wav --fondo selva --nivel-capa -2 --capa audio/OBRA-033_capa.wav</t>
         </is>
       </c>
-      <c r="R34" s="4" t="inlineStr">
+      <c r="T34" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="S34" s="4" t="inlineStr"/>
-      <c r="T34" s="4" t="inlineStr"/>
       <c r="U34" s="4" t="inlineStr"/>
-      <c r="V34" s="5">
-        <f>IFERROR(U34/T34*1000,"")</f>
+      <c r="V34" s="4" t="inlineStr"/>
+      <c r="W34" s="4" t="inlineStr"/>
+      <c r="X34" s="5">
+        <f>IFERROR(W34/V34*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -3802,91 +4243,104 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
+          <t>Focus Music · Ocean and Birds · 528 Hz · Three Hours · 3 Hours</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
           <t>Música para concentrarse · Mar y pájaros · 528 Hz · Tres horas · 3 horas</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Concentración</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>mar-aves</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Three Hours · 3 Hours
+To accompany work or study.
+Ambience: ocean and birds.
+Composed around a root of 264 Hz, the low octave of 528 Hz, in just intonation, yo mode.
+Breathing cycle: from 6.0 down to 5.5 breaths per minute, 40 % inhale / 60 % exhale.
+Original composition, synthesized from scratch, ambience included. No third-party samples.
+Chapters:
+00:00 [fill in after editing]</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>Tres horas · 3 horas
+Para acompañar el trabajo o el estudio.
+Ambiente: mar y pájaros.
 Compuesta con raíz en 264 Hz, la octava grave de 528 Hz, en entonación justa, modo yo.
-Para acompañar el trabajo o el estudio.
 Ciclo respiratorio: de 6.0 a 5.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Ambiente: mar y pájaros, sintetizado, sin grabaciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 528 Hz in just intonation, yo mode.
-To accompany work or study.
-Original composition, synthesized from scratch. No third-party samples.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Capítulos:
 00:00 [completar tras el montaje]</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>3 HORAS</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>#Concentración #MúsicaRelajante #528Hz</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>3 HOURS</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>#FocusMusic #Meditation #528Hz</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
         <is>
           <t>528 hz, música 528 hz, música para concentrarse, focus music, concentración, yo, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
         </is>
       </c>
-      <c r="I35" s="4" t="inlineStr"/>
-      <c r="J35" s="4" t="inlineStr"/>
-      <c r="K35" s="2" t="n">
+      <c r="K35" s="4" t="inlineStr"/>
+      <c r="L35" s="4" t="inlineStr"/>
+      <c r="M35" s="2" t="n">
         <v>528</v>
       </c>
-      <c r="L35" s="2" t="inlineStr">
+      <c r="N35" s="2" t="inlineStr">
         <is>
           <t>yo</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr">
+      <c r="O35" s="2" t="inlineStr">
         <is>
           <t>grave</t>
         </is>
       </c>
-      <c r="N35" s="2" t="n">
+      <c r="P35" s="2" t="n">
         <v>935486</v>
       </c>
-      <c r="O35" s="2" t="n">
+      <c r="Q35" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="P35" s="3" t="inlineStr">
+      <c r="R35" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 180 --raiz 528 --modo yo --semilla 935486 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="Q35" s="2" t="inlineStr">
+      <c r="S35" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py aves 10840 audio/OBRA-034_capa.wav --semilla 935486 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-034_528_yo.wav audio/OBRA-034_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-034_capa.wav</t>
         </is>
       </c>
-      <c r="R35" s="4" t="inlineStr">
+      <c r="T35" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="S35" s="4" t="inlineStr"/>
-      <c r="T35" s="4" t="inlineStr"/>
       <c r="U35" s="4" t="inlineStr"/>
-      <c r="V35" s="5">
-        <f>IFERROR(U35/T35*1000,"")</f>
+      <c r="V35" s="4" t="inlineStr"/>
+      <c r="W35" s="4" t="inlineStr"/>
+      <c r="X35" s="5">
+        <f>IFERROR(W35/V35*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -3898,91 +4352,104 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
+          <t>Focus Music · Tropical Rainforest · 741 Hz · No Interruptions · 2 Hours</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
           <t>Música para concentrarse · Selva tropical · 741 Hz · Sin interrupciones · 2 horas</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Concentración</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>selva</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>No Interruptions · 2 Hours
+To accompany work or study.
+Ambience: tropical rainforest.
+Composed around a root of 370.5 Hz, the low octave of 741 Hz, in just intonation, yo mode.
+Breathing cycle: from 6.0 down to 5.5 breaths per minute, 40 % inhale / 60 % exhale.
+Original composition, synthesized from scratch, ambience included. No third-party samples.
+Chapters:
+00:00 [fill in after editing]</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>Sin interrupciones · 2 horas
+Para acompañar el trabajo o el estudio.
+Ambiente: selva tropical.
 Compuesta con raíz en 370.5 Hz, la octava grave de 741 Hz, en entonación justa, modo yo.
-Para acompañar el trabajo o el estudio.
 Ciclo respiratorio: de 6.0 a 5.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Ambiente: selva tropical, sintetizado, sin grabaciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 741 Hz in just intonation, yo mode.
-To accompany work or study.
-Original composition, synthesized from scratch. No third-party samples.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Capítulos:
 00:00 [completar tras el montaje]</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>2 HORAS</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>#Concentración #MúsicaRelajante #741Hz</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>2 HOURS</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>#FocusMusic #Meditation #741Hz</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
         <is>
           <t>741 hz, música 741 hz, música para concentrarse, focus music, concentración, yo, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
         </is>
       </c>
-      <c r="I36" s="4" t="inlineStr"/>
-      <c r="J36" s="4" t="inlineStr"/>
-      <c r="K36" s="2" t="n">
+      <c r="K36" s="4" t="inlineStr"/>
+      <c r="L36" s="4" t="inlineStr"/>
+      <c r="M36" s="2" t="n">
         <v>741</v>
       </c>
-      <c r="L36" s="2" t="inlineStr">
+      <c r="N36" s="2" t="inlineStr">
         <is>
           <t>yo</t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr">
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>grave</t>
         </is>
       </c>
-      <c r="N36" s="2" t="n">
+      <c r="P36" s="2" t="n">
         <v>74636</v>
       </c>
-      <c r="O36" s="2" t="n">
+      <c r="Q36" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="P36" s="3" t="inlineStr">
+      <c r="R36" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 120 --raiz 741 --modo yo --semilla 74636 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="Q36" s="2" t="inlineStr">
+      <c r="S36" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py aves 7240 audio/OBRA-035_capa.wav --semilla 74636 --densidad 2 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-035_741_yo.wav audio/OBRA-035_final.wav --fondo selva --nivel-capa -2 --capa audio/OBRA-035_capa.wav</t>
         </is>
       </c>
-      <c r="R36" s="4" t="inlineStr">
+      <c r="T36" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="S36" s="4" t="inlineStr"/>
-      <c r="T36" s="4" t="inlineStr"/>
       <c r="U36" s="4" t="inlineStr"/>
-      <c r="V36" s="5">
-        <f>IFERROR(U36/T36*1000,"")</f>
+      <c r="V36" s="4" t="inlineStr"/>
+      <c r="W36" s="4" t="inlineStr"/>
+      <c r="X36" s="5">
+        <f>IFERROR(W36/V36*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -3994,91 +4461,104 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
+          <t>Focus Music · Ocean and Birds · 852 Hz · Morning Light · 90 Minutes</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
           <t>Música para concentrarse · Mar y pájaros · 852 Hz · Luz de mañana · 90 minutos</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Concentración</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>mar-aves</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Morning Light · 90 Minutes
+To accompany work or study.
+Ambience: ocean and birds.
+Composed around a root of 426 Hz, the low octave of 852 Hz, in just intonation, yo mode.
+Breathing cycle: from 6.0 down to 5.5 breaths per minute, 40 % inhale / 60 % exhale.
+Original composition, synthesized from scratch, ambience included. No third-party samples.
+Chapters:
+00:00 [fill in after editing]</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>Luz de mañana · 90 minutos
+Para acompañar el trabajo o el estudio.
+Ambiente: mar y pájaros.
 Compuesta con raíz en 426 Hz, la octava grave de 852 Hz, en entonación justa, modo yo.
-Para acompañar el trabajo o el estudio.
 Ciclo respiratorio: de 6.0 a 5.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Ambiente: mar y pájaros, sintetizado, sin grabaciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 852 Hz in just intonation, yo mode.
-To accompany work or study.
-Original composition, synthesized from scratch. No third-party samples.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Capítulos:
 00:00 [completar tras el montaje]</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>90 MIN</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>#Concentración #MúsicaRelajante #852Hz</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>#FocusMusic #Meditation #852Hz</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
         <is>
           <t>852 hz, música 852 hz, música para concentrarse, focus music, concentración, yo, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
         </is>
       </c>
-      <c r="I37" s="4" t="inlineStr"/>
-      <c r="J37" s="4" t="inlineStr"/>
-      <c r="K37" s="2" t="n">
+      <c r="K37" s="4" t="inlineStr"/>
+      <c r="L37" s="4" t="inlineStr"/>
+      <c r="M37" s="2" t="n">
         <v>852</v>
       </c>
-      <c r="L37" s="2" t="inlineStr">
+      <c r="N37" s="2" t="inlineStr">
         <is>
           <t>yo</t>
         </is>
       </c>
-      <c r="M37" s="2" t="inlineStr">
+      <c r="O37" s="2" t="inlineStr">
         <is>
           <t>grave</t>
         </is>
       </c>
-      <c r="N37" s="2" t="n">
+      <c r="P37" s="2" t="n">
         <v>903477</v>
       </c>
-      <c r="O37" s="2" t="n">
+      <c r="Q37" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="P37" s="3" t="inlineStr">
+      <c r="R37" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 90 --raiz 852 --modo yo --semilla 903477 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="Q37" s="2" t="inlineStr">
+      <c r="S37" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py aves 5440 audio/OBRA-036_capa.wav --semilla 903477 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-036_852_yo.wav audio/OBRA-036_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-036_capa.wav</t>
         </is>
       </c>
-      <c r="R37" s="4" t="inlineStr">
+      <c r="T37" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="S37" s="4" t="inlineStr"/>
-      <c r="T37" s="4" t="inlineStr"/>
       <c r="U37" s="4" t="inlineStr"/>
-      <c r="V37" s="5">
-        <f>IFERROR(U37/T37*1000,"")</f>
+      <c r="V37" s="4" t="inlineStr"/>
+      <c r="W37" s="4" t="inlineStr"/>
+      <c r="X37" s="5">
+        <f>IFERROR(W37/V37*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -4090,91 +4570,104 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
+          <t>Focus Music · Tropical Rainforest · 432 Hz · Slow Work · 2 Hours</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
           <t>Música para concentrarse · Selva tropical · 432 Hz · Trabajo lento · 2 horas</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Concentración</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>selva</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Slow Work · 2 Hours
+To accompany work or study.
+Ambience: tropical rainforest.
+Composed around a root of 216 Hz, the low octave of 432 Hz, in just intonation, yo mode.
+Breathing cycle: from 6.0 down to 5.5 breaths per minute, 40 % inhale / 60 % exhale.
+Original composition, synthesized from scratch, ambience included. No third-party samples.
+Chapters:
+00:00 [fill in after editing]</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>Trabajo lento · 2 horas
+Para acompañar el trabajo o el estudio.
+Ambiente: selva tropical.
 Compuesta con raíz en 216 Hz, la octava grave de 432 Hz, en entonación justa, modo yo.
-Para acompañar el trabajo o el estudio.
 Ciclo respiratorio: de 6.0 a 5.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Ambiente: selva tropical, sintetizado, sin grabaciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 432 Hz in just intonation, yo mode.
-To accompany work or study.
-Original composition, synthesized from scratch. No third-party samples.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Capítulos:
 00:00 [completar tras el montaje]</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>2 HORAS</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>#Concentración #MúsicaRelajante #432Hz</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>2 HOURS</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>#FocusMusic #Meditation #432Hz</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
         <is>
           <t>432 hz, música 432 hz, música para concentrarse, focus music, concentración, yo, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
         </is>
       </c>
-      <c r="I38" s="4" t="inlineStr"/>
-      <c r="J38" s="4" t="inlineStr"/>
-      <c r="K38" s="2" t="n">
+      <c r="K38" s="4" t="inlineStr"/>
+      <c r="L38" s="4" t="inlineStr"/>
+      <c r="M38" s="2" t="n">
         <v>432</v>
       </c>
-      <c r="L38" s="2" t="inlineStr">
+      <c r="N38" s="2" t="inlineStr">
         <is>
           <t>yo</t>
         </is>
       </c>
-      <c r="M38" s="2" t="inlineStr">
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>grave</t>
         </is>
       </c>
-      <c r="N38" s="2" t="n">
+      <c r="P38" s="2" t="n">
         <v>718809</v>
       </c>
-      <c r="O38" s="2" t="n">
+      <c r="Q38" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="P38" s="3" t="inlineStr">
+      <c r="R38" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 120 --raiz 432 --modo yo --semilla 718809 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="Q38" s="2" t="inlineStr">
+      <c r="S38" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py aves 7240 audio/OBRA-037_capa.wav --semilla 718809 --densidad 2 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-037_432_yo.wav audio/OBRA-037_final.wav --fondo selva --nivel-capa -2 --capa audio/OBRA-037_capa.wav</t>
         </is>
       </c>
-      <c r="R38" s="4" t="inlineStr">
+      <c r="T38" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="S38" s="4" t="inlineStr"/>
-      <c r="T38" s="4" t="inlineStr"/>
       <c r="U38" s="4" t="inlineStr"/>
-      <c r="V38" s="5">
-        <f>IFERROR(U38/T38*1000,"")</f>
+      <c r="V38" s="4" t="inlineStr"/>
+      <c r="W38" s="4" t="inlineStr"/>
+      <c r="X38" s="5">
+        <f>IFERROR(W38/V38*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -4186,91 +4679,104 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
+          <t>Focus Music · Ocean Waves · 528 Hz · One Thing · 2 Hours</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
           <t>Música para concentrarse · Olas del mar · 528 Hz · Una sola cosa · 2 horas</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Concentración</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>mar</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>One Thing · 2 Hours
+To accompany work or study.
+Ambience: ocean waves.
+Composed around a root of 264 Hz, the low octave of 528 Hz, in just intonation, shin mode.
+Breathing cycle: from 6.0 down to 5.5 breaths per minute, 40 % inhale / 60 % exhale.
+Original composition, synthesized from scratch, ambience included. No third-party samples.
+Chapters:
+00:00 [fill in after editing]</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>Una sola cosa · 2 horas
+Para acompañar el trabajo o el estudio.
+Ambiente: olas del mar.
 Compuesta con raíz en 264 Hz, la octava grave de 528 Hz, en entonación justa, modo shin.
-Para acompañar el trabajo o el estudio.
 Ciclo respiratorio: de 6.0 a 5.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Ambiente: olas del mar, sintetizado, sin grabaciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 528 Hz in just intonation, shin mode.
-To accompany work or study.
-Original composition, synthesized from scratch. No third-party samples.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Capítulos:
 00:00 [completar tras el montaje]</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>2 HORAS</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>#Concentración #MúsicaRelajante #528Hz</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>2 HOURS</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>#FocusMusic #Meditation #528Hz</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
         <is>
           <t>528 hz, música 528 hz, música para concentrarse, focus music, concentración, shin, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
         </is>
       </c>
-      <c r="I39" s="4" t="inlineStr"/>
-      <c r="J39" s="4" t="inlineStr"/>
-      <c r="K39" s="2" t="n">
+      <c r="K39" s="4" t="inlineStr"/>
+      <c r="L39" s="4" t="inlineStr"/>
+      <c r="M39" s="2" t="n">
         <v>528</v>
       </c>
-      <c r="L39" s="2" t="inlineStr">
+      <c r="N39" s="2" t="inlineStr">
         <is>
           <t>shin</t>
         </is>
       </c>
-      <c r="M39" s="2" t="inlineStr">
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t>grave</t>
         </is>
       </c>
-      <c r="N39" s="2" t="n">
+      <c r="P39" s="2" t="n">
         <v>203246</v>
       </c>
-      <c r="O39" s="2" t="n">
+      <c r="Q39" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="P39" s="3" t="inlineStr">
+      <c r="R39" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 120 --raiz 528 --modo shin --semilla 203246 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="Q39" s="2" t="inlineStr">
+      <c r="S39" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/ambiente.py audio/OBRA-038_528_shin.wav audio/OBRA-038_final.wav --fondo mar</t>
         </is>
       </c>
-      <c r="R39" s="4" t="inlineStr">
+      <c r="T39" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="S39" s="4" t="inlineStr"/>
-      <c r="T39" s="4" t="inlineStr"/>
       <c r="U39" s="4" t="inlineStr"/>
-      <c r="V39" s="5">
-        <f>IFERROR(U39/T39*1000,"")</f>
+      <c r="V39" s="4" t="inlineStr"/>
+      <c r="W39" s="4" t="inlineStr"/>
+      <c r="X39" s="5">
+        <f>IFERROR(W39/V39*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -4282,91 +4788,104 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
+          <t>Focus Music · Tropical Rainforest · 639 Hz · Open Window · 90 Minutes</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
           <t>Música para concentrarse · Selva tropical · 639 Hz · Ventana abierta · 90 minutos</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Concentración</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>selva</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Open Window · 90 Minutes
+To accompany work or study.
+Ambience: tropical rainforest.
+Composed around a root of 319.5 Hz, the low octave of 639 Hz, in just intonation, yo mode.
+Breathing cycle: from 6.0 down to 5.5 breaths per minute, 40 % inhale / 60 % exhale.
+Original composition, synthesized from scratch, ambience included. No third-party samples.
+Chapters:
+00:00 [fill in after editing]</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>Ventana abierta · 90 minutos
+Para acompañar el trabajo o el estudio.
+Ambiente: selva tropical.
 Compuesta con raíz en 319.5 Hz, la octava grave de 639 Hz, en entonación justa, modo yo.
-Para acompañar el trabajo o el estudio.
 Ciclo respiratorio: de 6.0 a 5.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Ambiente: selva tropical, sintetizado, sin grabaciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 639 Hz in just intonation, yo mode.
-To accompany work or study.
-Original composition, synthesized from scratch. No third-party samples.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Capítulos:
 00:00 [completar tras el montaje]</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>90 MIN</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>#Concentración #MúsicaRelajante #639Hz</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>#FocusMusic #Meditation #639Hz</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
         <is>
           <t>639 hz, música 639 hz, música para concentrarse, focus music, concentración, yo, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
         </is>
       </c>
-      <c r="I40" s="4" t="inlineStr"/>
-      <c r="J40" s="4" t="inlineStr"/>
-      <c r="K40" s="2" t="n">
+      <c r="K40" s="4" t="inlineStr"/>
+      <c r="L40" s="4" t="inlineStr"/>
+      <c r="M40" s="2" t="n">
         <v>639</v>
       </c>
-      <c r="L40" s="2" t="inlineStr">
+      <c r="N40" s="2" t="inlineStr">
         <is>
           <t>yo</t>
         </is>
       </c>
-      <c r="M40" s="2" t="inlineStr">
+      <c r="O40" s="2" t="inlineStr">
         <is>
           <t>grave</t>
         </is>
       </c>
-      <c r="N40" s="2" t="n">
+      <c r="P40" s="2" t="n">
         <v>281608</v>
       </c>
-      <c r="O40" s="2" t="n">
+      <c r="Q40" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="P40" s="3" t="inlineStr">
+      <c r="R40" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 90 --raiz 639 --modo yo --semilla 281608 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="Q40" s="2" t="inlineStr">
+      <c r="S40" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py aves 5440 audio/OBRA-039_capa.wav --semilla 281608 --densidad 2 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-039_639_yo.wav audio/OBRA-039_final.wav --fondo selva --nivel-capa -2 --capa audio/OBRA-039_capa.wav</t>
         </is>
       </c>
-      <c r="R40" s="4" t="inlineStr">
+      <c r="T40" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="S40" s="4" t="inlineStr"/>
-      <c r="T40" s="4" t="inlineStr"/>
       <c r="U40" s="4" t="inlineStr"/>
-      <c r="V40" s="5">
-        <f>IFERROR(U40/T40*1000,"")</f>
+      <c r="V40" s="4" t="inlineStr"/>
+      <c r="W40" s="4" t="inlineStr"/>
+      <c r="X40" s="5">
+        <f>IFERROR(W40/V40*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -4378,96 +4897,109 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
+          <t>Focus Music · Ocean and Birds · 741 Hz · Until It's Done · 3 Hours</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
           <t>Música para concentrarse · Mar y pájaros · 741 Hz · Hasta terminar · 3 horas</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Concentración</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>mar-aves</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Until It's Done · 3 Hours
+To accompany work or study.
+Ambience: ocean and birds.
+Composed around a root of 370.5 Hz, the low octave of 741 Hz, in just intonation, yo mode.
+Breathing cycle: from 6.0 down to 5.5 breaths per minute, 40 % inhale / 60 % exhale.
+Original composition, synthesized from scratch, ambience included. No third-party samples.
+Chapters:
+00:00 [fill in after editing]</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>Hasta terminar · 3 horas
+Para acompañar el trabajo o el estudio.
+Ambiente: mar y pájaros.
 Compuesta con raíz en 370.5 Hz, la octava grave de 741 Hz, en entonación justa, modo yo.
-Para acompañar el trabajo o el estudio.
 Ciclo respiratorio: de 6.0 a 5.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
-Ambiente: mar y pájaros, sintetizado, sin grabaciones.
-Composición original, sintetizada desde cero. Ninguna muestra procede de terceros.
-— English —
-Composed with a root of 741 Hz in just intonation, yo mode.
-To accompany work or study.
-Original composition, synthesized from scratch. No third-party samples.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Capítulos:
 00:00 [completar tras el montaje]</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>3 HORAS</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>#Concentración #MúsicaRelajante #741Hz</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>3 HOURS</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>#FocusMusic #Meditation #741Hz</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
         <is>
           <t>741 hz, música 741 hz, música para concentrarse, focus music, concentración, yo, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
         </is>
       </c>
-      <c r="I41" s="4" t="inlineStr"/>
-      <c r="J41" s="4" t="inlineStr"/>
-      <c r="K41" s="2" t="n">
+      <c r="K41" s="4" t="inlineStr"/>
+      <c r="L41" s="4" t="inlineStr"/>
+      <c r="M41" s="2" t="n">
         <v>741</v>
       </c>
-      <c r="L41" s="2" t="inlineStr">
+      <c r="N41" s="2" t="inlineStr">
         <is>
           <t>yo</t>
         </is>
       </c>
-      <c r="M41" s="2" t="inlineStr">
+      <c r="O41" s="2" t="inlineStr">
         <is>
           <t>grave</t>
         </is>
       </c>
-      <c r="N41" s="2" t="n">
+      <c r="P41" s="2" t="n">
         <v>883876</v>
       </c>
-      <c r="O41" s="2" t="n">
+      <c r="Q41" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="P41" s="3" t="inlineStr">
+      <c r="R41" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 180 --raiz 741 --modo yo --semilla 883876 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="Q41" s="2" t="inlineStr">
+      <c r="S41" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py aves 10840 audio/OBRA-040_capa.wav --semilla 883876 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-040_741_yo.wav audio/OBRA-040_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-040_capa.wav</t>
         </is>
       </c>
-      <c r="R41" s="4" t="inlineStr">
+      <c r="T41" s="4" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="S41" s="4" t="inlineStr"/>
-      <c r="T41" s="4" t="inlineStr"/>
       <c r="U41" s="4" t="inlineStr"/>
-      <c r="V41" s="5">
-        <f>IFERROR(U41/T41*1000,"")</f>
+      <c r="V41" s="4" t="inlineStr"/>
+      <c r="W41" s="4" t="inlineStr"/>
+      <c r="X41" s="5">
+        <f>IFERROR(W41/V41*1000,"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V41"/>
+  <autoFilter ref="A1:X41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4513,7 +5045,7 @@
         </is>
       </c>
       <c r="B3" s="7">
-        <f>COUNTIF(Catálogo!R2:R41,"pendiente")</f>
+        <f>COUNTIF(Catálogo!T2:T41,"pendiente")</f>
         <v/>
       </c>
     </row>
@@ -4524,7 +5056,7 @@
         </is>
       </c>
       <c r="B4" s="7">
-        <f>COUNTIF(Catálogo!R2:R41,"compuesta")</f>
+        <f>COUNTIF(Catálogo!T2:T41,"compuesta")</f>
         <v/>
       </c>
     </row>
@@ -4535,7 +5067,7 @@
         </is>
       </c>
       <c r="B5" s="7">
-        <f>COUNTIF(Catálogo!R2:R41,"montada")</f>
+        <f>COUNTIF(Catálogo!T2:T41,"montada")</f>
         <v/>
       </c>
     </row>
@@ -4546,7 +5078,7 @@
         </is>
       </c>
       <c r="B6" s="7">
-        <f>COUNTIF(Catálogo!R2:R41,"publicada")</f>
+        <f>COUNTIF(Catálogo!T2:T41,"publicada")</f>
         <v/>
       </c>
     </row>
@@ -4586,15 +5118,15 @@
         </is>
       </c>
       <c r="B10" s="7">
-        <f>COUNTIF(Catálogo!C2:C41,A10)</f>
+        <f>COUNTIF(Catálogo!D2:D41,A10)</f>
         <v/>
       </c>
       <c r="C10" s="7">
-        <f>COUNTIFS(Catálogo!C2:C41,A10,Catálogo!R2:R41,"publicada")</f>
+        <f>COUNTIFS(Catálogo!D2:D41,A10,Catálogo!T2:T41,"publicada")</f>
         <v/>
       </c>
       <c r="D10" s="7">
-        <f>SUMIF(Catálogo!C2:C41,A10,Catálogo!O2:O41)</f>
+        <f>SUMIF(Catálogo!D2:D41,A10,Catálogo!Q2:Q41)</f>
         <v/>
       </c>
     </row>
@@ -4605,15 +5137,15 @@
         </is>
       </c>
       <c r="B11" s="7">
-        <f>COUNTIF(Catálogo!C2:C41,A11)</f>
+        <f>COUNTIF(Catálogo!D2:D41,A11)</f>
         <v/>
       </c>
       <c r="C11" s="7">
-        <f>COUNTIFS(Catálogo!C2:C41,A11,Catálogo!R2:R41,"publicada")</f>
+        <f>COUNTIFS(Catálogo!D2:D41,A11,Catálogo!T2:T41,"publicada")</f>
         <v/>
       </c>
       <c r="D11" s="7">
-        <f>SUMIF(Catálogo!C2:C41,A11,Catálogo!O2:O41)</f>
+        <f>SUMIF(Catálogo!D2:D41,A11,Catálogo!Q2:Q41)</f>
         <v/>
       </c>
     </row>
@@ -4624,15 +5156,15 @@
         </is>
       </c>
       <c r="B12" s="7">
-        <f>COUNTIF(Catálogo!C2:C41,A12)</f>
+        <f>COUNTIF(Catálogo!D2:D41,A12)</f>
         <v/>
       </c>
       <c r="C12" s="7">
-        <f>COUNTIFS(Catálogo!C2:C41,A12,Catálogo!R2:R41,"publicada")</f>
+        <f>COUNTIFS(Catálogo!D2:D41,A12,Catálogo!T2:T41,"publicada")</f>
         <v/>
       </c>
       <c r="D12" s="7">
-        <f>SUMIF(Catálogo!C2:C41,A12,Catálogo!O2:O41)</f>
+        <f>SUMIF(Catálogo!D2:D41,A12,Catálogo!Q2:Q41)</f>
         <v/>
       </c>
     </row>
@@ -4643,15 +5175,15 @@
         </is>
       </c>
       <c r="B13" s="7">
-        <f>COUNTIF(Catálogo!C2:C41,A13)</f>
+        <f>COUNTIF(Catálogo!D2:D41,A13)</f>
         <v/>
       </c>
       <c r="C13" s="7">
-        <f>COUNTIFS(Catálogo!C2:C41,A13,Catálogo!R2:R41,"publicada")</f>
+        <f>COUNTIFS(Catálogo!D2:D41,A13,Catálogo!T2:T41,"publicada")</f>
         <v/>
       </c>
       <c r="D13" s="7">
-        <f>SUMIF(Catálogo!C2:C41,A13,Catálogo!O2:O41)</f>
+        <f>SUMIF(Catálogo!D2:D41,A13,Catálogo!Q2:Q41)</f>
         <v/>
       </c>
     </row>
@@ -4662,15 +5194,15 @@
         </is>
       </c>
       <c r="B14" s="7">
-        <f>COUNTIF(Catálogo!C2:C41,A14)</f>
+        <f>COUNTIF(Catálogo!D2:D41,A14)</f>
         <v/>
       </c>
       <c r="C14" s="7">
-        <f>COUNTIFS(Catálogo!C2:C41,A14,Catálogo!R2:R41,"publicada")</f>
+        <f>COUNTIFS(Catálogo!D2:D41,A14,Catálogo!T2:T41,"publicada")</f>
         <v/>
       </c>
       <c r="D14" s="7">
-        <f>SUMIF(Catálogo!C2:C41,A14,Catálogo!O2:O41)</f>
+        <f>SUMIF(Catálogo!D2:D41,A14,Catálogo!Q2:Q41)</f>
         <v/>
       </c>
     </row>
@@ -4707,7 +5239,7 @@
         </is>
       </c>
       <c r="B18" s="7">
-        <f>SUM(Catálogo!T2:T41)</f>
+        <f>SUM(Catálogo!V2:V41)</f>
         <v/>
       </c>
     </row>
@@ -4718,7 +5250,7 @@
         </is>
       </c>
       <c r="B19" s="7">
-        <f>SUM(Catálogo!U2:U41)</f>
+        <f>SUM(Catálogo!W2:W41)</f>
         <v/>
       </c>
     </row>
@@ -4749,7 +5281,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4820,193 +5352,217 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>tema</t>
+          <t>titulo / descripcion_optimizada</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Intención: qué acompaña la obra. Determina la palabra clave y el ciclo respiratorio.</t>
+          <t>En inglés, el idioma principal del canal.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>ambiente</t>
+          <t>titulo_es / descripcion_es</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Ambiente aprobado en escucha: mar, mar-aves, zen, selva o lluvia-tambor.</t>
+          <t>La traducción al español. Se carga en YouTube Studio → Subtítulos → Título y descripción.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>comando_ambiente</t>
+          <t>tema</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Segundo paso: envuelve la obra compuesta en su ambiente.</t>
+          <t>Intención: qué acompaña la obra. Determina la palabra clave y el ciclo respiratorio.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>descripcion_optimizada</t>
+          <t>ambiente</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Descripción bilingüe lista para pegar. Solo falta añadir los capítulos tras el montaje.</t>
+          <t>Ambiente aprobado en escucha: mar, mar-aves, zen, selva o lluvia-tambor.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>titulo_miniatura</t>
+          <t>comando_ambiente</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Texto de la miniatura: 2-4 palabras que COMPLETAN el título, nunca lo repiten.</t>
+          <t>Segundo paso: envuelve la obra compuesta en su ambiente.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>hashtags</t>
+          <t>descripcion_optimizada</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Tres, al final de la descripción.</t>
+          <t>Descripción bilingüe lista para pegar. Solo falta añadir los capítulos tras el montaje.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>etiquetas</t>
+          <t>titulo_miniatura</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Etiquetas del video, separadas por coma.</t>
+          <t>Texto de la miniatura: 2-4 palabras que COMPLETAN el título, nunca lo repiten.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>imagen_miniatura</t>
+          <t>hashtags</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>AMARILLA. Ruta o URL de la portada una vez generada.</t>
+          <t>Tres, al final de la descripción.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>url_video</t>
+          <t>etiquetas</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>AMARILLA. URL de YouTube una vez publicado.</t>
+          <t>Etiquetas del video, separadas por coma.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>raiz_hz / modo / registro / semilla</t>
+          <t>imagen_miniatura</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Parámetros de composición. El registro grave baja una octava (Dormir y Concentración). La semilla regenera la obra idéntica.</t>
+          <t>AMARILLA. Ruta o URL de la portada una vez generada.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>comando_regeneracion</t>
+          <t>url_video</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Comando exacto. Copiar, pegar y ejecutar: devuelve el mismo audio bit a bit.</t>
+          <t>AMARILLA. URL de YouTube una vez publicado.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>estado</t>
+          <t>raiz_hz / modo / registro / semilla</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>AMARILLA. pendiente / compuesta / montada / publicada</t>
+          <t>Parámetros de composición. El registro grave baja una octava (Dormir y Concentración). La semilla regenera la obra idéntica.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>fecha_publicacion</t>
+          <t>comando_regeneracion</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>AMARILLA. Formato AAAA-MM-DD.</t>
+          <t>Comando exacto. Copiar, pegar y ejecutar: devuelve el mismo audio bit a bit.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>vistas / suscriptores</t>
+          <t>estado</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>AMARILLA. Copiar de YouTube Studio a los 14 días de publicar.</t>
+          <t>AMARILLA. pendiente / compuesta / montada / publicada</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>subs_por_1000</t>
+          <t>fecha_publicacion</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>Calculada. Es la métrica que decide el canal: por debajo de 1, el problema es la portada, no la música.</t>
+          <t>AMARILLA. Formato AAAA-MM-DD.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr"/>
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>vistas / suscriptores</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>AMARILLA. Copiar de YouTube Studio a los 14 días de publicar.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
+          <t>subs_por_1000</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>Calculada. Es la métrica que decide el canal: por debajo de 1, el problema es la portada, no la música.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
           <t>Ejemplo de fila rellenada</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>imagen_miniatura: portadas/obra-001.png | url_video: https://youtu.be/XXXXXXXXXXX | estado: publicada | fecha_publicacion: 2026-10-07 | vistas: 4820 | suscriptores: 11</t>
         </is>

--- a/08-catalogo/catalogo_canal.xlsx
+++ b/08-catalogo/catalogo_canal.xlsx
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Music for Anxiety · Zen Temple · 528 Hz · Ten Minutes · 10 Minutes</t>
+          <t>Music for Anxiety · Zen Temple · 528 Hz · A Brief Pause · 10 Minutes</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Música para momentos de ansiedad · Templo zen · 528 Hz · Diez minutos · 10 minutos</t>
+          <t>Música para momentos de ansiedad · Templo zen · 528 Hz · Pausa breve · 10 minutos</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Ten Minutes · 10 Minutes
+          <t>A Brief Pause · 10 Minutes
 To accompany a pause when your mind won't stop.
 Ambience: zen temple.
 Composed around a root of 528 Hz, in just intonation, shin mode.
@@ -1877,7 +1877,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Diez minutos · 10 minutos
+          <t>Pausa breve · 10 minutos
 Para acompañar un momento de pausa cuando la cabeza no para.
 Ambiente: templo zen.
 Compuesta con raíz en 528 Hz, en entonación justa, modo shin.
@@ -1918,19 +1918,19 @@
         </is>
       </c>
       <c r="P13" s="2" t="n">
-        <v>207307</v>
+        <v>43734</v>
       </c>
       <c r="Q13" s="2" t="n">
         <v>10</v>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>python3 03-composicion/compositor.py --minutos 10 --raiz 528 --modo shin --semilla 207307 --caracter sin-cuenco</t>
+          <t>python3 03-composicion/compositor.py --minutos 10 --raiz 528 --modo shin --semilla 43734 --caracter sin-cuenco</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py zen 640 audio/OBRA-012_capa.wav --semilla 207307 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-012_528_shin.wav audio/OBRA-012_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-012_capa.wav</t>
+          <t>python3 03-composicion/capas.py zen 640 audio/OBRA-012_capa.wav --semilla 43734 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-012_528_shin.wav audio/OBRA-012_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-012_capa.wav</t>
         </is>
       </c>
       <c r="T13" s="4" t="inlineStr">
@@ -4243,12 +4243,12 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Focus Music · Ocean and Birds · 528 Hz · Three Hours · 3 Hours</t>
+          <t>Focus Music · Ocean and Birds · 528 Hz · Deep Work · 3 Hours</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Música para concentrarse · Mar y pájaros · 528 Hz · Tres horas · 3 horas</t>
+          <t>Música para concentrarse · Mar y pájaros · 528 Hz · Trabajo profundo · 3 horas</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Three Hours · 3 Hours
+          <t>Deep Work · 3 Hours
 To accompany work or study.
 Ambience: ocean and birds.
 Composed around a root of 264 Hz, the low octave of 528 Hz, in just intonation, yo mode.
@@ -4275,7 +4275,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Tres horas · 3 horas
+          <t>Trabajo profundo · 3 horas
 Para acompañar el trabajo o el estudio.
 Ambiente: mar y pájaros.
 Compuesta con raíz en 264 Hz, la octava grave de 528 Hz, en entonación justa, modo yo.
@@ -4316,19 +4316,19 @@
         </is>
       </c>
       <c r="P35" s="2" t="n">
-        <v>935486</v>
+        <v>249239</v>
       </c>
       <c r="Q35" s="2" t="n">
         <v>180</v>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>python3 03-composicion/compositor.py --minutos 180 --raiz 528 --modo yo --semilla 935486 --caracter sin-cuenco --registro grave</t>
+          <t>python3 03-composicion/compositor.py --minutos 180 --raiz 528 --modo yo --semilla 249239 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py aves 10840 audio/OBRA-034_capa.wav --semilla 935486 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-034_528_yo.wav audio/OBRA-034_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-034_capa.wav</t>
+          <t>python3 03-composicion/capas.py aves 10840 audio/OBRA-034_capa.wav --semilla 249239 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-034_528_yo.wav audio/OBRA-034_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-034_capa.wav</t>
         </is>
       </c>
       <c r="T35" s="4" t="inlineStr">

--- a/08-catalogo/catalogo_canal.xlsx
+++ b/08-catalogo/catalogo_canal.xlsx
@@ -672,8 +672,9 @@
 Composed around a root of 216 Hz, the low octave of 432 Hz, in just intonation, shin mode.
 Breathing cycle: from 4.5 down to 3.5 breaths per minute, 40 % inhale / 60 % exhale.
 Original composition, synthesized from scratch, ambience included. No third-party samples.
-Chapters:
-00:00 [fill in after editing]</t>
+Best at low volume.
+Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#SleepMusic #Meditation #432Hz</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -684,8 +685,9 @@
 Compuesta con raíz en 216 Hz, la octava grave de 432 Hz, en entonación justa, modo shin.
 Ciclo respiratorio: de 4.5 a 3.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
-Capítulos:
-00:00 [completar tras el montaje]</t>
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#SleepMusic #Meditation #432Hz</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -700,7 +702,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>432 hz, música 432 hz, música para dormir, sleep music, dormir, shin, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, singing bowls, just intonation</t>
+          <t>sleep music, 432 hz, 432 hz music, deep sleep, insomnia, ocean waves, sea sounds, relaxing music, meditation music, calming music, ambient music, just intonation, original composition, Rin, música para dormir</t>
         </is>
       </c>
       <c r="K2" s="4" t="inlineStr"/>
@@ -781,8 +783,9 @@
 Composed around a root of 264 Hz, the low octave of 528 Hz, in just intonation, kumoi mode.
 Breathing cycle: from 4.5 down to 3.5 breaths per minute, 40 % inhale / 60 % exhale.
 Original composition, synthesized from scratch, ambience included. No third-party samples.
-Chapters:
-00:00 [fill in after editing]</t>
+Best at low volume.
+Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#SleepMusic #Meditation #528Hz</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -793,8 +796,9 @@
 Compuesta con raíz en 264 Hz, la octava grave de 528 Hz, en entonación justa, modo kumoi.
 Ciclo respiratorio: de 4.5 a 3.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
-Capítulos:
-00:00 [completar tras el montaje]</t>
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#SleepMusic #Meditation #528Hz</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -809,7 +813,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>528 hz, música 528 hz, música para dormir, sleep music, dormir, kumoi, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, singing bowls, just intonation</t>
+          <t>sleep music, 528 hz, 528 hz music, deep sleep, insomnia, ocean waves, sea sounds, relaxing music, meditation music, calming music, ambient music, just intonation, original composition, Rin, música para dormir</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr"/>
@@ -890,8 +894,9 @@
 Composed around a root of 198 Hz, the low octave of 396 Hz, in just intonation, kumoi mode.
 Breathing cycle: from 4.5 down to 3.5 breaths per minute, 40 % inhale / 60 % exhale.
 Original composition, synthesized from scratch, ambience included. No third-party samples.
-Chapters:
-00:00 [fill in after editing]</t>
+Best at low volume.
+Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#SleepMusic #Meditation #396Hz</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -902,8 +907,9 @@
 Compuesta con raíz en 198 Hz, la octava grave de 396 Hz, en entonación justa, modo kumoi.
 Ciclo respiratorio: de 4.5 a 3.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
-Capítulos:
-00:00 [completar tras el montaje]</t>
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#SleepMusic #Meditation #396Hz</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -918,7 +924,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>396 hz, música 396 hz, música para dormir, sleep music, dormir, kumoi, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, singing bowls, just intonation</t>
+          <t>sleep music, 396 hz, 396 hz music, deep sleep, insomnia, ocean waves, sea sounds, relaxing music, meditation music, calming music, ambient music, just intonation, original composition, Rin, música para dormir</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr"/>
@@ -999,8 +1005,9 @@
 Composed around a root of 264 Hz, the low octave of 528 Hz, in just intonation, shin mode.
 Breathing cycle: from 4.5 down to 3.5 breaths per minute, 40 % inhale / 60 % exhale.
 Original composition, synthesized from scratch, ambience included. No third-party samples.
-Chapters:
-00:00 [fill in after editing]</t>
+Best at low volume.
+Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#SleepMusic #Meditation #528Hz</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1011,8 +1018,9 @@
 Compuesta con raíz en 264 Hz, la octava grave de 528 Hz, en entonación justa, modo shin.
 Ciclo respiratorio: de 4.5 a 3.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
-Capítulos:
-00:00 [completar tras el montaje]</t>
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#SleepMusic #Meditation #528Hz</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -1027,7 +1035,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>528 hz, música 528 hz, música para dormir, sleep music, dormir, shin, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, singing bowls, just intonation</t>
+          <t>sleep music, 528 hz, 528 hz music, deep sleep, insomnia, ocean waves, sea sounds, relaxing music, meditation music, calming music, ambient music, just intonation, original composition, Rin, música para dormir</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr"/>
@@ -1108,8 +1116,9 @@
 Composed around a root of 216 Hz, the low octave of 432 Hz, in just intonation, kumoi mode.
 Breathing cycle: from 4.5 down to 3.5 breaths per minute, 40 % inhale / 60 % exhale.
 Original composition, synthesized from scratch, ambience included. No third-party samples.
-Chapters:
-00:00 [fill in after editing]</t>
+Best at low volume.
+Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#SleepMusic #Meditation #432Hz</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1120,8 +1129,9 @@
 Compuesta con raíz en 216 Hz, la octava grave de 432 Hz, en entonación justa, modo kumoi.
 Ciclo respiratorio: de 4.5 a 3.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
-Capítulos:
-00:00 [completar tras el montaje]</t>
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#SleepMusic #Meditation #432Hz</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1136,7 +1146,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>432 hz, música 432 hz, música para dormir, sleep music, dormir, kumoi, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, singing bowls, just intonation</t>
+          <t>sleep music, 432 hz, 432 hz music, deep sleep, insomnia, ocean waves, sea sounds, relaxing music, meditation music, calming music, ambient music, just intonation, original composition, Rin, música para dormir</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr"/>
@@ -1217,8 +1227,9 @@
 Composed around a root of 208.5 Hz, the low octave of 417 Hz, in just intonation, kumoi mode.
 Breathing cycle: from 4.5 down to 3.5 breaths per minute, 40 % inhale / 60 % exhale.
 Original composition, synthesized from scratch, ambience included. No third-party samples.
-Chapters:
-00:00 [fill in after editing]</t>
+Best at low volume.
+Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#SleepMusic #Meditation #417Hz</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1229,8 +1240,9 @@
 Compuesta con raíz en 208.5 Hz, la octava grave de 417 Hz, en entonación justa, modo kumoi.
 Ciclo respiratorio: de 4.5 a 3.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
-Capítulos:
-00:00 [completar tras el montaje]</t>
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#SleepMusic #Meditation #417Hz</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1245,7 +1257,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>417 hz, música 417 hz, música para dormir, sleep music, dormir, kumoi, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, singing bowls, just intonation</t>
+          <t>sleep music, 417 hz, 417 hz music, deep sleep, insomnia, ocean waves, sea sounds, relaxing music, meditation music, calming music, ambient music, just intonation, original composition, Rin, música para dormir</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr"/>
@@ -1326,8 +1338,9 @@
 Composed around a root of 198 Hz, the low octave of 396 Hz, in just intonation, shin mode.
 Breathing cycle: from 4.5 down to 3.5 breaths per minute, 40 % inhale / 60 % exhale.
 Original composition, synthesized from scratch, ambience included. No third-party samples.
-Chapters:
-00:00 [fill in after editing]</t>
+Best at low volume.
+Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#SleepMusic #Meditation #396Hz</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1338,8 +1351,9 @@
 Compuesta con raíz en 198 Hz, la octava grave de 396 Hz, en entonación justa, modo shin.
 Ciclo respiratorio: de 4.5 a 3.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
-Capítulos:
-00:00 [completar tras el montaje]</t>
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#SleepMusic #Meditation #396Hz</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1354,7 +1368,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>396 hz, música 396 hz, música para dormir, sleep music, dormir, shin, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, singing bowls, just intonation</t>
+          <t>sleep music, 396 hz, 396 hz music, deep sleep, insomnia, ocean waves, sea sounds, relaxing music, meditation music, calming music, ambient music, just intonation, original composition, Rin, música para dormir</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr"/>
@@ -1435,8 +1449,9 @@
 Composed around a root of 216 Hz, the low octave of 432 Hz, in just intonation, kumoi mode.
 Breathing cycle: from 4.5 down to 3.5 breaths per minute, 40 % inhale / 60 % exhale.
 Original composition, synthesized from scratch, ambience included. No third-party samples.
-Chapters:
-00:00 [fill in after editing]</t>
+Best at low volume.
+Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#SleepMusic #Meditation #432Hz</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1447,8 +1462,9 @@
 Compuesta con raíz en 216 Hz, la octava grave de 432 Hz, en entonación justa, modo kumoi.
 Ciclo respiratorio: de 4.5 a 3.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
-Capítulos:
-00:00 [completar tras el montaje]</t>
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#SleepMusic #Meditation #432Hz</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1463,7 +1479,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>432 hz, música 432 hz, música para dormir, sleep music, dormir, kumoi, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, singing bowls, just intonation</t>
+          <t>sleep music, 432 hz, 432 hz music, deep sleep, insomnia, ocean waves, sea sounds, relaxing music, meditation music, calming music, ambient music, just intonation, original composition, Rin, música para dormir</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr"/>
@@ -1544,8 +1560,9 @@
 Composed around a root of 396 Hz, in just intonation, kumoi mode.
 Breathing cycle: from 6.0 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
 Original composition, synthesized from scratch, ambience included. No third-party samples.
-Chapters:
-00:00 [fill in after editing]</t>
+Best at low volume.
+Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#RelaxingMusic #Meditation #396Hz</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1556,8 +1573,9 @@
 Compuesta con raíz en 396 Hz, en entonación justa, modo kumoi.
 Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
-Capítulos:
-00:00 [completar tras el montaje]</t>
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#RelaxingMusic #Meditation #396Hz</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1572,7 +1590,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>396 hz, música 396 hz, música para momentos de ansiedad, music for anxiety, ansiedad, kumoi, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
+          <t>music for anxiety, 396 hz, 396 hz music, anxiety relief, stress relief, calming music, ocean waves, birdsong, nature sounds, relaxing music, meditation music, ambient music, just intonation, original composition, Rin, música para momentos de ansiedad</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr"/>
@@ -1653,8 +1671,9 @@
 Composed around a root of 432 Hz, in just intonation, hirajoshi mode.
 Breathing cycle: from 6.0 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
 Original composition, synthesized from scratch, ambience included. No third-party samples.
-Chapters:
-00:00 [fill in after editing]</t>
+Best at low volume.
+Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#RelaxingMusic #Meditation #432Hz</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1665,8 +1684,9 @@
 Compuesta con raíz en 432 Hz, en entonación justa, modo hirajoshi.
 Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
-Capítulos:
-00:00 [completar tras el montaje]</t>
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#RelaxingMusic #Meditation #432Hz</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1681,7 +1701,7 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>432 hz, música 432 hz, música para momentos de ansiedad, music for anxiety, ansiedad, hirajoshi, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
+          <t>music for anxiety, 432 hz, 432 hz music, anxiety relief, stress relief, calming music, zen temple, temple bells, wind chimes, relaxing music, meditation music, ambient music, just intonation, original composition, Rin, música para momentos de ansiedad</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr"/>
@@ -1762,8 +1782,9 @@
 Composed around a root of 528 Hz, in just intonation, hirajoshi mode.
 Breathing cycle: from 6.0 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
 Original composition, synthesized from scratch, ambience included. No third-party samples.
-Chapters:
-00:00 [fill in after editing]</t>
+Best at low volume.
+Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#RelaxingMusic #Meditation #528Hz</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1774,8 +1795,9 @@
 Compuesta con raíz en 528 Hz, en entonación justa, modo hirajoshi.
 Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
-Capítulos:
-00:00 [completar tras el montaje]</t>
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#RelaxingMusic #Meditation #528Hz</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1790,7 +1812,7 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>528 hz, música 528 hz, música para momentos de ansiedad, music for anxiety, ansiedad, hirajoshi, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
+          <t>music for anxiety, 528 hz, 528 hz music, anxiety relief, stress relief, calming music, ocean waves, birdsong, nature sounds, relaxing music, meditation music, ambient music, just intonation, original composition, Rin, música para momentos de ansiedad</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr"/>
@@ -1871,8 +1893,9 @@
 Composed around a root of 528 Hz, in just intonation, shin mode.
 Breathing cycle: from 6.0 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
 Original composition, synthesized from scratch, ambience included. No third-party samples.
-Chapters:
-00:00 [fill in after editing]</t>
+Best at low volume.
+Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#RelaxingMusic #Meditation #528Hz</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1883,8 +1906,9 @@
 Compuesta con raíz en 528 Hz, en entonación justa, modo shin.
 Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
-Capítulos:
-00:00 [completar tras el montaje]</t>
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#RelaxingMusic #Meditation #528Hz</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1899,7 +1923,7 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>528 hz, música 528 hz, música para momentos de ansiedad, music for anxiety, ansiedad, shin, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
+          <t>music for anxiety, 528 hz, 528 hz music, anxiety relief, stress relief, calming music, zen temple, temple bells, wind chimes, relaxing music, meditation music, ambient music, just intonation, original composition, Rin, música para momentos de ansiedad</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr"/>
@@ -1980,8 +2004,9 @@
 Composed around a root of 432 Hz, in just intonation, hirajoshi mode.
 Breathing cycle: from 6.0 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
 Original composition, synthesized from scratch, ambience included. No third-party samples.
-Chapters:
-00:00 [fill in after editing]</t>
+Best at low volume.
+Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#RelaxingMusic #Meditation #432Hz</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1992,8 +2017,9 @@
 Compuesta con raíz en 432 Hz, en entonación justa, modo hirajoshi.
 Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
-Capítulos:
-00:00 [completar tras el montaje]</t>
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#RelaxingMusic #Meditation #432Hz</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -2008,7 +2034,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>432 hz, música 432 hz, música para momentos de ansiedad, music for anxiety, ansiedad, hirajoshi, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
+          <t>music for anxiety, 432 hz, 432 hz music, anxiety relief, stress relief, calming music, ocean waves, birdsong, nature sounds, relaxing music, meditation music, ambient music, just intonation, original composition, Rin, música para momentos de ansiedad</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr"/>
@@ -2089,8 +2115,9 @@
 Composed around a root of 528 Hz, in just intonation, yo mode.
 Breathing cycle: from 6.0 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
 Original composition, synthesized from scratch, ambience included. No third-party samples.
-Chapters:
-00:00 [fill in after editing]</t>
+Best at low volume.
+Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#RelaxingMusic #Meditation #528Hz</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2101,8 +2128,9 @@
 Compuesta con raíz en 528 Hz, en entonación justa, modo yo.
 Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
-Capítulos:
-00:00 [completar tras el montaje]</t>
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#RelaxingMusic #Meditation #528Hz</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2117,7 +2145,7 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>528 hz, música 528 hz, música para momentos de ansiedad, music for anxiety, ansiedad, yo, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
+          <t>music for anxiety, 528 hz, 528 hz music, anxiety relief, stress relief, calming music, zen temple, temple bells, wind chimes, relaxing music, meditation music, ambient music, just intonation, original composition, Rin, música para momentos de ansiedad</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr"/>
@@ -2198,8 +2226,9 @@
 Composed around a root of 639 Hz, in just intonation, yo mode.
 Breathing cycle: from 6.0 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
 Original composition, synthesized from scratch, ambience included. No third-party samples.
-Chapters:
-00:00 [fill in after editing]</t>
+Best at low volume.
+Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#RelaxingMusic #Meditation #639Hz</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2210,8 +2239,9 @@
 Compuesta con raíz en 639 Hz, en entonación justa, modo yo.
 Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
-Capítulos:
-00:00 [completar tras el montaje]</t>
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#RelaxingMusic #Meditation #639Hz</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2226,7 +2256,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>639 hz, música 639 hz, música para momentos de ansiedad, music for anxiety, ansiedad, yo, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
+          <t>music for anxiety, 639 hz, 639 hz music, anxiety relief, stress relief, calming music, ocean waves, birdsong, nature sounds, relaxing music, meditation music, ambient music, just intonation, original composition, Rin, música para momentos de ansiedad</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr"/>
@@ -2307,8 +2337,9 @@
 Composed around a root of 417 Hz, in just intonation, kumoi mode.
 Breathing cycle: from 6.0 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
 Original composition, synthesized from scratch, ambience included. No third-party samples.
-Chapters:
-00:00 [fill in after editing]</t>
+Best at low volume.
+Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#RelaxingMusic #Meditation #417Hz</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2319,8 +2350,9 @@
 Compuesta con raíz en 417 Hz, en entonación justa, modo kumoi.
 Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
-Capítulos:
-00:00 [completar tras el montaje]</t>
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#RelaxingMusic #Meditation #417Hz</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2335,7 +2367,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>417 hz, música 417 hz, música para momentos de ansiedad, music for anxiety, ansiedad, kumoi, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
+          <t>music for anxiety, 417 hz, 417 hz music, anxiety relief, stress relief, calming music, rain sounds, rain on leaves, shamanic drum, relaxing music, meditation music, ambient music, just intonation, original composition, Rin, música para momentos de ansiedad</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr"/>
@@ -2416,8 +2448,9 @@
 Composed around a root of 417 Hz, in just intonation, hirajoshi mode.
 Breathing cycle: from 5.5 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
 Original composition, synthesized from scratch, ambience included. No third-party samples.
-Chapters:
-00:00 [fill in after editing]</t>
+Best at low volume.
+Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#MeditationMusic #Meditation #417Hz</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2428,8 +2461,9 @@
 Compuesta con raíz en 417 Hz, en entonación justa, modo hirajoshi.
 Ciclo respiratorio: de 5.5 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
-Capítulos:
-00:00 [completar tras el montaje]</t>
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#MeditationMusic #Meditation #417Hz</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2444,7 +2478,7 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>417 hz, música 417 hz, música para meditar, meditation music, meditar, hirajoshi, música relajante, meditación, relajación, entonación justa, composición original, relaxing music, sleep music, singing bowls, just intonation</t>
+          <t>meditation music, 417 hz, 417 hz music, mindfulness, zen music, yoga music, zen temple, temple bells, wind chimes, relaxing music, calming music, ambient music, just intonation, original composition, Rin, música para meditar</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr"/>
@@ -2525,8 +2559,9 @@
 Composed around a root of 528 Hz, in just intonation, hirajoshi mode.
 Breathing cycle: from 5.5 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
 Original composition, synthesized from scratch, ambience included. No third-party samples.
-Chapters:
-00:00 [fill in after editing]</t>
+Best at low volume.
+Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#MeditationMusic #Meditation #528Hz</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2537,8 +2572,9 @@
 Compuesta con raíz en 528 Hz, en entonación justa, modo hirajoshi.
 Ciclo respiratorio: de 5.5 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
-Capítulos:
-00:00 [completar tras el montaje]</t>
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#MeditationMusic #Meditation #528Hz</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2553,7 +2589,7 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>528 hz, música 528 hz, música para meditar, meditation music, meditar, hirajoshi, música relajante, meditación, relajación, entonación justa, composición original, relaxing music, sleep music, singing bowls, just intonation</t>
+          <t>meditation music, 528 hz, 528 hz music, mindfulness, zen music, yoga music, zen temple, temple bells, wind chimes, relaxing music, calming music, ambient music, just intonation, original composition, Rin, música para meditar</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr"/>
@@ -2634,8 +2670,9 @@
 Composed around a root of 432 Hz, in just intonation, shin mode.
 Breathing cycle: from 5.5 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
 Original composition, synthesized from scratch, ambience included. No third-party samples.
-Chapters:
-00:00 [fill in after editing]</t>
+Best at low volume.
+Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#MeditationMusic #Meditation #432Hz</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2646,8 +2683,9 @@
 Compuesta con raíz en 432 Hz, en entonación justa, modo shin.
 Ciclo respiratorio: de 5.5 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
-Capítulos:
-00:00 [completar tras el montaje]</t>
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#MeditationMusic #Meditation #432Hz</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2662,7 +2700,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>432 hz, música 432 hz, música para meditar, meditation music, meditar, shin, música relajante, meditación, relajación, entonación justa, composición original, relaxing music, sleep music, singing bowls, just intonation</t>
+          <t>meditation music, 432 hz, 432 hz music, mindfulness, zen music, yoga music, zen temple, temple bells, wind chimes, relaxing music, calming music, ambient music, just intonation, original composition, Rin, música para meditar</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr"/>
@@ -2743,8 +2781,9 @@
 Composed around a root of 528 Hz, in just intonation, shin mode.
 Breathing cycle: from 5.5 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
 Original composition, synthesized from scratch, ambience included. No third-party samples.
-Chapters:
-00:00 [fill in after editing]</t>
+Best at low volume.
+Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#MeditationMusic #Meditation #528Hz</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2755,8 +2794,9 @@
 Compuesta con raíz en 528 Hz, en entonación justa, modo shin.
 Ciclo respiratorio: de 5.5 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
-Capítulos:
-00:00 [completar tras el montaje]</t>
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#MeditationMusic #Meditation #528Hz</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2771,7 +2811,7 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>528 hz, música 528 hz, música para meditar, meditation music, meditar, shin, música relajante, meditación, relajación, entonación justa, composición original, relaxing music, sleep music, singing bowls, just intonation</t>
+          <t>meditation music, 528 hz, 528 hz music, mindfulness, zen music, yoga music, rain sounds, rain on leaves, shamanic drum, relaxing music, calming music, ambient music, just intonation, original composition, Rin, música para meditar</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr"/>
@@ -2852,8 +2892,9 @@
 Composed around a root of 396 Hz, in just intonation, kumoi mode.
 Breathing cycle: from 5.5 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
 Original composition, synthesized from scratch, ambience included. No third-party samples.
-Chapters:
-00:00 [fill in after editing]</t>
+Best at low volume.
+Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#MeditationMusic #Meditation #396Hz</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2864,8 +2905,9 @@
 Compuesta con raíz en 396 Hz, en entonación justa, modo kumoi.
 Ciclo respiratorio: de 5.5 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
-Capítulos:
-00:00 [completar tras el montaje]</t>
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#MeditationMusic #Meditation #396Hz</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2880,7 +2922,7 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>396 hz, música 396 hz, música para meditar, meditation music, meditar, kumoi, música relajante, meditación, relajación, entonación justa, composición original, relaxing music, sleep music, singing bowls, just intonation</t>
+          <t>meditation music, 396 hz, 396 hz music, mindfulness, zen music, yoga music, zen temple, temple bells, wind chimes, relaxing music, calming music, ambient music, just intonation, original composition, Rin, música para meditar</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr"/>
@@ -2961,8 +3003,9 @@
 Composed around a root of 639 Hz, in just intonation, yo mode.
 Breathing cycle: from 5.5 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
 Original composition, synthesized from scratch, ambience included. No third-party samples.
-Chapters:
-00:00 [fill in after editing]</t>
+Best at low volume.
+Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#MeditationMusic #Meditation #639Hz</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2973,8 +3016,9 @@
 Compuesta con raíz en 639 Hz, en entonación justa, modo yo.
 Ciclo respiratorio: de 5.5 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
-Capítulos:
-00:00 [completar tras el montaje]</t>
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#MeditationMusic #Meditation #639Hz</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2989,7 +3033,7 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>639 hz, música 639 hz, música para meditar, meditation music, meditar, yo, música relajante, meditación, relajación, entonación justa, composición original, relaxing music, sleep music, singing bowls, just intonation</t>
+          <t>meditation music, 639 hz, 639 hz music, mindfulness, zen music, yoga music, zen temple, temple bells, wind chimes, relaxing music, calming music, ambient music, just intonation, original composition, Rin, música para meditar</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr"/>
@@ -3070,8 +3114,9 @@
 Composed around a root of 528 Hz, in just intonation, shin mode.
 Breathing cycle: from 5.5 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
 Original composition, synthesized from scratch, ambience included. No third-party samples.
-Chapters:
-00:00 [fill in after editing]</t>
+Best at low volume.
+Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#MeditationMusic #Meditation #528Hz</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3082,8 +3127,9 @@
 Compuesta con raíz en 528 Hz, en entonación justa, modo shin.
 Ciclo respiratorio: de 5.5 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
-Capítulos:
-00:00 [completar tras el montaje]</t>
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#MeditationMusic #Meditation #528Hz</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -3098,7 +3144,7 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>528 hz, música 528 hz, música para meditar, meditation music, meditar, shin, música relajante, meditación, relajación, entonación justa, composición original, relaxing music, sleep music, singing bowls, just intonation</t>
+          <t>meditation music, 528 hz, 528 hz music, mindfulness, zen music, yoga music, zen temple, temple bells, wind chimes, relaxing music, calming music, ambient music, just intonation, original composition, Rin, música para meditar</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr"/>
@@ -3179,8 +3225,9 @@
 Composed around a root of 432 Hz, in just intonation, kumoi mode.
 Breathing cycle: from 5.5 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
 Original composition, synthesized from scratch, ambience included. No third-party samples.
-Chapters:
-00:00 [fill in after editing]</t>
+Best at low volume.
+Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#MeditationMusic #Meditation #432Hz</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3191,8 +3238,9 @@
 Compuesta con raíz en 432 Hz, en entonación justa, modo kumoi.
 Ciclo respiratorio: de 5.5 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
-Capítulos:
-00:00 [completar tras el montaje]</t>
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#MeditationMusic #Meditation #432Hz</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3207,7 +3255,7 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>432 hz, música 432 hz, música para meditar, meditation music, meditar, kumoi, música relajante, meditación, relajación, entonación justa, composición original, relaxing music, sleep music, singing bowls, just intonation</t>
+          <t>meditation music, 432 hz, 432 hz music, mindfulness, zen music, yoga music, rain sounds, rain on leaves, shamanic drum, relaxing music, calming music, ambient music, just intonation, original composition, Rin, música para meditar</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr"/>
@@ -3288,8 +3336,9 @@
 Composed around a root of 528 Hz, in just intonation, hirajoshi mode.
 Breathing cycle: from 6.0 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
 Original composition, synthesized from scratch, ambience included. No third-party samples.
-Chapters:
-00:00 [fill in after editing]</t>
+Best at low volume.
+Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#RelaxingMusic #Meditation #528Hz</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3300,8 +3349,9 @@
 Compuesta con raíz en 528 Hz, en entonación justa, modo hirajoshi.
 Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
-Capítulos:
-00:00 [completar tras el montaje]</t>
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#RelaxingMusic #Meditation #528Hz</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3316,7 +3366,7 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>528 hz, música 528 hz, música para soltar tensión, music to release tension, soltar, hirajoshi, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
+          <t>music to release tension, 528 hz, 528 hz music, stress relief, let go, healing music, ocean waves, birdsong, nature sounds, relaxing music, meditation music, calming music, ambient music, just intonation, original composition, Rin, música para soltar tensión</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr"/>
@@ -3397,8 +3447,9 @@
 Composed around a root of 432 Hz, in just intonation, kumoi mode.
 Breathing cycle: from 6.0 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
 Original composition, synthesized from scratch, ambience included. No third-party samples.
-Chapters:
-00:00 [fill in after editing]</t>
+Best at low volume.
+Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#RelaxingMusic #Meditation #432Hz</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3409,8 +3460,9 @@
 Compuesta con raíz en 432 Hz, en entonación justa, modo kumoi.
 Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
-Capítulos:
-00:00 [completar tras el montaje]</t>
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#RelaxingMusic #Meditation #432Hz</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -3425,7 +3477,7 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>432 hz, música 432 hz, música para soltar tensión, music to release tension, soltar, kumoi, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
+          <t>music to release tension, 432 hz, 432 hz music, stress relief, let go, healing music, ocean waves, sea sounds, relaxing music, meditation music, calming music, ambient music, just intonation, original composition, Rin, música para soltar tensión</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr"/>
@@ -3506,8 +3558,9 @@
 Composed around a root of 396 Hz, in just intonation, kumoi mode.
 Breathing cycle: from 6.0 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
 Original composition, synthesized from scratch, ambience included. No third-party samples.
-Chapters:
-00:00 [fill in after editing]</t>
+Best at low volume.
+Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#RelaxingMusic #Meditation #396Hz</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3518,8 +3571,9 @@
 Compuesta con raíz en 396 Hz, en entonación justa, modo kumoi.
 Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
-Capítulos:
-00:00 [completar tras el montaje]</t>
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#RelaxingMusic #Meditation #396Hz</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3534,7 +3588,7 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>396 hz, música 396 hz, música para soltar tensión, music to release tension, soltar, kumoi, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
+          <t>music to release tension, 396 hz, 396 hz music, stress relief, let go, healing music, rain sounds, rain on leaves, shamanic drum, relaxing music, meditation music, calming music, ambient music, just intonation, original composition, Rin, música para soltar tensión</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr"/>
@@ -3615,8 +3669,9 @@
 Composed around a root of 417 Hz, in just intonation, hirajoshi mode.
 Breathing cycle: from 6.0 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
 Original composition, synthesized from scratch, ambience included. No third-party samples.
-Chapters:
-00:00 [fill in after editing]</t>
+Best at low volume.
+Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#RelaxingMusic #Meditation #417Hz</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3627,8 +3682,9 @@
 Compuesta con raíz en 417 Hz, en entonación justa, modo hirajoshi.
 Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
-Capítulos:
-00:00 [completar tras el montaje]</t>
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#RelaxingMusic #Meditation #417Hz</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -3643,7 +3699,7 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>417 hz, música 417 hz, música para soltar tensión, music to release tension, soltar, hirajoshi, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
+          <t>music to release tension, 417 hz, 417 hz music, stress relief, let go, healing music, zen temple, temple bells, wind chimes, relaxing music, meditation music, calming music, ambient music, just intonation, original composition, Rin, música para soltar tensión</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr"/>
@@ -3724,8 +3780,9 @@
 Composed around a root of 639 Hz, in just intonation, yo mode.
 Breathing cycle: from 6.0 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
 Original composition, synthesized from scratch, ambience included. No third-party samples.
-Chapters:
-00:00 [fill in after editing]</t>
+Best at low volume.
+Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#RelaxingMusic #Meditation #639Hz</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3736,8 +3793,9 @@
 Compuesta con raíz en 639 Hz, en entonación justa, modo yo.
 Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
-Capítulos:
-00:00 [completar tras el montaje]</t>
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#RelaxingMusic #Meditation #639Hz</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3752,7 +3810,7 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>639 hz, música 639 hz, música para soltar tensión, music to release tension, soltar, yo, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
+          <t>music to release tension, 639 hz, 639 hz music, stress relief, let go, healing music, rainforest sounds, birdsong, nature sounds, relaxing music, meditation music, calming music, ambient music, just intonation, original composition, Rin, música para soltar tensión</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr"/>
@@ -3833,8 +3891,9 @@
 Composed around a root of 741 Hz, in just intonation, yo mode.
 Breathing cycle: from 6.0 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
 Original composition, synthesized from scratch, ambience included. No third-party samples.
-Chapters:
-00:00 [fill in after editing]</t>
+Best at low volume.
+Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#RelaxingMusic #Meditation #741Hz</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3845,8 +3904,9 @@
 Compuesta con raíz en 741 Hz, en entonación justa, modo yo.
 Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
-Capítulos:
-00:00 [completar tras el montaje]</t>
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#RelaxingMusic #Meditation #741Hz</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -3861,7 +3921,7 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>741 hz, música 741 hz, música para soltar tensión, music to release tension, soltar, yo, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
+          <t>music to release tension, 741 hz, 741 hz music, stress relief, let go, healing music, ocean waves, birdsong, nature sounds, relaxing music, meditation music, calming music, ambient music, just intonation, original composition, Rin, música para soltar tensión</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr"/>
@@ -3942,8 +4002,9 @@
 Composed around a root of 852 Hz, in just intonation, hirajoshi mode.
 Breathing cycle: from 6.0 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
 Original composition, synthesized from scratch, ambience included. No third-party samples.
-Chapters:
-00:00 [fill in after editing]</t>
+Best at low volume.
+Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#RelaxingMusic #Meditation #852Hz</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3954,8 +4015,9 @@
 Compuesta con raíz en 852 Hz, en entonación justa, modo hirajoshi.
 Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
-Capítulos:
-00:00 [completar tras el montaje]</t>
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#RelaxingMusic #Meditation #852Hz</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3970,7 +4032,7 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>852 hz, música 852 hz, música para soltar tensión, music to release tension, soltar, hirajoshi, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
+          <t>music to release tension, 852 hz, 852 hz music, stress relief, let go, healing music, zen temple, temple bells, wind chimes, relaxing music, meditation music, calming music, ambient music, just intonation, original composition, Rin, música para soltar tensión</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr"/>
@@ -4051,8 +4113,9 @@
 Composed around a root of 528 Hz, in just intonation, hirajoshi mode.
 Breathing cycle: from 6.0 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
 Original composition, synthesized from scratch, ambience included. No third-party samples.
-Chapters:
-00:00 [fill in after editing]</t>
+Best at low volume.
+Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#RelaxingMusic #Meditation #528Hz</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4063,8 +4126,9 @@
 Compuesta con raíz en 528 Hz, en entonación justa, modo hirajoshi.
 Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
-Capítulos:
-00:00 [completar tras el montaje]</t>
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#RelaxingMusic #Meditation #528Hz</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -4079,7 +4143,7 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>528 hz, música 528 hz, música para soltar tensión, music to release tension, soltar, hirajoshi, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
+          <t>music to release tension, 528 hz, 528 hz music, stress relief, let go, healing music, ocean waves, birdsong, nature sounds, relaxing music, meditation music, calming music, ambient music, just intonation, original composition, Rin, música para soltar tensión</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr"/>
@@ -4160,8 +4224,9 @@
 Composed around a root of 319.5 Hz, the low octave of 639 Hz, in just intonation, yo mode.
 Breathing cycle: from 6.0 down to 5.5 breaths per minute, 40 % inhale / 60 % exhale.
 Original composition, synthesized from scratch, ambience included. No third-party samples.
-Chapters:
-00:00 [fill in after editing]</t>
+Best at low volume.
+Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#FocusMusic #Meditation #639Hz</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4172,8 +4237,9 @@
 Compuesta con raíz en 319.5 Hz, la octava grave de 639 Hz, en entonación justa, modo yo.
 Ciclo respiratorio: de 6.0 a 5.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
-Capítulos:
-00:00 [completar tras el montaje]</t>
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#FocusMusic #Meditation #639Hz</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4188,7 +4254,7 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>639 hz, música 639 hz, música para concentrarse, focus music, concentración, yo, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
+          <t>focus music, 639 hz, 639 hz music, study music, deep focus, work music, rainforest sounds, birdsong, nature sounds, relaxing music, meditation music, calming music, ambient music, just intonation, original composition, Rin, música para concentrarse</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr"/>
@@ -4269,8 +4335,9 @@
 Composed around a root of 264 Hz, the low octave of 528 Hz, in just intonation, yo mode.
 Breathing cycle: from 6.0 down to 5.5 breaths per minute, 40 % inhale / 60 % exhale.
 Original composition, synthesized from scratch, ambience included. No third-party samples.
-Chapters:
-00:00 [fill in after editing]</t>
+Best at low volume.
+Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#FocusMusic #Meditation #528Hz</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4281,8 +4348,9 @@
 Compuesta con raíz en 264 Hz, la octava grave de 528 Hz, en entonación justa, modo yo.
 Ciclo respiratorio: de 6.0 a 5.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
-Capítulos:
-00:00 [completar tras el montaje]</t>
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#FocusMusic #Meditation #528Hz</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -4297,7 +4365,7 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>528 hz, música 528 hz, música para concentrarse, focus music, concentración, yo, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
+          <t>focus music, 528 hz, 528 hz music, study music, deep focus, work music, ocean waves, birdsong, nature sounds, relaxing music, meditation music, calming music, ambient music, just intonation, original composition, Rin, música para concentrarse</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr"/>
@@ -4378,8 +4446,9 @@
 Composed around a root of 370.5 Hz, the low octave of 741 Hz, in just intonation, yo mode.
 Breathing cycle: from 6.0 down to 5.5 breaths per minute, 40 % inhale / 60 % exhale.
 Original composition, synthesized from scratch, ambience included. No third-party samples.
-Chapters:
-00:00 [fill in after editing]</t>
+Best at low volume.
+Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#FocusMusic #Meditation #741Hz</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4390,8 +4459,9 @@
 Compuesta con raíz en 370.5 Hz, la octava grave de 741 Hz, en entonación justa, modo yo.
 Ciclo respiratorio: de 6.0 a 5.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
-Capítulos:
-00:00 [completar tras el montaje]</t>
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#FocusMusic #Meditation #741Hz</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -4406,7 +4476,7 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>741 hz, música 741 hz, música para concentrarse, focus music, concentración, yo, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
+          <t>focus music, 741 hz, 741 hz music, study music, deep focus, work music, rainforest sounds, birdsong, nature sounds, relaxing music, meditation music, calming music, ambient music, just intonation, original composition, Rin, música para concentrarse</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr"/>
@@ -4487,8 +4557,9 @@
 Composed around a root of 426 Hz, the low octave of 852 Hz, in just intonation, yo mode.
 Breathing cycle: from 6.0 down to 5.5 breaths per minute, 40 % inhale / 60 % exhale.
 Original composition, synthesized from scratch, ambience included. No third-party samples.
-Chapters:
-00:00 [fill in after editing]</t>
+Best at low volume.
+Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#FocusMusic #Meditation #852Hz</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4499,8 +4570,9 @@
 Compuesta con raíz en 426 Hz, la octava grave de 852 Hz, en entonación justa, modo yo.
 Ciclo respiratorio: de 6.0 a 5.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
-Capítulos:
-00:00 [completar tras el montaje]</t>
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#FocusMusic #Meditation #852Hz</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -4515,7 +4587,7 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>852 hz, música 852 hz, música para concentrarse, focus music, concentración, yo, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
+          <t>focus music, 852 hz, 852 hz music, study music, deep focus, work music, ocean waves, birdsong, nature sounds, relaxing music, meditation music, calming music, ambient music, just intonation, original composition, Rin, música para concentrarse</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr"/>
@@ -4596,8 +4668,9 @@
 Composed around a root of 216 Hz, the low octave of 432 Hz, in just intonation, yo mode.
 Breathing cycle: from 6.0 down to 5.5 breaths per minute, 40 % inhale / 60 % exhale.
 Original composition, synthesized from scratch, ambience included. No third-party samples.
-Chapters:
-00:00 [fill in after editing]</t>
+Best at low volume.
+Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#FocusMusic #Meditation #432Hz</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4608,8 +4681,9 @@
 Compuesta con raíz en 216 Hz, la octava grave de 432 Hz, en entonación justa, modo yo.
 Ciclo respiratorio: de 6.0 a 5.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
-Capítulos:
-00:00 [completar tras el montaje]</t>
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#FocusMusic #Meditation #432Hz</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -4624,7 +4698,7 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>432 hz, música 432 hz, música para concentrarse, focus music, concentración, yo, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
+          <t>focus music, 432 hz, 432 hz music, study music, deep focus, work music, rainforest sounds, birdsong, nature sounds, relaxing music, meditation music, calming music, ambient music, just intonation, original composition, Rin, música para concentrarse</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr"/>
@@ -4705,8 +4779,9 @@
 Composed around a root of 264 Hz, the low octave of 528 Hz, in just intonation, shin mode.
 Breathing cycle: from 6.0 down to 5.5 breaths per minute, 40 % inhale / 60 % exhale.
 Original composition, synthesized from scratch, ambience included. No third-party samples.
-Chapters:
-00:00 [fill in after editing]</t>
+Best at low volume.
+Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#FocusMusic #Meditation #528Hz</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4717,8 +4792,9 @@
 Compuesta con raíz en 264 Hz, la octava grave de 528 Hz, en entonación justa, modo shin.
 Ciclo respiratorio: de 6.0 a 5.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
-Capítulos:
-00:00 [completar tras el montaje]</t>
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#FocusMusic #Meditation #528Hz</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -4733,7 +4809,7 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>528 hz, música 528 hz, música para concentrarse, focus music, concentración, shin, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
+          <t>focus music, 528 hz, 528 hz music, study music, deep focus, work music, ocean waves, sea sounds, relaxing music, meditation music, calming music, ambient music, just intonation, original composition, Rin, música para concentrarse</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr"/>
@@ -4814,8 +4890,9 @@
 Composed around a root of 319.5 Hz, the low octave of 639 Hz, in just intonation, yo mode.
 Breathing cycle: from 6.0 down to 5.5 breaths per minute, 40 % inhale / 60 % exhale.
 Original composition, synthesized from scratch, ambience included. No third-party samples.
-Chapters:
-00:00 [fill in after editing]</t>
+Best at low volume.
+Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#FocusMusic #Meditation #639Hz</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4826,8 +4903,9 @@
 Compuesta con raíz en 319.5 Hz, la octava grave de 639 Hz, en entonación justa, modo yo.
 Ciclo respiratorio: de 6.0 a 5.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
-Capítulos:
-00:00 [completar tras el montaje]</t>
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#FocusMusic #Meditation #639Hz</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -4842,7 +4920,7 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>639 hz, música 639 hz, música para concentrarse, focus music, concentración, yo, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
+          <t>focus music, 639 hz, 639 hz music, study music, deep focus, work music, rainforest sounds, birdsong, nature sounds, relaxing music, meditation music, calming music, ambient music, just intonation, original composition, Rin, música para concentrarse</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr"/>
@@ -4923,8 +5001,9 @@
 Composed around a root of 370.5 Hz, the low octave of 741 Hz, in just intonation, yo mode.
 Breathing cycle: from 6.0 down to 5.5 breaths per minute, 40 % inhale / 60 % exhale.
 Original composition, synthesized from scratch, ambience included. No third-party samples.
-Chapters:
-00:00 [fill in after editing]</t>
+Best at low volume.
+Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#FocusMusic #Meditation #741Hz</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4935,8 +5014,9 @@
 Compuesta con raíz en 370.5 Hz, la octava grave de 741 Hz, en entonación justa, modo yo.
 Ciclo respiratorio: de 6.0 a 5.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
-Capítulos:
-00:00 [completar tras el montaje]</t>
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#FocusMusic #Meditation #741Hz</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -4951,7 +5031,7 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>741 hz, música 741 hz, música para concentrarse, focus music, concentración, yo, música relajante, meditación, relajación, entonación justa, composición original, meditation music, relaxing music, sleep music, singing bowls, just intonation</t>
+          <t>focus music, 741 hz, 741 hz music, study music, deep focus, work music, ocean waves, birdsong, nature sounds, relaxing music, meditation music, calming music, ambient music, just intonation, original composition, Rin, música para concentrarse</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr"/>

--- a/08-catalogo/catalogo_canal.xlsx
+++ b/08-catalogo/catalogo_canal.xlsx
@@ -1927,7 +1927,11 @@
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr"/>
-      <c r="L13" s="4" t="inlineStr"/>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/-ywSggvwt2E</t>
+        </is>
+      </c>
       <c r="M13" s="2" t="n">
         <v>528</v>
       </c>
@@ -1959,10 +1963,14 @@
       </c>
       <c r="T13" s="4" t="inlineStr">
         <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="U13" s="4" t="inlineStr"/>
+          <t>publicada</t>
+        </is>
+      </c>
+      <c r="U13" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
       <c r="V13" s="4" t="inlineStr"/>
       <c r="W13" s="4" t="inlineStr"/>
       <c r="X13" s="5">

--- a/08-catalogo/catalogo_canal.xlsx
+++ b/08-catalogo/catalogo_canal.xlsx
@@ -676,7 +676,7 @@
 Original composition, synthesized from scratch, ambience included. No third-party samples.
 Best at low volume.
 Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#SleepMusic #Meditation #432Hz</t>
+#sleepmusic #meditation #432hz</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Mejor a volumen bajo.
 Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#SleepMusic #Meditation #432Hz</t>
+#sleepmusic #meditation #432hz</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>#SleepMusic #Meditation #432Hz</t>
+          <t>#sleepmusic #meditation #432hz</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -787,7 +787,7 @@
 Original composition, synthesized from scratch, ambience included. No third-party samples.
 Best at low volume.
 Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#SleepMusic #Meditation #528Hz</t>
+#sleepmusic #meditation #528hz</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -800,7 +800,7 @@
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Mejor a volumen bajo.
 Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#SleepMusic #Meditation #528Hz</t>
+#sleepmusic #meditation #528hz</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>#SleepMusic #Meditation #528Hz</t>
+          <t>#sleepmusic #meditation #528hz</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -898,7 +898,7 @@
 Original composition, synthesized from scratch, ambience included. No third-party samples.
 Best at low volume.
 Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#SleepMusic #Meditation #396Hz</t>
+#sleepmusic #meditation #396hz</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -911,7 +911,7 @@
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Mejor a volumen bajo.
 Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#SleepMusic #Meditation #396Hz</t>
+#sleepmusic #meditation #396hz</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>#SleepMusic #Meditation #396Hz</t>
+          <t>#sleepmusic #meditation #396hz</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -1009,7 +1009,7 @@
 Original composition, synthesized from scratch, ambience included. No third-party samples.
 Best at low volume.
 Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#SleepMusic #Meditation #528Hz</t>
+#sleepmusic #meditation #528hz</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Mejor a volumen bajo.
 Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#SleepMusic #Meditation #528Hz</t>
+#sleepmusic #meditation #528hz</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>#SleepMusic #Meditation #528Hz</t>
+          <t>#sleepmusic #meditation #528hz</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -1120,7 +1120,7 @@
 Original composition, synthesized from scratch, ambience included. No third-party samples.
 Best at low volume.
 Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#SleepMusic #Meditation #432Hz</t>
+#sleepmusic #meditation #432hz</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Mejor a volumen bajo.
 Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#SleepMusic #Meditation #432Hz</t>
+#sleepmusic #meditation #432hz</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>#SleepMusic #Meditation #432Hz</t>
+          <t>#sleepmusic #meditation #432hz</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -1231,7 +1231,7 @@
 Original composition, synthesized from scratch, ambience included. No third-party samples.
 Best at low volume.
 Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#SleepMusic #Meditation #417Hz</t>
+#sleepmusic #meditation #417hz</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Mejor a volumen bajo.
 Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#SleepMusic #Meditation #417Hz</t>
+#sleepmusic #meditation #417hz</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>#SleepMusic #Meditation #417Hz</t>
+          <t>#sleepmusic #meditation #417hz</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1342,7 +1342,7 @@
 Original composition, synthesized from scratch, ambience included. No third-party samples.
 Best at low volume.
 Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#SleepMusic #Meditation #396Hz</t>
+#sleepmusic #meditation #396hz</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1355,7 +1355,7 @@
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Mejor a volumen bajo.
 Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#SleepMusic #Meditation #396Hz</t>
+#sleepmusic #meditation #396hz</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>#SleepMusic #Meditation #396Hz</t>
+          <t>#sleepmusic #meditation #396hz</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1453,7 +1453,7 @@
 Original composition, synthesized from scratch, ambience included. No third-party samples.
 Best at low volume.
 Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#SleepMusic #Meditation #432Hz</t>
+#sleepmusic #meditation #432hz</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1466,7 +1466,7 @@
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Mejor a volumen bajo.
 Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#SleepMusic #Meditation #432Hz</t>
+#sleepmusic #meditation #432hz</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>#SleepMusic #Meditation #432Hz</t>
+          <t>#sleepmusic #meditation #432hz</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1564,7 +1564,7 @@
 Original composition, synthesized from scratch, ambience included. No third-party samples.
 Best at low volume.
 Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#RelaxingMusic #Meditation #396Hz</t>
+#relaxingmusic #meditation #396hz</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1577,7 +1577,7 @@
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Mejor a volumen bajo.
 Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#RelaxingMusic #Meditation #396Hz</t>
+#relaxingmusic #meditation #396hz</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>#RelaxingMusic #Meditation #396Hz</t>
+          <t>#relaxingmusic #meditation #396hz</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1675,7 +1675,7 @@
 Original composition, synthesized from scratch, ambience included. No third-party samples.
 Best at low volume.
 Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#RelaxingMusic #Meditation #432Hz</t>
+#relaxingmusic #meditation #432hz</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1688,7 +1688,7 @@
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Mejor a volumen bajo.
 Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#RelaxingMusic #Meditation #432Hz</t>
+#relaxingmusic #meditation #432hz</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>#RelaxingMusic #Meditation #432Hz</t>
+          <t>#relaxingmusic #meditation #432hz</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1786,7 +1786,7 @@
 Original composition, synthesized from scratch, ambience included. No third-party samples.
 Best at low volume.
 Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#RelaxingMusic #Meditation #528Hz</t>
+#relaxingmusic #meditation #528hz</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1799,7 +1799,7 @@
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Mejor a volumen bajo.
 Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#RelaxingMusic #Meditation #528Hz</t>
+#relaxingmusic #meditation #528hz</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>#RelaxingMusic #Meditation #528Hz</t>
+          <t>#relaxingmusic #meditation #528hz</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1897,7 +1897,7 @@
 Original composition, synthesized from scratch, ambience included. No third-party samples.
 Best at low volume.
 Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#RelaxingMusic #Meditation #528Hz</t>
+#relaxingmusic #meditation #528hz</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Mejor a volumen bajo.
 Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#RelaxingMusic #Meditation #528Hz</t>
+#relaxingmusic #meditation #528hz</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>#RelaxingMusic #Meditation #528Hz</t>
+          <t>#relaxingmusic #meditation #528hz</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -2016,7 +2016,7 @@
 Original composition, synthesized from scratch, ambience included. No third-party samples.
 Best at low volume.
 Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#RelaxingMusic #Meditation #432Hz</t>
+#relaxingmusic #meditation #432hz</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2029,7 +2029,7 @@
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Mejor a volumen bajo.
 Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#RelaxingMusic #Meditation #432Hz</t>
+#relaxingmusic #meditation #432hz</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>#RelaxingMusic #Meditation #432Hz</t>
+          <t>#relaxingmusic #meditation #432hz</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -2127,7 +2127,7 @@
 Original composition, synthesized from scratch, ambience included. No third-party samples.
 Best at low volume.
 Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#RelaxingMusic #Meditation #528Hz</t>
+#relaxingmusic #meditation #528hz</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2140,7 +2140,7 @@
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Mejor a volumen bajo.
 Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#RelaxingMusic #Meditation #528Hz</t>
+#relaxingmusic #meditation #528hz</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>#RelaxingMusic #Meditation #528Hz</t>
+          <t>#relaxingmusic #meditation #528hz</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -2238,7 +2238,7 @@
 Original composition, synthesized from scratch, ambience included. No third-party samples.
 Best at low volume.
 Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#RelaxingMusic #Meditation #639Hz</t>
+#relaxingmusic #meditation #639hz</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2251,7 +2251,7 @@
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Mejor a volumen bajo.
 Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#RelaxingMusic #Meditation #639Hz</t>
+#relaxingmusic #meditation #639hz</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>#RelaxingMusic #Meditation #639Hz</t>
+          <t>#relaxingmusic #meditation #639hz</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -2357,7 +2357,7 @@
 Original composition, synthesized from scratch, ambience included. No third-party samples.
 Best at low volume.
 Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#RelaxingMusic #Meditation #417Hz</t>
+#relaxingmusic #meditation #417hz</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2370,7 +2370,7 @@
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Mejor a volumen bajo.
 Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#RelaxingMusic #Meditation #417Hz</t>
+#relaxingmusic #meditation #417hz</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>#RelaxingMusic #Meditation #417Hz</t>
+          <t>#relaxingmusic #meditation #417hz</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -2468,7 +2468,7 @@
 Original composition, synthesized from scratch, ambience included. No third-party samples.
 Best at low volume.
 Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#MeditationMusic #Meditation #417Hz</t>
+#meditationmusic #meditation #417hz</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2481,7 +2481,7 @@
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Mejor a volumen bajo.
 Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#MeditationMusic #Meditation #417Hz</t>
+#meditationmusic #meditation #417hz</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>#MeditationMusic #Meditation #417Hz</t>
+          <t>#meditationmusic #meditation #417hz</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -2579,7 +2579,7 @@
 Original composition, synthesized from scratch, ambience included. No third-party samples.
 Best at low volume.
 Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#MeditationMusic #Meditation #528Hz</t>
+#meditationmusic #meditation #528hz</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Mejor a volumen bajo.
 Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#MeditationMusic #Meditation #528Hz</t>
+#meditationmusic #meditation #528hz</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>#MeditationMusic #Meditation #528Hz</t>
+          <t>#meditationmusic #meditation #528hz</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -2690,7 +2690,7 @@
 Original composition, synthesized from scratch, ambience included. No third-party samples.
 Best at low volume.
 Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#MeditationMusic #Meditation #432Hz</t>
+#meditationmusic #meditation #432hz</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2703,7 +2703,7 @@
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Mejor a volumen bajo.
 Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#MeditationMusic #Meditation #432Hz</t>
+#meditationmusic #meditation #432hz</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>#MeditationMusic #Meditation #432Hz</t>
+          <t>#meditationmusic #meditation #432hz</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -2801,7 +2801,7 @@
 Original composition, synthesized from scratch, ambience included. No third-party samples.
 Best at low volume.
 Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#MeditationMusic #Meditation #528Hz</t>
+#meditationmusic #meditation #528hz</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2814,7 +2814,7 @@
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Mejor a volumen bajo.
 Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#MeditationMusic #Meditation #528Hz</t>
+#meditationmusic #meditation #528hz</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>#MeditationMusic #Meditation #528Hz</t>
+          <t>#meditationmusic #meditation #528hz</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -2912,7 +2912,7 @@
 Original composition, synthesized from scratch, ambience included. No third-party samples.
 Best at low volume.
 Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#MeditationMusic #Meditation #396Hz</t>
+#meditationmusic #meditation #396hz</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2925,7 +2925,7 @@
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Mejor a volumen bajo.
 Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#MeditationMusic #Meditation #396Hz</t>
+#meditationmusic #meditation #396hz</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>#MeditationMusic #Meditation #396Hz</t>
+          <t>#meditationmusic #meditation #396hz</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -3023,7 +3023,7 @@
 Original composition, synthesized from scratch, ambience included. No third-party samples.
 Best at low volume.
 Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#MeditationMusic #Meditation #639Hz</t>
+#meditationmusic #meditation #639hz</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3036,7 +3036,7 @@
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Mejor a volumen bajo.
 Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#MeditationMusic #Meditation #639Hz</t>
+#meditationmusic #meditation #639hz</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>#MeditationMusic #Meditation #639Hz</t>
+          <t>#meditationmusic #meditation #639hz</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -3134,7 +3134,7 @@
 Original composition, synthesized from scratch, ambience included. No third-party samples.
 Best at low volume.
 Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#MeditationMusic #Meditation #528Hz</t>
+#meditationmusic #meditation #528hz</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3147,7 +3147,7 @@
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Mejor a volumen bajo.
 Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#MeditationMusic #Meditation #528Hz</t>
+#meditationmusic #meditation #528hz</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>#MeditationMusic #Meditation #528Hz</t>
+          <t>#meditationmusic #meditation #528hz</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -3245,7 +3245,7 @@
 Original composition, synthesized from scratch, ambience included. No third-party samples.
 Best at low volume.
 Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#MeditationMusic #Meditation #432Hz</t>
+#meditationmusic #meditation #432hz</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3258,7 +3258,7 @@
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Mejor a volumen bajo.
 Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#MeditationMusic #Meditation #432Hz</t>
+#meditationmusic #meditation #432hz</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>#MeditationMusic #Meditation #432Hz</t>
+          <t>#meditationmusic #meditation #432hz</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -3356,7 +3356,7 @@
 Original composition, synthesized from scratch, ambience included. No third-party samples.
 Best at low volume.
 Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#RelaxingMusic #Meditation #528Hz</t>
+#relaxingmusic #meditation #528hz</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3369,7 +3369,7 @@
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Mejor a volumen bajo.
 Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#RelaxingMusic #Meditation #528Hz</t>
+#relaxingmusic #meditation #528hz</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>#RelaxingMusic #Meditation #528Hz</t>
+          <t>#relaxingmusic #meditation #528hz</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -3467,7 +3467,7 @@
 Original composition, synthesized from scratch, ambience included. No third-party samples.
 Best at low volume.
 Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#RelaxingMusic #Meditation #432Hz</t>
+#relaxingmusic #meditation #432hz</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3480,7 +3480,7 @@
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Mejor a volumen bajo.
 Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#RelaxingMusic #Meditation #432Hz</t>
+#relaxingmusic #meditation #432hz</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>#RelaxingMusic #Meditation #432Hz</t>
+          <t>#relaxingmusic #meditation #432hz</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -3578,7 +3578,7 @@
 Original composition, synthesized from scratch, ambience included. No third-party samples.
 Best at low volume.
 Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#RelaxingMusic #Meditation #396Hz</t>
+#relaxingmusic #meditation #396hz</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3591,7 +3591,7 @@
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Mejor a volumen bajo.
 Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#RelaxingMusic #Meditation #396Hz</t>
+#relaxingmusic #meditation #396hz</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>#RelaxingMusic #Meditation #396Hz</t>
+          <t>#relaxingmusic #meditation #396hz</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -3689,7 +3689,7 @@
 Original composition, synthesized from scratch, ambience included. No third-party samples.
 Best at low volume.
 Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#RelaxingMusic #Meditation #417Hz</t>
+#relaxingmusic #meditation #417hz</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3702,7 +3702,7 @@
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Mejor a volumen bajo.
 Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#RelaxingMusic #Meditation #417Hz</t>
+#relaxingmusic #meditation #417hz</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>#RelaxingMusic #Meditation #417Hz</t>
+          <t>#relaxingmusic #meditation #417hz</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -3800,7 +3800,7 @@
 Original composition, synthesized from scratch, ambience included. No third-party samples.
 Best at low volume.
 Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#RelaxingMusic #Meditation #639Hz</t>
+#relaxingmusic #meditation #639hz</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3813,7 +3813,7 @@
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Mejor a volumen bajo.
 Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#RelaxingMusic #Meditation #639Hz</t>
+#relaxingmusic #meditation #639hz</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>#RelaxingMusic #Meditation #639Hz</t>
+          <t>#relaxingmusic #meditation #639hz</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -3911,7 +3911,7 @@
 Original composition, synthesized from scratch, ambience included. No third-party samples.
 Best at low volume.
 Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#RelaxingMusic #Meditation #741Hz</t>
+#relaxingmusic #meditation #741hz</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3924,7 +3924,7 @@
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Mejor a volumen bajo.
 Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#RelaxingMusic #Meditation #741Hz</t>
+#relaxingmusic #meditation #741hz</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>#RelaxingMusic #Meditation #741Hz</t>
+          <t>#relaxingmusic #meditation #741hz</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -4022,7 +4022,7 @@
 Original composition, synthesized from scratch, ambience included. No third-party samples.
 Best at low volume.
 Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#RelaxingMusic #Meditation #852Hz</t>
+#relaxingmusic #meditation #852hz</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -4035,7 +4035,7 @@
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Mejor a volumen bajo.
 Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#RelaxingMusic #Meditation #852Hz</t>
+#relaxingmusic #meditation #852hz</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>#RelaxingMusic #Meditation #852Hz</t>
+          <t>#relaxingmusic #meditation #852hz</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -4133,7 +4133,7 @@
 Original composition, synthesized from scratch, ambience included. No third-party samples.
 Best at low volume.
 Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#RelaxingMusic #Meditation #528Hz</t>
+#relaxingmusic #meditation #528hz</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4146,7 +4146,7 @@
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Mejor a volumen bajo.
 Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#RelaxingMusic #Meditation #528Hz</t>
+#relaxingmusic #meditation #528hz</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>#RelaxingMusic #Meditation #528Hz</t>
+          <t>#relaxingmusic #meditation #528hz</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -4244,7 +4244,7 @@
 Original composition, synthesized from scratch, ambience included. No third-party samples.
 Best at low volume.
 Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#FocusMusic #Meditation #639Hz</t>
+#focusmusic #meditation #639hz</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4257,7 +4257,7 @@
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Mejor a volumen bajo.
 Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#FocusMusic #Meditation #639Hz</t>
+#focusmusic #meditation #639hz</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4267,7 +4267,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>#FocusMusic #Meditation #639Hz</t>
+          <t>#focusmusic #meditation #639hz</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -4355,7 +4355,7 @@
 Original composition, synthesized from scratch, ambience included. No third-party samples.
 Best at low volume.
 Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#FocusMusic #Meditation #528Hz</t>
+#focusmusic #meditation #528hz</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4368,7 +4368,7 @@
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Mejor a volumen bajo.
 Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#FocusMusic #Meditation #528Hz</t>
+#focusmusic #meditation #528hz</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>#FocusMusic #Meditation #528Hz</t>
+          <t>#focusmusic #meditation #528hz</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -4466,7 +4466,7 @@
 Original composition, synthesized from scratch, ambience included. No third-party samples.
 Best at low volume.
 Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#FocusMusic #Meditation #741Hz</t>
+#focusmusic #meditation #741hz</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4479,7 +4479,7 @@
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Mejor a volumen bajo.
 Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#FocusMusic #Meditation #741Hz</t>
+#focusmusic #meditation #741hz</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>#FocusMusic #Meditation #741Hz</t>
+          <t>#focusmusic #meditation #741hz</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
@@ -4577,7 +4577,7 @@
 Original composition, synthesized from scratch, ambience included. No third-party samples.
 Best at low volume.
 Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#FocusMusic #Meditation #852Hz</t>
+#focusmusic #meditation #852hz</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4590,7 +4590,7 @@
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Mejor a volumen bajo.
 Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#FocusMusic #Meditation #852Hz</t>
+#focusmusic #meditation #852hz</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>#FocusMusic #Meditation #852Hz</t>
+          <t>#focusmusic #meditation #852hz</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -4688,7 +4688,7 @@
 Original composition, synthesized from scratch, ambience included. No third-party samples.
 Best at low volume.
 Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#FocusMusic #Meditation #432Hz</t>
+#focusmusic #meditation #432hz</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4701,7 +4701,7 @@
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Mejor a volumen bajo.
 Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#FocusMusic #Meditation #432Hz</t>
+#focusmusic #meditation #432hz</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>#FocusMusic #Meditation #432Hz</t>
+          <t>#focusmusic #meditation #432hz</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
@@ -4799,7 +4799,7 @@
 Original composition, synthesized from scratch, ambience included. No third-party samples.
 Best at low volume.
 Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#FocusMusic #Meditation #528Hz</t>
+#focusmusic #meditation #528hz</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4812,7 +4812,7 @@
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Mejor a volumen bajo.
 Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#FocusMusic #Meditation #528Hz</t>
+#focusmusic #meditation #528hz</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>#FocusMusic #Meditation #528Hz</t>
+          <t>#focusmusic #meditation #528hz</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
@@ -4910,7 +4910,7 @@
 Original composition, synthesized from scratch, ambience included. No third-party samples.
 Best at low volume.
 Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#FocusMusic #Meditation #639Hz</t>
+#focusmusic #meditation #639hz</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4923,7 +4923,7 @@
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Mejor a volumen bajo.
 Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#FocusMusic #Meditation #639Hz</t>
+#focusmusic #meditation #639hz</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>#FocusMusic #Meditation #639Hz</t>
+          <t>#focusmusic #meditation #639hz</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -5021,7 +5021,7 @@
 Original composition, synthesized from scratch, ambience included. No third-party samples.
 Best at low volume.
 Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#FocusMusic #Meditation #741Hz</t>
+#focusmusic #meditation #741hz</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5034,7 +5034,7 @@
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
 Mejor a volumen bajo.
 Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#FocusMusic #Meditation #741Hz</t>
+#focusmusic #meditation #741hz</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>#FocusMusic #Meditation #741Hz</t>
+          <t>#focusmusic #meditation #741hz</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -9231,6 +9231,7 @@
         <is>
           <t>Save this for the next hard moment.
 Full piece (10 min): Music for Anxiety · Zen Temple · 528 Hz · A Brief Pause · 10 Minutes
+https://youtu.be/-ywSggvwt2E
 #anxietyrelief #calm #relaxingmusic #528hz #shorts</t>
         </is>
       </c>
@@ -9307,6 +9308,7 @@
         <is>
           <t>Headphones on. Exhale slowly.
 Full piece (10 min): Music for Anxiety · Zen Temple · 528 Hz · A Brief Pause · 10 Minutes
+https://youtu.be/-ywSggvwt2E
 #anxietyrelief #calm #relaxingmusic #528hz #shorts</t>
         </is>
       </c>
@@ -9383,6 +9385,7 @@
         <is>
           <t>Stay for one full breath.
 Full piece (10 min): Music for Anxiety · Zen Temple · 528 Hz · A Brief Pause · 10 Minutes
+https://youtu.be/-ywSggvwt2E
 #anxietyrelief #calm #relaxingmusic #528hz #shorts</t>
         </is>
       </c>
@@ -9459,6 +9462,7 @@
         <is>
           <t>A small pause in the middle of the day.
 Full piece (10 min): Music for Anxiety · Zen Temple · 528 Hz · A Brief Pause · 10 Minutes
+https://youtu.be/-ywSggvwt2E
 #anxietyrelief #calm #relaxingmusic #528hz #shorts</t>
         </is>
       </c>
@@ -9535,6 +9539,7 @@
         <is>
           <t>Send this to someone who needs a pause.
 Full piece (10 min): Music for Anxiety · Zen Temple · 528 Hz · A Brief Pause · 10 Minutes
+https://youtu.be/-ywSggvwt2E
 #anxietyrelief #calm #relaxingmusic #528hz #shorts</t>
         </is>
       </c>
@@ -10331,6 +10336,7 @@
         <is>
           <t>Save this for the next hard moment.
 Full piece (15 min): Music for Anxiety · Ocean and Birds · 639 Hz · Before You Begin · 15 Minutes
+https://youtu.be/nN2uPKczsrc
 #anxietyrelief #calm #relaxingmusic #639hz #shorts</t>
         </is>
       </c>
@@ -10407,6 +10413,7 @@
         <is>
           <t>Headphones on. Exhale slowly.
 Full piece (15 min): Music for Anxiety · Ocean and Birds · 639 Hz · Before You Begin · 15 Minutes
+https://youtu.be/nN2uPKczsrc
 #anxietyrelief #calm #relaxingmusic #639hz #shorts</t>
         </is>
       </c>
@@ -10483,6 +10490,7 @@
         <is>
           <t>Stay for one full breath.
 Full piece (15 min): Music for Anxiety · Ocean and Birds · 639 Hz · Before You Begin · 15 Minutes
+https://youtu.be/nN2uPKczsrc
 #anxietyrelief #calm #relaxingmusic #639hz #shorts</t>
         </is>
       </c>
@@ -10559,6 +10567,7 @@
         <is>
           <t>A small pause in the middle of the day.
 Full piece (15 min): Music for Anxiety · Ocean and Birds · 639 Hz · Before You Begin · 15 Minutes
+https://youtu.be/nN2uPKczsrc
 #anxietyrelief #calm #relaxingmusic #639hz #shorts</t>
         </is>
       </c>
@@ -10635,6 +10644,7 @@
         <is>
           <t>Send this to someone who needs a pause.
 Full piece (15 min): Music for Anxiety · Ocean and Birds · 639 Hz · Before You Begin · 15 Minutes
+https://youtu.be/nN2uPKczsrc
 #anxietyrelief #calm #relaxingmusic #639hz #shorts</t>
         </is>
       </c>

--- a/08-catalogo/catalogo_canal.xlsx
+++ b/08-catalogo/catalogo_canal.xlsx
@@ -2833,7 +2833,11 @@
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr"/>
-      <c r="L21" s="4" t="inlineStr"/>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/QvcXe4ZDq8o</t>
+        </is>
+      </c>
       <c r="M21" s="2" t="n">
         <v>528</v>
       </c>
@@ -2865,10 +2869,14 @@
       </c>
       <c r="T21" s="4" t="inlineStr">
         <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="U21" s="4" t="inlineStr"/>
+          <t>publicada</t>
+        </is>
+      </c>
+      <c r="U21" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
       <c r="V21" s="4" t="inlineStr"/>
       <c r="W21" s="4" t="inlineStr"/>
       <c r="X21" s="5">
@@ -11098,7 +11106,7 @@
       <c r="N82" s="3" t="inlineStr">
         <is>
           <t>Save this for your next sit. Full 45 min piece on YouTube: Rin.
-#meditationmusic #meditation #mindfulness #417hz #meditation</t>
+#meditationmusic #meditation #mindfulness #417hz</t>
         </is>
       </c>
       <c r="O82" s="4" t="inlineStr">
@@ -11170,7 +11178,7 @@
       <c r="N83" s="3" t="inlineStr">
         <is>
           <t>Close your eyes for 45 seconds. Full 45 min piece on YouTube: Rin.
-#meditationmusic #meditation #mindfulness #417hz #meditation</t>
+#meditationmusic #meditation #mindfulness #417hz</t>
         </is>
       </c>
       <c r="O83" s="4" t="inlineStr">
@@ -11242,7 +11250,7 @@
       <c r="N84" s="3" t="inlineStr">
         <is>
           <t>Listen until the sound fades. Full 45 min piece on YouTube: Rin.
-#meditationmusic #meditation #mindfulness #417hz #meditation</t>
+#meditationmusic #meditation #mindfulness #417hz</t>
         </is>
       </c>
       <c r="O84" s="4" t="inlineStr">
@@ -11314,7 +11322,7 @@
       <c r="N85" s="3" t="inlineStr">
         <is>
           <t>A minute of stillness. Full 45 min piece on YouTube: Rin.
-#meditationmusic #meditation #mindfulness #417hz #meditation</t>
+#meditationmusic #meditation #mindfulness #417hz</t>
         </is>
       </c>
       <c r="O85" s="4" t="inlineStr">
@@ -11386,7 +11394,7 @@
       <c r="N86" s="3" t="inlineStr">
         <is>
           <t>Send this to someone who meditates. Full 45 min piece on YouTube: Rin.
-#meditationmusic #meditation #mindfulness #417hz #meditation</t>
+#meditationmusic #meditation #mindfulness #417hz</t>
         </is>
       </c>
       <c r="O86" s="4" t="inlineStr">
@@ -11458,7 +11466,7 @@
       <c r="N87" s="3" t="inlineStr">
         <is>
           <t>Save this for your next sit. Full 45 min piece on YouTube: Rin.
-#meditationmusic #meditation #mindfulness #528hz #meditation</t>
+#meditationmusic #meditation #mindfulness #528hz</t>
         </is>
       </c>
       <c r="O87" s="4" t="inlineStr">
@@ -11530,7 +11538,7 @@
       <c r="N88" s="3" t="inlineStr">
         <is>
           <t>Close your eyes for 45 seconds. Full 45 min piece on YouTube: Rin.
-#meditationmusic #meditation #mindfulness #528hz #meditation</t>
+#meditationmusic #meditation #mindfulness #528hz</t>
         </is>
       </c>
       <c r="O88" s="4" t="inlineStr">
@@ -11602,7 +11610,7 @@
       <c r="N89" s="3" t="inlineStr">
         <is>
           <t>Listen until the sound fades. Full 45 min piece on YouTube: Rin.
-#meditationmusic #meditation #mindfulness #528hz #meditation</t>
+#meditationmusic #meditation #mindfulness #528hz</t>
         </is>
       </c>
       <c r="O89" s="4" t="inlineStr">
@@ -11674,7 +11682,7 @@
       <c r="N90" s="3" t="inlineStr">
         <is>
           <t>A minute of stillness. Full 45 min piece on YouTube: Rin.
-#meditationmusic #meditation #mindfulness #528hz #meditation</t>
+#meditationmusic #meditation #mindfulness #528hz</t>
         </is>
       </c>
       <c r="O90" s="4" t="inlineStr">
@@ -11746,7 +11754,7 @@
       <c r="N91" s="3" t="inlineStr">
         <is>
           <t>Send this to someone who meditates. Full 45 min piece on YouTube: Rin.
-#meditationmusic #meditation #mindfulness #528hz #meditation</t>
+#meditationmusic #meditation #mindfulness #528hz</t>
         </is>
       </c>
       <c r="O91" s="4" t="inlineStr">
@@ -11818,7 +11826,7 @@
       <c r="N92" s="3" t="inlineStr">
         <is>
           <t>Save this for your next sit. Full 1 h piece on YouTube: Rin.
-#meditationmusic #meditation #mindfulness #432hz #meditation</t>
+#meditationmusic #meditation #mindfulness #432hz</t>
         </is>
       </c>
       <c r="O92" s="4" t="inlineStr">
@@ -11890,7 +11898,7 @@
       <c r="N93" s="3" t="inlineStr">
         <is>
           <t>Close your eyes for 45 seconds. Full 1 h piece on YouTube: Rin.
-#meditationmusic #meditation #mindfulness #432hz #meditation</t>
+#meditationmusic #meditation #mindfulness #432hz</t>
         </is>
       </c>
       <c r="O93" s="4" t="inlineStr">
@@ -11962,7 +11970,7 @@
       <c r="N94" s="3" t="inlineStr">
         <is>
           <t>Listen until the sound fades. Full 1 h piece on YouTube: Rin.
-#meditationmusic #meditation #mindfulness #432hz #meditation</t>
+#meditationmusic #meditation #mindfulness #432hz</t>
         </is>
       </c>
       <c r="O94" s="4" t="inlineStr">
@@ -12034,7 +12042,7 @@
       <c r="N95" s="3" t="inlineStr">
         <is>
           <t>A minute of stillness. Full 1 h piece on YouTube: Rin.
-#meditationmusic #meditation #mindfulness #432hz #meditation</t>
+#meditationmusic #meditation #mindfulness #432hz</t>
         </is>
       </c>
       <c r="O95" s="4" t="inlineStr">
@@ -12106,7 +12114,7 @@
       <c r="N96" s="3" t="inlineStr">
         <is>
           <t>Send this to someone who meditates. Full 1 h piece on YouTube: Rin.
-#meditationmusic #meditation #mindfulness #432hz #meditation</t>
+#meditationmusic #meditation #mindfulness #432hz</t>
         </is>
       </c>
       <c r="O96" s="4" t="inlineStr">
@@ -12161,6 +12169,7 @@
         <is>
           <t>Save this for your next sit.
 Full piece (30 min): Meditation Music · Rain on Leaves · 528 Hz · Strike and Silence · 30 Minutes
+https://youtu.be/QvcXe4ZDq8o
 #meditationmusic #meditation #mindfulness #528hz #shorts</t>
         </is>
       </c>
@@ -12169,7 +12178,11 @@
           <t>meditation music, mindfulness, 528 hz, rain on leaves, Rin</t>
         </is>
       </c>
-      <c r="L97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>https://youtu.be/QvcXe4ZDq8o</t>
+        </is>
+      </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
           <t>528 Hz · meditate</t>
@@ -12178,7 +12191,7 @@
       <c r="N97" s="3" t="inlineStr">
         <is>
           <t>Save this for your next sit. Full 30 min piece on YouTube: Rin.
-#meditationmusic #meditation #mindfulness #528hz #meditation</t>
+#meditationmusic #meditation #mindfulness #528hz</t>
         </is>
       </c>
       <c r="O97" s="4" t="inlineStr">
@@ -12233,6 +12246,7 @@
         <is>
           <t>Close your eyes for 45 seconds.
 Full piece (30 min): Meditation Music · Rain on Leaves · 528 Hz · Strike and Silence · 30 Minutes
+https://youtu.be/QvcXe4ZDq8o
 #meditationmusic #meditation #mindfulness #528hz #shorts</t>
         </is>
       </c>
@@ -12241,7 +12255,11 @@
           <t>meditation music, mindfulness, 528 hz, rain on leaves, Rin</t>
         </is>
       </c>
-      <c r="L98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>https://youtu.be/QvcXe4ZDq8o</t>
+        </is>
+      </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
           <t>528 Hz · stillness</t>
@@ -12250,7 +12268,7 @@
       <c r="N98" s="3" t="inlineStr">
         <is>
           <t>Close your eyes for 45 seconds. Full 30 min piece on YouTube: Rin.
-#meditationmusic #meditation #mindfulness #528hz #meditation</t>
+#meditationmusic #meditation #mindfulness #528hz</t>
         </is>
       </c>
       <c r="O98" s="4" t="inlineStr">
@@ -12305,6 +12323,7 @@
         <is>
           <t>Listen until the sound fades.
 Full piece (30 min): Meditation Music · Rain on Leaves · 528 Hz · Strike and Silence · 30 Minutes
+https://youtu.be/QvcXe4ZDq8o
 #meditationmusic #meditation #mindfulness #528hz #shorts</t>
         </is>
       </c>
@@ -12313,7 +12332,11 @@
           <t>meditation music, mindfulness, 528 hz, rain on leaves, Rin</t>
         </is>
       </c>
-      <c r="L99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>https://youtu.be/QvcXe4ZDq8o</t>
+        </is>
+      </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
           <t>528 Hz · listen</t>
@@ -12322,7 +12345,7 @@
       <c r="N99" s="3" t="inlineStr">
         <is>
           <t>Listen until the sound fades. Full 30 min piece on YouTube: Rin.
-#meditationmusic #meditation #mindfulness #528hz #meditation</t>
+#meditationmusic #meditation #mindfulness #528hz</t>
         </is>
       </c>
       <c r="O99" s="4" t="inlineStr">
@@ -12377,6 +12400,7 @@
         <is>
           <t>A minute of stillness.
 Full piece (30 min): Meditation Music · Rain on Leaves · 528 Hz · Strike and Silence · 30 Minutes
+https://youtu.be/QvcXe4ZDq8o
 #meditationmusic #meditation #mindfulness #528hz #shorts</t>
         </is>
       </c>
@@ -12385,7 +12409,11 @@
           <t>meditation music, mindfulness, 528 hz, rain on leaves, Rin</t>
         </is>
       </c>
-      <c r="L100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>https://youtu.be/QvcXe4ZDq8o</t>
+        </is>
+      </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
           <t>528 Hz · sit</t>
@@ -12394,7 +12422,7 @@
       <c r="N100" s="3" t="inlineStr">
         <is>
           <t>A minute of stillness. Full 30 min piece on YouTube: Rin.
-#meditationmusic #meditation #mindfulness #528hz #meditation</t>
+#meditationmusic #meditation #mindfulness #528hz</t>
         </is>
       </c>
       <c r="O100" s="4" t="inlineStr">
@@ -12449,6 +12477,7 @@
         <is>
           <t>Send this to someone who meditates.
 Full piece (30 min): Meditation Music · Rain on Leaves · 528 Hz · Strike and Silence · 30 Minutes
+https://youtu.be/QvcXe4ZDq8o
 #meditationmusic #meditation #mindfulness #528hz #shorts</t>
         </is>
       </c>
@@ -12457,7 +12486,11 @@
           <t>meditation music, mindfulness, 528 hz, rain on leaves, Rin</t>
         </is>
       </c>
-      <c r="L101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>https://youtu.be/QvcXe4ZDq8o</t>
+        </is>
+      </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
           <t>528 Hz · silence</t>
@@ -12466,7 +12499,7 @@
       <c r="N101" s="3" t="inlineStr">
         <is>
           <t>Send this to someone who meditates. Full 30 min piece on YouTube: Rin.
-#meditationmusic #meditation #mindfulness #528hz #meditation</t>
+#meditationmusic #meditation #mindfulness #528hz</t>
         </is>
       </c>
       <c r="O101" s="4" t="inlineStr">
@@ -12538,7 +12571,7 @@
       <c r="N102" s="3" t="inlineStr">
         <is>
           <t>Save this for your next sit. Full 45 min piece on YouTube: Rin.
-#meditationmusic #meditation #mindfulness #396hz #meditation</t>
+#meditationmusic #meditation #mindfulness #396hz</t>
         </is>
       </c>
       <c r="O102" s="4" t="inlineStr">
@@ -12610,7 +12643,7 @@
       <c r="N103" s="3" t="inlineStr">
         <is>
           <t>Close your eyes for 45 seconds. Full 45 min piece on YouTube: Rin.
-#meditationmusic #meditation #mindfulness #396hz #meditation</t>
+#meditationmusic #meditation #mindfulness #396hz</t>
         </is>
       </c>
       <c r="O103" s="4" t="inlineStr">
@@ -12682,7 +12715,7 @@
       <c r="N104" s="3" t="inlineStr">
         <is>
           <t>Listen until the sound fades. Full 45 min piece on YouTube: Rin.
-#meditationmusic #meditation #mindfulness #396hz #meditation</t>
+#meditationmusic #meditation #mindfulness #396hz</t>
         </is>
       </c>
       <c r="O104" s="4" t="inlineStr">
@@ -12754,7 +12787,7 @@
       <c r="N105" s="3" t="inlineStr">
         <is>
           <t>A minute of stillness. Full 45 min piece on YouTube: Rin.
-#meditationmusic #meditation #mindfulness #396hz #meditation</t>
+#meditationmusic #meditation #mindfulness #396hz</t>
         </is>
       </c>
       <c r="O105" s="4" t="inlineStr">
@@ -12826,7 +12859,7 @@
       <c r="N106" s="3" t="inlineStr">
         <is>
           <t>Send this to someone who meditates. Full 45 min piece on YouTube: Rin.
-#meditationmusic #meditation #mindfulness #396hz #meditation</t>
+#meditationmusic #meditation #mindfulness #396hz</t>
         </is>
       </c>
       <c r="O106" s="4" t="inlineStr">
@@ -12898,7 +12931,7 @@
       <c r="N107" s="3" t="inlineStr">
         <is>
           <t>Save this for your next sit. Full 1 h piece on YouTube: Rin.
-#meditationmusic #meditation #mindfulness #639hz #meditation</t>
+#meditationmusic #meditation #mindfulness #639hz</t>
         </is>
       </c>
       <c r="O107" s="4" t="inlineStr">
@@ -12970,7 +13003,7 @@
       <c r="N108" s="3" t="inlineStr">
         <is>
           <t>Close your eyes for 45 seconds. Full 1 h piece on YouTube: Rin.
-#meditationmusic #meditation #mindfulness #639hz #meditation</t>
+#meditationmusic #meditation #mindfulness #639hz</t>
         </is>
       </c>
       <c r="O108" s="4" t="inlineStr">
@@ -13042,7 +13075,7 @@
       <c r="N109" s="3" t="inlineStr">
         <is>
           <t>Listen until the sound fades. Full 1 h piece on YouTube: Rin.
-#meditationmusic #meditation #mindfulness #639hz #meditation</t>
+#meditationmusic #meditation #mindfulness #639hz</t>
         </is>
       </c>
       <c r="O109" s="4" t="inlineStr">
@@ -13114,7 +13147,7 @@
       <c r="N110" s="3" t="inlineStr">
         <is>
           <t>A minute of stillness. Full 1 h piece on YouTube: Rin.
-#meditationmusic #meditation #mindfulness #639hz #meditation</t>
+#meditationmusic #meditation #mindfulness #639hz</t>
         </is>
       </c>
       <c r="O110" s="4" t="inlineStr">
@@ -13186,7 +13219,7 @@
       <c r="N111" s="3" t="inlineStr">
         <is>
           <t>Send this to someone who meditates. Full 1 h piece on YouTube: Rin.
-#meditationmusic #meditation #mindfulness #639hz #meditation</t>
+#meditationmusic #meditation #mindfulness #639hz</t>
         </is>
       </c>
       <c r="O111" s="4" t="inlineStr">
@@ -13258,7 +13291,7 @@
       <c r="N112" s="3" t="inlineStr">
         <is>
           <t>Save this for your next sit. Full 20 min piece on YouTube: Rin.
-#meditationmusic #meditation #mindfulness #528hz #meditation</t>
+#meditationmusic #meditation #mindfulness #528hz</t>
         </is>
       </c>
       <c r="O112" s="4" t="inlineStr">
@@ -13330,7 +13363,7 @@
       <c r="N113" s="3" t="inlineStr">
         <is>
           <t>Close your eyes for 45 seconds. Full 20 min piece on YouTube: Rin.
-#meditationmusic #meditation #mindfulness #528hz #meditation</t>
+#meditationmusic #meditation #mindfulness #528hz</t>
         </is>
       </c>
       <c r="O113" s="4" t="inlineStr">
@@ -13402,7 +13435,7 @@
       <c r="N114" s="3" t="inlineStr">
         <is>
           <t>Listen until the sound fades. Full 20 min piece on YouTube: Rin.
-#meditationmusic #meditation #mindfulness #528hz #meditation</t>
+#meditationmusic #meditation #mindfulness #528hz</t>
         </is>
       </c>
       <c r="O114" s="4" t="inlineStr">
@@ -13474,7 +13507,7 @@
       <c r="N115" s="3" t="inlineStr">
         <is>
           <t>A minute of stillness. Full 20 min piece on YouTube: Rin.
-#meditationmusic #meditation #mindfulness #528hz #meditation</t>
+#meditationmusic #meditation #mindfulness #528hz</t>
         </is>
       </c>
       <c r="O115" s="4" t="inlineStr">
@@ -13546,7 +13579,7 @@
       <c r="N116" s="3" t="inlineStr">
         <is>
           <t>Send this to someone who meditates. Full 20 min piece on YouTube: Rin.
-#meditationmusic #meditation #mindfulness #528hz #meditation</t>
+#meditationmusic #meditation #mindfulness #528hz</t>
         </is>
       </c>
       <c r="O116" s="4" t="inlineStr">
@@ -13618,7 +13651,7 @@
       <c r="N117" s="3" t="inlineStr">
         <is>
           <t>Save this for your next sit. Full 1 h piece on YouTube: Rin.
-#meditationmusic #meditation #mindfulness #432hz #meditation</t>
+#meditationmusic #meditation #mindfulness #432hz</t>
         </is>
       </c>
       <c r="O117" s="4" t="inlineStr">
@@ -13690,7 +13723,7 @@
       <c r="N118" s="3" t="inlineStr">
         <is>
           <t>Close your eyes for 45 seconds. Full 1 h piece on YouTube: Rin.
-#meditationmusic #meditation #mindfulness #432hz #meditation</t>
+#meditationmusic #meditation #mindfulness #432hz</t>
         </is>
       </c>
       <c r="O118" s="4" t="inlineStr">
@@ -13762,7 +13795,7 @@
       <c r="N119" s="3" t="inlineStr">
         <is>
           <t>Listen until the sound fades. Full 1 h piece on YouTube: Rin.
-#meditationmusic #meditation #mindfulness #432hz #meditation</t>
+#meditationmusic #meditation #mindfulness #432hz</t>
         </is>
       </c>
       <c r="O119" s="4" t="inlineStr">
@@ -13834,7 +13867,7 @@
       <c r="N120" s="3" t="inlineStr">
         <is>
           <t>A minute of stillness. Full 1 h piece on YouTube: Rin.
-#meditationmusic #meditation #mindfulness #432hz #meditation</t>
+#meditationmusic #meditation #mindfulness #432hz</t>
         </is>
       </c>
       <c r="O120" s="4" t="inlineStr">
@@ -13906,7 +13939,7 @@
       <c r="N121" s="3" t="inlineStr">
         <is>
           <t>Send this to someone who meditates. Full 1 h piece on YouTube: Rin.
-#meditationmusic #meditation #mindfulness #432hz #meditation</t>
+#meditationmusic #meditation #mindfulness #432hz</t>
         </is>
       </c>
       <c r="O121" s="4" t="inlineStr">

--- a/08-catalogo/catalogo_canal.xlsx
+++ b/08-catalogo/catalogo_canal.xlsx
@@ -1284,7 +1284,11 @@
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr"/>
-      <c r="L7" s="4" t="inlineStr"/>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/cECOoUGLqes</t>
+        </is>
+      </c>
       <c r="M7" s="2" t="n">
         <v>417</v>
       </c>
@@ -1319,10 +1323,14 @@
       </c>
       <c r="U7" s="4" t="inlineStr">
         <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="V7" s="4" t="inlineStr"/>
+          <t>publicada</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
       <c r="W7" s="4" t="inlineStr"/>
       <c r="X7" s="4" t="inlineStr"/>
       <c r="Y7" s="5">
@@ -7925,6 +7933,7 @@
         <is>
           <t>Save this for tonight.
 Full piece (90 min): Sleep Music · Ocean Waves · 417 Hz · Before Dawn · 90 Minutes
+https://youtu.be/cECOoUGLqes
 #sleepmusic #sleep #relaxingmusic #417hz #shorts</t>
         </is>
       </c>
@@ -7933,7 +7942,11 @@
           <t>sleep music, deep sleep, 417 hz, ocean waves, Rin</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>https://youtu.be/cECOoUGLqes</t>
+        </is>
+      </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
           <t>417 Hz · sleep</t>
@@ -7997,6 +8010,7 @@
         <is>
           <t>Lights off, volume low.
 Full piece (90 min): Sleep Music · Ocean Waves · 417 Hz · Before Dawn · 90 Minutes
+https://youtu.be/cECOoUGLqes
 #sleepmusic #sleep #relaxingmusic #417hz #shorts</t>
         </is>
       </c>
@@ -8005,7 +8019,11 @@
           <t>sleep music, deep sleep, 417 hz, ocean waves, Rin</t>
         </is>
       </c>
-      <c r="L38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>https://youtu.be/cECOoUGLqes</t>
+        </is>
+      </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
           <t>417 Hz · night</t>
@@ -8069,6 +8087,7 @@
         <is>
           <t>Stay until your breathing slows.
 Full piece (90 min): Sleep Music · Ocean Waves · 417 Hz · Before Dawn · 90 Minutes
+https://youtu.be/cECOoUGLqes
 #sleepmusic #sleep #relaxingmusic #417hz #shorts</t>
         </is>
       </c>
@@ -8077,7 +8096,11 @@
           <t>sleep music, deep sleep, 417 hz, ocean waves, Rin</t>
         </is>
       </c>
-      <c r="L39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>https://youtu.be/cECOoUGLqes</t>
+        </is>
+      </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
           <t>417 Hz · rest</t>
@@ -8141,6 +8164,7 @@
         <is>
           <t>The quiet hour before sleep.
 Full piece (90 min): Sleep Music · Ocean Waves · 417 Hz · Before Dawn · 90 Minutes
+https://youtu.be/cECOoUGLqes
 #sleepmusic #sleep #relaxingmusic #417hz #shorts</t>
         </is>
       </c>
@@ -8149,7 +8173,11 @@
           <t>sleep music, deep sleep, 417 hz, ocean waves, Rin</t>
         </is>
       </c>
-      <c r="L40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>https://youtu.be/cECOoUGLqes</t>
+        </is>
+      </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
           <t>417 Hz · dark room</t>
@@ -8213,6 +8241,7 @@
         <is>
           <t>Send this to someone who can't sleep.
 Full piece (90 min): Sleep Music · Ocean Waves · 417 Hz · Before Dawn · 90 Minutes
+https://youtu.be/cECOoUGLqes
 #sleepmusic #sleep #relaxingmusic #417hz #shorts</t>
         </is>
       </c>
@@ -8221,7 +8250,11 @@
           <t>sleep music, deep sleep, 417 hz, ocean waves, Rin</t>
         </is>
       </c>
-      <c r="L41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>https://youtu.be/cECOoUGLqes</t>
+        </is>
+      </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
           <t>417 Hz · drift off</t>
@@ -8285,6 +8318,7 @@
         <is>
           <t>Turn the brightness down and stay.
 Full piece (90 min): Sleep Music · Ocean Waves · 417 Hz · Before Dawn · 90 Minutes
+https://youtu.be/cECOoUGLqes
 #sleepmusic #sleep #relaxingmusic #417hz #shorts</t>
         </is>
       </c>
@@ -8293,7 +8327,11 @@
           <t>sleep music, deep sleep, 417 hz, ocean waves, Rin</t>
         </is>
       </c>
-      <c r="L42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>https://youtu.be/cECOoUGLqes</t>
+        </is>
+      </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
           <t>417 Hz · lights off</t>
@@ -8357,6 +8395,7 @@
         <is>
           <t>Play it as the last thing tonight.
 Full piece (90 min): Sleep Music · Ocean Waves · 417 Hz · Before Dawn · 90 Minutes
+https://youtu.be/cECOoUGLqes
 #sleepmusic #sleep #relaxingmusic #417hz #shorts</t>
         </is>
       </c>
@@ -8365,7 +8404,11 @@
           <t>sleep music, deep sleep, 417 hz, ocean waves, Rin</t>
         </is>
       </c>
-      <c r="L43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>https://youtu.be/cECOoUGLqes</t>
+        </is>
+      </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
           <t>417 Hz · deep rest</t>

--- a/08-catalogo/catalogo_canal.xlsx
+++ b/08-catalogo/catalogo_canal.xlsx
@@ -13,8 +13,8 @@
     <sheet name="Leyenda" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$Y$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Shorts'!$A$1:$S$281</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$Y$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Shorts'!$A$1:$S$288</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y41"/>
+  <dimension ref="A1:Y42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py aves 1540 audio/OBRA-009_capa.wav --semilla 555819 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-009_396_kumoi.wav audio/OBRA-009_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-009_capa.wav</t>
+          <t>python3 03-composicion/capas.py aves 1540 audio/OBRA-009_capa.wav --semilla 555819 --raiz 396 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-009_396_kumoi.wav audio/OBRA-009_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-009_capa.wav</t>
         </is>
       </c>
       <c r="U10" s="4" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py zen 1840 audio/OBRA-010_capa.wav --semilla 739461 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-010_432_hirajoshi.wav audio/OBRA-010_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-010_capa.wav</t>
+          <t>python3 03-composicion/capas.py zen 1840 audio/OBRA-010_capa.wav --semilla 739461 --raiz 432 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-010_432_hirajoshi.wav audio/OBRA-010_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-010_capa.wav</t>
         </is>
       </c>
       <c r="U11" s="4" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py aves 1240 audio/OBRA-011_capa.wav --semilla 913368 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-011_528_hirajoshi.wav audio/OBRA-011_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-011_capa.wav</t>
+          <t>python3 03-composicion/capas.py aves 1240 audio/OBRA-011_capa.wav --semilla 913368 --raiz 528 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-011_528_hirajoshi.wav audio/OBRA-011_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-011_capa.wav</t>
         </is>
       </c>
       <c r="U12" s="4" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py zen 640 audio/OBRA-012_capa.wav --semilla 43734 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-012_528_shin.wav audio/OBRA-012_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-012_capa.wav</t>
+          <t>python3 03-composicion/capas.py zen 640 audio/OBRA-012_capa.wav --semilla 43734 --raiz 528 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-012_528_shin.wav audio/OBRA-012_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-012_capa.wav</t>
         </is>
       </c>
       <c r="U13" s="4" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py aves 1240 audio/OBRA-013_capa.wav --semilla 627771 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-013_432_hirajoshi.wav audio/OBRA-013_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-013_capa.wav</t>
+          <t>python3 03-composicion/capas.py aves 1240 audio/OBRA-013_capa.wav --semilla 627771 --raiz 432 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-013_432_hirajoshi.wav audio/OBRA-013_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-013_capa.wav</t>
         </is>
       </c>
       <c r="U14" s="4" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py zen 1240 audio/OBRA-014_capa.wav --semilla 310137 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-014_528_yo.wav audio/OBRA-014_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-014_capa.wav</t>
+          <t>python3 03-composicion/capas.py zen 1240 audio/OBRA-014_capa.wav --semilla 310137 --raiz 528 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-014_528_yo.wav audio/OBRA-014_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-014_capa.wav</t>
         </is>
       </c>
       <c r="U15" s="4" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py aves 940 audio/OBRA-015_capa.wav --semilla 592463 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-015_639_yo.wav audio/OBRA-015_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-015_capa.wav</t>
+          <t>python3 03-composicion/capas.py aves 940 audio/OBRA-015_capa.wav --semilla 592463 --raiz 639 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-015_639_yo.wav audio/OBRA-015_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-015_capa.wav</t>
         </is>
       </c>
       <c r="U16" s="4" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py ancestral 1840 audio/OBRA-016_capa.wav --semilla 250697 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-016_417_kumoi.wav audio/OBRA-016_final.wav --fondo fuego --nivel-capa 0 --nivel-obra -20 --capa audio/OBRA-016_capa.wav</t>
+          <t>python3 03-composicion/capas.py ancestral 1840 audio/OBRA-016_capa.wav --semilla 250697 --raiz 417 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-016_417_kumoi.wav audio/OBRA-016_final.wav --fondo fuego --nivel-capa 0 --nivel-obra -20 --capa audio/OBRA-016_capa.wav</t>
         </is>
       </c>
       <c r="U17" s="4" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py zen 2740 audio/OBRA-017_capa.wav --semilla 714152 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-017_417_hirajoshi.wav audio/OBRA-017_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-017_capa.wav</t>
+          <t>python3 03-composicion/capas.py zen 2740 audio/OBRA-017_capa.wav --semilla 714152 --raiz 417 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-017_417_hirajoshi.wav audio/OBRA-017_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-017_capa.wav</t>
         </is>
       </c>
       <c r="U18" s="4" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py zen 2740 audio/OBRA-018_capa.wav --semilla 735455 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-018_528_hirajoshi.wav audio/OBRA-018_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-018_capa.wav</t>
+          <t>python3 03-composicion/capas.py zen 2740 audio/OBRA-018_capa.wav --semilla 735455 --raiz 528 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-018_528_hirajoshi.wav audio/OBRA-018_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-018_capa.wav</t>
         </is>
       </c>
       <c r="U19" s="4" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py zen 3640 audio/OBRA-019_capa.wav --semilla 627577 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-019_432_shin.wav audio/OBRA-019_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-019_capa.wav</t>
+          <t>python3 03-composicion/capas.py zen 3640 audio/OBRA-019_capa.wav --semilla 627577 --raiz 432 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-019_432_shin.wav audio/OBRA-019_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-019_capa.wav</t>
         </is>
       </c>
       <c r="U20" s="4" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py ancestral 1840 audio/OBRA-020_capa.wav --semilla 632595 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-020_528_shin.wav audio/OBRA-020_final.wav --fondo fuego --nivel-capa 0 --nivel-obra -20 --capa audio/OBRA-020_capa.wav</t>
+          <t>python3 03-composicion/capas.py ancestral 1840 audio/OBRA-020_capa.wav --semilla 632595 --raiz 528 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-020_528_shin.wav audio/OBRA-020_final.wav --fondo fuego --nivel-capa 0 --nivel-obra -20 --capa audio/OBRA-020_capa.wav</t>
         </is>
       </c>
       <c r="U21" s="4" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py zen 2740 audio/OBRA-021_capa.wav --semilla 864630 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-021_396_kumoi.wav audio/OBRA-021_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-021_capa.wav</t>
+          <t>python3 03-composicion/capas.py zen 2740 audio/OBRA-021_capa.wav --semilla 864630 --raiz 396 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-021_396_kumoi.wav audio/OBRA-021_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-021_capa.wav</t>
         </is>
       </c>
       <c r="U22" s="4" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py zen 3640 audio/OBRA-022_capa.wav --semilla 335798 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-022_639_yo.wav audio/OBRA-022_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-022_capa.wav</t>
+          <t>python3 03-composicion/capas.py zen 3640 audio/OBRA-022_capa.wav --semilla 335798 --raiz 639 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-022_639_yo.wav audio/OBRA-022_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-022_capa.wav</t>
         </is>
       </c>
       <c r="U23" s="4" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py zen 1240 audio/OBRA-023_capa.wav --semilla 299306 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-023_528_shin.wav audio/OBRA-023_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-023_capa.wav</t>
+          <t>python3 03-composicion/capas.py zen 1240 audio/OBRA-023_capa.wav --semilla 299306 --raiz 528 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-023_528_shin.wav audio/OBRA-023_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-023_capa.wav</t>
         </is>
       </c>
       <c r="U24" s="4" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py ancestral 3640 audio/OBRA-024_capa.wav --semilla 926202 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-024_432_kumoi.wav audio/OBRA-024_final.wav --fondo fuego --nivel-capa 0 --nivel-obra -20 --capa audio/OBRA-024_capa.wav</t>
+          <t>python3 03-composicion/capas.py ancestral 3640 audio/OBRA-024_capa.wav --semilla 926202 --raiz 432 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-024_432_kumoi.wav audio/OBRA-024_final.wav --fondo fuego --nivel-capa 0 --nivel-obra -20 --capa audio/OBRA-024_capa.wav</t>
         </is>
       </c>
       <c r="U25" s="4" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py aves 3640 audio/OBRA-025_capa.wav --semilla 454078 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-025_528_hirajoshi.wav audio/OBRA-025_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-025_capa.wav</t>
+          <t>python3 03-composicion/capas.py aves 3640 audio/OBRA-025_capa.wav --semilla 454078 --raiz 528 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-025_528_hirajoshi.wav audio/OBRA-025_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-025_capa.wav</t>
         </is>
       </c>
       <c r="U26" s="4" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py ancestral 3640 audio/OBRA-027_capa.wav --semilla 338018 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-027_396_kumoi.wav audio/OBRA-027_final.wav --fondo fuego --nivel-capa 0 --nivel-obra -20 --capa audio/OBRA-027_capa.wav</t>
+          <t>python3 03-composicion/capas.py ancestral 3640 audio/OBRA-027_capa.wav --semilla 338018 --raiz 396 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-027_396_kumoi.wav audio/OBRA-027_final.wav --fondo fuego --nivel-capa 0 --nivel-obra -20 --capa audio/OBRA-027_capa.wav</t>
         </is>
       </c>
       <c r="U28" s="4" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py zen 2740 audio/OBRA-028_capa.wav --semilla 409966 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-028_417_hirajoshi.wav audio/OBRA-028_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-028_capa.wav</t>
+          <t>python3 03-composicion/capas.py zen 2740 audio/OBRA-028_capa.wav --semilla 409966 --raiz 417 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-028_417_hirajoshi.wav audio/OBRA-028_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-028_capa.wav</t>
         </is>
       </c>
       <c r="U29" s="4" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py aves 3640 audio/OBRA-029_capa.wav --semilla 133046 --densidad 2 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-029_639_yo.wav audio/OBRA-029_final.wav --fondo selva --nivel-capa -2 --capa audio/OBRA-029_capa.wav</t>
+          <t>python3 03-composicion/capas.py aves 3640 audio/OBRA-029_capa.wav --semilla 133046 --raiz 639 --densidad 2 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-029_639_yo.wav audio/OBRA-029_final.wav --fondo selva --nivel-capa -2 --capa audio/OBRA-029_capa.wav</t>
         </is>
       </c>
       <c r="U30" s="4" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py aves 2740 audio/OBRA-030_capa.wav --semilla 244487 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-030_741_yo.wav audio/OBRA-030_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-030_capa.wav</t>
+          <t>python3 03-composicion/capas.py aves 2740 audio/OBRA-030_capa.wav --semilla 244487 --raiz 741 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-030_741_yo.wav audio/OBRA-030_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-030_capa.wav</t>
         </is>
       </c>
       <c r="U31" s="4" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py zen 2740 audio/OBRA-031_capa.wav --semilla 288169 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-031_852_hirajoshi.wav audio/OBRA-031_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-031_capa.wav</t>
+          <t>python3 03-composicion/capas.py zen 2740 audio/OBRA-031_capa.wav --semilla 288169 --raiz 852 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-031_852_hirajoshi.wav audio/OBRA-031_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-031_capa.wav</t>
         </is>
       </c>
       <c r="U32" s="4" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py aves 10840 audio/OBRA-032_capa.wav --semilla 638156 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-032_528_hirajoshi.wav audio/OBRA-032_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-032_capa.wav</t>
+          <t>python3 03-composicion/capas.py aves 10840 audio/OBRA-032_capa.wav --semilla 638156 --raiz 528 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-032_528_hirajoshi.wav audio/OBRA-032_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-032_capa.wav</t>
         </is>
       </c>
       <c r="U33" s="4" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py aves 7240 audio/OBRA-033_capa.wav --semilla 112334 --densidad 2 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-033_639_yo.wav audio/OBRA-033_final.wav --fondo selva --nivel-capa -2 --capa audio/OBRA-033_capa.wav</t>
+          <t>python3 03-composicion/capas.py aves 7240 audio/OBRA-033_capa.wav --semilla 112334 --raiz 639 --densidad 2 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-033_639_yo.wav audio/OBRA-033_final.wav --fondo selva --nivel-capa -2 --capa audio/OBRA-033_capa.wav</t>
         </is>
       </c>
       <c r="U34" s="4" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py aves 10840 audio/OBRA-034_capa.wav --semilla 249239 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-034_528_yo.wav audio/OBRA-034_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-034_capa.wav</t>
+          <t>python3 03-composicion/capas.py aves 10840 audio/OBRA-034_capa.wav --semilla 249239 --raiz 528 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-034_528_yo.wav audio/OBRA-034_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-034_capa.wav</t>
         </is>
       </c>
       <c r="U35" s="4" t="inlineStr">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py aves 7240 audio/OBRA-035_capa.wav --semilla 74636 --densidad 2 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-035_741_yo.wav audio/OBRA-035_final.wav --fondo selva --nivel-capa -2 --capa audio/OBRA-035_capa.wav</t>
+          <t>python3 03-composicion/capas.py aves 7240 audio/OBRA-035_capa.wav --semilla 74636 --raiz 741 --densidad 2 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-035_741_yo.wav audio/OBRA-035_final.wav --fondo selva --nivel-capa -2 --capa audio/OBRA-035_capa.wav</t>
         </is>
       </c>
       <c r="U36" s="4" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py aves 5440 audio/OBRA-036_capa.wav --semilla 903477 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-036_852_yo.wav audio/OBRA-036_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-036_capa.wav</t>
+          <t>python3 03-composicion/capas.py aves 5440 audio/OBRA-036_capa.wav --semilla 903477 --raiz 852 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-036_852_yo.wav audio/OBRA-036_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-036_capa.wav</t>
         </is>
       </c>
       <c r="U37" s="4" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py aves 7240 audio/OBRA-037_capa.wav --semilla 718809 --densidad 2 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-037_432_yo.wav audio/OBRA-037_final.wav --fondo selva --nivel-capa -2 --capa audio/OBRA-037_capa.wav</t>
+          <t>python3 03-composicion/capas.py aves 7240 audio/OBRA-037_capa.wav --semilla 718809 --raiz 432 --densidad 2 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-037_432_yo.wav audio/OBRA-037_final.wav --fondo selva --nivel-capa -2 --capa audio/OBRA-037_capa.wav</t>
         </is>
       </c>
       <c r="U38" s="4" t="inlineStr">
@@ -5108,7 +5108,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py aves 5440 audio/OBRA-039_capa.wav --semilla 281608 --densidad 2 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-039_639_yo.wav audio/OBRA-039_final.wav --fondo selva --nivel-capa -2 --capa audio/OBRA-039_capa.wav</t>
+          <t>python3 03-composicion/capas.py aves 5440 audio/OBRA-039_capa.wav --semilla 281608 --raiz 639 --densidad 2 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-039_639_yo.wav audio/OBRA-039_final.wav --fondo selva --nivel-capa -2 --capa audio/OBRA-039_capa.wav</t>
         </is>
       </c>
       <c r="U40" s="4" t="inlineStr">
@@ -5222,7 +5222,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py aves 10840 audio/OBRA-040_capa.wav --semilla 883876 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-040_741_yo.wav audio/OBRA-040_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-040_capa.wav</t>
+          <t>python3 03-composicion/capas.py aves 10840 audio/OBRA-040_capa.wav --semilla 883876 --raiz 741 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-040_741_yo.wav audio/OBRA-040_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-040_capa.wav</t>
         </is>
       </c>
       <c r="U41" s="4" t="inlineStr">
@@ -5238,8 +5238,122 @@
         <v/>
       </c>
     </row>
+    <row r="42" ht="58" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-041</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Music for Anxiety · Birds and Temple Bells · 432 Hz · Stop Overthinking · 1 Hour</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Música para momentos de ansiedad · Pájaros y campanas del templo · 432 Hz · Dejar de pensar · 1 hora</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Ansiedad</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>jardin</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Stop Overthinking · 1 Hour
+To accompany a pause when your mind won't stop.
+Ambience: birds and temple bells.
+Composed around a root of 432 Hz, in just intonation, hirajoshi mode.
+Breathing cycle: from 6.0 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
+Original composition, synthesized from scratch, ambience included. No third-party samples.
+Best at low volume.
+Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#relaxingmusic #meditation #432hz</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Dejar de pensar · 1 hora
+Para acompañar un momento de pausa cuando la cabeza no para.
+Ambiente: pájaros y campanas del templo.
+Compuesta con raíz en 432 Hz, en entonación justa, modo hirajoshi.
+Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#relaxingmusic #meditation #432hz</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>60 MIN</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>#relaxingmusic #meditation #432hz</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>music for anxiety, 432 hz, 432 hz music, anxiety relief, stress relief, calming music, birdsong, wind chimes, zen garden, relaxing music, meditation music, ambient music, just intonation, original composition, Rin, música para momentos de ansiedad</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr"/>
+      <c r="L42" s="4" t="inlineStr"/>
+      <c r="M42" s="2" t="n">
+        <v>432</v>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>hirajoshi</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="n">
+        <v>304617</v>
+      </c>
+      <c r="Q42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="S42" s="3" t="inlineStr">
+        <is>
+          <t>python3 03-composicion/compositor.py --minutos 60 --raiz 432 --modo hirajoshi --semilla 304617 --caracter sin-cuenco</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>python3 03-composicion/capas.py jardin 3640 audio/OBRA-041_capa.wav --semilla 304617 --raiz 432 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-041_432_hirajoshi.wav audio/OBRA-041_final.wav --fondo mar --nivel-fondo -8 --nivel-capa 0 --capa audio/OBRA-041_capa.wav</t>
+        </is>
+      </c>
+      <c r="U42" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="V42" s="4" t="inlineStr"/>
+      <c r="W42" s="4" t="inlineStr"/>
+      <c r="X42" s="4" t="inlineStr"/>
+      <c r="Y42" s="5">
+        <f>IFERROR(X42/W42*1000,"")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y41"/>
+  <autoFilter ref="A1:Y42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5250,7 +5364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S281"/>
+  <dimension ref="A1:S288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -25671,8 +25785,512 @@
       <c r="R281" s="4" t="inlineStr"/>
       <c r="S281" s="4" t="inlineStr"/>
     </row>
+    <row r="282" ht="58" customHeight="1">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-041-S1</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-041</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>short-1.mp4</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="F282" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G282" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H282" s="2" t="inlineStr">
+        <is>
+          <t>for when your mind won't stop</t>
+        </is>
+      </c>
+      <c r="I282" s="3" t="inlineStr">
+        <is>
+          <t>For when your mind won't stop · 432 Hz · Birds and Temple Bells</t>
+        </is>
+      </c>
+      <c r="J282" s="3" t="inlineStr">
+        <is>
+          <t>Save this for the next hard moment.
+Full piece (1 h): Music for Anxiety · Birds and Temple Bells · 432 Hz · Stop Overthinking · 1 Hour
+#anxietyrelief #calm #relaxingmusic #432hz #shorts</t>
+        </is>
+      </c>
+      <c r="K282" s="2" t="inlineStr">
+        <is>
+          <t>anxiety relief, calming music, 432 hz, birds and temple bells, Rin</t>
+        </is>
+      </c>
+      <c r="L282" s="2" t="inlineStr"/>
+      <c r="M282" s="2" t="inlineStr">
+        <is>
+          <t>432 Hz · calm</t>
+        </is>
+      </c>
+      <c r="N282" s="3" t="inlineStr">
+        <is>
+          <t>Save this for the next hard moment. Full 1 h piece on YouTube: Rin.
+#anxietyrelief #calm #relaxingmusic #432hz #meditation</t>
+        </is>
+      </c>
+      <c r="O282" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="P282" s="4" t="inlineStr"/>
+      <c r="Q282" s="4" t="inlineStr"/>
+      <c r="R282" s="4" t="inlineStr"/>
+      <c r="S282" s="4" t="inlineStr"/>
+    </row>
+    <row r="283" ht="58" customHeight="1">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-041-S2</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-041</t>
+        </is>
+      </c>
+      <c r="C283" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D283" s="2" t="inlineStr">
+        <is>
+          <t>short-2.mp4</t>
+        </is>
+      </c>
+      <c r="E283" s="2" t="n">
+        <v>961</v>
+      </c>
+      <c r="F283" s="2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="G283" s="2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H283" s="2" t="inlineStr">
+        <is>
+          <t>breathe out longer than you breathe in</t>
+        </is>
+      </c>
+      <c r="I283" s="3" t="inlineStr">
+        <is>
+          <t>Breathe out longer than you breathe in · 432 Hz · Birds and Temple Bells</t>
+        </is>
+      </c>
+      <c r="J283" s="3" t="inlineStr">
+        <is>
+          <t>Headphones on. Exhale slowly.
+Full piece (1 h): Music for Anxiety · Birds and Temple Bells · 432 Hz · Stop Overthinking · 1 Hour
+#anxietyrelief #calm #relaxingmusic #432hz #shorts</t>
+        </is>
+      </c>
+      <c r="K283" s="2" t="inlineStr">
+        <is>
+          <t>anxiety relief, calming music, 432 hz, birds and temple bells, Rin</t>
+        </is>
+      </c>
+      <c r="L283" s="2" t="inlineStr"/>
+      <c r="M283" s="2" t="inlineStr">
+        <is>
+          <t>432 Hz · exhale</t>
+        </is>
+      </c>
+      <c r="N283" s="3" t="inlineStr">
+        <is>
+          <t>Headphones on. Exhale slowly. Full 1 h piece on YouTube: Rin.
+#anxietyrelief #calm #relaxingmusic #432hz #meditation</t>
+        </is>
+      </c>
+      <c r="O283" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="P283" s="4" t="inlineStr"/>
+      <c r="Q283" s="4" t="inlineStr"/>
+      <c r="R283" s="4" t="inlineStr"/>
+      <c r="S283" s="4" t="inlineStr"/>
+    </row>
+    <row r="284" ht="58" customHeight="1">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-041-S3</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-041</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D284" s="2" t="inlineStr">
+        <is>
+          <t>short-3.mp4</t>
+        </is>
+      </c>
+      <c r="E284" s="2" t="n">
+        <v>1832</v>
+      </c>
+      <c r="F284" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G284" s="2" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="H284" s="2" t="inlineStr">
+        <is>
+          <t>a pause, just for you</t>
+        </is>
+      </c>
+      <c r="I284" s="3" t="inlineStr">
+        <is>
+          <t>A pause, just for you · 432 Hz · Birds and Temple Bells</t>
+        </is>
+      </c>
+      <c r="J284" s="3" t="inlineStr">
+        <is>
+          <t>Stay for one full breath.
+Full piece (1 h): Music for Anxiety · Birds and Temple Bells · 432 Hz · Stop Overthinking · 1 Hour
+#anxietyrelief #calm #relaxingmusic #432hz #shorts</t>
+        </is>
+      </c>
+      <c r="K284" s="2" t="inlineStr">
+        <is>
+          <t>anxiety relief, calming music, 432 hz, birds and temple bells, Rin</t>
+        </is>
+      </c>
+      <c r="L284" s="2" t="inlineStr"/>
+      <c r="M284" s="2" t="inlineStr">
+        <is>
+          <t>432 Hz · pause</t>
+        </is>
+      </c>
+      <c r="N284" s="3" t="inlineStr">
+        <is>
+          <t>Stay for one full breath. Full 1 h piece on YouTube: Rin.
+#anxietyrelief #calm #relaxingmusic #432hz #meditation</t>
+        </is>
+      </c>
+      <c r="O284" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="P284" s="4" t="inlineStr"/>
+      <c r="Q284" s="4" t="inlineStr"/>
+      <c r="R284" s="4" t="inlineStr"/>
+      <c r="S284" s="4" t="inlineStr"/>
+    </row>
+    <row r="285" ht="58" customHeight="1">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-041-S4</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-041</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D285" s="2" t="inlineStr">
+        <is>
+          <t>short-4.mp4</t>
+        </is>
+      </c>
+      <c r="E285" s="2" t="n">
+        <v>2704</v>
+      </c>
+      <c r="F285" s="2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="G285" s="2" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="H285" s="2" t="inlineStr">
+        <is>
+          <t>slow down, one breath at a time</t>
+        </is>
+      </c>
+      <c r="I285" s="3" t="inlineStr">
+        <is>
+          <t>Slow down, one breath at a time · 432 Hz · Birds and Temple Bells</t>
+        </is>
+      </c>
+      <c r="J285" s="3" t="inlineStr">
+        <is>
+          <t>A small pause in the middle of the day.
+Full piece (1 h): Music for Anxiety · Birds and Temple Bells · 432 Hz · Stop Overthinking · 1 Hour
+#anxietyrelief #calm #relaxingmusic #432hz #shorts</t>
+        </is>
+      </c>
+      <c r="K285" s="2" t="inlineStr">
+        <is>
+          <t>anxiety relief, calming music, 432 hz, birds and temple bells, Rin</t>
+        </is>
+      </c>
+      <c r="L285" s="2" t="inlineStr"/>
+      <c r="M285" s="2" t="inlineStr">
+        <is>
+          <t>432 Hz · breathe</t>
+        </is>
+      </c>
+      <c r="N285" s="3" t="inlineStr">
+        <is>
+          <t>A small pause in the middle of the day. Full 1 h piece on YouTube: Rin.
+#anxietyrelief #calm #relaxingmusic #432hz #meditation</t>
+        </is>
+      </c>
+      <c r="O285" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="P285" s="4" t="inlineStr"/>
+      <c r="Q285" s="4" t="inlineStr"/>
+      <c r="R285" s="4" t="inlineStr"/>
+      <c r="S285" s="4" t="inlineStr"/>
+    </row>
+    <row r="286" ht="58" customHeight="1">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-041-S5</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-041</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D286" s="2" t="inlineStr">
+        <is>
+          <t>short-5.mp4</t>
+        </is>
+      </c>
+      <c r="E286" s="2" t="n">
+        <v>3575</v>
+      </c>
+      <c r="F286" s="2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="G286" s="2" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="H286" s="2" t="inlineStr">
+        <is>
+          <t>before you begin</t>
+        </is>
+      </c>
+      <c r="I286" s="3" t="inlineStr">
+        <is>
+          <t>Before you begin · 432 Hz · Birds and Temple Bells</t>
+        </is>
+      </c>
+      <c r="J286" s="3" t="inlineStr">
+        <is>
+          <t>Send this to someone who needs a pause.
+Full piece (1 h): Music for Anxiety · Birds and Temple Bells · 432 Hz · Stop Overthinking · 1 Hour
+#anxietyrelief #calm #relaxingmusic #432hz #shorts</t>
+        </is>
+      </c>
+      <c r="K286" s="2" t="inlineStr">
+        <is>
+          <t>anxiety relief, calming music, 432 hz, birds and temple bells, Rin</t>
+        </is>
+      </c>
+      <c r="L286" s="2" t="inlineStr"/>
+      <c r="M286" s="2" t="inlineStr">
+        <is>
+          <t>432 Hz · slow down</t>
+        </is>
+      </c>
+      <c r="N286" s="3" t="inlineStr">
+        <is>
+          <t>Send this to someone who needs a pause. Full 1 h piece on YouTube: Rin.
+#anxietyrelief #calm #relaxingmusic #432hz #meditation</t>
+        </is>
+      </c>
+      <c r="O286" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="P286" s="4" t="inlineStr"/>
+      <c r="Q286" s="4" t="inlineStr"/>
+      <c r="R286" s="4" t="inlineStr"/>
+      <c r="S286" s="4" t="inlineStr"/>
+    </row>
+    <row r="287" ht="58" customHeight="1">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-041-S6</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-041</t>
+        </is>
+      </c>
+      <c r="C287" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D287" s="2" t="inlineStr">
+        <is>
+          <t>short-6.mp4</t>
+        </is>
+      </c>
+      <c r="E287" s="2" t="n">
+        <v>526</v>
+      </c>
+      <c r="F287" s="2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="G287" s="2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H287" s="2" t="inlineStr">
+        <is>
+          <t>you can put it down for now</t>
+        </is>
+      </c>
+      <c r="I287" s="3" t="inlineStr">
+        <is>
+          <t>You can put it down for now · 432 Hz · Birds and Temple Bells</t>
+        </is>
+      </c>
+      <c r="J287" s="3" t="inlineStr">
+        <is>
+          <t>Breathe with the sound for a moment.
+Full piece (1 h): Music for Anxiety · Birds and Temple Bells · 432 Hz · Stop Overthinking · 1 Hour
+#anxietyrelief #calm #relaxingmusic #432hz #shorts</t>
+        </is>
+      </c>
+      <c r="K287" s="2" t="inlineStr">
+        <is>
+          <t>anxiety relief, calming music, 432 hz, birds and temple bells, Rin</t>
+        </is>
+      </c>
+      <c r="L287" s="2" t="inlineStr"/>
+      <c r="M287" s="2" t="inlineStr">
+        <is>
+          <t>432 Hz · let go</t>
+        </is>
+      </c>
+      <c r="N287" s="3" t="inlineStr">
+        <is>
+          <t>Breathe with the sound for a moment. Full 1 h piece on YouTube: Rin.
+#anxietyrelief #calm #relaxingmusic #432hz #meditation</t>
+        </is>
+      </c>
+      <c r="O287" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="P287" s="4" t="inlineStr"/>
+      <c r="Q287" s="4" t="inlineStr"/>
+      <c r="R287" s="4" t="inlineStr"/>
+      <c r="S287" s="4" t="inlineStr"/>
+    </row>
+    <row r="288" ht="58" customHeight="1">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-041-S7</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-041</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D288" s="2" t="inlineStr">
+        <is>
+          <t>short-7.mp4</t>
+        </is>
+      </c>
+      <c r="E288" s="2" t="n">
+        <v>2268</v>
+      </c>
+      <c r="F288" s="2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G288" s="2" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="H288" s="2" t="inlineStr">
+        <is>
+          <t>one minute of quiet</t>
+        </is>
+      </c>
+      <c r="I288" s="3" t="inlineStr">
+        <is>
+          <t>One minute of quiet · 432 Hz · Birds and Temple Bells</t>
+        </is>
+      </c>
+      <c r="J288" s="3" t="inlineStr">
+        <is>
+          <t>Come back to this when you need it.
+Full piece (1 h): Music for Anxiety · Birds and Temple Bells · 432 Hz · Stop Overthinking · 1 Hour
+#anxietyrelief #calm #relaxingmusic #432hz #shorts</t>
+        </is>
+      </c>
+      <c r="K288" s="2" t="inlineStr">
+        <is>
+          <t>anxiety relief, calming music, 432 hz, birds and temple bells, Rin</t>
+        </is>
+      </c>
+      <c r="L288" s="2" t="inlineStr"/>
+      <c r="M288" s="2" t="inlineStr">
+        <is>
+          <t>432 Hz · quiet</t>
+        </is>
+      </c>
+      <c r="N288" s="3" t="inlineStr">
+        <is>
+          <t>Come back to this when you need it. Full 1 h piece on YouTube: Rin.
+#anxietyrelief #calm #relaxingmusic #432hz #meditation</t>
+        </is>
+      </c>
+      <c r="O288" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="P288" s="4" t="inlineStr"/>
+      <c r="Q288" s="4" t="inlineStr"/>
+      <c r="R288" s="4" t="inlineStr"/>
+      <c r="S288" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S281"/>
+  <autoFilter ref="A1:S288"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -25707,7 +26325,7 @@
         </is>
       </c>
       <c r="B2" s="7">
-        <f>COUNTA(Catálogo!A2:A41)</f>
+        <f>COUNTA(Catálogo!A2:A42)</f>
         <v/>
       </c>
     </row>
@@ -25718,7 +26336,7 @@
         </is>
       </c>
       <c r="B3" s="7">
-        <f>COUNTIF(Catálogo!U2:U41,"pendiente")</f>
+        <f>COUNTIF(Catálogo!U2:U42,"pendiente")</f>
         <v/>
       </c>
     </row>
@@ -25729,7 +26347,7 @@
         </is>
       </c>
       <c r="B4" s="7">
-        <f>COUNTIF(Catálogo!U2:U41,"compuesta")</f>
+        <f>COUNTIF(Catálogo!U2:U42,"compuesta")</f>
         <v/>
       </c>
     </row>
@@ -25740,7 +26358,7 @@
         </is>
       </c>
       <c r="B5" s="7">
-        <f>COUNTIF(Catálogo!U2:U41,"montada")</f>
+        <f>COUNTIF(Catálogo!U2:U42,"montada")</f>
         <v/>
       </c>
     </row>
@@ -25751,7 +26369,7 @@
         </is>
       </c>
       <c r="B6" s="7">
-        <f>COUNTIF(Catálogo!U2:U41,"publicada")</f>
+        <f>COUNTIF(Catálogo!U2:U42,"publicada")</f>
         <v/>
       </c>
     </row>
@@ -25791,15 +26409,15 @@
         </is>
       </c>
       <c r="B10" s="7">
-        <f>COUNTIF(Catálogo!D2:D41,A10)</f>
+        <f>COUNTIF(Catálogo!D2:D42,A10)</f>
         <v/>
       </c>
       <c r="C10" s="7">
-        <f>COUNTIFS(Catálogo!D2:D41,A10,Catálogo!U2:U41,"publicada")</f>
+        <f>COUNTIFS(Catálogo!D2:D42,A10,Catálogo!U2:U42,"publicada")</f>
         <v/>
       </c>
       <c r="D10" s="7">
-        <f>SUMIF(Catálogo!D2:D41,A10,Catálogo!R2:R41)</f>
+        <f>SUMIF(Catálogo!D2:D42,A10,Catálogo!R2:R42)</f>
         <v/>
       </c>
     </row>
@@ -25810,15 +26428,15 @@
         </is>
       </c>
       <c r="B11" s="7">
-        <f>COUNTIF(Catálogo!D2:D41,A11)</f>
+        <f>COUNTIF(Catálogo!D2:D42,A11)</f>
         <v/>
       </c>
       <c r="C11" s="7">
-        <f>COUNTIFS(Catálogo!D2:D41,A11,Catálogo!U2:U41,"publicada")</f>
+        <f>COUNTIFS(Catálogo!D2:D42,A11,Catálogo!U2:U42,"publicada")</f>
         <v/>
       </c>
       <c r="D11" s="7">
-        <f>SUMIF(Catálogo!D2:D41,A11,Catálogo!R2:R41)</f>
+        <f>SUMIF(Catálogo!D2:D42,A11,Catálogo!R2:R42)</f>
         <v/>
       </c>
     </row>
@@ -25829,15 +26447,15 @@
         </is>
       </c>
       <c r="B12" s="7">
-        <f>COUNTIF(Catálogo!D2:D41,A12)</f>
+        <f>COUNTIF(Catálogo!D2:D42,A12)</f>
         <v/>
       </c>
       <c r="C12" s="7">
-        <f>COUNTIFS(Catálogo!D2:D41,A12,Catálogo!U2:U41,"publicada")</f>
+        <f>COUNTIFS(Catálogo!D2:D42,A12,Catálogo!U2:U42,"publicada")</f>
         <v/>
       </c>
       <c r="D12" s="7">
-        <f>SUMIF(Catálogo!D2:D41,A12,Catálogo!R2:R41)</f>
+        <f>SUMIF(Catálogo!D2:D42,A12,Catálogo!R2:R42)</f>
         <v/>
       </c>
     </row>
@@ -25848,15 +26466,15 @@
         </is>
       </c>
       <c r="B13" s="7">
-        <f>COUNTIF(Catálogo!D2:D41,A13)</f>
+        <f>COUNTIF(Catálogo!D2:D42,A13)</f>
         <v/>
       </c>
       <c r="C13" s="7">
-        <f>COUNTIFS(Catálogo!D2:D41,A13,Catálogo!U2:U41,"publicada")</f>
+        <f>COUNTIFS(Catálogo!D2:D42,A13,Catálogo!U2:U42,"publicada")</f>
         <v/>
       </c>
       <c r="D13" s="7">
-        <f>SUMIF(Catálogo!D2:D41,A13,Catálogo!R2:R41)</f>
+        <f>SUMIF(Catálogo!D2:D42,A13,Catálogo!R2:R42)</f>
         <v/>
       </c>
     </row>
@@ -25867,15 +26485,15 @@
         </is>
       </c>
       <c r="B14" s="7">
-        <f>COUNTIF(Catálogo!D2:D41,A14)</f>
+        <f>COUNTIF(Catálogo!D2:D42,A14)</f>
         <v/>
       </c>
       <c r="C14" s="7">
-        <f>COUNTIFS(Catálogo!D2:D41,A14,Catálogo!U2:U41,"publicada")</f>
+        <f>COUNTIFS(Catálogo!D2:D42,A14,Catálogo!U2:U42,"publicada")</f>
         <v/>
       </c>
       <c r="D14" s="7">
-        <f>SUMIF(Catálogo!D2:D41,A14,Catálogo!R2:R41)</f>
+        <f>SUMIF(Catálogo!D2:D42,A14,Catálogo!R2:R42)</f>
         <v/>
       </c>
     </row>
@@ -25912,7 +26530,7 @@
         </is>
       </c>
       <c r="B18" s="7">
-        <f>SUM(Catálogo!W2:W41)</f>
+        <f>SUM(Catálogo!W2:W42)</f>
         <v/>
       </c>
     </row>
@@ -25923,7 +26541,7 @@
         </is>
       </c>
       <c r="B19" s="7">
-        <f>SUM(Catálogo!X2:X41)</f>
+        <f>SUM(Catálogo!X2:X42)</f>
         <v/>
       </c>
     </row>
@@ -26066,7 +26684,7 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Ambiente aprobado en escucha: mar, mar-aves, zen, selva o lluvia-tambor.</t>
+          <t>Ambiente aprobado en escucha: mar, mar-aves, zen, selva, lluvia-tambor o jardin.</t>
         </is>
       </c>
     </row>

--- a/08-catalogo/catalogo_canal.xlsx
+++ b/08-catalogo/catalogo_canal.xlsx
@@ -13,8 +13,8 @@
     <sheet name="Leyenda" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$Y$42</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Shorts'!$A$1:$S$288</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$Y$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Shorts'!$A$1:$S$295</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y42"/>
+  <dimension ref="A1:Y43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Music for Anxiety · Birds and Temple Bells · 432 Hz · Stop Overthinking · 1 Hour</t>
+          <t>Stop Overthinking 🌿 Calming Music for Anxiety · Birdsong &amp; Temple Bells · 432 Hz · 1 Hour</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -5266,15 +5266,12 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Stop Overthinking · 1 Hour
-To accompany a pause when your mind won't stop.
-Ambience: birds and temple bells.
-Composed around a root of 432 Hz, in just intonation, hirajoshi mode.
-Breathing cycle: from 6.0 down to 4.5 breaths per minute, 40 % inhale / 60 % exhale.
-Original composition, synthesized from scratch, ambience included. No third-party samples.
-Best at low volume.
-Subscribe for new pieces: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
-#relaxingmusic #meditation #432hz</t>
+          <t>One hour to stop overthinking. Calming music for anxiety with birdsong and soft temple bells, and a slower breath.
+The music slows from 6 to 4.5 breaths per minute: breathe out longer than you breathe in, and let it lead.
+🎧 Headphones, low volume. You don't have to solve anything tonight. Just listen.
+🌿 Subscribe for a new calm piece every week: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+Original composition by Rin, synthesized from scratch in just intonation around 432 Hz, hirajoshi mode. No samples.
+#calmingmusic #musicforanxiety #432hz</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5297,16 +5294,20 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>#relaxingmusic #meditation #432hz</t>
+          <t>#calmingmusic #musicforanxiety #432hz</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>music for anxiety, 432 hz, 432 hz music, anxiety relief, stress relief, calming music, birdsong, wind chimes, zen garden, relaxing music, meditation music, ambient music, just intonation, original composition, Rin, música para momentos de ansiedad</t>
+          <t>stop overthinking, stop overthinking music, calming music, music for anxiety, calming music for anxiety, anxiety relief, stress relief music, calm your nervous system, nervous system regulation, relaxing music, meditation music, calm music, birdsong, birds singing, temple bells, wind chimes, zen garden, 432 hz, 432 hz music, rin, música para la ansiedad</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr"/>
-      <c r="L42" s="4" t="inlineStr"/>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/LRXFSFZO_uI</t>
+        </is>
+      </c>
       <c r="M42" s="2" t="n">
         <v>432</v>
       </c>
@@ -5341,10 +5342,14 @@
       </c>
       <c r="U42" s="4" t="inlineStr">
         <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="V42" s="4" t="inlineStr"/>
+          <t>publicada</t>
+        </is>
+      </c>
+      <c r="V42" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
       <c r="W42" s="4" t="inlineStr"/>
       <c r="X42" s="4" t="inlineStr"/>
       <c r="Y42" s="5">
@@ -5352,8 +5357,119 @@
         <v/>
       </c>
     </row>
+    <row r="43" ht="58" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-042</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Calm Your Nervous System 🌿 Zen Temple Bells · 528 Hz · Music for Anxiety &amp; Sleep · 3 Hours</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Música para momentos de ansiedad · Templo zen · 528 Hz · Calmar el sistema nervioso · 3 horas</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Ansiedad</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>zen</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Three hours of calm for an anxious mind and a restless night. Soft zen temple bells over a warm, steady drone.
+The music slows from 6 to 4.5 breaths per minute: breathe out longer than you breathe in, and let your body follow.
+🌙 Play it low while you rest, read, work or fall asleep.
+🌿 Subscribe for a new calm piece every week: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+Original composition by Rin, synthesized from scratch in just intonation around 528 Hz, shin mode. No samples.
+#calmingmusic #sleepmusic #528hz</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Calmar el sistema nervioso · 3 horas
+Para acompañar un momento de pausa cuando la cabeza no para.
+Ambiente: templo zen.
+Compuesta con raíz en 528 Hz, en entonación justa, modo shin.
+Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#relaxingmusic #meditation #528hz</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>180 MIN</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>#calmingmusic #sleepmusic #528hz</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>calm your nervous system, nervous system regulation, calming music, music for anxiety, anxiety relief, sleep music, meditation for sleep, deep sleep music, stress relief music, zen music, zen temple, temple bells, 528 hz, 528 hz music, relaxing music, meditation music, 3 hours, rin, música para la ansiedad</t>
+        </is>
+      </c>
+      <c r="K43" s="4" t="inlineStr"/>
+      <c r="L43" s="4" t="inlineStr"/>
+      <c r="M43" s="2" t="n">
+        <v>528</v>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>shin</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="n">
+        <v>266691</v>
+      </c>
+      <c r="Q43" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="R43" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t>python3 03-composicion/compositor.py --minutos 180 --raiz 528 --modo shin --semilla 266691 --caracter sin-cuenco</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>python3 03-composicion/capas.py zen 10840 audio/OBRA-042_capa.wav --semilla 266691 --raiz 528 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-042_528_shin.wav audio/OBRA-042_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-042_capa.wav</t>
+        </is>
+      </c>
+      <c r="U43" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="V43" s="4" t="inlineStr"/>
+      <c r="W43" s="4" t="inlineStr"/>
+      <c r="X43" s="4" t="inlineStr"/>
+      <c r="Y43" s="5">
+        <f>IFERROR(X43/W43*1000,"")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y42"/>
+  <autoFilter ref="A1:Y43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5364,7 +5480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S288"/>
+  <dimension ref="A1:S295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -25826,7 +25942,8 @@
       <c r="J282" s="3" t="inlineStr">
         <is>
           <t>Save this for the next hard moment.
-Full piece (1 h): Music for Anxiety · Birds and Temple Bells · 432 Hz · Stop Overthinking · 1 Hour
+Full piece (1 h): Stop Overthinking 🌿 Calming Music for Anxiety · Birdsong &amp; Temple Bells · 432 Hz · 1 Hour
+https://youtu.be/LRXFSFZO_uI
 #anxietyrelief #calm #relaxingmusic #432hz #shorts</t>
         </is>
       </c>
@@ -25835,7 +25952,11 @@
           <t>anxiety relief, calming music, 432 hz, birds and temple bells, Rin</t>
         </is>
       </c>
-      <c r="L282" s="2" t="inlineStr"/>
+      <c r="L282" s="2" t="inlineStr">
+        <is>
+          <t>https://youtu.be/LRXFSFZO_uI</t>
+        </is>
+      </c>
       <c r="M282" s="2" t="inlineStr">
         <is>
           <t>432 Hz · calm</t>
@@ -25898,7 +26019,8 @@
       <c r="J283" s="3" t="inlineStr">
         <is>
           <t>Headphones on. Exhale slowly.
-Full piece (1 h): Music for Anxiety · Birds and Temple Bells · 432 Hz · Stop Overthinking · 1 Hour
+Full piece (1 h): Stop Overthinking 🌿 Calming Music for Anxiety · Birdsong &amp; Temple Bells · 432 Hz · 1 Hour
+https://youtu.be/LRXFSFZO_uI
 #anxietyrelief #calm #relaxingmusic #432hz #shorts</t>
         </is>
       </c>
@@ -25907,7 +26029,11 @@
           <t>anxiety relief, calming music, 432 hz, birds and temple bells, Rin</t>
         </is>
       </c>
-      <c r="L283" s="2" t="inlineStr"/>
+      <c r="L283" s="2" t="inlineStr">
+        <is>
+          <t>https://youtu.be/LRXFSFZO_uI</t>
+        </is>
+      </c>
       <c r="M283" s="2" t="inlineStr">
         <is>
           <t>432 Hz · exhale</t>
@@ -25970,7 +26096,8 @@
       <c r="J284" s="3" t="inlineStr">
         <is>
           <t>Stay for one full breath.
-Full piece (1 h): Music for Anxiety · Birds and Temple Bells · 432 Hz · Stop Overthinking · 1 Hour
+Full piece (1 h): Stop Overthinking 🌿 Calming Music for Anxiety · Birdsong &amp; Temple Bells · 432 Hz · 1 Hour
+https://youtu.be/LRXFSFZO_uI
 #anxietyrelief #calm #relaxingmusic #432hz #shorts</t>
         </is>
       </c>
@@ -25979,7 +26106,11 @@
           <t>anxiety relief, calming music, 432 hz, birds and temple bells, Rin</t>
         </is>
       </c>
-      <c r="L284" s="2" t="inlineStr"/>
+      <c r="L284" s="2" t="inlineStr">
+        <is>
+          <t>https://youtu.be/LRXFSFZO_uI</t>
+        </is>
+      </c>
       <c r="M284" s="2" t="inlineStr">
         <is>
           <t>432 Hz · pause</t>
@@ -26042,7 +26173,8 @@
       <c r="J285" s="3" t="inlineStr">
         <is>
           <t>A small pause in the middle of the day.
-Full piece (1 h): Music for Anxiety · Birds and Temple Bells · 432 Hz · Stop Overthinking · 1 Hour
+Full piece (1 h): Stop Overthinking 🌿 Calming Music for Anxiety · Birdsong &amp; Temple Bells · 432 Hz · 1 Hour
+https://youtu.be/LRXFSFZO_uI
 #anxietyrelief #calm #relaxingmusic #432hz #shorts</t>
         </is>
       </c>
@@ -26051,7 +26183,11 @@
           <t>anxiety relief, calming music, 432 hz, birds and temple bells, Rin</t>
         </is>
       </c>
-      <c r="L285" s="2" t="inlineStr"/>
+      <c r="L285" s="2" t="inlineStr">
+        <is>
+          <t>https://youtu.be/LRXFSFZO_uI</t>
+        </is>
+      </c>
       <c r="M285" s="2" t="inlineStr">
         <is>
           <t>432 Hz · breathe</t>
@@ -26114,7 +26250,8 @@
       <c r="J286" s="3" t="inlineStr">
         <is>
           <t>Send this to someone who needs a pause.
-Full piece (1 h): Music for Anxiety · Birds and Temple Bells · 432 Hz · Stop Overthinking · 1 Hour
+Full piece (1 h): Stop Overthinking 🌿 Calming Music for Anxiety · Birdsong &amp; Temple Bells · 432 Hz · 1 Hour
+https://youtu.be/LRXFSFZO_uI
 #anxietyrelief #calm #relaxingmusic #432hz #shorts</t>
         </is>
       </c>
@@ -26123,7 +26260,11 @@
           <t>anxiety relief, calming music, 432 hz, birds and temple bells, Rin</t>
         </is>
       </c>
-      <c r="L286" s="2" t="inlineStr"/>
+      <c r="L286" s="2" t="inlineStr">
+        <is>
+          <t>https://youtu.be/LRXFSFZO_uI</t>
+        </is>
+      </c>
       <c r="M286" s="2" t="inlineStr">
         <is>
           <t>432 Hz · slow down</t>
@@ -26186,7 +26327,8 @@
       <c r="J287" s="3" t="inlineStr">
         <is>
           <t>Breathe with the sound for a moment.
-Full piece (1 h): Music for Anxiety · Birds and Temple Bells · 432 Hz · Stop Overthinking · 1 Hour
+Full piece (1 h): Stop Overthinking 🌿 Calming Music for Anxiety · Birdsong &amp; Temple Bells · 432 Hz · 1 Hour
+https://youtu.be/LRXFSFZO_uI
 #anxietyrelief #calm #relaxingmusic #432hz #shorts</t>
         </is>
       </c>
@@ -26195,7 +26337,11 @@
           <t>anxiety relief, calming music, 432 hz, birds and temple bells, Rin</t>
         </is>
       </c>
-      <c r="L287" s="2" t="inlineStr"/>
+      <c r="L287" s="2" t="inlineStr">
+        <is>
+          <t>https://youtu.be/LRXFSFZO_uI</t>
+        </is>
+      </c>
       <c r="M287" s="2" t="inlineStr">
         <is>
           <t>432 Hz · let go</t>
@@ -26258,7 +26404,8 @@
       <c r="J288" s="3" t="inlineStr">
         <is>
           <t>Come back to this when you need it.
-Full piece (1 h): Music for Anxiety · Birds and Temple Bells · 432 Hz · Stop Overthinking · 1 Hour
+Full piece (1 h): Stop Overthinking 🌿 Calming Music for Anxiety · Birdsong &amp; Temple Bells · 432 Hz · 1 Hour
+https://youtu.be/LRXFSFZO_uI
 #anxietyrelief #calm #relaxingmusic #432hz #shorts</t>
         </is>
       </c>
@@ -26267,7 +26414,11 @@
           <t>anxiety relief, calming music, 432 hz, birds and temple bells, Rin</t>
         </is>
       </c>
-      <c r="L288" s="2" t="inlineStr"/>
+      <c r="L288" s="2" t="inlineStr">
+        <is>
+          <t>https://youtu.be/LRXFSFZO_uI</t>
+        </is>
+      </c>
       <c r="M288" s="2" t="inlineStr">
         <is>
           <t>432 Hz · quiet</t>
@@ -26289,8 +26440,512 @@
       <c r="R288" s="4" t="inlineStr"/>
       <c r="S288" s="4" t="inlineStr"/>
     </row>
+    <row r="289" ht="58" customHeight="1">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-042-S1</t>
+        </is>
+      </c>
+      <c r="B289" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-042</t>
+        </is>
+      </c>
+      <c r="C289" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D289" s="2" t="inlineStr">
+        <is>
+          <t>short-1.mp4</t>
+        </is>
+      </c>
+      <c r="E289" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="F289" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G289" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H289" s="2" t="inlineStr">
+        <is>
+          <t>for when your mind won't stop</t>
+        </is>
+      </c>
+      <c r="I289" s="3" t="inlineStr">
+        <is>
+          <t>For when your mind won't stop · 528 Hz · Zen Temple</t>
+        </is>
+      </c>
+      <c r="J289" s="3" t="inlineStr">
+        <is>
+          <t>Save this for the next hard moment.
+Full piece (3 h): Calm Your Nervous System 🌿 Zen Temple Bells · 528 Hz · Music for Anxiety &amp; Sleep · 3 Hours
+#anxietyrelief #calm #relaxingmusic #528hz #shorts</t>
+        </is>
+      </c>
+      <c r="K289" s="2" t="inlineStr">
+        <is>
+          <t>anxiety relief, calming music, 528 hz, zen temple, Rin</t>
+        </is>
+      </c>
+      <c r="L289" s="2" t="inlineStr"/>
+      <c r="M289" s="2" t="inlineStr">
+        <is>
+          <t>528 Hz · calm</t>
+        </is>
+      </c>
+      <c r="N289" s="3" t="inlineStr">
+        <is>
+          <t>Save this for the next hard moment. Full 3 h piece on YouTube: Rin.
+#anxietyrelief #calm #relaxingmusic #528hz #meditation</t>
+        </is>
+      </c>
+      <c r="O289" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="P289" s="4" t="inlineStr"/>
+      <c r="Q289" s="4" t="inlineStr"/>
+      <c r="R289" s="4" t="inlineStr"/>
+      <c r="S289" s="4" t="inlineStr"/>
+    </row>
+    <row r="290" ht="58" customHeight="1">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-042-S2</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-042</t>
+        </is>
+      </c>
+      <c r="C290" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D290" s="2" t="inlineStr">
+        <is>
+          <t>short-2.mp4</t>
+        </is>
+      </c>
+      <c r="E290" s="2" t="n">
+        <v>2761</v>
+      </c>
+      <c r="F290" s="2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="G290" s="2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H290" s="2" t="inlineStr">
+        <is>
+          <t>breathe out longer than you breathe in</t>
+        </is>
+      </c>
+      <c r="I290" s="3" t="inlineStr">
+        <is>
+          <t>Breathe out longer than you breathe in · 528 Hz · Zen Temple</t>
+        </is>
+      </c>
+      <c r="J290" s="3" t="inlineStr">
+        <is>
+          <t>Headphones on. Exhale slowly.
+Full piece (3 h): Calm Your Nervous System 🌿 Zen Temple Bells · 528 Hz · Music for Anxiety &amp; Sleep · 3 Hours
+#anxietyrelief #calm #relaxingmusic #528hz #shorts</t>
+        </is>
+      </c>
+      <c r="K290" s="2" t="inlineStr">
+        <is>
+          <t>anxiety relief, calming music, 528 hz, zen temple, Rin</t>
+        </is>
+      </c>
+      <c r="L290" s="2" t="inlineStr"/>
+      <c r="M290" s="2" t="inlineStr">
+        <is>
+          <t>528 Hz · exhale</t>
+        </is>
+      </c>
+      <c r="N290" s="3" t="inlineStr">
+        <is>
+          <t>Headphones on. Exhale slowly. Full 3 h piece on YouTube: Rin.
+#anxietyrelief #calm #relaxingmusic #528hz #meditation</t>
+        </is>
+      </c>
+      <c r="O290" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="P290" s="4" t="inlineStr"/>
+      <c r="Q290" s="4" t="inlineStr"/>
+      <c r="R290" s="4" t="inlineStr"/>
+      <c r="S290" s="4" t="inlineStr"/>
+    </row>
+    <row r="291" ht="58" customHeight="1">
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-042-S3</t>
+        </is>
+      </c>
+      <c r="B291" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-042</t>
+        </is>
+      </c>
+      <c r="C291" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D291" s="2" t="inlineStr">
+        <is>
+          <t>short-3.mp4</t>
+        </is>
+      </c>
+      <c r="E291" s="2" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F291" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G291" s="2" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="H291" s="2" t="inlineStr">
+        <is>
+          <t>a pause, just for you</t>
+        </is>
+      </c>
+      <c r="I291" s="3" t="inlineStr">
+        <is>
+          <t>A pause, just for you · 528 Hz · Zen Temple</t>
+        </is>
+      </c>
+      <c r="J291" s="3" t="inlineStr">
+        <is>
+          <t>Stay for one full breath.
+Full piece (3 h): Calm Your Nervous System 🌿 Zen Temple Bells · 528 Hz · Music for Anxiety &amp; Sleep · 3 Hours
+#anxietyrelief #calm #relaxingmusic #528hz #shorts</t>
+        </is>
+      </c>
+      <c r="K291" s="2" t="inlineStr">
+        <is>
+          <t>anxiety relief, calming music, 528 hz, zen temple, Rin</t>
+        </is>
+      </c>
+      <c r="L291" s="2" t="inlineStr"/>
+      <c r="M291" s="2" t="inlineStr">
+        <is>
+          <t>528 Hz · pause</t>
+        </is>
+      </c>
+      <c r="N291" s="3" t="inlineStr">
+        <is>
+          <t>Stay for one full breath. Full 3 h piece on YouTube: Rin.
+#anxietyrelief #calm #relaxingmusic #528hz #meditation</t>
+        </is>
+      </c>
+      <c r="O291" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="P291" s="4" t="inlineStr"/>
+      <c r="Q291" s="4" t="inlineStr"/>
+      <c r="R291" s="4" t="inlineStr"/>
+      <c r="S291" s="4" t="inlineStr"/>
+    </row>
+    <row r="292" ht="58" customHeight="1">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-042-S4</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-042</t>
+        </is>
+      </c>
+      <c r="C292" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D292" s="2" t="inlineStr">
+        <is>
+          <t>short-4.mp4</t>
+        </is>
+      </c>
+      <c r="E292" s="2" t="n">
+        <v>8104</v>
+      </c>
+      <c r="F292" s="2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="G292" s="2" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="H292" s="2" t="inlineStr">
+        <is>
+          <t>slow down, one breath at a time</t>
+        </is>
+      </c>
+      <c r="I292" s="3" t="inlineStr">
+        <is>
+          <t>Slow down, one breath at a time · 528 Hz · Zen Temple</t>
+        </is>
+      </c>
+      <c r="J292" s="3" t="inlineStr">
+        <is>
+          <t>A small pause in the middle of the day.
+Full piece (3 h): Calm Your Nervous System 🌿 Zen Temple Bells · 528 Hz · Music for Anxiety &amp; Sleep · 3 Hours
+#anxietyrelief #calm #relaxingmusic #528hz #shorts</t>
+        </is>
+      </c>
+      <c r="K292" s="2" t="inlineStr">
+        <is>
+          <t>anxiety relief, calming music, 528 hz, zen temple, Rin</t>
+        </is>
+      </c>
+      <c r="L292" s="2" t="inlineStr"/>
+      <c r="M292" s="2" t="inlineStr">
+        <is>
+          <t>528 Hz · breathe</t>
+        </is>
+      </c>
+      <c r="N292" s="3" t="inlineStr">
+        <is>
+          <t>A small pause in the middle of the day. Full 3 h piece on YouTube: Rin.
+#anxietyrelief #calm #relaxingmusic #528hz #meditation</t>
+        </is>
+      </c>
+      <c r="O292" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="P292" s="4" t="inlineStr"/>
+      <c r="Q292" s="4" t="inlineStr"/>
+      <c r="R292" s="4" t="inlineStr"/>
+      <c r="S292" s="4" t="inlineStr"/>
+    </row>
+    <row r="293" ht="58" customHeight="1">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-042-S5</t>
+        </is>
+      </c>
+      <c r="B293" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-042</t>
+        </is>
+      </c>
+      <c r="C293" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D293" s="2" t="inlineStr">
+        <is>
+          <t>short-5.mp4</t>
+        </is>
+      </c>
+      <c r="E293" s="2" t="n">
+        <v>10775</v>
+      </c>
+      <c r="F293" s="2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="G293" s="2" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="H293" s="2" t="inlineStr">
+        <is>
+          <t>before you begin</t>
+        </is>
+      </c>
+      <c r="I293" s="3" t="inlineStr">
+        <is>
+          <t>Before you begin · 528 Hz · Zen Temple</t>
+        </is>
+      </c>
+      <c r="J293" s="3" t="inlineStr">
+        <is>
+          <t>Send this to someone who needs a pause.
+Full piece (3 h): Calm Your Nervous System 🌿 Zen Temple Bells · 528 Hz · Music for Anxiety &amp; Sleep · 3 Hours
+#anxietyrelief #calm #relaxingmusic #528hz #shorts</t>
+        </is>
+      </c>
+      <c r="K293" s="2" t="inlineStr">
+        <is>
+          <t>anxiety relief, calming music, 528 hz, zen temple, Rin</t>
+        </is>
+      </c>
+      <c r="L293" s="2" t="inlineStr"/>
+      <c r="M293" s="2" t="inlineStr">
+        <is>
+          <t>528 Hz · slow down</t>
+        </is>
+      </c>
+      <c r="N293" s="3" t="inlineStr">
+        <is>
+          <t>Send this to someone who needs a pause. Full 3 h piece on YouTube: Rin.
+#anxietyrelief #calm #relaxingmusic #528hz #meditation</t>
+        </is>
+      </c>
+      <c r="O293" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="P293" s="4" t="inlineStr"/>
+      <c r="Q293" s="4" t="inlineStr"/>
+      <c r="R293" s="4" t="inlineStr"/>
+      <c r="S293" s="4" t="inlineStr"/>
+    </row>
+    <row r="294" ht="58" customHeight="1">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-042-S6</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-042</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D294" s="2" t="inlineStr">
+        <is>
+          <t>short-6.mp4</t>
+        </is>
+      </c>
+      <c r="E294" s="2" t="n">
+        <v>1426</v>
+      </c>
+      <c r="F294" s="2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="G294" s="2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H294" s="2" t="inlineStr">
+        <is>
+          <t>you can put it down for now</t>
+        </is>
+      </c>
+      <c r="I294" s="3" t="inlineStr">
+        <is>
+          <t>You can put it down for now · 528 Hz · Zen Temple</t>
+        </is>
+      </c>
+      <c r="J294" s="3" t="inlineStr">
+        <is>
+          <t>Breathe with the sound for a moment.
+Full piece (3 h): Calm Your Nervous System 🌿 Zen Temple Bells · 528 Hz · Music for Anxiety &amp; Sleep · 3 Hours
+#anxietyrelief #calm #relaxingmusic #528hz #shorts</t>
+        </is>
+      </c>
+      <c r="K294" s="2" t="inlineStr">
+        <is>
+          <t>anxiety relief, calming music, 528 hz, zen temple, Rin</t>
+        </is>
+      </c>
+      <c r="L294" s="2" t="inlineStr"/>
+      <c r="M294" s="2" t="inlineStr">
+        <is>
+          <t>528 Hz · let go</t>
+        </is>
+      </c>
+      <c r="N294" s="3" t="inlineStr">
+        <is>
+          <t>Breathe with the sound for a moment. Full 3 h piece on YouTube: Rin.
+#anxietyrelief #calm #relaxingmusic #528hz #meditation</t>
+        </is>
+      </c>
+      <c r="O294" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="P294" s="4" t="inlineStr"/>
+      <c r="Q294" s="4" t="inlineStr"/>
+      <c r="R294" s="4" t="inlineStr"/>
+      <c r="S294" s="4" t="inlineStr"/>
+    </row>
+    <row r="295" ht="58" customHeight="1">
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-042-S7</t>
+        </is>
+      </c>
+      <c r="B295" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-042</t>
+        </is>
+      </c>
+      <c r="C295" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D295" s="2" t="inlineStr">
+        <is>
+          <t>short-7.mp4</t>
+        </is>
+      </c>
+      <c r="E295" s="2" t="n">
+        <v>6768</v>
+      </c>
+      <c r="F295" s="2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G295" s="2" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="H295" s="2" t="inlineStr">
+        <is>
+          <t>one minute of quiet</t>
+        </is>
+      </c>
+      <c r="I295" s="3" t="inlineStr">
+        <is>
+          <t>One minute of quiet · 528 Hz · Zen Temple</t>
+        </is>
+      </c>
+      <c r="J295" s="3" t="inlineStr">
+        <is>
+          <t>Come back to this when you need it.
+Full piece (3 h): Calm Your Nervous System 🌿 Zen Temple Bells · 528 Hz · Music for Anxiety &amp; Sleep · 3 Hours
+#anxietyrelief #calm #relaxingmusic #528hz #shorts</t>
+        </is>
+      </c>
+      <c r="K295" s="2" t="inlineStr">
+        <is>
+          <t>anxiety relief, calming music, 528 hz, zen temple, Rin</t>
+        </is>
+      </c>
+      <c r="L295" s="2" t="inlineStr"/>
+      <c r="M295" s="2" t="inlineStr">
+        <is>
+          <t>528 Hz · quiet</t>
+        </is>
+      </c>
+      <c r="N295" s="3" t="inlineStr">
+        <is>
+          <t>Come back to this when you need it. Full 3 h piece on YouTube: Rin.
+#anxietyrelief #calm #relaxingmusic #528hz #meditation</t>
+        </is>
+      </c>
+      <c r="O295" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="P295" s="4" t="inlineStr"/>
+      <c r="Q295" s="4" t="inlineStr"/>
+      <c r="R295" s="4" t="inlineStr"/>
+      <c r="S295" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S288"/>
+  <autoFilter ref="A1:S295"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -26325,7 +26980,7 @@
         </is>
       </c>
       <c r="B2" s="7">
-        <f>COUNTA(Catálogo!A2:A42)</f>
+        <f>COUNTA(Catálogo!A2:A43)</f>
         <v/>
       </c>
     </row>
@@ -26336,7 +26991,7 @@
         </is>
       </c>
       <c r="B3" s="7">
-        <f>COUNTIF(Catálogo!U2:U42,"pendiente")</f>
+        <f>COUNTIF(Catálogo!U2:U43,"pendiente")</f>
         <v/>
       </c>
     </row>
@@ -26347,7 +27002,7 @@
         </is>
       </c>
       <c r="B4" s="7">
-        <f>COUNTIF(Catálogo!U2:U42,"compuesta")</f>
+        <f>COUNTIF(Catálogo!U2:U43,"compuesta")</f>
         <v/>
       </c>
     </row>
@@ -26358,7 +27013,7 @@
         </is>
       </c>
       <c r="B5" s="7">
-        <f>COUNTIF(Catálogo!U2:U42,"montada")</f>
+        <f>COUNTIF(Catálogo!U2:U43,"montada")</f>
         <v/>
       </c>
     </row>
@@ -26369,7 +27024,7 @@
         </is>
       </c>
       <c r="B6" s="7">
-        <f>COUNTIF(Catálogo!U2:U42,"publicada")</f>
+        <f>COUNTIF(Catálogo!U2:U43,"publicada")</f>
         <v/>
       </c>
     </row>
@@ -26409,15 +27064,15 @@
         </is>
       </c>
       <c r="B10" s="7">
-        <f>COUNTIF(Catálogo!D2:D42,A10)</f>
+        <f>COUNTIF(Catálogo!D2:D43,A10)</f>
         <v/>
       </c>
       <c r="C10" s="7">
-        <f>COUNTIFS(Catálogo!D2:D42,A10,Catálogo!U2:U42,"publicada")</f>
+        <f>COUNTIFS(Catálogo!D2:D43,A10,Catálogo!U2:U43,"publicada")</f>
         <v/>
       </c>
       <c r="D10" s="7">
-        <f>SUMIF(Catálogo!D2:D42,A10,Catálogo!R2:R42)</f>
+        <f>SUMIF(Catálogo!D2:D43,A10,Catálogo!R2:R43)</f>
         <v/>
       </c>
     </row>
@@ -26428,15 +27083,15 @@
         </is>
       </c>
       <c r="B11" s="7">
-        <f>COUNTIF(Catálogo!D2:D42,A11)</f>
+        <f>COUNTIF(Catálogo!D2:D43,A11)</f>
         <v/>
       </c>
       <c r="C11" s="7">
-        <f>COUNTIFS(Catálogo!D2:D42,A11,Catálogo!U2:U42,"publicada")</f>
+        <f>COUNTIFS(Catálogo!D2:D43,A11,Catálogo!U2:U43,"publicada")</f>
         <v/>
       </c>
       <c r="D11" s="7">
-        <f>SUMIF(Catálogo!D2:D42,A11,Catálogo!R2:R42)</f>
+        <f>SUMIF(Catálogo!D2:D43,A11,Catálogo!R2:R43)</f>
         <v/>
       </c>
     </row>
@@ -26447,15 +27102,15 @@
         </is>
       </c>
       <c r="B12" s="7">
-        <f>COUNTIF(Catálogo!D2:D42,A12)</f>
+        <f>COUNTIF(Catálogo!D2:D43,A12)</f>
         <v/>
       </c>
       <c r="C12" s="7">
-        <f>COUNTIFS(Catálogo!D2:D42,A12,Catálogo!U2:U42,"publicada")</f>
+        <f>COUNTIFS(Catálogo!D2:D43,A12,Catálogo!U2:U43,"publicada")</f>
         <v/>
       </c>
       <c r="D12" s="7">
-        <f>SUMIF(Catálogo!D2:D42,A12,Catálogo!R2:R42)</f>
+        <f>SUMIF(Catálogo!D2:D43,A12,Catálogo!R2:R43)</f>
         <v/>
       </c>
     </row>
@@ -26466,15 +27121,15 @@
         </is>
       </c>
       <c r="B13" s="7">
-        <f>COUNTIF(Catálogo!D2:D42,A13)</f>
+        <f>COUNTIF(Catálogo!D2:D43,A13)</f>
         <v/>
       </c>
       <c r="C13" s="7">
-        <f>COUNTIFS(Catálogo!D2:D42,A13,Catálogo!U2:U42,"publicada")</f>
+        <f>COUNTIFS(Catálogo!D2:D43,A13,Catálogo!U2:U43,"publicada")</f>
         <v/>
       </c>
       <c r="D13" s="7">
-        <f>SUMIF(Catálogo!D2:D42,A13,Catálogo!R2:R42)</f>
+        <f>SUMIF(Catálogo!D2:D43,A13,Catálogo!R2:R43)</f>
         <v/>
       </c>
     </row>
@@ -26485,15 +27140,15 @@
         </is>
       </c>
       <c r="B14" s="7">
-        <f>COUNTIF(Catálogo!D2:D42,A14)</f>
+        <f>COUNTIF(Catálogo!D2:D43,A14)</f>
         <v/>
       </c>
       <c r="C14" s="7">
-        <f>COUNTIFS(Catálogo!D2:D42,A14,Catálogo!U2:U42,"publicada")</f>
+        <f>COUNTIFS(Catálogo!D2:D43,A14,Catálogo!U2:U43,"publicada")</f>
         <v/>
       </c>
       <c r="D14" s="7">
-        <f>SUMIF(Catálogo!D2:D42,A14,Catálogo!R2:R42)</f>
+        <f>SUMIF(Catálogo!D2:D43,A14,Catálogo!R2:R43)</f>
         <v/>
       </c>
     </row>
@@ -26530,7 +27185,7 @@
         </is>
       </c>
       <c r="B18" s="7">
-        <f>SUM(Catálogo!W2:W42)</f>
+        <f>SUM(Catálogo!W2:W43)</f>
         <v/>
       </c>
     </row>
@@ -26541,7 +27196,7 @@
         </is>
       </c>
       <c r="B19" s="7">
-        <f>SUM(Catálogo!X2:X42)</f>
+        <f>SUM(Catálogo!X2:X43)</f>
         <v/>
       </c>
     </row>

--- a/08-catalogo/catalogo_canal.xlsx
+++ b/08-catalogo/catalogo_canal.xlsx
@@ -5422,7 +5422,11 @@
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr"/>
-      <c r="L43" s="4" t="inlineStr"/>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/tt0cPixnquE</t>
+        </is>
+      </c>
       <c r="M43" s="2" t="n">
         <v>528</v>
       </c>
@@ -5457,10 +5461,14 @@
       </c>
       <c r="U43" s="4" t="inlineStr">
         <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="V43" s="4" t="inlineStr"/>
+          <t>publicada</t>
+        </is>
+      </c>
+      <c r="V43" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
       <c r="W43" s="4" t="inlineStr"/>
       <c r="X43" s="4" t="inlineStr"/>
       <c r="Y43" s="5">
@@ -26482,6 +26490,7 @@
         <is>
           <t>Save this for the next hard moment.
 Full piece (3 h): Calm Your Nervous System 🌿 Zen Temple Bells · 528 Hz · Music for Anxiety &amp; Sleep · 3 Hours
+https://youtu.be/tt0cPixnquE
 #anxietyrelief #calm #relaxingmusic #528hz #shorts</t>
         </is>
       </c>
@@ -26490,7 +26499,11 @@
           <t>anxiety relief, calming music, 528 hz, zen temple, Rin</t>
         </is>
       </c>
-      <c r="L289" s="2" t="inlineStr"/>
+      <c r="L289" s="2" t="inlineStr">
+        <is>
+          <t>https://youtu.be/tt0cPixnquE</t>
+        </is>
+      </c>
       <c r="M289" s="2" t="inlineStr">
         <is>
           <t>528 Hz · calm</t>
@@ -26554,6 +26567,7 @@
         <is>
           <t>Headphones on. Exhale slowly.
 Full piece (3 h): Calm Your Nervous System 🌿 Zen Temple Bells · 528 Hz · Music for Anxiety &amp; Sleep · 3 Hours
+https://youtu.be/tt0cPixnquE
 #anxietyrelief #calm #relaxingmusic #528hz #shorts</t>
         </is>
       </c>
@@ -26562,7 +26576,11 @@
           <t>anxiety relief, calming music, 528 hz, zen temple, Rin</t>
         </is>
       </c>
-      <c r="L290" s="2" t="inlineStr"/>
+      <c r="L290" s="2" t="inlineStr">
+        <is>
+          <t>https://youtu.be/tt0cPixnquE</t>
+        </is>
+      </c>
       <c r="M290" s="2" t="inlineStr">
         <is>
           <t>528 Hz · exhale</t>
@@ -26626,6 +26644,7 @@
         <is>
           <t>Stay for one full breath.
 Full piece (3 h): Calm Your Nervous System 🌿 Zen Temple Bells · 528 Hz · Music for Anxiety &amp; Sleep · 3 Hours
+https://youtu.be/tt0cPixnquE
 #anxietyrelief #calm #relaxingmusic #528hz #shorts</t>
         </is>
       </c>
@@ -26634,7 +26653,11 @@
           <t>anxiety relief, calming music, 528 hz, zen temple, Rin</t>
         </is>
       </c>
-      <c r="L291" s="2" t="inlineStr"/>
+      <c r="L291" s="2" t="inlineStr">
+        <is>
+          <t>https://youtu.be/tt0cPixnquE</t>
+        </is>
+      </c>
       <c r="M291" s="2" t="inlineStr">
         <is>
           <t>528 Hz · pause</t>
@@ -26698,6 +26721,7 @@
         <is>
           <t>A small pause in the middle of the day.
 Full piece (3 h): Calm Your Nervous System 🌿 Zen Temple Bells · 528 Hz · Music for Anxiety &amp; Sleep · 3 Hours
+https://youtu.be/tt0cPixnquE
 #anxietyrelief #calm #relaxingmusic #528hz #shorts</t>
         </is>
       </c>
@@ -26706,7 +26730,11 @@
           <t>anxiety relief, calming music, 528 hz, zen temple, Rin</t>
         </is>
       </c>
-      <c r="L292" s="2" t="inlineStr"/>
+      <c r="L292" s="2" t="inlineStr">
+        <is>
+          <t>https://youtu.be/tt0cPixnquE</t>
+        </is>
+      </c>
       <c r="M292" s="2" t="inlineStr">
         <is>
           <t>528 Hz · breathe</t>
@@ -26770,6 +26798,7 @@
         <is>
           <t>Send this to someone who needs a pause.
 Full piece (3 h): Calm Your Nervous System 🌿 Zen Temple Bells · 528 Hz · Music for Anxiety &amp; Sleep · 3 Hours
+https://youtu.be/tt0cPixnquE
 #anxietyrelief #calm #relaxingmusic #528hz #shorts</t>
         </is>
       </c>
@@ -26778,7 +26807,11 @@
           <t>anxiety relief, calming music, 528 hz, zen temple, Rin</t>
         </is>
       </c>
-      <c r="L293" s="2" t="inlineStr"/>
+      <c r="L293" s="2" t="inlineStr">
+        <is>
+          <t>https://youtu.be/tt0cPixnquE</t>
+        </is>
+      </c>
       <c r="M293" s="2" t="inlineStr">
         <is>
           <t>528 Hz · slow down</t>
@@ -26842,6 +26875,7 @@
         <is>
           <t>Breathe with the sound for a moment.
 Full piece (3 h): Calm Your Nervous System 🌿 Zen Temple Bells · 528 Hz · Music for Anxiety &amp; Sleep · 3 Hours
+https://youtu.be/tt0cPixnquE
 #anxietyrelief #calm #relaxingmusic #528hz #shorts</t>
         </is>
       </c>
@@ -26850,7 +26884,11 @@
           <t>anxiety relief, calming music, 528 hz, zen temple, Rin</t>
         </is>
       </c>
-      <c r="L294" s="2" t="inlineStr"/>
+      <c r="L294" s="2" t="inlineStr">
+        <is>
+          <t>https://youtu.be/tt0cPixnquE</t>
+        </is>
+      </c>
       <c r="M294" s="2" t="inlineStr">
         <is>
           <t>528 Hz · let go</t>
@@ -26914,6 +26952,7 @@
         <is>
           <t>Come back to this when you need it.
 Full piece (3 h): Calm Your Nervous System 🌿 Zen Temple Bells · 528 Hz · Music for Anxiety &amp; Sleep · 3 Hours
+https://youtu.be/tt0cPixnquE
 #anxietyrelief #calm #relaxingmusic #528hz #shorts</t>
         </is>
       </c>
@@ -26922,7 +26961,11 @@
           <t>anxiety relief, calming music, 528 hz, zen temple, Rin</t>
         </is>
       </c>
-      <c r="L295" s="2" t="inlineStr"/>
+      <c r="L295" s="2" t="inlineStr">
+        <is>
+          <t>https://youtu.be/tt0cPixnquE</t>
+        </is>
+      </c>
       <c r="M295" s="2" t="inlineStr">
         <is>
           <t>528 Hz · quiet</t>

--- a/08-catalogo/catalogo_canal.xlsx
+++ b/08-catalogo/catalogo_canal.xlsx
@@ -13,8 +13,8 @@
     <sheet name="Leyenda" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$Y$43</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Shorts'!$A$1:$S$295</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$Z$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Shorts'!$A$1:$S$298</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y43"/>
+  <dimension ref="A1:Z44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -510,13 +510,14 @@
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="6" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="62" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
     <col width="62" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
-    <col width="18" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
-    <col width="13" customWidth="1" min="24" max="24"/>
-    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="62" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="18" customWidth="1" min="23" max="23"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -612,35 +613,40 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>pantalla_oscura_min</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>comando_regeneracion</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>comando_ambiente</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>estado</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>fecha_publicacion</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>vistas</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>suscriptores</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>subs_por_1000</t>
         </is>
@@ -737,26 +743,29 @@
       <c r="R2" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="S2" s="3" t="inlineStr">
+      <c r="S2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 180 --raiz 432 --modo shin --semilla 505716 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="T2" s="2" t="inlineStr">
+      <c r="U2" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/ambiente.py audio/OBRA-001_432_shin.wav audio/OBRA-001_final.wav --fondo mar</t>
         </is>
       </c>
-      <c r="U2" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="V2" s="4" t="inlineStr"/>
+      <c r="V2" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="W2" s="4" t="inlineStr"/>
       <c r="X2" s="4" t="inlineStr"/>
-      <c r="Y2" s="5">
-        <f>IFERROR(X2/W2*1000,"")</f>
+      <c r="Y2" s="4" t="inlineStr"/>
+      <c r="Z2" s="5">
+        <f>IFERROR(Y2/X2*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -851,26 +860,29 @@
       <c r="R3" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="S3" s="3" t="inlineStr">
+      <c r="S3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 120 --raiz 528 --modo kumoi --semilla 443547 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="T3" s="2" t="inlineStr">
+      <c r="U3" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/ambiente.py audio/OBRA-002_528_kumoi.wav audio/OBRA-002_final.wav --fondo mar</t>
         </is>
       </c>
-      <c r="U3" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="V3" s="4" t="inlineStr"/>
+      <c r="V3" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="W3" s="4" t="inlineStr"/>
       <c r="X3" s="4" t="inlineStr"/>
-      <c r="Y3" s="5">
-        <f>IFERROR(X3/W3*1000,"")</f>
+      <c r="Y3" s="4" t="inlineStr"/>
+      <c r="Z3" s="5">
+        <f>IFERROR(Y3/X3*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -965,26 +977,29 @@
       <c r="R4" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="S4" s="3" t="inlineStr">
+      <c r="S4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 120 --raiz 396 --modo kumoi --semilla 692584 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="T4" s="2" t="inlineStr">
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/ambiente.py audio/OBRA-003_396_kumoi.wav audio/OBRA-003_final.wav --fondo mar</t>
         </is>
       </c>
-      <c r="U4" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="V4" s="4" t="inlineStr"/>
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="W4" s="4" t="inlineStr"/>
       <c r="X4" s="4" t="inlineStr"/>
-      <c r="Y4" s="5">
-        <f>IFERROR(X4/W4*1000,"")</f>
+      <c r="Y4" s="4" t="inlineStr"/>
+      <c r="Z4" s="5">
+        <f>IFERROR(Y4/X4*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -1079,26 +1094,29 @@
       <c r="R5" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="S5" s="3" t="inlineStr">
+      <c r="S5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 180 --raiz 528 --modo shin --semilla 751043 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="T5" s="2" t="inlineStr">
+      <c r="U5" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/ambiente.py audio/OBRA-004_528_shin.wav audio/OBRA-004_final.wav --fondo mar</t>
         </is>
       </c>
-      <c r="U5" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="V5" s="4" t="inlineStr"/>
+      <c r="V5" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="W5" s="4" t="inlineStr"/>
       <c r="X5" s="4" t="inlineStr"/>
-      <c r="Y5" s="5">
-        <f>IFERROR(X5/W5*1000,"")</f>
+      <c r="Y5" s="4" t="inlineStr"/>
+      <c r="Z5" s="5">
+        <f>IFERROR(Y5/X5*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -1193,26 +1211,29 @@
       <c r="R6" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="S6" s="3" t="inlineStr">
+      <c r="S6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 120 --raiz 432 --modo kumoi --semilla 531725 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="T6" s="2" t="inlineStr">
+      <c r="U6" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/ambiente.py audio/OBRA-005_432_kumoi.wav audio/OBRA-005_final.wav --fondo mar</t>
         </is>
       </c>
-      <c r="U6" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="V6" s="4" t="inlineStr"/>
+      <c r="V6" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="W6" s="4" t="inlineStr"/>
       <c r="X6" s="4" t="inlineStr"/>
-      <c r="Y6" s="5">
-        <f>IFERROR(X6/W6*1000,"")</f>
+      <c r="Y6" s="4" t="inlineStr"/>
+      <c r="Z6" s="5">
+        <f>IFERROR(Y6/X6*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -1311,30 +1332,33 @@
       <c r="R7" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="S7" s="3" t="inlineStr">
+      <c r="S7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 90 --raiz 417 --modo kumoi --semilla 813147 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="T7" s="2" t="inlineStr">
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/ambiente.py audio/OBRA-006_417_kumoi.wav audio/OBRA-006_final.wav --fondo mar</t>
         </is>
       </c>
-      <c r="U7" s="4" t="inlineStr">
+      <c r="V7" s="4" t="inlineStr">
         <is>
           <t>publicada</t>
         </is>
       </c>
-      <c r="V7" s="4" t="inlineStr">
+      <c r="W7" s="4" t="inlineStr">
         <is>
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="W7" s="4" t="inlineStr"/>
       <c r="X7" s="4" t="inlineStr"/>
-      <c r="Y7" s="5">
-        <f>IFERROR(X7/W7*1000,"")</f>
+      <c r="Y7" s="4" t="inlineStr"/>
+      <c r="Z7" s="5">
+        <f>IFERROR(Y7/X7*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -1429,26 +1453,29 @@
       <c r="R8" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="S8" s="3" t="inlineStr">
+      <c r="S8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 120 --raiz 396 --modo shin --semilla 885916 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="T8" s="2" t="inlineStr">
+      <c r="U8" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/ambiente.py audio/OBRA-007_396_shin.wav audio/OBRA-007_final.wav --fondo mar</t>
         </is>
       </c>
-      <c r="U8" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="V8" s="4" t="inlineStr"/>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="W8" s="4" t="inlineStr"/>
       <c r="X8" s="4" t="inlineStr"/>
-      <c r="Y8" s="5">
-        <f>IFERROR(X8/W8*1000,"")</f>
+      <c r="Y8" s="4" t="inlineStr"/>
+      <c r="Z8" s="5">
+        <f>IFERROR(Y8/X8*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -1543,26 +1570,29 @@
       <c r="R9" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="S9" s="3" t="inlineStr">
+      <c r="S9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 180 --raiz 432 --modo kumoi --semilla 295910 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="T9" s="2" t="inlineStr">
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/ambiente.py audio/OBRA-008_432_kumoi.wav audio/OBRA-008_final.wav --fondo mar</t>
         </is>
       </c>
-      <c r="U9" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="V9" s="4" t="inlineStr"/>
+      <c r="V9" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="W9" s="4" t="inlineStr"/>
       <c r="X9" s="4" t="inlineStr"/>
-      <c r="Y9" s="5">
-        <f>IFERROR(X9/W9*1000,"")</f>
+      <c r="Y9" s="4" t="inlineStr"/>
+      <c r="Z9" s="5">
+        <f>IFERROR(Y9/X9*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -1657,26 +1687,29 @@
       <c r="R10" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="S10" s="3" t="inlineStr">
+      <c r="S10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 25 --raiz 396 --modo kumoi --semilla 555819 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="T10" s="2" t="inlineStr">
+      <c r="U10" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py aves 1540 audio/OBRA-009_capa.wav --semilla 555819 --raiz 396 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-009_396_kumoi.wav audio/OBRA-009_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-009_capa.wav</t>
         </is>
       </c>
-      <c r="U10" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="V10" s="4" t="inlineStr"/>
+      <c r="V10" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="W10" s="4" t="inlineStr"/>
       <c r="X10" s="4" t="inlineStr"/>
-      <c r="Y10" s="5">
-        <f>IFERROR(X10/W10*1000,"")</f>
+      <c r="Y10" s="4" t="inlineStr"/>
+      <c r="Z10" s="5">
+        <f>IFERROR(Y10/X10*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -1771,26 +1804,29 @@
       <c r="R11" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="S11" s="3" t="inlineStr">
+      <c r="S11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 30 --raiz 432 --modo hirajoshi --semilla 739461 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="T11" s="2" t="inlineStr">
+      <c r="U11" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py zen 1840 audio/OBRA-010_capa.wav --semilla 739461 --raiz 432 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-010_432_hirajoshi.wav audio/OBRA-010_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-010_capa.wav</t>
         </is>
       </c>
-      <c r="U11" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="V11" s="4" t="inlineStr"/>
+      <c r="V11" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="W11" s="4" t="inlineStr"/>
       <c r="X11" s="4" t="inlineStr"/>
-      <c r="Y11" s="5">
-        <f>IFERROR(X11/W11*1000,"")</f>
+      <c r="Y11" s="4" t="inlineStr"/>
+      <c r="Z11" s="5">
+        <f>IFERROR(Y11/X11*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -1885,26 +1921,29 @@
       <c r="R12" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="S12" s="3" t="inlineStr">
+      <c r="S12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 20 --raiz 528 --modo hirajoshi --semilla 913368 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="T12" s="2" t="inlineStr">
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py aves 1240 audio/OBRA-011_capa.wav --semilla 913368 --raiz 528 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-011_528_hirajoshi.wav audio/OBRA-011_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-011_capa.wav</t>
         </is>
       </c>
-      <c r="U12" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="V12" s="4" t="inlineStr"/>
+      <c r="V12" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="W12" s="4" t="inlineStr"/>
       <c r="X12" s="4" t="inlineStr"/>
-      <c r="Y12" s="5">
-        <f>IFERROR(X12/W12*1000,"")</f>
+      <c r="Y12" s="4" t="inlineStr"/>
+      <c r="Z12" s="5">
+        <f>IFERROR(Y12/X12*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -2003,30 +2042,33 @@
       <c r="R13" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="S13" s="3" t="inlineStr">
+      <c r="S13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 10 --raiz 528 --modo shin --semilla 43734 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="T13" s="2" t="inlineStr">
+      <c r="U13" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py zen 640 audio/OBRA-012_capa.wav --semilla 43734 --raiz 528 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-012_528_shin.wav audio/OBRA-012_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-012_capa.wav</t>
         </is>
       </c>
-      <c r="U13" s="4" t="inlineStr">
+      <c r="V13" s="4" t="inlineStr">
         <is>
           <t>publicada</t>
         </is>
       </c>
-      <c r="V13" s="4" t="inlineStr">
+      <c r="W13" s="4" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="W13" s="4" t="inlineStr"/>
       <c r="X13" s="4" t="inlineStr"/>
-      <c r="Y13" s="5">
-        <f>IFERROR(X13/W13*1000,"")</f>
+      <c r="Y13" s="4" t="inlineStr"/>
+      <c r="Z13" s="5">
+        <f>IFERROR(Y13/X13*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -2121,26 +2163,29 @@
       <c r="R14" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="S14" s="3" t="inlineStr">
+      <c r="S14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 20 --raiz 432 --modo hirajoshi --semilla 627771 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="T14" s="2" t="inlineStr">
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py aves 1240 audio/OBRA-013_capa.wav --semilla 627771 --raiz 432 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-013_432_hirajoshi.wav audio/OBRA-013_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-013_capa.wav</t>
         </is>
       </c>
-      <c r="U14" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="V14" s="4" t="inlineStr"/>
+      <c r="V14" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="W14" s="4" t="inlineStr"/>
       <c r="X14" s="4" t="inlineStr"/>
-      <c r="Y14" s="5">
-        <f>IFERROR(X14/W14*1000,"")</f>
+      <c r="Y14" s="4" t="inlineStr"/>
+      <c r="Z14" s="5">
+        <f>IFERROR(Y14/X14*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -2235,26 +2280,29 @@
       <c r="R15" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="S15" s="3" t="inlineStr">
+      <c r="S15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 20 --raiz 528 --modo yo --semilla 310137 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="T15" s="2" t="inlineStr">
+      <c r="U15" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py zen 1240 audio/OBRA-014_capa.wav --semilla 310137 --raiz 528 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-014_528_yo.wav audio/OBRA-014_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-014_capa.wav</t>
         </is>
       </c>
-      <c r="U15" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="V15" s="4" t="inlineStr"/>
+      <c r="V15" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="W15" s="4" t="inlineStr"/>
       <c r="X15" s="4" t="inlineStr"/>
-      <c r="Y15" s="5">
-        <f>IFERROR(X15/W15*1000,"")</f>
+      <c r="Y15" s="4" t="inlineStr"/>
+      <c r="Z15" s="5">
+        <f>IFERROR(Y15/X15*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -2353,30 +2401,33 @@
       <c r="R16" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="S16" s="3" t="inlineStr">
+      <c r="S16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 15 --raiz 639 --modo yo --semilla 592463 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="T16" s="2" t="inlineStr">
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py aves 940 audio/OBRA-015_capa.wav --semilla 592463 --raiz 639 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-015_639_yo.wav audio/OBRA-015_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-015_capa.wav</t>
         </is>
       </c>
-      <c r="U16" s="4" t="inlineStr">
+      <c r="V16" s="4" t="inlineStr">
         <is>
           <t>publicada</t>
         </is>
       </c>
-      <c r="V16" s="4" t="inlineStr">
+      <c r="W16" s="4" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="W16" s="4" t="inlineStr"/>
       <c r="X16" s="4" t="inlineStr"/>
-      <c r="Y16" s="5">
-        <f>IFERROR(X16/W16*1000,"")</f>
+      <c r="Y16" s="4" t="inlineStr"/>
+      <c r="Z16" s="5">
+        <f>IFERROR(Y16/X16*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -2471,26 +2522,29 @@
       <c r="R17" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="S17" s="3" t="inlineStr">
+      <c r="S17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 30 --raiz 417 --modo kumoi --semilla 250697 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="T17" s="2" t="inlineStr">
+      <c r="U17" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py ancestral 1840 audio/OBRA-016_capa.wav --semilla 250697 --raiz 417 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-016_417_kumoi.wav audio/OBRA-016_final.wav --fondo fuego --nivel-capa 0 --nivel-obra -20 --capa audio/OBRA-016_capa.wav</t>
         </is>
       </c>
-      <c r="U17" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="V17" s="4" t="inlineStr"/>
+      <c r="V17" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="W17" s="4" t="inlineStr"/>
       <c r="X17" s="4" t="inlineStr"/>
-      <c r="Y17" s="5">
-        <f>IFERROR(X17/W17*1000,"")</f>
+      <c r="Y17" s="4" t="inlineStr"/>
+      <c r="Z17" s="5">
+        <f>IFERROR(Y17/X17*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -2585,26 +2639,29 @@
       <c r="R18" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="S18" s="3" t="inlineStr">
+      <c r="S18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 45 --raiz 417 --modo hirajoshi --semilla 714152 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="T18" s="2" t="inlineStr">
+      <c r="U18" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py zen 2740 audio/OBRA-017_capa.wav --semilla 714152 --raiz 417 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-017_417_hirajoshi.wav audio/OBRA-017_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-017_capa.wav</t>
         </is>
       </c>
-      <c r="U18" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="V18" s="4" t="inlineStr"/>
+      <c r="V18" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="W18" s="4" t="inlineStr"/>
       <c r="X18" s="4" t="inlineStr"/>
-      <c r="Y18" s="5">
-        <f>IFERROR(X18/W18*1000,"")</f>
+      <c r="Y18" s="4" t="inlineStr"/>
+      <c r="Z18" s="5">
+        <f>IFERROR(Y18/X18*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -2699,26 +2756,29 @@
       <c r="R19" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="S19" s="3" t="inlineStr">
+      <c r="S19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 45 --raiz 528 --modo hirajoshi --semilla 735455 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="T19" s="2" t="inlineStr">
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py zen 2740 audio/OBRA-018_capa.wav --semilla 735455 --raiz 528 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-018_528_hirajoshi.wav audio/OBRA-018_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-018_capa.wav</t>
         </is>
       </c>
-      <c r="U19" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="V19" s="4" t="inlineStr"/>
+      <c r="V19" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="W19" s="4" t="inlineStr"/>
       <c r="X19" s="4" t="inlineStr"/>
-      <c r="Y19" s="5">
-        <f>IFERROR(X19/W19*1000,"")</f>
+      <c r="Y19" s="4" t="inlineStr"/>
+      <c r="Z19" s="5">
+        <f>IFERROR(Y19/X19*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -2813,26 +2873,29 @@
       <c r="R20" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="S20" s="3" t="inlineStr">
+      <c r="S20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 60 --raiz 432 --modo shin --semilla 627577 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="T20" s="2" t="inlineStr">
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py zen 3640 audio/OBRA-019_capa.wav --semilla 627577 --raiz 432 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-019_432_shin.wav audio/OBRA-019_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-019_capa.wav</t>
         </is>
       </c>
-      <c r="U20" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="V20" s="4" t="inlineStr"/>
+      <c r="V20" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="W20" s="4" t="inlineStr"/>
       <c r="X20" s="4" t="inlineStr"/>
-      <c r="Y20" s="5">
-        <f>IFERROR(X20/W20*1000,"")</f>
+      <c r="Y20" s="4" t="inlineStr"/>
+      <c r="Z20" s="5">
+        <f>IFERROR(Y20/X20*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -2931,30 +2994,33 @@
       <c r="R21" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="S21" s="3" t="inlineStr">
+      <c r="S21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 30 --raiz 528 --modo shin --semilla 632595 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="T21" s="2" t="inlineStr">
+      <c r="U21" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py ancestral 1840 audio/OBRA-020_capa.wav --semilla 632595 --raiz 528 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-020_528_shin.wav audio/OBRA-020_final.wav --fondo fuego --nivel-capa 0 --nivel-obra -20 --capa audio/OBRA-020_capa.wav</t>
         </is>
       </c>
-      <c r="U21" s="4" t="inlineStr">
+      <c r="V21" s="4" t="inlineStr">
         <is>
           <t>publicada</t>
         </is>
       </c>
-      <c r="V21" s="4" t="inlineStr">
+      <c r="W21" s="4" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="W21" s="4" t="inlineStr"/>
       <c r="X21" s="4" t="inlineStr"/>
-      <c r="Y21" s="5">
-        <f>IFERROR(X21/W21*1000,"")</f>
+      <c r="Y21" s="4" t="inlineStr"/>
+      <c r="Z21" s="5">
+        <f>IFERROR(Y21/X21*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -3049,26 +3115,29 @@
       <c r="R22" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="S22" s="3" t="inlineStr">
+      <c r="S22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 45 --raiz 396 --modo kumoi --semilla 864630 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="T22" s="2" t="inlineStr">
+      <c r="U22" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py zen 2740 audio/OBRA-021_capa.wav --semilla 864630 --raiz 396 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-021_396_kumoi.wav audio/OBRA-021_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-021_capa.wav</t>
         </is>
       </c>
-      <c r="U22" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="V22" s="4" t="inlineStr"/>
+      <c r="V22" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="W22" s="4" t="inlineStr"/>
       <c r="X22" s="4" t="inlineStr"/>
-      <c r="Y22" s="5">
-        <f>IFERROR(X22/W22*1000,"")</f>
+      <c r="Y22" s="4" t="inlineStr"/>
+      <c r="Z22" s="5">
+        <f>IFERROR(Y22/X22*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -3163,26 +3232,29 @@
       <c r="R23" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="S23" s="3" t="inlineStr">
+      <c r="S23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 60 --raiz 639 --modo yo --semilla 335798 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="T23" s="2" t="inlineStr">
+      <c r="U23" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py zen 3640 audio/OBRA-022_capa.wav --semilla 335798 --raiz 639 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-022_639_yo.wav audio/OBRA-022_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-022_capa.wav</t>
         </is>
       </c>
-      <c r="U23" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="V23" s="4" t="inlineStr"/>
+      <c r="V23" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="W23" s="4" t="inlineStr"/>
       <c r="X23" s="4" t="inlineStr"/>
-      <c r="Y23" s="5">
-        <f>IFERROR(X23/W23*1000,"")</f>
+      <c r="Y23" s="4" t="inlineStr"/>
+      <c r="Z23" s="5">
+        <f>IFERROR(Y23/X23*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -3277,26 +3349,29 @@
       <c r="R24" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="S24" s="3" t="inlineStr">
+      <c r="S24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 20 --raiz 528 --modo shin --semilla 299306 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="T24" s="2" t="inlineStr">
+      <c r="U24" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py zen 1240 audio/OBRA-023_capa.wav --semilla 299306 --raiz 528 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-023_528_shin.wav audio/OBRA-023_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-023_capa.wav</t>
         </is>
       </c>
-      <c r="U24" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="V24" s="4" t="inlineStr"/>
+      <c r="V24" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="W24" s="4" t="inlineStr"/>
       <c r="X24" s="4" t="inlineStr"/>
-      <c r="Y24" s="5">
-        <f>IFERROR(X24/W24*1000,"")</f>
+      <c r="Y24" s="4" t="inlineStr"/>
+      <c r="Z24" s="5">
+        <f>IFERROR(Y24/X24*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -3391,26 +3466,29 @@
       <c r="R25" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="S25" s="3" t="inlineStr">
+      <c r="S25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 60 --raiz 432 --modo kumoi --semilla 926202 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="T25" s="2" t="inlineStr">
+      <c r="U25" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py ancestral 3640 audio/OBRA-024_capa.wav --semilla 926202 --raiz 432 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-024_432_kumoi.wav audio/OBRA-024_final.wav --fondo fuego --nivel-capa 0 --nivel-obra -20 --capa audio/OBRA-024_capa.wav</t>
         </is>
       </c>
-      <c r="U25" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="V25" s="4" t="inlineStr"/>
+      <c r="V25" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="W25" s="4" t="inlineStr"/>
       <c r="X25" s="4" t="inlineStr"/>
-      <c r="Y25" s="5">
-        <f>IFERROR(X25/W25*1000,"")</f>
+      <c r="Y25" s="4" t="inlineStr"/>
+      <c r="Z25" s="5">
+        <f>IFERROR(Y25/X25*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -3505,26 +3583,29 @@
       <c r="R26" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="S26" s="3" t="inlineStr">
+      <c r="S26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 60 --raiz 528 --modo hirajoshi --semilla 454078 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="T26" s="2" t="inlineStr">
+      <c r="U26" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py aves 3640 audio/OBRA-025_capa.wav --semilla 454078 --raiz 528 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-025_528_hirajoshi.wav audio/OBRA-025_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-025_capa.wav</t>
         </is>
       </c>
-      <c r="U26" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="V26" s="4" t="inlineStr"/>
+      <c r="V26" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="W26" s="4" t="inlineStr"/>
       <c r="X26" s="4" t="inlineStr"/>
-      <c r="Y26" s="5">
-        <f>IFERROR(X26/W26*1000,"")</f>
+      <c r="Y26" s="4" t="inlineStr"/>
+      <c r="Z26" s="5">
+        <f>IFERROR(Y26/X26*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -3619,26 +3700,29 @@
       <c r="R27" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="S27" s="3" t="inlineStr">
+      <c r="S27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 60 --raiz 432 --modo kumoi --semilla 146597 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="T27" s="2" t="inlineStr">
+      <c r="U27" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/ambiente.py audio/OBRA-026_432_kumoi.wav audio/OBRA-026_final.wav --fondo mar</t>
         </is>
       </c>
-      <c r="U27" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="V27" s="4" t="inlineStr"/>
+      <c r="V27" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="W27" s="4" t="inlineStr"/>
       <c r="X27" s="4" t="inlineStr"/>
-      <c r="Y27" s="5">
-        <f>IFERROR(X27/W27*1000,"")</f>
+      <c r="Y27" s="4" t="inlineStr"/>
+      <c r="Z27" s="5">
+        <f>IFERROR(Y27/X27*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -3733,26 +3817,29 @@
       <c r="R28" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="S28" s="3" t="inlineStr">
+      <c r="S28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 60 --raiz 396 --modo kumoi --semilla 338018 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="T28" s="2" t="inlineStr">
+      <c r="U28" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py ancestral 3640 audio/OBRA-027_capa.wav --semilla 338018 --raiz 396 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-027_396_kumoi.wav audio/OBRA-027_final.wav --fondo fuego --nivel-capa 0 --nivel-obra -20 --capa audio/OBRA-027_capa.wav</t>
         </is>
       </c>
-      <c r="U28" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="V28" s="4" t="inlineStr"/>
+      <c r="V28" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="W28" s="4" t="inlineStr"/>
       <c r="X28" s="4" t="inlineStr"/>
-      <c r="Y28" s="5">
-        <f>IFERROR(X28/W28*1000,"")</f>
+      <c r="Y28" s="4" t="inlineStr"/>
+      <c r="Z28" s="5">
+        <f>IFERROR(Y28/X28*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -3847,26 +3934,29 @@
       <c r="R29" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="S29" s="3" t="inlineStr">
+      <c r="S29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 45 --raiz 417 --modo hirajoshi --semilla 409966 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="T29" s="2" t="inlineStr">
+      <c r="U29" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py zen 2740 audio/OBRA-028_capa.wav --semilla 409966 --raiz 417 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-028_417_hirajoshi.wav audio/OBRA-028_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-028_capa.wav</t>
         </is>
       </c>
-      <c r="U29" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="V29" s="4" t="inlineStr"/>
+      <c r="V29" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="W29" s="4" t="inlineStr"/>
       <c r="X29" s="4" t="inlineStr"/>
-      <c r="Y29" s="5">
-        <f>IFERROR(X29/W29*1000,"")</f>
+      <c r="Y29" s="4" t="inlineStr"/>
+      <c r="Z29" s="5">
+        <f>IFERROR(Y29/X29*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -3961,26 +4051,29 @@
       <c r="R30" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="S30" s="3" t="inlineStr">
+      <c r="S30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 60 --raiz 639 --modo yo --semilla 133046 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="T30" s="2" t="inlineStr">
+      <c r="U30" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py aves 3640 audio/OBRA-029_capa.wav --semilla 133046 --raiz 639 --densidad 2 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-029_639_yo.wav audio/OBRA-029_final.wav --fondo selva --nivel-capa -2 --capa audio/OBRA-029_capa.wav</t>
         </is>
       </c>
-      <c r="U30" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="V30" s="4" t="inlineStr"/>
+      <c r="V30" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="W30" s="4" t="inlineStr"/>
       <c r="X30" s="4" t="inlineStr"/>
-      <c r="Y30" s="5">
-        <f>IFERROR(X30/W30*1000,"")</f>
+      <c r="Y30" s="4" t="inlineStr"/>
+      <c r="Z30" s="5">
+        <f>IFERROR(Y30/X30*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -4075,26 +4168,29 @@
       <c r="R31" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="S31" s="3" t="inlineStr">
+      <c r="S31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 45 --raiz 741 --modo yo --semilla 244487 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="T31" s="2" t="inlineStr">
+      <c r="U31" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py aves 2740 audio/OBRA-030_capa.wav --semilla 244487 --raiz 741 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-030_741_yo.wav audio/OBRA-030_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-030_capa.wav</t>
         </is>
       </c>
-      <c r="U31" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="V31" s="4" t="inlineStr"/>
+      <c r="V31" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="W31" s="4" t="inlineStr"/>
       <c r="X31" s="4" t="inlineStr"/>
-      <c r="Y31" s="5">
-        <f>IFERROR(X31/W31*1000,"")</f>
+      <c r="Y31" s="4" t="inlineStr"/>
+      <c r="Z31" s="5">
+        <f>IFERROR(Y31/X31*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -4189,26 +4285,29 @@
       <c r="R32" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="S32" s="3" t="inlineStr">
+      <c r="S32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 45 --raiz 852 --modo hirajoshi --semilla 288169 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="T32" s="2" t="inlineStr">
+      <c r="U32" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py zen 2740 audio/OBRA-031_capa.wav --semilla 288169 --raiz 852 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-031_852_hirajoshi.wav audio/OBRA-031_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-031_capa.wav</t>
         </is>
       </c>
-      <c r="U32" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="V32" s="4" t="inlineStr"/>
+      <c r="V32" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="W32" s="4" t="inlineStr"/>
       <c r="X32" s="4" t="inlineStr"/>
-      <c r="Y32" s="5">
-        <f>IFERROR(X32/W32*1000,"")</f>
+      <c r="Y32" s="4" t="inlineStr"/>
+      <c r="Z32" s="5">
+        <f>IFERROR(Y32/X32*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -4303,26 +4402,29 @@
       <c r="R33" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="S33" s="3" t="inlineStr">
+      <c r="S33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 180 --raiz 528 --modo hirajoshi --semilla 638156 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="T33" s="2" t="inlineStr">
+      <c r="U33" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py aves 10840 audio/OBRA-032_capa.wav --semilla 638156 --raiz 528 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-032_528_hirajoshi.wav audio/OBRA-032_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-032_capa.wav</t>
         </is>
       </c>
-      <c r="U33" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="V33" s="4" t="inlineStr"/>
+      <c r="V33" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="W33" s="4" t="inlineStr"/>
       <c r="X33" s="4" t="inlineStr"/>
-      <c r="Y33" s="5">
-        <f>IFERROR(X33/W33*1000,"")</f>
+      <c r="Y33" s="4" t="inlineStr"/>
+      <c r="Z33" s="5">
+        <f>IFERROR(Y33/X33*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -4417,26 +4519,29 @@
       <c r="R34" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="S34" s="3" t="inlineStr">
+      <c r="S34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 120 --raiz 639 --modo yo --semilla 112334 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="T34" s="2" t="inlineStr">
+      <c r="U34" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py aves 7240 audio/OBRA-033_capa.wav --semilla 112334 --raiz 639 --densidad 2 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-033_639_yo.wav audio/OBRA-033_final.wav --fondo selva --nivel-capa -2 --capa audio/OBRA-033_capa.wav</t>
         </is>
       </c>
-      <c r="U34" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="V34" s="4" t="inlineStr"/>
+      <c r="V34" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="W34" s="4" t="inlineStr"/>
       <c r="X34" s="4" t="inlineStr"/>
-      <c r="Y34" s="5">
-        <f>IFERROR(X34/W34*1000,"")</f>
+      <c r="Y34" s="4" t="inlineStr"/>
+      <c r="Z34" s="5">
+        <f>IFERROR(Y34/X34*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -4531,26 +4636,29 @@
       <c r="R35" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="S35" s="3" t="inlineStr">
+      <c r="S35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 180 --raiz 528 --modo yo --semilla 249239 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="T35" s="2" t="inlineStr">
+      <c r="U35" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py aves 10840 audio/OBRA-034_capa.wav --semilla 249239 --raiz 528 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-034_528_yo.wav audio/OBRA-034_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-034_capa.wav</t>
         </is>
       </c>
-      <c r="U35" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="V35" s="4" t="inlineStr"/>
+      <c r="V35" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="W35" s="4" t="inlineStr"/>
       <c r="X35" s="4" t="inlineStr"/>
-      <c r="Y35" s="5">
-        <f>IFERROR(X35/W35*1000,"")</f>
+      <c r="Y35" s="4" t="inlineStr"/>
+      <c r="Z35" s="5">
+        <f>IFERROR(Y35/X35*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -4645,26 +4753,29 @@
       <c r="R36" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="S36" s="3" t="inlineStr">
+      <c r="S36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 120 --raiz 741 --modo yo --semilla 74636 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="T36" s="2" t="inlineStr">
+      <c r="U36" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py aves 7240 audio/OBRA-035_capa.wav --semilla 74636 --raiz 741 --densidad 2 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-035_741_yo.wav audio/OBRA-035_final.wav --fondo selva --nivel-capa -2 --capa audio/OBRA-035_capa.wav</t>
         </is>
       </c>
-      <c r="U36" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="V36" s="4" t="inlineStr"/>
+      <c r="V36" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="W36" s="4" t="inlineStr"/>
       <c r="X36" s="4" t="inlineStr"/>
-      <c r="Y36" s="5">
-        <f>IFERROR(X36/W36*1000,"")</f>
+      <c r="Y36" s="4" t="inlineStr"/>
+      <c r="Z36" s="5">
+        <f>IFERROR(Y36/X36*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -4759,26 +4870,29 @@
       <c r="R37" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="S37" s="3" t="inlineStr">
+      <c r="S37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 90 --raiz 852 --modo yo --semilla 903477 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="T37" s="2" t="inlineStr">
+      <c r="U37" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py aves 5440 audio/OBRA-036_capa.wav --semilla 903477 --raiz 852 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-036_852_yo.wav audio/OBRA-036_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-036_capa.wav</t>
         </is>
       </c>
-      <c r="U37" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="V37" s="4" t="inlineStr"/>
+      <c r="V37" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="W37" s="4" t="inlineStr"/>
       <c r="X37" s="4" t="inlineStr"/>
-      <c r="Y37" s="5">
-        <f>IFERROR(X37/W37*1000,"")</f>
+      <c r="Y37" s="4" t="inlineStr"/>
+      <c r="Z37" s="5">
+        <f>IFERROR(Y37/X37*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -4873,26 +4987,29 @@
       <c r="R38" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="S38" s="3" t="inlineStr">
+      <c r="S38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 120 --raiz 432 --modo yo --semilla 718809 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="T38" s="2" t="inlineStr">
+      <c r="U38" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py aves 7240 audio/OBRA-037_capa.wav --semilla 718809 --raiz 432 --densidad 2 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-037_432_yo.wav audio/OBRA-037_final.wav --fondo selva --nivel-capa -2 --capa audio/OBRA-037_capa.wav</t>
         </is>
       </c>
-      <c r="U38" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="V38" s="4" t="inlineStr"/>
+      <c r="V38" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="W38" s="4" t="inlineStr"/>
       <c r="X38" s="4" t="inlineStr"/>
-      <c r="Y38" s="5">
-        <f>IFERROR(X38/W38*1000,"")</f>
+      <c r="Y38" s="4" t="inlineStr"/>
+      <c r="Z38" s="5">
+        <f>IFERROR(Y38/X38*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -4987,26 +5104,29 @@
       <c r="R39" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="S39" s="3" t="inlineStr">
+      <c r="S39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 120 --raiz 528 --modo shin --semilla 203246 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="T39" s="2" t="inlineStr">
+      <c r="U39" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/ambiente.py audio/OBRA-038_528_shin.wav audio/OBRA-038_final.wav --fondo mar</t>
         </is>
       </c>
-      <c r="U39" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="V39" s="4" t="inlineStr"/>
+      <c r="V39" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="W39" s="4" t="inlineStr"/>
       <c r="X39" s="4" t="inlineStr"/>
-      <c r="Y39" s="5">
-        <f>IFERROR(X39/W39*1000,"")</f>
+      <c r="Y39" s="4" t="inlineStr"/>
+      <c r="Z39" s="5">
+        <f>IFERROR(Y39/X39*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -5101,26 +5221,29 @@
       <c r="R40" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="S40" s="3" t="inlineStr">
+      <c r="S40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 90 --raiz 639 --modo yo --semilla 281608 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="T40" s="2" t="inlineStr">
+      <c r="U40" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py aves 5440 audio/OBRA-039_capa.wav --semilla 281608 --raiz 639 --densidad 2 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-039_639_yo.wav audio/OBRA-039_final.wav --fondo selva --nivel-capa -2 --capa audio/OBRA-039_capa.wav</t>
         </is>
       </c>
-      <c r="U40" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="V40" s="4" t="inlineStr"/>
+      <c r="V40" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="W40" s="4" t="inlineStr"/>
       <c r="X40" s="4" t="inlineStr"/>
-      <c r="Y40" s="5">
-        <f>IFERROR(X40/W40*1000,"")</f>
+      <c r="Y40" s="4" t="inlineStr"/>
+      <c r="Z40" s="5">
+        <f>IFERROR(Y40/X40*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -5215,26 +5338,29 @@
       <c r="R41" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="S41" s="3" t="inlineStr">
+      <c r="S41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 180 --raiz 741 --modo yo --semilla 883876 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="T41" s="2" t="inlineStr">
+      <c r="U41" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py aves 10840 audio/OBRA-040_capa.wav --semilla 883876 --raiz 741 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-040_741_yo.wav audio/OBRA-040_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-040_capa.wav</t>
         </is>
       </c>
-      <c r="U41" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="V41" s="4" t="inlineStr"/>
+      <c r="V41" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="W41" s="4" t="inlineStr"/>
       <c r="X41" s="4" t="inlineStr"/>
-      <c r="Y41" s="5">
-        <f>IFERROR(X41/W41*1000,"")</f>
+      <c r="Y41" s="4" t="inlineStr"/>
+      <c r="Z41" s="5">
+        <f>IFERROR(Y41/X41*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -5330,30 +5456,33 @@
       <c r="R42" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="S42" s="3" t="inlineStr">
+      <c r="S42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 60 --raiz 432 --modo hirajoshi --semilla 304617 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="T42" s="2" t="inlineStr">
+      <c r="U42" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py jardin 3640 audio/OBRA-041_capa.wav --semilla 304617 --raiz 432 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-041_432_hirajoshi.wav audio/OBRA-041_final.wav --fondo mar --nivel-fondo -8 --nivel-capa 0 --capa audio/OBRA-041_capa.wav</t>
         </is>
       </c>
-      <c r="U42" s="4" t="inlineStr">
+      <c r="V42" s="4" t="inlineStr">
         <is>
           <t>publicada</t>
         </is>
       </c>
-      <c r="V42" s="4" t="inlineStr">
+      <c r="W42" s="4" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="W42" s="4" t="inlineStr"/>
       <c r="X42" s="4" t="inlineStr"/>
-      <c r="Y42" s="5">
-        <f>IFERROR(X42/W42*1000,"")</f>
+      <c r="Y42" s="4" t="inlineStr"/>
+      <c r="Z42" s="5">
+        <f>IFERROR(Y42/X42*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -5449,35 +5578,152 @@
       <c r="R43" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="S43" s="3" t="inlineStr">
+      <c r="S43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 180 --raiz 528 --modo shin --semilla 266691 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="T43" s="2" t="inlineStr">
+      <c r="U43" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py zen 10840 audio/OBRA-042_capa.wav --semilla 266691 --raiz 528 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-042_528_shin.wav audio/OBRA-042_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-042_capa.wav</t>
         </is>
       </c>
-      <c r="U43" s="4" t="inlineStr">
+      <c r="V43" s="4" t="inlineStr">
         <is>
           <t>publicada</t>
         </is>
       </c>
-      <c r="V43" s="4" t="inlineStr">
+      <c r="W43" s="4" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="W43" s="4" t="inlineStr"/>
       <c r="X43" s="4" t="inlineStr"/>
-      <c r="Y43" s="5">
-        <f>IFERROR(X43/W43*1000,"")</f>
+      <c r="Y43" s="4" t="inlineStr"/>
+      <c r="Z43" s="5">
+        <f>IFERROR(Y43/X43*1000,"")</f>
         <v/>
       </c>
     </row>
+    <row r="44" ht="58" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-043</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Dark Screen Sleep Music 🌙 Gentle Rain for Deep Sleep · Fall Asleep Fast · 432 Hz · 3 Hours</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Música para dormir · Lluvia suave · 432 Hz · Pantalla oscura · 3 horas</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Dormir</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>lluvia</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Three hours of dark screen sleep music: gentle rain and a slow, warm drone for deep sleep.
+The screen fades to black after 3 minutes, so no light keeps you awake. The music slows to 3.5 breaths per minute: let your breathing follow it down.
+🌙 Lights off, phone face down, volume low. Nothing else to do tonight.
+🌿 Subscribe for a new calm piece every week: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+Original composition by Rin, synthesized from scratch in just intonation around 216 Hz, the low octave of 432 Hz, kumoi mode. No samples.
+#sleepmusic #darkscreen #432hz</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Pantalla oscura · 3 horas
+Para acompañar el sueño.
+Ambiente: lluvia suave.
+Compuesta con raíz en 216 Hz, la octava grave de 432 Hz, en entonación justa, modo kumoi.
+Ciclo respiratorio: de 4.5 a 3.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#sleepmusic #meditation #432hz</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>3 HOURS</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>#sleepmusic #darkscreen #432hz</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>dark screen sleep music, black screen sleep music, sleep music, deep sleep music, sleeping music for deep sleeping, fall asleep fast, rain sounds for sleeping, gentle rain, sleep music for anxiety, insomnia, cortisol reset, relaxing sleep music, music for sleep, 432 hz, 432 hz sleep music, 3 hours, rin, música para dormir</t>
+        </is>
+      </c>
+      <c r="K44" s="4" t="inlineStr"/>
+      <c r="L44" s="4" t="inlineStr"/>
+      <c r="M44" s="2" t="n">
+        <v>432</v>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>kumoi</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>grave</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="n">
+        <v>615127</v>
+      </c>
+      <c r="Q44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="S44" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T44" s="3" t="inlineStr">
+        <is>
+          <t>python3 03-composicion/compositor.py --minutos 180 --raiz 432 --modo kumoi --semilla 615127 --caracter sin-cuenco --registro grave</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>python3 03-composicion/ambiente.py audio/OBRA-043_432_kumoi.wav audio/OBRA-043_final.wav --fondo lluvia</t>
+        </is>
+      </c>
+      <c r="V44" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="W44" s="4" t="inlineStr"/>
+      <c r="X44" s="4" t="inlineStr"/>
+      <c r="Y44" s="4" t="inlineStr"/>
+      <c r="Z44" s="5">
+        <f>IFERROR(Y44/X44*1000,"")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y43"/>
+  <autoFilter ref="A1:Z44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5488,7 +5734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S295"/>
+  <dimension ref="A1:S298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -26987,8 +27233,224 @@
       <c r="R295" s="4" t="inlineStr"/>
       <c r="S295" s="4" t="inlineStr"/>
     </row>
+    <row r="296" ht="58" customHeight="1">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-043-S1</t>
+        </is>
+      </c>
+      <c r="B296" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-043</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D296" s="2" t="inlineStr">
+        <is>
+          <t>short-1.mp4</t>
+        </is>
+      </c>
+      <c r="E296" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="F296" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G296" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H296" s="2" t="inlineStr">
+        <is>
+          <t>to fall asleep</t>
+        </is>
+      </c>
+      <c r="I296" s="3" t="inlineStr">
+        <is>
+          <t>To fall asleep · 432 Hz · Gentle Rain</t>
+        </is>
+      </c>
+      <c r="J296" s="3" t="inlineStr">
+        <is>
+          <t>Save this for tonight.
+Full piece (3 h): Dark Screen Sleep Music 🌙 Gentle Rain for Deep Sleep · Fall Asleep Fast · 432 Hz · 3 Hours
+#sleepmusic #sleep #relaxingmusic #432hz #shorts</t>
+        </is>
+      </c>
+      <c r="K296" s="2" t="inlineStr">
+        <is>
+          <t>sleep music, deep sleep, 432 hz, gentle rain, Rin</t>
+        </is>
+      </c>
+      <c r="L296" s="2" t="inlineStr"/>
+      <c r="M296" s="2" t="inlineStr">
+        <is>
+          <t>432 Hz · sleep</t>
+        </is>
+      </c>
+      <c r="N296" s="3" t="inlineStr">
+        <is>
+          <t>Save this for tonight. Full 3 h piece on YouTube: Rin.
+#sleepmusic #sleep #relaxingmusic #432hz #meditation</t>
+        </is>
+      </c>
+      <c r="O296" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="P296" s="4" t="inlineStr"/>
+      <c r="Q296" s="4" t="inlineStr"/>
+      <c r="R296" s="4" t="inlineStr"/>
+      <c r="S296" s="4" t="inlineStr"/>
+    </row>
+    <row r="297" ht="58" customHeight="1">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-043-S2</t>
+        </is>
+      </c>
+      <c r="B297" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-043</t>
+        </is>
+      </c>
+      <c r="C297" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D297" s="2" t="inlineStr">
+        <is>
+          <t>short-2.mp4</t>
+        </is>
+      </c>
+      <c r="E297" s="2" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F297" s="2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="G297" s="2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H297" s="2" t="inlineStr">
+        <is>
+          <t>let the day go quiet</t>
+        </is>
+      </c>
+      <c r="I297" s="3" t="inlineStr">
+        <is>
+          <t>Let the day go quiet · 432 Hz · Gentle Rain</t>
+        </is>
+      </c>
+      <c r="J297" s="3" t="inlineStr">
+        <is>
+          <t>Lights off, volume low.
+Full piece (3 h): Dark Screen Sleep Music 🌙 Gentle Rain for Deep Sleep · Fall Asleep Fast · 432 Hz · 3 Hours
+#sleepmusic #sleep #relaxingmusic #432hz #shorts</t>
+        </is>
+      </c>
+      <c r="K297" s="2" t="inlineStr">
+        <is>
+          <t>sleep music, deep sleep, 432 hz, gentle rain, Rin</t>
+        </is>
+      </c>
+      <c r="L297" s="2" t="inlineStr"/>
+      <c r="M297" s="2" t="inlineStr">
+        <is>
+          <t>432 Hz · night</t>
+        </is>
+      </c>
+      <c r="N297" s="3" t="inlineStr">
+        <is>
+          <t>Lights off, volume low. Full 3 h piece on YouTube: Rin.
+#sleepmusic #sleep #relaxingmusic #432hz #meditation</t>
+        </is>
+      </c>
+      <c r="O297" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="P297" s="4" t="inlineStr"/>
+      <c r="Q297" s="4" t="inlineStr"/>
+      <c r="R297" s="4" t="inlineStr"/>
+      <c r="S297" s="4" t="inlineStr"/>
+    </row>
+    <row r="298" ht="58" customHeight="1">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-043-S3</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-043</t>
+        </is>
+      </c>
+      <c r="C298" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D298" s="2" t="inlineStr">
+        <is>
+          <t>short-3.mp4</t>
+        </is>
+      </c>
+      <c r="E298" s="2" t="n">
+        <v>10775</v>
+      </c>
+      <c r="F298" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G298" s="2" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="H298" s="2" t="inlineStr">
+        <is>
+          <t>lights off, breathe slower</t>
+        </is>
+      </c>
+      <c r="I298" s="3" t="inlineStr">
+        <is>
+          <t>Lights off, breathe slower · 432 Hz · Gentle Rain</t>
+        </is>
+      </c>
+      <c r="J298" s="3" t="inlineStr">
+        <is>
+          <t>Stay until your breathing slows.
+Full piece (3 h): Dark Screen Sleep Music 🌙 Gentle Rain for Deep Sleep · Fall Asleep Fast · 432 Hz · 3 Hours
+#sleepmusic #sleep #relaxingmusic #432hz #shorts</t>
+        </is>
+      </c>
+      <c r="K298" s="2" t="inlineStr">
+        <is>
+          <t>sleep music, deep sleep, 432 hz, gentle rain, Rin</t>
+        </is>
+      </c>
+      <c r="L298" s="2" t="inlineStr"/>
+      <c r="M298" s="2" t="inlineStr">
+        <is>
+          <t>432 Hz · rest</t>
+        </is>
+      </c>
+      <c r="N298" s="3" t="inlineStr">
+        <is>
+          <t>Stay until your breathing slows. Full 3 h piece on YouTube: Rin.
+#sleepmusic #sleep #relaxingmusic #432hz #meditation</t>
+        </is>
+      </c>
+      <c r="O298" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="P298" s="4" t="inlineStr"/>
+      <c r="Q298" s="4" t="inlineStr"/>
+      <c r="R298" s="4" t="inlineStr"/>
+      <c r="S298" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S295"/>
+  <autoFilter ref="A1:S298"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -27023,7 +27485,7 @@
         </is>
       </c>
       <c r="B2" s="7">
-        <f>COUNTA(Catálogo!A2:A43)</f>
+        <f>COUNTA(Catálogo!A2:A44)</f>
         <v/>
       </c>
     </row>
@@ -27034,7 +27496,7 @@
         </is>
       </c>
       <c r="B3" s="7">
-        <f>COUNTIF(Catálogo!U2:U43,"pendiente")</f>
+        <f>COUNTIF(Catálogo!V2:V44,"pendiente")</f>
         <v/>
       </c>
     </row>
@@ -27045,7 +27507,7 @@
         </is>
       </c>
       <c r="B4" s="7">
-        <f>COUNTIF(Catálogo!U2:U43,"compuesta")</f>
+        <f>COUNTIF(Catálogo!V2:V44,"compuesta")</f>
         <v/>
       </c>
     </row>
@@ -27056,7 +27518,7 @@
         </is>
       </c>
       <c r="B5" s="7">
-        <f>COUNTIF(Catálogo!U2:U43,"montada")</f>
+        <f>COUNTIF(Catálogo!V2:V44,"montada")</f>
         <v/>
       </c>
     </row>
@@ -27067,7 +27529,7 @@
         </is>
       </c>
       <c r="B6" s="7">
-        <f>COUNTIF(Catálogo!U2:U43,"publicada")</f>
+        <f>COUNTIF(Catálogo!V2:V44,"publicada")</f>
         <v/>
       </c>
     </row>
@@ -27107,15 +27569,15 @@
         </is>
       </c>
       <c r="B10" s="7">
-        <f>COUNTIF(Catálogo!D2:D43,A10)</f>
+        <f>COUNTIF(Catálogo!D2:D44,A10)</f>
         <v/>
       </c>
       <c r="C10" s="7">
-        <f>COUNTIFS(Catálogo!D2:D43,A10,Catálogo!U2:U43,"publicada")</f>
+        <f>COUNTIFS(Catálogo!D2:D44,A10,Catálogo!V2:V44,"publicada")</f>
         <v/>
       </c>
       <c r="D10" s="7">
-        <f>SUMIF(Catálogo!D2:D43,A10,Catálogo!R2:R43)</f>
+        <f>SUMIF(Catálogo!D2:D44,A10,Catálogo!R2:R44)</f>
         <v/>
       </c>
     </row>
@@ -27126,15 +27588,15 @@
         </is>
       </c>
       <c r="B11" s="7">
-        <f>COUNTIF(Catálogo!D2:D43,A11)</f>
+        <f>COUNTIF(Catálogo!D2:D44,A11)</f>
         <v/>
       </c>
       <c r="C11" s="7">
-        <f>COUNTIFS(Catálogo!D2:D43,A11,Catálogo!U2:U43,"publicada")</f>
+        <f>COUNTIFS(Catálogo!D2:D44,A11,Catálogo!V2:V44,"publicada")</f>
         <v/>
       </c>
       <c r="D11" s="7">
-        <f>SUMIF(Catálogo!D2:D43,A11,Catálogo!R2:R43)</f>
+        <f>SUMIF(Catálogo!D2:D44,A11,Catálogo!R2:R44)</f>
         <v/>
       </c>
     </row>
@@ -27145,15 +27607,15 @@
         </is>
       </c>
       <c r="B12" s="7">
-        <f>COUNTIF(Catálogo!D2:D43,A12)</f>
+        <f>COUNTIF(Catálogo!D2:D44,A12)</f>
         <v/>
       </c>
       <c r="C12" s="7">
-        <f>COUNTIFS(Catálogo!D2:D43,A12,Catálogo!U2:U43,"publicada")</f>
+        <f>COUNTIFS(Catálogo!D2:D44,A12,Catálogo!V2:V44,"publicada")</f>
         <v/>
       </c>
       <c r="D12" s="7">
-        <f>SUMIF(Catálogo!D2:D43,A12,Catálogo!R2:R43)</f>
+        <f>SUMIF(Catálogo!D2:D44,A12,Catálogo!R2:R44)</f>
         <v/>
       </c>
     </row>
@@ -27164,15 +27626,15 @@
         </is>
       </c>
       <c r="B13" s="7">
-        <f>COUNTIF(Catálogo!D2:D43,A13)</f>
+        <f>COUNTIF(Catálogo!D2:D44,A13)</f>
         <v/>
       </c>
       <c r="C13" s="7">
-        <f>COUNTIFS(Catálogo!D2:D43,A13,Catálogo!U2:U43,"publicada")</f>
+        <f>COUNTIFS(Catálogo!D2:D44,A13,Catálogo!V2:V44,"publicada")</f>
         <v/>
       </c>
       <c r="D13" s="7">
-        <f>SUMIF(Catálogo!D2:D43,A13,Catálogo!R2:R43)</f>
+        <f>SUMIF(Catálogo!D2:D44,A13,Catálogo!R2:R44)</f>
         <v/>
       </c>
     </row>
@@ -27183,15 +27645,15 @@
         </is>
       </c>
       <c r="B14" s="7">
-        <f>COUNTIF(Catálogo!D2:D43,A14)</f>
+        <f>COUNTIF(Catálogo!D2:D44,A14)</f>
         <v/>
       </c>
       <c r="C14" s="7">
-        <f>COUNTIFS(Catálogo!D2:D43,A14,Catálogo!U2:U43,"publicada")</f>
+        <f>COUNTIFS(Catálogo!D2:D44,A14,Catálogo!V2:V44,"publicada")</f>
         <v/>
       </c>
       <c r="D14" s="7">
-        <f>SUMIF(Catálogo!D2:D43,A14,Catálogo!R2:R43)</f>
+        <f>SUMIF(Catálogo!D2:D44,A14,Catálogo!R2:R44)</f>
         <v/>
       </c>
     </row>
@@ -27228,7 +27690,7 @@
         </is>
       </c>
       <c r="B18" s="7">
-        <f>SUM(Catálogo!W2:W43)</f>
+        <f>SUM(Catálogo!X2:X44)</f>
         <v/>
       </c>
     </row>
@@ -27239,7 +27701,7 @@
         </is>
       </c>
       <c r="B19" s="7">
-        <f>SUM(Catálogo!X2:X43)</f>
+        <f>SUM(Catálogo!Y2:Y44)</f>
         <v/>
       </c>
     </row>
@@ -27270,7 +27732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -27382,7 +27844,7 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Ambiente aprobado en escucha: mar, mar-aves, zen, selva, lluvia-tambor o jardin.</t>
+          <t>Ambiente aprobado en escucha: mar, mar-aves, zen, selva, lluvia-tambor, jardin o lluvia.</t>
         </is>
       </c>
     </row>
@@ -27401,208 +27863,220 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>descripcion_optimizada</t>
+          <t>pantalla_oscura_min</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Descripción bilingüe lista para pegar. Solo falta añadir los capítulos tras el montaje.</t>
+          <t>Minutos de mandala antes de que la pantalla se funda a negro (videos para dormir). 0: el mandala dura todo el video.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>titulo_miniatura</t>
+          <t>descripcion_optimizada</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Texto de la miniatura: 2-4 palabras que COMPLETAN el título, nunca lo repiten.</t>
+          <t>Descripción bilingüe lista para pegar. Solo falta añadir los capítulos tras el montaje.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>hashtags</t>
+          <t>titulo_miniatura</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Tres, al final de la descripción.</t>
+          <t>Texto de la miniatura: 2-4 palabras que COMPLETAN el título, nunca lo repiten.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>etiquetas</t>
+          <t>hashtags</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Etiquetas del video, separadas por coma.</t>
+          <t>Tres, al final de la descripción.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>imagen_miniatura</t>
+          <t>etiquetas</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>AMARILLA. Ruta o URL de la portada una vez generada.</t>
+          <t>Etiquetas del video, separadas por coma.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>url_video</t>
+          <t>imagen_miniatura</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>AMARILLA. URL de YouTube una vez publicado.</t>
+          <t>AMARILLA. Ruta o URL de la portada una vez generada.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>raiz_hz / modo / registro / semilla</t>
+          <t>url_video</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Parámetros de composición. El registro grave baja una octava (Dormir y Concentración). La semilla regenera la obra idéntica.</t>
+          <t>AMARILLA. URL de YouTube una vez publicado.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>comando_regeneracion</t>
+          <t>raiz_hz / modo / registro / semilla</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Comando exacto. Copiar, pegar y ejecutar: devuelve el mismo audio bit a bit.</t>
+          <t>Parámetros de composición. El registro grave baja una octava (Dormir y Concentración). La semilla regenera la obra idéntica.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>estado</t>
+          <t>comando_regeneracion</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>AMARILLA. pendiente / compuesta / montada / publicada</t>
+          <t>Comando exacto. Copiar, pegar y ejecutar: devuelve el mismo audio bit a bit.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>fecha_publicacion</t>
+          <t>estado</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>AMARILLA. Formato AAAA-MM-DD.</t>
+          <t>AMARILLA. pendiente / compuesta / montada / publicada</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>vistas / suscriptores</t>
+          <t>fecha_publicacion</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>AMARILLA. Copiar de YouTube Studio a los 14 días de publicar.</t>
+          <t>AMARILLA. Formato AAAA-MM-DD.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
+          <t>vistas / suscriptores</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>AMARILLA. Copiar de YouTube Studio a los 14 días de publicar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
           <t>subs_por_1000</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>Calculada. Es la métrica que decide el canal: por debajo de 1, el problema es la portada, no la música.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr"/>
-    </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>Hoja Shorts</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>5 por obra. Cada uno cambia de tramo de la obra, encuadre, instante del mandala y frase.</t>
-        </is>
-      </c>
+      <c r="A26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>tiktok_portada</t>
+          <t>Hoja Shorts</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>El título de la portada en TikTok (el que se ve en el perfil). Distinto de la descripción.</t>
+          <t>5 por obra. Cada uno cambia de tramo de la obra, encuadre, instante del mandala y frase.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>tiktok_descripcion</t>
+          <t>tiktok_portada</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>El texto que acompaña al video en TikTok, con hashtags. En Metricool, nunca en el campo título.</t>
+          <t>El título de la portada en TikTok (el que se ve en el perfil). Distinto de la descripción.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
+          <t>tiktok_descripcion</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>El texto que acompaña al video en TikTok, con hashtags. En Metricool, nunca en el campo título.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
           <t>yt_video_relacionado</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>El video largo. En YouTube Studio va en «Video relacionado» del Short.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr"/>
-    </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>Ejemplo de fila rellenada</t>
         </is>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>imagen_miniatura: portadas/obra-001.png | url_video: https://youtu.be/XXXXXXXXXXX | estado: publicada | fecha_publicacion: 2026-10-07 | vistas: 4820 | suscriptores: 11</t>
         </is>

--- a/08-catalogo/catalogo_canal.xlsx
+++ b/08-catalogo/catalogo_canal.xlsx
@@ -5673,7 +5673,11 @@
         </is>
       </c>
       <c r="K44" s="4" t="inlineStr"/>
-      <c r="L44" s="4" t="inlineStr"/>
+      <c r="L44" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/YtFJIL4q4SI</t>
+        </is>
+      </c>
       <c r="M44" s="2" t="n">
         <v>432</v>
       </c>
@@ -5711,10 +5715,14 @@
       </c>
       <c r="V44" s="4" t="inlineStr">
         <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W44" s="4" t="inlineStr"/>
+          <t>publicada</t>
+        </is>
+      </c>
+      <c r="W44" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="X44" s="4" t="inlineStr"/>
       <c r="Y44" s="4" t="inlineStr"/>
       <c r="Z44" s="5">
@@ -27275,6 +27283,7 @@
         <is>
           <t>Save this for tonight.
 Full piece (3 h): Dark Screen Sleep Music 🌙 Gentle Rain for Deep Sleep · Fall Asleep Fast · 432 Hz · 3 Hours
+https://youtu.be/YtFJIL4q4SI
 #sleepmusic #sleep #relaxingmusic #432hz #shorts</t>
         </is>
       </c>
@@ -27283,7 +27292,11 @@
           <t>sleep music, deep sleep, 432 hz, gentle rain, Rin</t>
         </is>
       </c>
-      <c r="L296" s="2" t="inlineStr"/>
+      <c r="L296" s="2" t="inlineStr">
+        <is>
+          <t>https://youtu.be/YtFJIL4q4SI</t>
+        </is>
+      </c>
       <c r="M296" s="2" t="inlineStr">
         <is>
           <t>432 Hz · sleep</t>
@@ -27347,6 +27360,7 @@
         <is>
           <t>Lights off, volume low.
 Full piece (3 h): Dark Screen Sleep Music 🌙 Gentle Rain for Deep Sleep · Fall Asleep Fast · 432 Hz · 3 Hours
+https://youtu.be/YtFJIL4q4SI
 #sleepmusic #sleep #relaxingmusic #432hz #shorts</t>
         </is>
       </c>
@@ -27355,7 +27369,11 @@
           <t>sleep music, deep sleep, 432 hz, gentle rain, Rin</t>
         </is>
       </c>
-      <c r="L297" s="2" t="inlineStr"/>
+      <c r="L297" s="2" t="inlineStr">
+        <is>
+          <t>https://youtu.be/YtFJIL4q4SI</t>
+        </is>
+      </c>
       <c r="M297" s="2" t="inlineStr">
         <is>
           <t>432 Hz · night</t>
@@ -27419,6 +27437,7 @@
         <is>
           <t>Stay until your breathing slows.
 Full piece (3 h): Dark Screen Sleep Music 🌙 Gentle Rain for Deep Sleep · Fall Asleep Fast · 432 Hz · 3 Hours
+https://youtu.be/YtFJIL4q4SI
 #sleepmusic #sleep #relaxingmusic #432hz #shorts</t>
         </is>
       </c>
@@ -27427,7 +27446,11 @@
           <t>sleep music, deep sleep, 432 hz, gentle rain, Rin</t>
         </is>
       </c>
-      <c r="L298" s="2" t="inlineStr"/>
+      <c r="L298" s="2" t="inlineStr">
+        <is>
+          <t>https://youtu.be/YtFJIL4q4SI</t>
+        </is>
+      </c>
       <c r="M298" s="2" t="inlineStr">
         <is>
           <t>432 Hz · rest</t>

--- a/08-catalogo/catalogo_canal.xlsx
+++ b/08-catalogo/catalogo_canal.xlsx
@@ -13,8 +13,8 @@
     <sheet name="Leyenda" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$Z$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Shorts'!$A$1:$S$298</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$Z$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Shorts'!$A$1:$S$301</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z44"/>
+  <dimension ref="A1:Z45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -5730,8 +5730,122 @@
         <v/>
       </c>
     </row>
+    <row r="45" ht="58" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-044</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Deep Sleep Theta Waves 🌙 Turn Off Your Thoughts · Dark Screen · Fall Asleep Fast · 3 Hours</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Música para dormir · Mar lejano y ondas theta · 432 Hz · Ondas theta · 3 horas</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Dormir</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>theta</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Three hours of theta waves for deep sleep, over a distant ocean and a slow, warm drone.
+🎧 Use headphones: the left and right ears hear two tones 6 Hz apart. Over the hours the difference slows from theta (6 Hz, drifting off) to delta (2 Hz, deep sleep). The screen fades to black after 3 minutes.
+🌙 Lights off, phone face down, volume low. Let your thoughts go quiet.
+🌿 Subscribe for a new calm piece every week: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+Original composition by Rin, synthesized from scratch in just intonation around 216 Hz, the low octave of 432 Hz, shin mode. No samples.
+#thetawaves #sleepmusic #darkscreen</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Ondas theta · 3 horas
+Para acompañar el sueño.
+Ambiente: mar lejano y ondas theta.
+Compuesta con raíz en 216 Hz, la octava grave de 432 Hz, en entonación justa, modo shin.
+Ciclo respiratorio: de 4.5 a 3.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#sleepmusic #meditation #432hz</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>3 HOURS</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>#thetawaves #sleepmusic #darkscreen</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>theta waves, theta waves sleep, deep sleep theta waves, binaural beats, binaural beats for sleep, delta waves, dark screen sleep music, black screen sleep music, deep sleep music, fall asleep fast, turn off your thoughts, stop overthinking, sleep meditation, ocean waves, 432 hz, 3 hours, rin, música para dormir</t>
+        </is>
+      </c>
+      <c r="K45" s="4" t="inlineStr"/>
+      <c r="L45" s="4" t="inlineStr"/>
+      <c r="M45" s="2" t="n">
+        <v>432</v>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>shin</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>grave</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="n">
+        <v>810318</v>
+      </c>
+      <c r="Q45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="S45" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T45" s="3" t="inlineStr">
+        <is>
+          <t>python3 03-composicion/compositor.py --minutos 180 --raiz 432 --modo shin --semilla 810318 --caracter sin-cuenco --registro grave</t>
+        </is>
+      </c>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>python3 03-composicion/capas.py theta 10840 audio/OBRA-044_capa.wav --semilla 810318 --raiz 432 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-044_432_shin.wav audio/OBRA-044_final.wav --fondo mar --nivel-fondo -4 --nivel-capa -11 --capa audio/OBRA-044_capa.wav</t>
+        </is>
+      </c>
+      <c r="V45" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="W45" s="4" t="inlineStr"/>
+      <c r="X45" s="4" t="inlineStr"/>
+      <c r="Y45" s="4" t="inlineStr"/>
+      <c r="Z45" s="5">
+        <f>IFERROR(Y45/X45*1000,"")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z44"/>
+  <autoFilter ref="A1:Z45"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5742,7 +5856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S298"/>
+  <dimension ref="A1:S301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -27472,8 +27586,224 @@
       <c r="R298" s="4" t="inlineStr"/>
       <c r="S298" s="4" t="inlineStr"/>
     </row>
+    <row r="299" ht="58" customHeight="1">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-044-S1</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-044</t>
+        </is>
+      </c>
+      <c r="C299" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D299" s="2" t="inlineStr">
+        <is>
+          <t>short-1.mp4</t>
+        </is>
+      </c>
+      <c r="E299" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="F299" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G299" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H299" s="2" t="inlineStr">
+        <is>
+          <t>Breathe out longer than you breathe in</t>
+        </is>
+      </c>
+      <c r="I299" s="3" t="inlineStr">
+        <is>
+          <t>Breathe out longer than you breathe in · 432 Hz · Theta Waves</t>
+        </is>
+      </c>
+      <c r="J299" s="3" t="inlineStr">
+        <is>
+          <t>Save this for tonight.
+Full piece (3 h): Deep Sleep Theta Waves 🌙 Turn Off Your Thoughts · Dark Screen · Fall Asleep Fast · 3 Hours
+#sleepmusic #sleep #relaxingmusic #432hz #shorts</t>
+        </is>
+      </c>
+      <c r="K299" s="2" t="inlineStr">
+        <is>
+          <t>sleep music, deep sleep, 432 hz, theta waves, Rin</t>
+        </is>
+      </c>
+      <c r="L299" s="2" t="inlineStr"/>
+      <c r="M299" s="2" t="inlineStr">
+        <is>
+          <t>432 Hz · sleep</t>
+        </is>
+      </c>
+      <c r="N299" s="3" t="inlineStr">
+        <is>
+          <t>Save this for tonight. Full 3 h piece on YouTube: Rin.
+#sleepmusic #sleep #relaxingmusic #432hz #meditation</t>
+        </is>
+      </c>
+      <c r="O299" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="P299" s="4" t="inlineStr"/>
+      <c r="Q299" s="4" t="inlineStr"/>
+      <c r="R299" s="4" t="inlineStr"/>
+      <c r="S299" s="4" t="inlineStr"/>
+    </row>
+    <row r="300" ht="58" customHeight="1">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-044-S2</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-044</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D300" s="2" t="inlineStr">
+        <is>
+          <t>short-2.mp4</t>
+        </is>
+      </c>
+      <c r="E300" s="2" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F300" s="2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="G300" s="2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H300" s="2" t="inlineStr">
+        <is>
+          <t>Unclench your jaw. Let the pillow hold you</t>
+        </is>
+      </c>
+      <c r="I300" s="3" t="inlineStr">
+        <is>
+          <t>Unclench your jaw. Let the pillow hold you · 432 Hz · Theta Waves</t>
+        </is>
+      </c>
+      <c r="J300" s="3" t="inlineStr">
+        <is>
+          <t>Lights off, volume low.
+Full piece (3 h): Deep Sleep Theta Waves 🌙 Turn Off Your Thoughts · Dark Screen · Fall Asleep Fast · 3 Hours
+#sleepmusic #sleep #relaxingmusic #432hz #shorts</t>
+        </is>
+      </c>
+      <c r="K300" s="2" t="inlineStr">
+        <is>
+          <t>sleep music, deep sleep, 432 hz, theta waves, Rin</t>
+        </is>
+      </c>
+      <c r="L300" s="2" t="inlineStr"/>
+      <c r="M300" s="2" t="inlineStr">
+        <is>
+          <t>432 Hz · night</t>
+        </is>
+      </c>
+      <c r="N300" s="3" t="inlineStr">
+        <is>
+          <t>Lights off, volume low. Full 3 h piece on YouTube: Rin.
+#sleepmusic #sleep #relaxingmusic #432hz #meditation</t>
+        </is>
+      </c>
+      <c r="O300" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="P300" s="4" t="inlineStr"/>
+      <c r="Q300" s="4" t="inlineStr"/>
+      <c r="R300" s="4" t="inlineStr"/>
+      <c r="S300" s="4" t="inlineStr"/>
+    </row>
+    <row r="301" ht="58" customHeight="1">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-044-S3</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-044</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D301" s="2" t="inlineStr">
+        <is>
+          <t>short-3.mp4</t>
+        </is>
+      </c>
+      <c r="E301" s="2" t="n">
+        <v>10775</v>
+      </c>
+      <c r="F301" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G301" s="2" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="H301" s="2" t="inlineStr">
+        <is>
+          <t>Close your eyes. Just listen</t>
+        </is>
+      </c>
+      <c r="I301" s="3" t="inlineStr">
+        <is>
+          <t>Close your eyes. Just listen · 432 Hz · Theta Waves</t>
+        </is>
+      </c>
+      <c r="J301" s="3" t="inlineStr">
+        <is>
+          <t>Stay until your breathing slows.
+Full piece (3 h): Deep Sleep Theta Waves 🌙 Turn Off Your Thoughts · Dark Screen · Fall Asleep Fast · 3 Hours
+#sleepmusic #sleep #relaxingmusic #432hz #shorts</t>
+        </is>
+      </c>
+      <c r="K301" s="2" t="inlineStr">
+        <is>
+          <t>sleep music, deep sleep, 432 hz, theta waves, Rin</t>
+        </is>
+      </c>
+      <c r="L301" s="2" t="inlineStr"/>
+      <c r="M301" s="2" t="inlineStr">
+        <is>
+          <t>432 Hz · rest</t>
+        </is>
+      </c>
+      <c r="N301" s="3" t="inlineStr">
+        <is>
+          <t>Stay until your breathing slows. Full 3 h piece on YouTube: Rin.
+#sleepmusic #sleep #relaxingmusic #432hz #meditation</t>
+        </is>
+      </c>
+      <c r="O301" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="P301" s="4" t="inlineStr"/>
+      <c r="Q301" s="4" t="inlineStr"/>
+      <c r="R301" s="4" t="inlineStr"/>
+      <c r="S301" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S298"/>
+  <autoFilter ref="A1:S301"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -27508,7 +27838,7 @@
         </is>
       </c>
       <c r="B2" s="7">
-        <f>COUNTA(Catálogo!A2:A44)</f>
+        <f>COUNTA(Catálogo!A2:A45)</f>
         <v/>
       </c>
     </row>
@@ -27519,7 +27849,7 @@
         </is>
       </c>
       <c r="B3" s="7">
-        <f>COUNTIF(Catálogo!V2:V44,"pendiente")</f>
+        <f>COUNTIF(Catálogo!V2:V45,"pendiente")</f>
         <v/>
       </c>
     </row>
@@ -27530,7 +27860,7 @@
         </is>
       </c>
       <c r="B4" s="7">
-        <f>COUNTIF(Catálogo!V2:V44,"compuesta")</f>
+        <f>COUNTIF(Catálogo!V2:V45,"compuesta")</f>
         <v/>
       </c>
     </row>
@@ -27541,7 +27871,7 @@
         </is>
       </c>
       <c r="B5" s="7">
-        <f>COUNTIF(Catálogo!V2:V44,"montada")</f>
+        <f>COUNTIF(Catálogo!V2:V45,"montada")</f>
         <v/>
       </c>
     </row>
@@ -27552,7 +27882,7 @@
         </is>
       </c>
       <c r="B6" s="7">
-        <f>COUNTIF(Catálogo!V2:V44,"publicada")</f>
+        <f>COUNTIF(Catálogo!V2:V45,"publicada")</f>
         <v/>
       </c>
     </row>
@@ -27592,15 +27922,15 @@
         </is>
       </c>
       <c r="B10" s="7">
-        <f>COUNTIF(Catálogo!D2:D44,A10)</f>
+        <f>COUNTIF(Catálogo!D2:D45,A10)</f>
         <v/>
       </c>
       <c r="C10" s="7">
-        <f>COUNTIFS(Catálogo!D2:D44,A10,Catálogo!V2:V44,"publicada")</f>
+        <f>COUNTIFS(Catálogo!D2:D45,A10,Catálogo!V2:V45,"publicada")</f>
         <v/>
       </c>
       <c r="D10" s="7">
-        <f>SUMIF(Catálogo!D2:D44,A10,Catálogo!R2:R44)</f>
+        <f>SUMIF(Catálogo!D2:D45,A10,Catálogo!R2:R45)</f>
         <v/>
       </c>
     </row>
@@ -27611,15 +27941,15 @@
         </is>
       </c>
       <c r="B11" s="7">
-        <f>COUNTIF(Catálogo!D2:D44,A11)</f>
+        <f>COUNTIF(Catálogo!D2:D45,A11)</f>
         <v/>
       </c>
       <c r="C11" s="7">
-        <f>COUNTIFS(Catálogo!D2:D44,A11,Catálogo!V2:V44,"publicada")</f>
+        <f>COUNTIFS(Catálogo!D2:D45,A11,Catálogo!V2:V45,"publicada")</f>
         <v/>
       </c>
       <c r="D11" s="7">
-        <f>SUMIF(Catálogo!D2:D44,A11,Catálogo!R2:R44)</f>
+        <f>SUMIF(Catálogo!D2:D45,A11,Catálogo!R2:R45)</f>
         <v/>
       </c>
     </row>
@@ -27630,15 +27960,15 @@
         </is>
       </c>
       <c r="B12" s="7">
-        <f>COUNTIF(Catálogo!D2:D44,A12)</f>
+        <f>COUNTIF(Catálogo!D2:D45,A12)</f>
         <v/>
       </c>
       <c r="C12" s="7">
-        <f>COUNTIFS(Catálogo!D2:D44,A12,Catálogo!V2:V44,"publicada")</f>
+        <f>COUNTIFS(Catálogo!D2:D45,A12,Catálogo!V2:V45,"publicada")</f>
         <v/>
       </c>
       <c r="D12" s="7">
-        <f>SUMIF(Catálogo!D2:D44,A12,Catálogo!R2:R44)</f>
+        <f>SUMIF(Catálogo!D2:D45,A12,Catálogo!R2:R45)</f>
         <v/>
       </c>
     </row>
@@ -27649,15 +27979,15 @@
         </is>
       </c>
       <c r="B13" s="7">
-        <f>COUNTIF(Catálogo!D2:D44,A13)</f>
+        <f>COUNTIF(Catálogo!D2:D45,A13)</f>
         <v/>
       </c>
       <c r="C13" s="7">
-        <f>COUNTIFS(Catálogo!D2:D44,A13,Catálogo!V2:V44,"publicada")</f>
+        <f>COUNTIFS(Catálogo!D2:D45,A13,Catálogo!V2:V45,"publicada")</f>
         <v/>
       </c>
       <c r="D13" s="7">
-        <f>SUMIF(Catálogo!D2:D44,A13,Catálogo!R2:R44)</f>
+        <f>SUMIF(Catálogo!D2:D45,A13,Catálogo!R2:R45)</f>
         <v/>
       </c>
     </row>
@@ -27668,15 +27998,15 @@
         </is>
       </c>
       <c r="B14" s="7">
-        <f>COUNTIF(Catálogo!D2:D44,A14)</f>
+        <f>COUNTIF(Catálogo!D2:D45,A14)</f>
         <v/>
       </c>
       <c r="C14" s="7">
-        <f>COUNTIFS(Catálogo!D2:D44,A14,Catálogo!V2:V44,"publicada")</f>
+        <f>COUNTIFS(Catálogo!D2:D45,A14,Catálogo!V2:V45,"publicada")</f>
         <v/>
       </c>
       <c r="D14" s="7">
-        <f>SUMIF(Catálogo!D2:D44,A14,Catálogo!R2:R44)</f>
+        <f>SUMIF(Catálogo!D2:D45,A14,Catálogo!R2:R45)</f>
         <v/>
       </c>
     </row>
@@ -27713,7 +28043,7 @@
         </is>
       </c>
       <c r="B18" s="7">
-        <f>SUM(Catálogo!X2:X44)</f>
+        <f>SUM(Catálogo!X2:X45)</f>
         <v/>
       </c>
     </row>
@@ -27724,7 +28054,7 @@
         </is>
       </c>
       <c r="B19" s="7">
-        <f>SUM(Catálogo!Y2:Y44)</f>
+        <f>SUM(Catálogo!Y2:Y45)</f>
         <v/>
       </c>
     </row>
@@ -27867,7 +28197,7 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Ambiente aprobado en escucha: mar, mar-aves, zen, selva, lluvia-tambor, jardin o lluvia.</t>
+          <t>Ambiente aprobado en escucha: mar, mar-aves, zen, selva, lluvia-tambor, jardin, lluvia o theta.</t>
         </is>
       </c>
     </row>

--- a/08-catalogo/catalogo_canal.xlsx
+++ b/08-catalogo/catalogo_canal.xlsx
@@ -5758,8 +5758,8 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>Three hours of theta waves for deep sleep, over a distant ocean and a slow, warm drone.
-🎧 Use headphones: the left and right ears hear two tones 6 Hz apart. Over the hours the difference slows from theta (6 Hz, drifting off) to delta (2 Hz, deep sleep). The screen fades to black after 3 minutes.
+          <t>Three hours of theta waves for deep sleep, over a distant ocean and a slow, warm drone. 🎧 Use headphones for the best experience.
+With headphones, each ear hears a slightly different tone, 6 Hz apart. Over the hours the difference slows from theta (6 Hz, drifting off) to delta (2 Hz, deep sleep). The screen fades to black after 3 minutes.
 🌙 Lights off, phone face down, volume low. Let your thoughts go quiet.
 🌿 Subscribe for a new calm piece every week: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
 Original composition by Rin, synthesized from scratch in just intonation around 216 Hz, the low octave of 432 Hz, shin mode. No samples.
@@ -5771,6 +5771,7 @@
           <t>Ondas theta · 3 horas
 Para acompañar el sueño.
 Ambiente: mar lejano y ondas theta.
+🎧 Usa auriculares para una mejor experiencia: cada oído escucha un tono apenas distinto y la diferencia baja de theta (6 Hz) a delta (2 Hz).
 Compuesta con raíz en 216 Hz, la octava grave de 432 Hz, en entonación justa, modo shin.
 Ciclo respiratorio: de 4.5 a 3.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
@@ -27626,7 +27627,7 @@
       </c>
       <c r="J299" s="3" t="inlineStr">
         <is>
-          <t>Save this for tonight.
+          <t>🎧 Use headphones for the best experience. Save this for tonight.
 Full piece (3 h): Deep Sleep Theta Waves 🌙 Turn Off Your Thoughts · Dark Screen · Fall Asleep Fast · 3 Hours
 #sleepmusic #sleep #relaxingmusic #432hz #shorts</t>
         </is>
@@ -27644,7 +27645,7 @@
       </c>
       <c r="N299" s="3" t="inlineStr">
         <is>
-          <t>Save this for tonight. Full 3 h piece on YouTube: Rin.
+          <t>🎧 Use headphones for the best experience. Save this for tonight. Full 3 h piece on YouTube: Rin.
 #sleepmusic #sleep #relaxingmusic #432hz #meditation</t>
         </is>
       </c>
@@ -27698,7 +27699,7 @@
       </c>
       <c r="J300" s="3" t="inlineStr">
         <is>
-          <t>Lights off, volume low.
+          <t>🎧 Use headphones for the best experience. Lights off, volume low.
 Full piece (3 h): Deep Sleep Theta Waves 🌙 Turn Off Your Thoughts · Dark Screen · Fall Asleep Fast · 3 Hours
 #sleepmusic #sleep #relaxingmusic #432hz #shorts</t>
         </is>
@@ -27716,7 +27717,7 @@
       </c>
       <c r="N300" s="3" t="inlineStr">
         <is>
-          <t>Lights off, volume low. Full 3 h piece on YouTube: Rin.
+          <t>🎧 Use headphones for the best experience. Lights off, volume low. Full 3 h piece on YouTube: Rin.
 #sleepmusic #sleep #relaxingmusic #432hz #meditation</t>
         </is>
       </c>
@@ -27770,7 +27771,7 @@
       </c>
       <c r="J301" s="3" t="inlineStr">
         <is>
-          <t>Stay until your breathing slows.
+          <t>🎧 Use headphones for the best experience. Stay until your breathing slows.
 Full piece (3 h): Deep Sleep Theta Waves 🌙 Turn Off Your Thoughts · Dark Screen · Fall Asleep Fast · 3 Hours
 #sleepmusic #sleep #relaxingmusic #432hz #shorts</t>
         </is>
@@ -27788,7 +27789,7 @@
       </c>
       <c r="N301" s="3" t="inlineStr">
         <is>
-          <t>Stay until your breathing slows. Full 3 h piece on YouTube: Rin.
+          <t>🎧 Use headphones for the best experience. Stay until your breathing slows. Full 3 h piece on YouTube: Rin.
 #sleepmusic #sleep #relaxingmusic #432hz #meditation</t>
         </is>
       </c>

--- a/08-catalogo/catalogo_canal.xlsx
+++ b/08-catalogo/catalogo_canal.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Leyenda" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$Z$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$AA$45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Shorts'!$A$1:$S$301</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z45"/>
+  <dimension ref="A1:AA45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -511,13 +511,14 @@
     <col width="6" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="62" customWidth="1" min="20" max="20"/>
+    <col width="40" customWidth="1" min="20" max="20"/>
     <col width="62" customWidth="1" min="21" max="21"/>
-    <col width="13" customWidth="1" min="22" max="22"/>
-    <col width="18" customWidth="1" min="23" max="23"/>
-    <col width="10" customWidth="1" min="24" max="24"/>
-    <col width="13" customWidth="1" min="25" max="25"/>
-    <col width="14" customWidth="1" min="26" max="26"/>
+    <col width="62" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="26" max="26"/>
+    <col width="14" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -618,35 +619,40 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>comentario_fijado</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
           <t>comando_regeneracion</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>comando_ambiente</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>estado</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>fecha_publicacion</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>vistas</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>suscriptores</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>subs_por_1000</t>
         </is>
@@ -746,26 +752,31 @@
       <c r="S2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" s="3" t="inlineStr">
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>What keeps you awake at night? 🌙 Write it here and leave it with us. Then press play and let it go. A new sleep piece every week.</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 180 --raiz 432 --modo shin --semilla 505716 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="U2" s="2" t="inlineStr">
+      <c r="V2" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/ambiente.py audio/OBRA-001_432_shin.wav audio/OBRA-001_final.wav --fondo mar</t>
         </is>
       </c>
-      <c r="V2" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W2" s="4" t="inlineStr"/>
+      <c r="W2" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="X2" s="4" t="inlineStr"/>
       <c r="Y2" s="4" t="inlineStr"/>
-      <c r="Z2" s="5">
-        <f>IFERROR(Y2/X2*1000,"")</f>
+      <c r="Z2" s="4" t="inlineStr"/>
+      <c r="AA2" s="5">
+        <f>IFERROR(Z2/Y2*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -863,26 +874,31 @@
       <c r="S3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T3" s="3" t="inlineStr">
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>What keeps you awake at night? 🌙 Write it here and leave it with us. Then press play and let it go. A new sleep piece every week.</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 120 --raiz 528 --modo kumoi --semilla 443547 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="U3" s="2" t="inlineStr">
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/ambiente.py audio/OBRA-002_528_kumoi.wav audio/OBRA-002_final.wav --fondo mar</t>
         </is>
       </c>
-      <c r="V3" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W3" s="4" t="inlineStr"/>
+      <c r="W3" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="X3" s="4" t="inlineStr"/>
       <c r="Y3" s="4" t="inlineStr"/>
-      <c r="Z3" s="5">
-        <f>IFERROR(Y3/X3*1000,"")</f>
+      <c r="Z3" s="4" t="inlineStr"/>
+      <c r="AA3" s="5">
+        <f>IFERROR(Z3/Y3*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -980,26 +996,31 @@
       <c r="S4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T4" s="3" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>What keeps you awake at night? 🌙 Write it here and leave it with us. Then press play and let it go. A new sleep piece every week.</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 120 --raiz 396 --modo kumoi --semilla 692584 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="U4" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/ambiente.py audio/OBRA-003_396_kumoi.wav audio/OBRA-003_final.wav --fondo mar</t>
         </is>
       </c>
-      <c r="V4" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W4" s="4" t="inlineStr"/>
+      <c r="W4" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="X4" s="4" t="inlineStr"/>
       <c r="Y4" s="4" t="inlineStr"/>
-      <c r="Z4" s="5">
-        <f>IFERROR(Y4/X4*1000,"")</f>
+      <c r="Z4" s="4" t="inlineStr"/>
+      <c r="AA4" s="5">
+        <f>IFERROR(Z4/Y4*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -1097,26 +1118,31 @@
       <c r="S5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T5" s="3" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>What keeps you awake at night? 🌙 Write it here and leave it with us. Then press play and let it go. A new sleep piece every week.</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 180 --raiz 528 --modo shin --semilla 751043 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="U5" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/ambiente.py audio/OBRA-004_528_shin.wav audio/OBRA-004_final.wav --fondo mar</t>
         </is>
       </c>
-      <c r="V5" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W5" s="4" t="inlineStr"/>
+      <c r="W5" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="X5" s="4" t="inlineStr"/>
       <c r="Y5" s="4" t="inlineStr"/>
-      <c r="Z5" s="5">
-        <f>IFERROR(Y5/X5*1000,"")</f>
+      <c r="Z5" s="4" t="inlineStr"/>
+      <c r="AA5" s="5">
+        <f>IFERROR(Z5/Y5*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -1214,26 +1240,31 @@
       <c r="S6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T6" s="3" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>What keeps you awake at night? 🌙 Write it here and leave it with us. Then press play and let it go. A new sleep piece every week.</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 120 --raiz 432 --modo kumoi --semilla 531725 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="U6" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/ambiente.py audio/OBRA-005_432_kumoi.wav audio/OBRA-005_final.wav --fondo mar</t>
         </is>
       </c>
-      <c r="V6" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W6" s="4" t="inlineStr"/>
+      <c r="W6" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="X6" s="4" t="inlineStr"/>
       <c r="Y6" s="4" t="inlineStr"/>
-      <c r="Z6" s="5">
-        <f>IFERROR(Y6/X6*1000,"")</f>
+      <c r="Z6" s="4" t="inlineStr"/>
+      <c r="AA6" s="5">
+        <f>IFERROR(Z6/Y6*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -1335,30 +1366,35 @@
       <c r="S7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T7" s="3" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>What keeps you awake at night? 🌙 Write it here and leave it with us. Then press play and let it go. A new sleep piece every week.</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 90 --raiz 417 --modo kumoi --semilla 813147 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="U7" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/ambiente.py audio/OBRA-006_417_kumoi.wav audio/OBRA-006_final.wav --fondo mar</t>
         </is>
       </c>
-      <c r="V7" s="4" t="inlineStr">
+      <c r="W7" s="4" t="inlineStr">
         <is>
           <t>publicada</t>
         </is>
       </c>
-      <c r="W7" s="4" t="inlineStr">
+      <c r="X7" s="4" t="inlineStr">
         <is>
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="X7" s="4" t="inlineStr"/>
       <c r="Y7" s="4" t="inlineStr"/>
-      <c r="Z7" s="5">
-        <f>IFERROR(Y7/X7*1000,"")</f>
+      <c r="Z7" s="4" t="inlineStr"/>
+      <c r="AA7" s="5">
+        <f>IFERROR(Z7/Y7*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -1456,26 +1492,31 @@
       <c r="S8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T8" s="3" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>What keeps you awake at night? 🌙 Write it here and leave it with us. Then press play and let it go. A new sleep piece every week.</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 120 --raiz 396 --modo shin --semilla 885916 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="U8" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/ambiente.py audio/OBRA-007_396_shin.wav audio/OBRA-007_final.wav --fondo mar</t>
         </is>
       </c>
-      <c r="V8" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W8" s="4" t="inlineStr"/>
+      <c r="W8" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="X8" s="4" t="inlineStr"/>
       <c r="Y8" s="4" t="inlineStr"/>
-      <c r="Z8" s="5">
-        <f>IFERROR(Y8/X8*1000,"")</f>
+      <c r="Z8" s="4" t="inlineStr"/>
+      <c r="AA8" s="5">
+        <f>IFERROR(Z8/Y8*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -1573,26 +1614,31 @@
       <c r="S9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T9" s="3" t="inlineStr">
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>What keeps you awake at night? 🌙 Write it here and leave it with us. Then press play and let it go. A new sleep piece every week.</t>
+        </is>
+      </c>
+      <c r="U9" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 180 --raiz 432 --modo kumoi --semilla 295910 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="U9" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/ambiente.py audio/OBRA-008_432_kumoi.wav audio/OBRA-008_final.wav --fondo mar</t>
         </is>
       </c>
-      <c r="V9" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W9" s="4" t="inlineStr"/>
+      <c r="W9" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="X9" s="4" t="inlineStr"/>
       <c r="Y9" s="4" t="inlineStr"/>
-      <c r="Z9" s="5">
-        <f>IFERROR(Y9/X9*1000,"")</f>
+      <c r="Z9" s="4" t="inlineStr"/>
+      <c r="AA9" s="5">
+        <f>IFERROR(Z9/Y9*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -1690,26 +1736,31 @@
       <c r="S10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T10" s="3" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>What's on your mind right now? 🌿 Write it here and leave it with us. Sometimes saying it is enough to set it down.</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 25 --raiz 396 --modo kumoi --semilla 555819 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="U10" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py aves 1540 audio/OBRA-009_capa.wav --semilla 555819 --raiz 396 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-009_396_kumoi.wav audio/OBRA-009_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-009_capa.wav</t>
         </is>
       </c>
-      <c r="V10" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W10" s="4" t="inlineStr"/>
+      <c r="W10" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="X10" s="4" t="inlineStr"/>
       <c r="Y10" s="4" t="inlineStr"/>
-      <c r="Z10" s="5">
-        <f>IFERROR(Y10/X10*1000,"")</f>
+      <c r="Z10" s="4" t="inlineStr"/>
+      <c r="AA10" s="5">
+        <f>IFERROR(Z10/Y10*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -1807,26 +1858,31 @@
       <c r="S11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T11" s="3" t="inlineStr">
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>What's on your mind right now? 🌿 Write it here and leave it with us. Sometimes saying it is enough to set it down.</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 30 --raiz 432 --modo hirajoshi --semilla 739461 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="U11" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py zen 1840 audio/OBRA-010_capa.wav --semilla 739461 --raiz 432 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-010_432_hirajoshi.wav audio/OBRA-010_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-010_capa.wav</t>
         </is>
       </c>
-      <c r="V11" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W11" s="4" t="inlineStr"/>
+      <c r="W11" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="X11" s="4" t="inlineStr"/>
       <c r="Y11" s="4" t="inlineStr"/>
-      <c r="Z11" s="5">
-        <f>IFERROR(Y11/X11*1000,"")</f>
+      <c r="Z11" s="4" t="inlineStr"/>
+      <c r="AA11" s="5">
+        <f>IFERROR(Z11/Y11*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -1924,26 +1980,31 @@
       <c r="S12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T12" s="3" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>What's on your mind right now? 🌿 Write it here and leave it with us. Sometimes saying it is enough to set it down.</t>
+        </is>
+      </c>
+      <c r="U12" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 20 --raiz 528 --modo hirajoshi --semilla 913368 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="U12" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py aves 1240 audio/OBRA-011_capa.wav --semilla 913368 --raiz 528 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-011_528_hirajoshi.wav audio/OBRA-011_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-011_capa.wav</t>
         </is>
       </c>
-      <c r="V12" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W12" s="4" t="inlineStr"/>
+      <c r="W12" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="X12" s="4" t="inlineStr"/>
       <c r="Y12" s="4" t="inlineStr"/>
-      <c r="Z12" s="5">
-        <f>IFERROR(Y12/X12*1000,"")</f>
+      <c r="Z12" s="4" t="inlineStr"/>
+      <c r="AA12" s="5">
+        <f>IFERROR(Z12/Y12*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -2045,30 +2106,35 @@
       <c r="S13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T13" s="3" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>What's on your mind right now? 🌿 Write it here and leave it with us. Sometimes saying it is enough to set it down.</t>
+        </is>
+      </c>
+      <c r="U13" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 10 --raiz 528 --modo shin --semilla 43734 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="U13" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py zen 640 audio/OBRA-012_capa.wav --semilla 43734 --raiz 528 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-012_528_shin.wav audio/OBRA-012_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-012_capa.wav</t>
         </is>
       </c>
-      <c r="V13" s="4" t="inlineStr">
+      <c r="W13" s="4" t="inlineStr">
         <is>
           <t>publicada</t>
         </is>
       </c>
-      <c r="W13" s="4" t="inlineStr">
+      <c r="X13" s="4" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="X13" s="4" t="inlineStr"/>
       <c r="Y13" s="4" t="inlineStr"/>
-      <c r="Z13" s="5">
-        <f>IFERROR(Y13/X13*1000,"")</f>
+      <c r="Z13" s="4" t="inlineStr"/>
+      <c r="AA13" s="5">
+        <f>IFERROR(Z13/Y13*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -2166,26 +2232,31 @@
       <c r="S14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T14" s="3" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>What's on your mind right now? 🌿 Write it here and leave it with us. Sometimes saying it is enough to set it down.</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 20 --raiz 432 --modo hirajoshi --semilla 627771 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="U14" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py aves 1240 audio/OBRA-013_capa.wav --semilla 627771 --raiz 432 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-013_432_hirajoshi.wav audio/OBRA-013_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-013_capa.wav</t>
         </is>
       </c>
-      <c r="V14" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W14" s="4" t="inlineStr"/>
+      <c r="W14" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="X14" s="4" t="inlineStr"/>
       <c r="Y14" s="4" t="inlineStr"/>
-      <c r="Z14" s="5">
-        <f>IFERROR(Y14/X14*1000,"")</f>
+      <c r="Z14" s="4" t="inlineStr"/>
+      <c r="AA14" s="5">
+        <f>IFERROR(Z14/Y14*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -2283,26 +2354,31 @@
       <c r="S15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T15" s="3" t="inlineStr">
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>What's on your mind right now? 🌿 Write it here and leave it with us. Sometimes saying it is enough to set it down.</t>
+        </is>
+      </c>
+      <c r="U15" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 20 --raiz 528 --modo yo --semilla 310137 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="U15" s="2" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py zen 1240 audio/OBRA-014_capa.wav --semilla 310137 --raiz 528 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-014_528_yo.wav audio/OBRA-014_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-014_capa.wav</t>
         </is>
       </c>
-      <c r="V15" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W15" s="4" t="inlineStr"/>
+      <c r="W15" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="X15" s="4" t="inlineStr"/>
       <c r="Y15" s="4" t="inlineStr"/>
-      <c r="Z15" s="5">
-        <f>IFERROR(Y15/X15*1000,"")</f>
+      <c r="Z15" s="4" t="inlineStr"/>
+      <c r="AA15" s="5">
+        <f>IFERROR(Z15/Y15*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -2404,30 +2480,35 @@
       <c r="S16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T16" s="3" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>What's on your mind right now? 🌿 Write it here and leave it with us. Sometimes saying it is enough to set it down.</t>
+        </is>
+      </c>
+      <c r="U16" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 15 --raiz 639 --modo yo --semilla 592463 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="U16" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py aves 940 audio/OBRA-015_capa.wav --semilla 592463 --raiz 639 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-015_639_yo.wav audio/OBRA-015_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-015_capa.wav</t>
         </is>
       </c>
-      <c r="V16" s="4" t="inlineStr">
+      <c r="W16" s="4" t="inlineStr">
         <is>
           <t>publicada</t>
         </is>
       </c>
-      <c r="W16" s="4" t="inlineStr">
+      <c r="X16" s="4" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="X16" s="4" t="inlineStr"/>
       <c r="Y16" s="4" t="inlineStr"/>
-      <c r="Z16" s="5">
-        <f>IFERROR(Y16/X16*1000,"")</f>
+      <c r="Z16" s="4" t="inlineStr"/>
+      <c r="AA16" s="5">
+        <f>IFERROR(Z16/Y16*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -2525,26 +2606,31 @@
       <c r="S17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T17" s="3" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>What's on your mind right now? 🌿 Write it here and leave it with us. Sometimes saying it is enough to set it down.</t>
+        </is>
+      </c>
+      <c r="U17" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 30 --raiz 417 --modo kumoi --semilla 250697 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="U17" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py ancestral 1840 audio/OBRA-016_capa.wav --semilla 250697 --raiz 417 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-016_417_kumoi.wav audio/OBRA-016_final.wav --fondo fuego --nivel-capa 0 --nivel-obra -20 --capa audio/OBRA-016_capa.wav</t>
         </is>
       </c>
-      <c r="V17" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W17" s="4" t="inlineStr"/>
+      <c r="W17" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="X17" s="4" t="inlineStr"/>
       <c r="Y17" s="4" t="inlineStr"/>
-      <c r="Z17" s="5">
-        <f>IFERROR(Y17/X17*1000,"")</f>
+      <c r="Z17" s="4" t="inlineStr"/>
+      <c r="AA17" s="5">
+        <f>IFERROR(Z17/Y17*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -2642,26 +2728,31 @@
       <c r="S18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T18" s="3" t="inlineStr">
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>Where are you listening from today? 🌿 A new piece every week.</t>
+        </is>
+      </c>
+      <c r="U18" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 45 --raiz 417 --modo hirajoshi --semilla 714152 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="U18" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py zen 2740 audio/OBRA-017_capa.wav --semilla 714152 --raiz 417 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-017_417_hirajoshi.wav audio/OBRA-017_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-017_capa.wav</t>
         </is>
       </c>
-      <c r="V18" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W18" s="4" t="inlineStr"/>
+      <c r="W18" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="X18" s="4" t="inlineStr"/>
       <c r="Y18" s="4" t="inlineStr"/>
-      <c r="Z18" s="5">
-        <f>IFERROR(Y18/X18*1000,"")</f>
+      <c r="Z18" s="4" t="inlineStr"/>
+      <c r="AA18" s="5">
+        <f>IFERROR(Z18/Y18*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -2759,26 +2850,31 @@
       <c r="S19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T19" s="3" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>Where are you listening from today? 🌿 A new piece every week.</t>
+        </is>
+      </c>
+      <c r="U19" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 45 --raiz 528 --modo hirajoshi --semilla 735455 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="U19" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py zen 2740 audio/OBRA-018_capa.wav --semilla 735455 --raiz 528 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-018_528_hirajoshi.wav audio/OBRA-018_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-018_capa.wav</t>
         </is>
       </c>
-      <c r="V19" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W19" s="4" t="inlineStr"/>
+      <c r="W19" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="X19" s="4" t="inlineStr"/>
       <c r="Y19" s="4" t="inlineStr"/>
-      <c r="Z19" s="5">
-        <f>IFERROR(Y19/X19*1000,"")</f>
+      <c r="Z19" s="4" t="inlineStr"/>
+      <c r="AA19" s="5">
+        <f>IFERROR(Z19/Y19*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -2876,26 +2972,31 @@
       <c r="S20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T20" s="3" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>Where are you listening from today? 🌿 A new piece every week.</t>
+        </is>
+      </c>
+      <c r="U20" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 60 --raiz 432 --modo shin --semilla 627577 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="U20" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py zen 3640 audio/OBRA-019_capa.wav --semilla 627577 --raiz 432 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-019_432_shin.wav audio/OBRA-019_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-019_capa.wav</t>
         </is>
       </c>
-      <c r="V20" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W20" s="4" t="inlineStr"/>
+      <c r="W20" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="X20" s="4" t="inlineStr"/>
       <c r="Y20" s="4" t="inlineStr"/>
-      <c r="Z20" s="5">
-        <f>IFERROR(Y20/X20*1000,"")</f>
+      <c r="Z20" s="4" t="inlineStr"/>
+      <c r="AA20" s="5">
+        <f>IFERROR(Z20/Y20*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -2997,30 +3098,35 @@
       <c r="S21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T21" s="3" t="inlineStr">
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>Where are you listening from today? 🌿 A new piece every week.</t>
+        </is>
+      </c>
+      <c r="U21" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 30 --raiz 528 --modo shin --semilla 632595 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="U21" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py ancestral 1840 audio/OBRA-020_capa.wav --semilla 632595 --raiz 528 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-020_528_shin.wav audio/OBRA-020_final.wav --fondo fuego --nivel-capa 0 --nivel-obra -20 --capa audio/OBRA-020_capa.wav</t>
         </is>
       </c>
-      <c r="V21" s="4" t="inlineStr">
+      <c r="W21" s="4" t="inlineStr">
         <is>
           <t>publicada</t>
         </is>
       </c>
-      <c r="W21" s="4" t="inlineStr">
+      <c r="X21" s="4" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="X21" s="4" t="inlineStr"/>
       <c r="Y21" s="4" t="inlineStr"/>
-      <c r="Z21" s="5">
-        <f>IFERROR(Y21/X21*1000,"")</f>
+      <c r="Z21" s="4" t="inlineStr"/>
+      <c r="AA21" s="5">
+        <f>IFERROR(Z21/Y21*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -3118,26 +3224,31 @@
       <c r="S22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T22" s="3" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>Where are you listening from today? 🌿 A new piece every week.</t>
+        </is>
+      </c>
+      <c r="U22" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 45 --raiz 396 --modo kumoi --semilla 864630 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="U22" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py zen 2740 audio/OBRA-021_capa.wav --semilla 864630 --raiz 396 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-021_396_kumoi.wav audio/OBRA-021_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-021_capa.wav</t>
         </is>
       </c>
-      <c r="V22" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W22" s="4" t="inlineStr"/>
+      <c r="W22" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="X22" s="4" t="inlineStr"/>
       <c r="Y22" s="4" t="inlineStr"/>
-      <c r="Z22" s="5">
-        <f>IFERROR(Y22/X22*1000,"")</f>
+      <c r="Z22" s="4" t="inlineStr"/>
+      <c r="AA22" s="5">
+        <f>IFERROR(Z22/Y22*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -3235,26 +3346,31 @@
       <c r="S23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T23" s="3" t="inlineStr">
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>Where are you listening from today? 🌿 A new piece every week.</t>
+        </is>
+      </c>
+      <c r="U23" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 60 --raiz 639 --modo yo --semilla 335798 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="U23" s="2" t="inlineStr">
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py zen 3640 audio/OBRA-022_capa.wav --semilla 335798 --raiz 639 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-022_639_yo.wav audio/OBRA-022_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-022_capa.wav</t>
         </is>
       </c>
-      <c r="V23" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W23" s="4" t="inlineStr"/>
+      <c r="W23" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="X23" s="4" t="inlineStr"/>
       <c r="Y23" s="4" t="inlineStr"/>
-      <c r="Z23" s="5">
-        <f>IFERROR(Y23/X23*1000,"")</f>
+      <c r="Z23" s="4" t="inlineStr"/>
+      <c r="AA23" s="5">
+        <f>IFERROR(Z23/Y23*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -3352,26 +3468,31 @@
       <c r="S24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T24" s="3" t="inlineStr">
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>Where are you listening from today? 🌿 A new piece every week.</t>
+        </is>
+      </c>
+      <c r="U24" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 20 --raiz 528 --modo shin --semilla 299306 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="U24" s="2" t="inlineStr">
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py zen 1240 audio/OBRA-023_capa.wav --semilla 299306 --raiz 528 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-023_528_shin.wav audio/OBRA-023_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-023_capa.wav</t>
         </is>
       </c>
-      <c r="V24" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W24" s="4" t="inlineStr"/>
+      <c r="W24" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="X24" s="4" t="inlineStr"/>
       <c r="Y24" s="4" t="inlineStr"/>
-      <c r="Z24" s="5">
-        <f>IFERROR(Y24/X24*1000,"")</f>
+      <c r="Z24" s="4" t="inlineStr"/>
+      <c r="AA24" s="5">
+        <f>IFERROR(Z24/Y24*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -3469,26 +3590,31 @@
       <c r="S25" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T25" s="3" t="inlineStr">
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>Where are you listening from today? 🌿 A new piece every week.</t>
+        </is>
+      </c>
+      <c r="U25" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 60 --raiz 432 --modo kumoi --semilla 926202 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="U25" s="2" t="inlineStr">
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py ancestral 3640 audio/OBRA-024_capa.wav --semilla 926202 --raiz 432 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-024_432_kumoi.wav audio/OBRA-024_final.wav --fondo fuego --nivel-capa 0 --nivel-obra -20 --capa audio/OBRA-024_capa.wav</t>
         </is>
       </c>
-      <c r="V25" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W25" s="4" t="inlineStr"/>
+      <c r="W25" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="X25" s="4" t="inlineStr"/>
       <c r="Y25" s="4" t="inlineStr"/>
-      <c r="Z25" s="5">
-        <f>IFERROR(Y25/X25*1000,"")</f>
+      <c r="Z25" s="4" t="inlineStr"/>
+      <c r="AA25" s="5">
+        <f>IFERROR(Z25/Y25*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -3586,26 +3712,31 @@
       <c r="S26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T26" s="3" t="inlineStr">
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>What are you letting go of today? 🌿 Write one word.</t>
+        </is>
+      </c>
+      <c r="U26" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 60 --raiz 528 --modo hirajoshi --semilla 454078 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="U26" s="2" t="inlineStr">
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py aves 3640 audio/OBRA-025_capa.wav --semilla 454078 --raiz 528 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-025_528_hirajoshi.wav audio/OBRA-025_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-025_capa.wav</t>
         </is>
       </c>
-      <c r="V26" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W26" s="4" t="inlineStr"/>
+      <c r="W26" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="X26" s="4" t="inlineStr"/>
       <c r="Y26" s="4" t="inlineStr"/>
-      <c r="Z26" s="5">
-        <f>IFERROR(Y26/X26*1000,"")</f>
+      <c r="Z26" s="4" t="inlineStr"/>
+      <c r="AA26" s="5">
+        <f>IFERROR(Z26/Y26*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -3703,26 +3834,31 @@
       <c r="S27" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T27" s="3" t="inlineStr">
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>What are you letting go of today? 🌿 Write one word.</t>
+        </is>
+      </c>
+      <c r="U27" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 60 --raiz 432 --modo kumoi --semilla 146597 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="U27" s="2" t="inlineStr">
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/ambiente.py audio/OBRA-026_432_kumoi.wav audio/OBRA-026_final.wav --fondo mar</t>
         </is>
       </c>
-      <c r="V27" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W27" s="4" t="inlineStr"/>
+      <c r="W27" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="X27" s="4" t="inlineStr"/>
       <c r="Y27" s="4" t="inlineStr"/>
-      <c r="Z27" s="5">
-        <f>IFERROR(Y27/X27*1000,"")</f>
+      <c r="Z27" s="4" t="inlineStr"/>
+      <c r="AA27" s="5">
+        <f>IFERROR(Z27/Y27*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -3820,26 +3956,31 @@
       <c r="S28" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T28" s="3" t="inlineStr">
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>What are you letting go of today? 🌿 Write one word.</t>
+        </is>
+      </c>
+      <c r="U28" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 60 --raiz 396 --modo kumoi --semilla 338018 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="U28" s="2" t="inlineStr">
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py ancestral 3640 audio/OBRA-027_capa.wav --semilla 338018 --raiz 396 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-027_396_kumoi.wav audio/OBRA-027_final.wav --fondo fuego --nivel-capa 0 --nivel-obra -20 --capa audio/OBRA-027_capa.wav</t>
         </is>
       </c>
-      <c r="V28" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W28" s="4" t="inlineStr"/>
+      <c r="W28" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="X28" s="4" t="inlineStr"/>
       <c r="Y28" s="4" t="inlineStr"/>
-      <c r="Z28" s="5">
-        <f>IFERROR(Y28/X28*1000,"")</f>
+      <c r="Z28" s="4" t="inlineStr"/>
+      <c r="AA28" s="5">
+        <f>IFERROR(Z28/Y28*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -3937,26 +4078,31 @@
       <c r="S29" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="inlineStr">
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>What are you letting go of today? 🌿 Write one word.</t>
+        </is>
+      </c>
+      <c r="U29" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 45 --raiz 417 --modo hirajoshi --semilla 409966 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="U29" s="2" t="inlineStr">
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py zen 2740 audio/OBRA-028_capa.wav --semilla 409966 --raiz 417 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-028_417_hirajoshi.wav audio/OBRA-028_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-028_capa.wav</t>
         </is>
       </c>
-      <c r="V29" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W29" s="4" t="inlineStr"/>
+      <c r="W29" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="X29" s="4" t="inlineStr"/>
       <c r="Y29" s="4" t="inlineStr"/>
-      <c r="Z29" s="5">
-        <f>IFERROR(Y29/X29*1000,"")</f>
+      <c r="Z29" s="4" t="inlineStr"/>
+      <c r="AA29" s="5">
+        <f>IFERROR(Z29/Y29*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -4054,26 +4200,31 @@
       <c r="S30" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T30" s="3" t="inlineStr">
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>What are you letting go of today? 🌿 Write one word.</t>
+        </is>
+      </c>
+      <c r="U30" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 60 --raiz 639 --modo yo --semilla 133046 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="U30" s="2" t="inlineStr">
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py aves 3640 audio/OBRA-029_capa.wav --semilla 133046 --raiz 639 --densidad 2 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-029_639_yo.wav audio/OBRA-029_final.wav --fondo selva --nivel-capa -2 --capa audio/OBRA-029_capa.wav</t>
         </is>
       </c>
-      <c r="V30" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W30" s="4" t="inlineStr"/>
+      <c r="W30" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="X30" s="4" t="inlineStr"/>
       <c r="Y30" s="4" t="inlineStr"/>
-      <c r="Z30" s="5">
-        <f>IFERROR(Y30/X30*1000,"")</f>
+      <c r="Z30" s="4" t="inlineStr"/>
+      <c r="AA30" s="5">
+        <f>IFERROR(Z30/Y30*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -4171,26 +4322,31 @@
       <c r="S31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T31" s="3" t="inlineStr">
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>What are you letting go of today? 🌿 Write one word.</t>
+        </is>
+      </c>
+      <c r="U31" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 45 --raiz 741 --modo yo --semilla 244487 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="U31" s="2" t="inlineStr">
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py aves 2740 audio/OBRA-030_capa.wav --semilla 244487 --raiz 741 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-030_741_yo.wav audio/OBRA-030_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-030_capa.wav</t>
         </is>
       </c>
-      <c r="V31" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W31" s="4" t="inlineStr"/>
+      <c r="W31" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="X31" s="4" t="inlineStr"/>
       <c r="Y31" s="4" t="inlineStr"/>
-      <c r="Z31" s="5">
-        <f>IFERROR(Y31/X31*1000,"")</f>
+      <c r="Z31" s="4" t="inlineStr"/>
+      <c r="AA31" s="5">
+        <f>IFERROR(Z31/Y31*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -4288,26 +4444,31 @@
       <c r="S32" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T32" s="3" t="inlineStr">
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>What are you letting go of today? 🌿 Write one word.</t>
+        </is>
+      </c>
+      <c r="U32" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 45 --raiz 852 --modo hirajoshi --semilla 288169 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="U32" s="2" t="inlineStr">
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py zen 2740 audio/OBRA-031_capa.wav --semilla 288169 --raiz 852 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-031_852_hirajoshi.wav audio/OBRA-031_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-031_capa.wav</t>
         </is>
       </c>
-      <c r="V32" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W32" s="4" t="inlineStr"/>
+      <c r="W32" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="X32" s="4" t="inlineStr"/>
       <c r="Y32" s="4" t="inlineStr"/>
-      <c r="Z32" s="5">
-        <f>IFERROR(Y32/X32*1000,"")</f>
+      <c r="Z32" s="4" t="inlineStr"/>
+      <c r="AA32" s="5">
+        <f>IFERROR(Z32/Y32*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -4405,26 +4566,31 @@
       <c r="S33" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T33" s="3" t="inlineStr">
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>What are you letting go of today? 🌿 Write one word.</t>
+        </is>
+      </c>
+      <c r="U33" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 180 --raiz 528 --modo hirajoshi --semilla 638156 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="U33" s="2" t="inlineStr">
+      <c r="V33" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py aves 10840 audio/OBRA-032_capa.wav --semilla 638156 --raiz 528 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-032_528_hirajoshi.wav audio/OBRA-032_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-032_capa.wav</t>
         </is>
       </c>
-      <c r="V33" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W33" s="4" t="inlineStr"/>
+      <c r="W33" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="X33" s="4" t="inlineStr"/>
       <c r="Y33" s="4" t="inlineStr"/>
-      <c r="Z33" s="5">
-        <f>IFERROR(Y33/X33*1000,"")</f>
+      <c r="Z33" s="4" t="inlineStr"/>
+      <c r="AA33" s="5">
+        <f>IFERROR(Z33/Y33*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -4522,26 +4688,31 @@
       <c r="S34" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T34" s="3" t="inlineStr">
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>What are you working on? ✍️ Tell us, and we'll keep you company.</t>
+        </is>
+      </c>
+      <c r="U34" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 120 --raiz 639 --modo yo --semilla 112334 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="U34" s="2" t="inlineStr">
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py aves 7240 audio/OBRA-033_capa.wav --semilla 112334 --raiz 639 --densidad 2 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-033_639_yo.wav audio/OBRA-033_final.wav --fondo selva --nivel-capa -2 --capa audio/OBRA-033_capa.wav</t>
         </is>
       </c>
-      <c r="V34" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W34" s="4" t="inlineStr"/>
+      <c r="W34" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="X34" s="4" t="inlineStr"/>
       <c r="Y34" s="4" t="inlineStr"/>
-      <c r="Z34" s="5">
-        <f>IFERROR(Y34/X34*1000,"")</f>
+      <c r="Z34" s="4" t="inlineStr"/>
+      <c r="AA34" s="5">
+        <f>IFERROR(Z34/Y34*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -4639,26 +4810,31 @@
       <c r="S35" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T35" s="3" t="inlineStr">
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>What are you working on? ✍️ Tell us, and we'll keep you company.</t>
+        </is>
+      </c>
+      <c r="U35" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 180 --raiz 528 --modo yo --semilla 249239 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="U35" s="2" t="inlineStr">
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py aves 10840 audio/OBRA-034_capa.wav --semilla 249239 --raiz 528 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-034_528_yo.wav audio/OBRA-034_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-034_capa.wav</t>
         </is>
       </c>
-      <c r="V35" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W35" s="4" t="inlineStr"/>
+      <c r="W35" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="X35" s="4" t="inlineStr"/>
       <c r="Y35" s="4" t="inlineStr"/>
-      <c r="Z35" s="5">
-        <f>IFERROR(Y35/X35*1000,"")</f>
+      <c r="Z35" s="4" t="inlineStr"/>
+      <c r="AA35" s="5">
+        <f>IFERROR(Z35/Y35*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -4756,26 +4932,31 @@
       <c r="S36" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T36" s="3" t="inlineStr">
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>What are you working on? ✍️ Tell us, and we'll keep you company.</t>
+        </is>
+      </c>
+      <c r="U36" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 120 --raiz 741 --modo yo --semilla 74636 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="U36" s="2" t="inlineStr">
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py aves 7240 audio/OBRA-035_capa.wav --semilla 74636 --raiz 741 --densidad 2 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-035_741_yo.wav audio/OBRA-035_final.wav --fondo selva --nivel-capa -2 --capa audio/OBRA-035_capa.wav</t>
         </is>
       </c>
-      <c r="V36" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W36" s="4" t="inlineStr"/>
+      <c r="W36" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="X36" s="4" t="inlineStr"/>
       <c r="Y36" s="4" t="inlineStr"/>
-      <c r="Z36" s="5">
-        <f>IFERROR(Y36/X36*1000,"")</f>
+      <c r="Z36" s="4" t="inlineStr"/>
+      <c r="AA36" s="5">
+        <f>IFERROR(Z36/Y36*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -4873,26 +5054,31 @@
       <c r="S37" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T37" s="3" t="inlineStr">
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>What are you working on? ✍️ Tell us, and we'll keep you company.</t>
+        </is>
+      </c>
+      <c r="U37" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 90 --raiz 852 --modo yo --semilla 903477 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="U37" s="2" t="inlineStr">
+      <c r="V37" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py aves 5440 audio/OBRA-036_capa.wav --semilla 903477 --raiz 852 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-036_852_yo.wav audio/OBRA-036_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-036_capa.wav</t>
         </is>
       </c>
-      <c r="V37" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W37" s="4" t="inlineStr"/>
+      <c r="W37" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="X37" s="4" t="inlineStr"/>
       <c r="Y37" s="4" t="inlineStr"/>
-      <c r="Z37" s="5">
-        <f>IFERROR(Y37/X37*1000,"")</f>
+      <c r="Z37" s="4" t="inlineStr"/>
+      <c r="AA37" s="5">
+        <f>IFERROR(Z37/Y37*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -4990,26 +5176,31 @@
       <c r="S38" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T38" s="3" t="inlineStr">
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>What are you working on? ✍️ Tell us, and we'll keep you company.</t>
+        </is>
+      </c>
+      <c r="U38" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 120 --raiz 432 --modo yo --semilla 718809 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="U38" s="2" t="inlineStr">
+      <c r="V38" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py aves 7240 audio/OBRA-037_capa.wav --semilla 718809 --raiz 432 --densidad 2 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-037_432_yo.wav audio/OBRA-037_final.wav --fondo selva --nivel-capa -2 --capa audio/OBRA-037_capa.wav</t>
         </is>
       </c>
-      <c r="V38" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W38" s="4" t="inlineStr"/>
+      <c r="W38" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="X38" s="4" t="inlineStr"/>
       <c r="Y38" s="4" t="inlineStr"/>
-      <c r="Z38" s="5">
-        <f>IFERROR(Y38/X38*1000,"")</f>
+      <c r="Z38" s="4" t="inlineStr"/>
+      <c r="AA38" s="5">
+        <f>IFERROR(Z38/Y38*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -5107,26 +5298,31 @@
       <c r="S39" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T39" s="3" t="inlineStr">
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>What are you working on? ✍️ Tell us, and we'll keep you company.</t>
+        </is>
+      </c>
+      <c r="U39" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 120 --raiz 528 --modo shin --semilla 203246 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="U39" s="2" t="inlineStr">
+      <c r="V39" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/ambiente.py audio/OBRA-038_528_shin.wav audio/OBRA-038_final.wav --fondo mar</t>
         </is>
       </c>
-      <c r="V39" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W39" s="4" t="inlineStr"/>
+      <c r="W39" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="X39" s="4" t="inlineStr"/>
       <c r="Y39" s="4" t="inlineStr"/>
-      <c r="Z39" s="5">
-        <f>IFERROR(Y39/X39*1000,"")</f>
+      <c r="Z39" s="4" t="inlineStr"/>
+      <c r="AA39" s="5">
+        <f>IFERROR(Z39/Y39*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -5224,26 +5420,31 @@
       <c r="S40" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T40" s="3" t="inlineStr">
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>What are you working on? ✍️ Tell us, and we'll keep you company.</t>
+        </is>
+      </c>
+      <c r="U40" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 90 --raiz 639 --modo yo --semilla 281608 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="U40" s="2" t="inlineStr">
+      <c r="V40" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py aves 5440 audio/OBRA-039_capa.wav --semilla 281608 --raiz 639 --densidad 2 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-039_639_yo.wav audio/OBRA-039_final.wav --fondo selva --nivel-capa -2 --capa audio/OBRA-039_capa.wav</t>
         </is>
       </c>
-      <c r="V40" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W40" s="4" t="inlineStr"/>
+      <c r="W40" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="X40" s="4" t="inlineStr"/>
       <c r="Y40" s="4" t="inlineStr"/>
-      <c r="Z40" s="5">
-        <f>IFERROR(Y40/X40*1000,"")</f>
+      <c r="Z40" s="4" t="inlineStr"/>
+      <c r="AA40" s="5">
+        <f>IFERROR(Z40/Y40*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -5341,26 +5542,31 @@
       <c r="S41" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T41" s="3" t="inlineStr">
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>What are you working on? ✍️ Tell us, and we'll keep you company.</t>
+        </is>
+      </c>
+      <c r="U41" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 180 --raiz 741 --modo yo --semilla 883876 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="U41" s="2" t="inlineStr">
+      <c r="V41" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py aves 10840 audio/OBRA-040_capa.wav --semilla 883876 --raiz 741 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-040_741_yo.wav audio/OBRA-040_final.wav --fondo mar --nivel-capa -4 --capa audio/OBRA-040_capa.wav</t>
         </is>
       </c>
-      <c r="V41" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W41" s="4" t="inlineStr"/>
+      <c r="W41" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="X41" s="4" t="inlineStr"/>
       <c r="Y41" s="4" t="inlineStr"/>
-      <c r="Z41" s="5">
-        <f>IFERROR(Y41/X41*1000,"")</f>
+      <c r="Z41" s="4" t="inlineStr"/>
+      <c r="AA41" s="5">
+        <f>IFERROR(Z41/Y41*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -5459,30 +5665,35 @@
       <c r="S42" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T42" s="3" t="inlineStr">
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>What's on your mind right now? 🌿 Write it here and leave it with us. Sometimes saying it is enough to set it down.</t>
+        </is>
+      </c>
+      <c r="U42" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 60 --raiz 432 --modo hirajoshi --semilla 304617 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="U42" s="2" t="inlineStr">
+      <c r="V42" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py jardin 3640 audio/OBRA-041_capa.wav --semilla 304617 --raiz 432 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-041_432_hirajoshi.wav audio/OBRA-041_final.wav --fondo mar --nivel-fondo -8 --nivel-capa 0 --capa audio/OBRA-041_capa.wav</t>
         </is>
       </c>
-      <c r="V42" s="4" t="inlineStr">
+      <c r="W42" s="4" t="inlineStr">
         <is>
           <t>publicada</t>
         </is>
       </c>
-      <c r="W42" s="4" t="inlineStr">
+      <c r="X42" s="4" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="X42" s="4" t="inlineStr"/>
       <c r="Y42" s="4" t="inlineStr"/>
-      <c r="Z42" s="5">
-        <f>IFERROR(Y42/X42*1000,"")</f>
+      <c r="Z42" s="4" t="inlineStr"/>
+      <c r="AA42" s="5">
+        <f>IFERROR(Z42/Y42*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -5581,30 +5792,35 @@
       <c r="S43" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T43" s="3" t="inlineStr">
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>What's on your mind right now? 🌿 Write it here and leave it with us. Sometimes saying it is enough to set it down.</t>
+        </is>
+      </c>
+      <c r="U43" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 180 --raiz 528 --modo shin --semilla 266691 --caracter sin-cuenco</t>
         </is>
       </c>
-      <c r="U43" s="2" t="inlineStr">
+      <c r="V43" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py zen 10840 audio/OBRA-042_capa.wav --semilla 266691 --raiz 528 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-042_528_shin.wav audio/OBRA-042_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-042_capa.wav</t>
         </is>
       </c>
-      <c r="V43" s="4" t="inlineStr">
+      <c r="W43" s="4" t="inlineStr">
         <is>
           <t>publicada</t>
         </is>
       </c>
-      <c r="W43" s="4" t="inlineStr">
+      <c r="X43" s="4" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="X43" s="4" t="inlineStr"/>
       <c r="Y43" s="4" t="inlineStr"/>
-      <c r="Z43" s="5">
-        <f>IFERROR(Y43/X43*1000,"")</f>
+      <c r="Z43" s="4" t="inlineStr"/>
+      <c r="AA43" s="5">
+        <f>IFERROR(Z43/Y43*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -5703,30 +5919,35 @@
       <c r="S44" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="T44" s="3" t="inlineStr">
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>How long did the rain take to put you to sleep? 🌧️ Tell us in minutes. If you're reading this awake: lights off, phone face down, and press play again.</t>
+        </is>
+      </c>
+      <c r="U44" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 180 --raiz 432 --modo kumoi --semilla 615127 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="U44" s="2" t="inlineStr">
+      <c r="V44" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/ambiente.py audio/OBRA-043_432_kumoi.wav audio/OBRA-043_final.wav --fondo lluvia</t>
         </is>
       </c>
-      <c r="V44" s="4" t="inlineStr">
+      <c r="W44" s="4" t="inlineStr">
         <is>
           <t>publicada</t>
         </is>
       </c>
-      <c r="W44" s="4" t="inlineStr">
+      <c r="X44" s="4" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="X44" s="4" t="inlineStr"/>
       <c r="Y44" s="4" t="inlineStr"/>
-      <c r="Z44" s="5">
-        <f>IFERROR(Y44/X44*1000,"")</f>
+      <c r="Z44" s="4" t="inlineStr"/>
+      <c r="AA44" s="5">
+        <f>IFERROR(Z44/Y44*1000,"")</f>
         <v/>
       </c>
     </row>
@@ -5822,31 +6043,36 @@
       <c r="S45" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="T45" s="3" t="inlineStr">
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t>Headphones or speaker? 🎧 Tell us which, and how far into the theta waves you got before falling asleep.</t>
+        </is>
+      </c>
+      <c r="U45" s="3" t="inlineStr">
         <is>
           <t>python3 03-composicion/compositor.py --minutos 180 --raiz 432 --modo shin --semilla 810318 --caracter sin-cuenco --registro grave</t>
         </is>
       </c>
-      <c r="U45" s="2" t="inlineStr">
+      <c r="V45" s="2" t="inlineStr">
         <is>
           <t>python3 03-composicion/capas.py theta 10840 audio/OBRA-044_capa.wav --semilla 810318 --raiz 432 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-044_432_shin.wav audio/OBRA-044_final.wav --fondo mar --nivel-fondo -4 --nivel-capa -11 --capa audio/OBRA-044_capa.wav</t>
         </is>
       </c>
-      <c r="V45" s="4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W45" s="4" t="inlineStr"/>
+      <c r="W45" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
       <c r="X45" s="4" t="inlineStr"/>
       <c r="Y45" s="4" t="inlineStr"/>
-      <c r="Z45" s="5">
-        <f>IFERROR(Y45/X45*1000,"")</f>
+      <c r="Z45" s="4" t="inlineStr"/>
+      <c r="AA45" s="5">
+        <f>IFERROR(Z45/Y45*1000,"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z45"/>
+  <autoFilter ref="A1:AA45"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -27850,7 +28076,7 @@
         </is>
       </c>
       <c r="B3" s="7">
-        <f>COUNTIF(Catálogo!V2:V45,"pendiente")</f>
+        <f>COUNTIF(Catálogo!W2:W45,"pendiente")</f>
         <v/>
       </c>
     </row>
@@ -27861,7 +28087,7 @@
         </is>
       </c>
       <c r="B4" s="7">
-        <f>COUNTIF(Catálogo!V2:V45,"compuesta")</f>
+        <f>COUNTIF(Catálogo!W2:W45,"compuesta")</f>
         <v/>
       </c>
     </row>
@@ -27872,7 +28098,7 @@
         </is>
       </c>
       <c r="B5" s="7">
-        <f>COUNTIF(Catálogo!V2:V45,"montada")</f>
+        <f>COUNTIF(Catálogo!W2:W45,"montada")</f>
         <v/>
       </c>
     </row>
@@ -27883,7 +28109,7 @@
         </is>
       </c>
       <c r="B6" s="7">
-        <f>COUNTIF(Catálogo!V2:V45,"publicada")</f>
+        <f>COUNTIF(Catálogo!W2:W45,"publicada")</f>
         <v/>
       </c>
     </row>
@@ -27927,7 +28153,7 @@
         <v/>
       </c>
       <c r="C10" s="7">
-        <f>COUNTIFS(Catálogo!D2:D45,A10,Catálogo!V2:V45,"publicada")</f>
+        <f>COUNTIFS(Catálogo!D2:D45,A10,Catálogo!W2:W45,"publicada")</f>
         <v/>
       </c>
       <c r="D10" s="7">
@@ -27946,7 +28172,7 @@
         <v/>
       </c>
       <c r="C11" s="7">
-        <f>COUNTIFS(Catálogo!D2:D45,A11,Catálogo!V2:V45,"publicada")</f>
+        <f>COUNTIFS(Catálogo!D2:D45,A11,Catálogo!W2:W45,"publicada")</f>
         <v/>
       </c>
       <c r="D11" s="7">
@@ -27965,7 +28191,7 @@
         <v/>
       </c>
       <c r="C12" s="7">
-        <f>COUNTIFS(Catálogo!D2:D45,A12,Catálogo!V2:V45,"publicada")</f>
+        <f>COUNTIFS(Catálogo!D2:D45,A12,Catálogo!W2:W45,"publicada")</f>
         <v/>
       </c>
       <c r="D12" s="7">
@@ -27984,7 +28210,7 @@
         <v/>
       </c>
       <c r="C13" s="7">
-        <f>COUNTIFS(Catálogo!D2:D45,A13,Catálogo!V2:V45,"publicada")</f>
+        <f>COUNTIFS(Catálogo!D2:D45,A13,Catálogo!W2:W45,"publicada")</f>
         <v/>
       </c>
       <c r="D13" s="7">
@@ -28003,7 +28229,7 @@
         <v/>
       </c>
       <c r="C14" s="7">
-        <f>COUNTIFS(Catálogo!D2:D45,A14,Catálogo!V2:V45,"publicada")</f>
+        <f>COUNTIFS(Catálogo!D2:D45,A14,Catálogo!W2:W45,"publicada")</f>
         <v/>
       </c>
       <c r="D14" s="7">
@@ -28044,7 +28270,7 @@
         </is>
       </c>
       <c r="B18" s="7">
-        <f>SUM(Catálogo!X2:X45)</f>
+        <f>SUM(Catálogo!Y2:Y45)</f>
         <v/>
       </c>
     </row>
@@ -28055,7 +28281,7 @@
         </is>
       </c>
       <c r="B19" s="7">
-        <f>SUM(Catálogo!Y2:Y45)</f>
+        <f>SUM(Catálogo!Z2:Z45)</f>
         <v/>
       </c>
     </row>
@@ -28086,7 +28312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -28217,220 +28443,232 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>pantalla_oscura_min</t>
+          <t>comentario_fijado</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Minutos de mandala antes de que la pantalla se funda a negro (videos para dormir). 0: el mandala dura todo el video.</t>
+          <t>Comentario para escribir y fijar apenas se publica: una pregunta fácil de contestar.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>descripcion_optimizada</t>
+          <t>pantalla_oscura_min</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Descripción bilingüe lista para pegar. Solo falta añadir los capítulos tras el montaje.</t>
+          <t>Minutos de mandala antes de que la pantalla se funda a negro (videos para dormir). 0: el mandala dura todo el video.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>titulo_miniatura</t>
+          <t>descripcion_optimizada</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Texto de la miniatura: 2-4 palabras que COMPLETAN el título, nunca lo repiten.</t>
+          <t>Descripción bilingüe lista para pegar. Solo falta añadir los capítulos tras el montaje.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>hashtags</t>
+          <t>titulo_miniatura</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Tres, al final de la descripción.</t>
+          <t>Texto de la miniatura: 2-4 palabras que COMPLETAN el título, nunca lo repiten.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>etiquetas</t>
+          <t>hashtags</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Etiquetas del video, separadas por coma.</t>
+          <t>Tres, al final de la descripción.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>imagen_miniatura</t>
+          <t>etiquetas</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>AMARILLA. Ruta o URL de la portada una vez generada.</t>
+          <t>Etiquetas del video, separadas por coma.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>url_video</t>
+          <t>imagen_miniatura</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>AMARILLA. URL de YouTube una vez publicado.</t>
+          <t>AMARILLA. Ruta o URL de la portada una vez generada.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>raiz_hz / modo / registro / semilla</t>
+          <t>url_video</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Parámetros de composición. El registro grave baja una octava (Dormir y Concentración). La semilla regenera la obra idéntica.</t>
+          <t>AMARILLA. URL de YouTube una vez publicado.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>comando_regeneracion</t>
+          <t>raiz_hz / modo / registro / semilla</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>Comando exacto. Copiar, pegar y ejecutar: devuelve el mismo audio bit a bit.</t>
+          <t>Parámetros de composición. El registro grave baja una octava (Dormir y Concentración). La semilla regenera la obra idéntica.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>estado</t>
+          <t>comando_regeneracion</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>AMARILLA. pendiente / compuesta / montada / publicada</t>
+          <t>Comando exacto. Copiar, pegar y ejecutar: devuelve el mismo audio bit a bit.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>fecha_publicacion</t>
+          <t>estado</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>AMARILLA. Formato AAAA-MM-DD.</t>
+          <t>AMARILLA. pendiente / compuesta / montada / publicada</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>vistas / suscriptores</t>
+          <t>fecha_publicacion</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>AMARILLA. Copiar de YouTube Studio a los 14 días de publicar.</t>
+          <t>AMARILLA. Formato AAAA-MM-DD.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
+          <t>vistas / suscriptores</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>AMARILLA. Copiar de YouTube Studio a los 14 días de publicar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
           <t>subs_por_1000</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>Calculada. Es la métrica que decide el canal: por debajo de 1, el problema es la portada, no la música.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr"/>
-    </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>Hoja Shorts</t>
-        </is>
-      </c>
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>5 por obra. Cada uno cambia de tramo de la obra, encuadre, instante del mandala y frase.</t>
-        </is>
-      </c>
+      <c r="A27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>tiktok_portada</t>
+          <t>Hoja Shorts</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>El título de la portada en TikTok (el que se ve en el perfil). Distinto de la descripción.</t>
+          <t>5 por obra. Cada uno cambia de tramo de la obra, encuadre, instante del mandala y frase.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>tiktok_descripcion</t>
+          <t>tiktok_portada</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>El texto que acompaña al video en TikTok, con hashtags. En Metricool, nunca en el campo título.</t>
+          <t>El título de la portada en TikTok (el que se ve en el perfil). Distinto de la descripción.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
+          <t>tiktok_descripcion</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>El texto que acompaña al video en TikTok, con hashtags. En Metricool, nunca en el campo título.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
           <t>yt_video_relacionado</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>El video largo. En YouTube Studio va en «Video relacionado» del Short.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr"/>
-    </row>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>Ejemplo de fila rellenada</t>
         </is>
       </c>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>imagen_miniatura: portadas/obra-001.png | url_video: https://youtu.be/XXXXXXXXXXX | estado: publicada | fecha_publicacion: 2026-10-07 | vistas: 4820 | suscriptores: 11</t>
         </is>

--- a/08-catalogo/catalogo_canal.xlsx
+++ b/08-catalogo/catalogo_canal.xlsx
@@ -13,8 +13,8 @@
     <sheet name="Leyenda" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$AA$45</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Shorts'!$A$1:$S$301</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$AA$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Shorts'!$A$1:$S$304</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA45"/>
+  <dimension ref="A1:AA46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -6071,8 +6071,127 @@
         <v/>
       </c>
     </row>
+    <row r="46" ht="58" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-045</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Woke Up at 3 AM? 🌙 Chinese Guqin &amp; Rain to Fall Back Asleep · Dark Screen · 3 Hours</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Música para dormir · Guqin y lluvia · 432 Hz · Las tres de la mañana · 3 horas</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Dormir</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>guqin</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Woke up at 3 AM again? Three hours of guqin, xiao flute and gentle rain to fall back asleep.
+In the Chinese body clock, 1 to 3 AM is the liver's hour: the hour of what you couldn't let go of. Don't check the time. Breathe out slowly through your lips, "shhh" (xū), six times, and let the strings take it from there. The screen fades to black after 3 minutes.
+🌙 Phone face down, volume low. The music thins out over the hours, until only the rain is left.
+🌿 Subscribe for a new calm piece every week: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+Original composition by Rin, synthesized from scratch in just intonation around 432 Hz, yu mode. No samples. The yu scale is the one Chinese five-element music keeps for the night. A 2,000-year-old tradition, not medical advice.
+#sleepmusic #guqin #chinesemusic</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Las tres de la mañana · 3 horas
+Para acompañar el sueño.
+Ambiente: guqin y lluvia.
+Compuesta con raíz en 432 Hz, en entonación justa, modo yu.
+Ciclo respiratorio: de 4.5 a 3.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#sleepmusic #meditation #432hz</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>3 HOURS</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>#sleepmusic #guqin #chinesemusic</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>woke up at 3am, fall back asleep, music to fall back asleep, chinese sleep music, guqin, guqin music, chinese meditation music, chinese music for sleep, rain sounds for sleeping, dark screen sleep music, black screen sleep music, deep sleep music, sleep music, traditional chinese medicine, chinamaxxing, 3 hours, rin, música para dormir</t>
+        </is>
+      </c>
+      <c r="K46" s="4" t="inlineStr"/>
+      <c r="L46" s="4" t="inlineStr"/>
+      <c r="M46" s="2" t="n">
+        <v>432</v>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>yu</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>grave</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="n">
+        <v>270978</v>
+      </c>
+      <c r="Q46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="S46" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>What time did you wake up tonight? 🌙 Tell us, then press play and breathe out slowly: shhh.</t>
+        </is>
+      </c>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t>python3 03-composicion/tao_largo.py --minutos 180 --raiz 432 --modo yu --semilla 270978</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>python3 03-composicion/ambiente.py audio/OBRA-045_432_yu.wav audio/OBRA-045_final.wav --fondo lluvia --nivel-obra 0 --nivel-fondo -6 --entrada-obra 6</t>
+        </is>
+      </c>
+      <c r="W46" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="X46" s="4" t="inlineStr"/>
+      <c r="Y46" s="4" t="inlineStr"/>
+      <c r="Z46" s="4" t="inlineStr"/>
+      <c r="AA46" s="5">
+        <f>IFERROR(Z46/Y46*1000,"")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AA45"/>
+  <autoFilter ref="A1:AA46"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6083,7 +6202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S301"/>
+  <dimension ref="A1:S304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -28029,8 +28148,224 @@
       <c r="R301" s="4" t="inlineStr"/>
       <c r="S301" s="4" t="inlineStr"/>
     </row>
+    <row r="302" ht="58" customHeight="1">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-045-S1</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-045</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D302" s="2" t="inlineStr">
+        <is>
+          <t>short-1.mp4</t>
+        </is>
+      </c>
+      <c r="E302" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="F302" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G302" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H302" s="2" t="inlineStr">
+        <is>
+          <t>Breathe out longer than you breathe in</t>
+        </is>
+      </c>
+      <c r="I302" s="3" t="inlineStr">
+        <is>
+          <t>Breathe out longer than you breathe in · 432 Hz · Guqin and Rain</t>
+        </is>
+      </c>
+      <c r="J302" s="3" t="inlineStr">
+        <is>
+          <t>Save this for tonight.
+Full piece (3 h): Woke Up at 3 AM? 🌙 Chinese Guqin &amp; Rain to Fall Back Asleep · Dark Screen · 3 Hours
+#sleepmusic #sleep #relaxingmusic #432hz #shorts</t>
+        </is>
+      </c>
+      <c r="K302" s="2" t="inlineStr">
+        <is>
+          <t>sleep music, deep sleep, 432 hz, guqin and rain, Rin</t>
+        </is>
+      </c>
+      <c r="L302" s="2" t="inlineStr"/>
+      <c r="M302" s="2" t="inlineStr">
+        <is>
+          <t>432 Hz · sleep</t>
+        </is>
+      </c>
+      <c r="N302" s="3" t="inlineStr">
+        <is>
+          <t>Save this for tonight. Full 3 h piece on YouTube: Rin.
+#sleepmusic #sleep #relaxingmusic #432hz #meditation</t>
+        </is>
+      </c>
+      <c r="O302" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="P302" s="4" t="inlineStr"/>
+      <c r="Q302" s="4" t="inlineStr"/>
+      <c r="R302" s="4" t="inlineStr"/>
+      <c r="S302" s="4" t="inlineStr"/>
+    </row>
+    <row r="303" ht="58" customHeight="1">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-045-S2</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-045</t>
+        </is>
+      </c>
+      <c r="C303" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D303" s="2" t="inlineStr">
+        <is>
+          <t>short-2.mp4</t>
+        </is>
+      </c>
+      <c r="E303" s="2" t="n">
+        <v>960</v>
+      </c>
+      <c r="F303" s="2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="G303" s="2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H303" s="2" t="inlineStr">
+        <is>
+          <t>Unclench your jaw. Let the pillow hold you</t>
+        </is>
+      </c>
+      <c r="I303" s="3" t="inlineStr">
+        <is>
+          <t>Unclench your jaw. Let the pillow hold you · 432 Hz · Guqin and Rain</t>
+        </is>
+      </c>
+      <c r="J303" s="3" t="inlineStr">
+        <is>
+          <t>Lights off, volume low.
+Full piece (3 h): Woke Up at 3 AM? 🌙 Chinese Guqin &amp; Rain to Fall Back Asleep · Dark Screen · 3 Hours
+#sleepmusic #sleep #relaxingmusic #432hz #shorts</t>
+        </is>
+      </c>
+      <c r="K303" s="2" t="inlineStr">
+        <is>
+          <t>sleep music, deep sleep, 432 hz, guqin and rain, Rin</t>
+        </is>
+      </c>
+      <c r="L303" s="2" t="inlineStr"/>
+      <c r="M303" s="2" t="inlineStr">
+        <is>
+          <t>432 Hz · night</t>
+        </is>
+      </c>
+      <c r="N303" s="3" t="inlineStr">
+        <is>
+          <t>Lights off, volume low. Full 3 h piece on YouTube: Rin.
+#sleepmusic #sleep #relaxingmusic #432hz #meditation</t>
+        </is>
+      </c>
+      <c r="O303" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="P303" s="4" t="inlineStr"/>
+      <c r="Q303" s="4" t="inlineStr"/>
+      <c r="R303" s="4" t="inlineStr"/>
+      <c r="S303" s="4" t="inlineStr"/>
+    </row>
+    <row r="304" ht="58" customHeight="1">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-045-S3</t>
+        </is>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-045</t>
+        </is>
+      </c>
+      <c r="C304" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D304" s="2" t="inlineStr">
+        <is>
+          <t>short-3.mp4</t>
+        </is>
+      </c>
+      <c r="E304" s="2" t="n">
+        <v>1980</v>
+      </c>
+      <c r="F304" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G304" s="2" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="H304" s="2" t="inlineStr">
+        <is>
+          <t>Close your eyes. Just listen</t>
+        </is>
+      </c>
+      <c r="I304" s="3" t="inlineStr">
+        <is>
+          <t>Close your eyes. Just listen · 432 Hz · Guqin and Rain</t>
+        </is>
+      </c>
+      <c r="J304" s="3" t="inlineStr">
+        <is>
+          <t>Stay until your breathing slows.
+Full piece (3 h): Woke Up at 3 AM? 🌙 Chinese Guqin &amp; Rain to Fall Back Asleep · Dark Screen · 3 Hours
+#sleepmusic #sleep #relaxingmusic #432hz #shorts</t>
+        </is>
+      </c>
+      <c r="K304" s="2" t="inlineStr">
+        <is>
+          <t>sleep music, deep sleep, 432 hz, guqin and rain, Rin</t>
+        </is>
+      </c>
+      <c r="L304" s="2" t="inlineStr"/>
+      <c r="M304" s="2" t="inlineStr">
+        <is>
+          <t>432 Hz · rest</t>
+        </is>
+      </c>
+      <c r="N304" s="3" t="inlineStr">
+        <is>
+          <t>Stay until your breathing slows. Full 3 h piece on YouTube: Rin.
+#sleepmusic #sleep #relaxingmusic #432hz #meditation</t>
+        </is>
+      </c>
+      <c r="O304" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="P304" s="4" t="inlineStr"/>
+      <c r="Q304" s="4" t="inlineStr"/>
+      <c r="R304" s="4" t="inlineStr"/>
+      <c r="S304" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S301"/>
+  <autoFilter ref="A1:S304"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -28065,7 +28400,7 @@
         </is>
       </c>
       <c r="B2" s="7">
-        <f>COUNTA(Catálogo!A2:A45)</f>
+        <f>COUNTA(Catálogo!A2:A46)</f>
         <v/>
       </c>
     </row>
@@ -28076,7 +28411,7 @@
         </is>
       </c>
       <c r="B3" s="7">
-        <f>COUNTIF(Catálogo!W2:W45,"pendiente")</f>
+        <f>COUNTIF(Catálogo!W2:W46,"pendiente")</f>
         <v/>
       </c>
     </row>
@@ -28087,7 +28422,7 @@
         </is>
       </c>
       <c r="B4" s="7">
-        <f>COUNTIF(Catálogo!W2:W45,"compuesta")</f>
+        <f>COUNTIF(Catálogo!W2:W46,"compuesta")</f>
         <v/>
       </c>
     </row>
@@ -28098,7 +28433,7 @@
         </is>
       </c>
       <c r="B5" s="7">
-        <f>COUNTIF(Catálogo!W2:W45,"montada")</f>
+        <f>COUNTIF(Catálogo!W2:W46,"montada")</f>
         <v/>
       </c>
     </row>
@@ -28109,7 +28444,7 @@
         </is>
       </c>
       <c r="B6" s="7">
-        <f>COUNTIF(Catálogo!W2:W45,"publicada")</f>
+        <f>COUNTIF(Catálogo!W2:W46,"publicada")</f>
         <v/>
       </c>
     </row>
@@ -28149,15 +28484,15 @@
         </is>
       </c>
       <c r="B10" s="7">
-        <f>COUNTIF(Catálogo!D2:D45,A10)</f>
+        <f>COUNTIF(Catálogo!D2:D46,A10)</f>
         <v/>
       </c>
       <c r="C10" s="7">
-        <f>COUNTIFS(Catálogo!D2:D45,A10,Catálogo!W2:W45,"publicada")</f>
+        <f>COUNTIFS(Catálogo!D2:D46,A10,Catálogo!W2:W46,"publicada")</f>
         <v/>
       </c>
       <c r="D10" s="7">
-        <f>SUMIF(Catálogo!D2:D45,A10,Catálogo!R2:R45)</f>
+        <f>SUMIF(Catálogo!D2:D46,A10,Catálogo!R2:R46)</f>
         <v/>
       </c>
     </row>
@@ -28168,15 +28503,15 @@
         </is>
       </c>
       <c r="B11" s="7">
-        <f>COUNTIF(Catálogo!D2:D45,A11)</f>
+        <f>COUNTIF(Catálogo!D2:D46,A11)</f>
         <v/>
       </c>
       <c r="C11" s="7">
-        <f>COUNTIFS(Catálogo!D2:D45,A11,Catálogo!W2:W45,"publicada")</f>
+        <f>COUNTIFS(Catálogo!D2:D46,A11,Catálogo!W2:W46,"publicada")</f>
         <v/>
       </c>
       <c r="D11" s="7">
-        <f>SUMIF(Catálogo!D2:D45,A11,Catálogo!R2:R45)</f>
+        <f>SUMIF(Catálogo!D2:D46,A11,Catálogo!R2:R46)</f>
         <v/>
       </c>
     </row>
@@ -28187,15 +28522,15 @@
         </is>
       </c>
       <c r="B12" s="7">
-        <f>COUNTIF(Catálogo!D2:D45,A12)</f>
+        <f>COUNTIF(Catálogo!D2:D46,A12)</f>
         <v/>
       </c>
       <c r="C12" s="7">
-        <f>COUNTIFS(Catálogo!D2:D45,A12,Catálogo!W2:W45,"publicada")</f>
+        <f>COUNTIFS(Catálogo!D2:D46,A12,Catálogo!W2:W46,"publicada")</f>
         <v/>
       </c>
       <c r="D12" s="7">
-        <f>SUMIF(Catálogo!D2:D45,A12,Catálogo!R2:R45)</f>
+        <f>SUMIF(Catálogo!D2:D46,A12,Catálogo!R2:R46)</f>
         <v/>
       </c>
     </row>
@@ -28206,15 +28541,15 @@
         </is>
       </c>
       <c r="B13" s="7">
-        <f>COUNTIF(Catálogo!D2:D45,A13)</f>
+        <f>COUNTIF(Catálogo!D2:D46,A13)</f>
         <v/>
       </c>
       <c r="C13" s="7">
-        <f>COUNTIFS(Catálogo!D2:D45,A13,Catálogo!W2:W45,"publicada")</f>
+        <f>COUNTIFS(Catálogo!D2:D46,A13,Catálogo!W2:W46,"publicada")</f>
         <v/>
       </c>
       <c r="D13" s="7">
-        <f>SUMIF(Catálogo!D2:D45,A13,Catálogo!R2:R45)</f>
+        <f>SUMIF(Catálogo!D2:D46,A13,Catálogo!R2:R46)</f>
         <v/>
       </c>
     </row>
@@ -28225,15 +28560,15 @@
         </is>
       </c>
       <c r="B14" s="7">
-        <f>COUNTIF(Catálogo!D2:D45,A14)</f>
+        <f>COUNTIF(Catálogo!D2:D46,A14)</f>
         <v/>
       </c>
       <c r="C14" s="7">
-        <f>COUNTIFS(Catálogo!D2:D45,A14,Catálogo!W2:W45,"publicada")</f>
+        <f>COUNTIFS(Catálogo!D2:D46,A14,Catálogo!W2:W46,"publicada")</f>
         <v/>
       </c>
       <c r="D14" s="7">
-        <f>SUMIF(Catálogo!D2:D45,A14,Catálogo!R2:R45)</f>
+        <f>SUMIF(Catálogo!D2:D46,A14,Catálogo!R2:R46)</f>
         <v/>
       </c>
     </row>
@@ -28270,7 +28605,7 @@
         </is>
       </c>
       <c r="B18" s="7">
-        <f>SUM(Catálogo!Y2:Y45)</f>
+        <f>SUM(Catálogo!Y2:Y46)</f>
         <v/>
       </c>
     </row>
@@ -28281,7 +28616,7 @@
         </is>
       </c>
       <c r="B19" s="7">
-        <f>SUM(Catálogo!Z2:Z45)</f>
+        <f>SUM(Catálogo!Z2:Z46)</f>
         <v/>
       </c>
     </row>
@@ -28424,7 +28759,7 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Ambiente aprobado en escucha: mar, mar-aves, zen, selva, lluvia-tambor, jardin, lluvia o theta.</t>
+          <t>Ambiente aprobado en escucha: mar, mar-aves, zen, selva, lluvia-tambor, jardin, lluvia, theta o guqin.</t>
         </is>
       </c>
     </row>

--- a/08-catalogo/catalogo_canal.xlsx
+++ b/08-catalogo/catalogo_canal.xlsx
@@ -13,8 +13,8 @@
     <sheet name="Leyenda" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$AA$46</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Shorts'!$A$1:$S$304</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$AA$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Shorts'!$A$1:$S$316</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA46"/>
+  <dimension ref="A1:AA50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -6190,8 +6190,484 @@
         <v/>
       </c>
     </row>
+    <row r="47" ht="58" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-046</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>3 AM Reset 🌙 10 Minutes of Guqin &amp; Rain to Fall Back Asleep · Chinese Sleep Music</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Música para dormir · Guqin y lluvia · 432 Hz · Volver a dormir · 10 minutos</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Dormir</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>guqin</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Woke up at 3 AM? Ten minutes of guqin, xiao flute and gentle rain to fall back asleep.
+Don't check the time. Breathe out slowly through your lips, "shhh", six times, and let the strings take it from there.
+🌙 Phone face down, volume low. If you're still awake at the end, the full 3 hours are on the channel.
+🌿 Subscribe for a new calm piece every week: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+Original composition by Rin, synthesized from scratch in just intonation around 432 Hz, yu mode. No samples. The yu scale is the one Chinese five-element music keeps for the night. A 2,000-year-old tradition, not medical advice.
+#sleepmusic #guqin #3am</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Volver a dormir · 10 minutos
+Para acompañar el sueño.
+Ambiente: guqin y lluvia.
+Compuesta con raíz en 432 Hz, en entonación justa, modo yu.
+Ciclo respiratorio: de 4.5 a 3.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#sleepmusic #meditation #432hz</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>10 MIN</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>#sleepmusic #guqin #3am</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>3am reset, fall back asleep, woke up at 3am, music to fall back asleep, guqin, chinese sleep music, 10 minute sleep music, rain sounds for sleeping, sleep music, chinese meditation music, rin, música para dormir</t>
+        </is>
+      </c>
+      <c r="K47" s="4" t="inlineStr"/>
+      <c r="L47" s="4" t="inlineStr"/>
+      <c r="M47" s="2" t="n">
+        <v>432</v>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>yu</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>grave</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="n">
+        <v>926874</v>
+      </c>
+      <c r="Q47" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="R47" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="S47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>What time did you wake up tonight? 🌙 Tell us, then breathe out slowly: shhh.</t>
+        </is>
+      </c>
+      <c r="U47" s="3" t="inlineStr">
+        <is>
+          <t>python3 03-composicion/tao_largo.py --minutos 10 --raiz 432 --modo yu --semilla 926874</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>python3 03-composicion/ambiente.py audio/OBRA-046_432_yu.wav audio/OBRA-046_final.wav --fondo lluvia --nivel-obra 0 --nivel-fondo -6 --entrada-obra 6</t>
+        </is>
+      </c>
+      <c r="W47" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="X47" s="4" t="inlineStr"/>
+      <c r="Y47" s="4" t="inlineStr"/>
+      <c r="Z47" s="4" t="inlineStr"/>
+      <c r="AA47" s="5">
+        <f>IFERROR(Z47/Y47*1000,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="58" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-047</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>5-Minute Nervous System Reset 🔔 Zen Temple Bells to Calm Anxiety Fast · 528 Hz</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Música para momentos de ansiedad · Templo zen · 528 Hz · Reinicio de cinco minutos · 5 minutos</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Ansiedad</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>zen</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Five minutes to calm your nervous system: zen temple bells over a warm, slow drone.
+Drop your shoulders. Breathe out longer than you breathe in, and let the bells keep you company until the end.
+🎧 Use it between meetings, before a hard conversation, or whenever your chest feels tight.
+🌿 Subscribe for a new calm piece every week: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+Original composition by Rin, synthesized from scratch in just intonation around 528 Hz, shin mode. No samples.
+#nervoussystemreset #anxietyrelief #528hz</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Reinicio de cinco minutos · 5 minutos
+Para acompañar un momento de pausa cuando la cabeza no para.
+Ambiente: templo zen.
+Compuesta con raíz en 528 Hz, en entonación justa, modo shin.
+Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#relaxingmusic #meditation #528hz</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>5 MIN</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>#nervoussystemreset #anxietyrelief #528hz</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>nervous system reset, 5 minute nervous system reset, calm anxiety fast, anxiety relief, 5 minute meditation, zen temple bells, temple bells, calming music, 528 hz, nervous system regulation, quick calm, rin, música para la ansiedad</t>
+        </is>
+      </c>
+      <c r="K48" s="4" t="inlineStr"/>
+      <c r="L48" s="4" t="inlineStr"/>
+      <c r="M48" s="2" t="n">
+        <v>528</v>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>shin</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="n">
+        <v>756077</v>
+      </c>
+      <c r="Q48" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="R48" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="S48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>Where are you listening from right now? 🔔 Work, bed, car? Tell us.</t>
+        </is>
+      </c>
+      <c r="U48" s="3" t="inlineStr">
+        <is>
+          <t>python3 03-composicion/compositor.py --minutos 5 --raiz 528 --modo shin --semilla 756077 --caracter sin-cuenco</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>python3 03-composicion/capas.py zen 340 audio/OBRA-047_capa.wav --semilla 756077 --raiz 528 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-047_528_shin.wav audio/OBRA-047_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-047_capa.wav</t>
+        </is>
+      </c>
+      <c r="W48" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="X48" s="4" t="inlineStr"/>
+      <c r="Y48" s="4" t="inlineStr"/>
+      <c r="Z48" s="4" t="inlineStr"/>
+      <c r="AA48" s="5">
+        <f>IFERROR(Z48/Y48*1000,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" ht="58" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-048</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Zen Temple Bells for Deep Sleep 🌙 Dark Screen · Calm Your Mind · 432 Hz · 3 Hours</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Música para dormir · Templo zen · 432 Hz · Campanas para dormir · 3 horas</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Dormir</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>zen</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Three hours of soft zen temple bells over a distant ocean, for deep sleep.
+The bells grow sparse as the night goes on. The screen fades to black after 3 minutes, so no light keeps you awake.
+🌙 Lights off, phone face down, volume low.
+🌿 Subscribe for a new calm piece every week: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+Original composition by Rin, synthesized from scratch in just intonation around 216 Hz, the low octave of 432 Hz, kumoi mode. No samples.
+#sleepmusic #templebells #darkscreen</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Campanas para dormir · 3 horas
+Para acompañar el sueño.
+Ambiente: templo zen.
+Compuesta con raíz en 216 Hz, la octava grave de 432 Hz, en entonación justa, modo kumoi.
+Ciclo respiratorio: de 4.5 a 3.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#sleepmusic #meditation #432hz</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>3 HOURS</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>#sleepmusic #templebells #darkscreen</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>zen temple bells, temple bells sleep, zen sleep music, dark screen sleep music, black screen sleep music, deep sleep music, sleep music, calm your mind, zen music, meditation music, 432 hz, 3 hours, rin, música para dormir</t>
+        </is>
+      </c>
+      <c r="K49" s="4" t="inlineStr"/>
+      <c r="L49" s="4" t="inlineStr"/>
+      <c r="M49" s="2" t="n">
+        <v>432</v>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>kumoi</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>grave</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="n">
+        <v>762820</v>
+      </c>
+      <c r="Q49" s="2" t="n">
+        <v>-70</v>
+      </c>
+      <c r="R49" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="S49" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T49" s="2" t="inlineStr">
+        <is>
+          <t>Do bells help you sleep, or do you prefer rain? 🔔🌧️ Tell us, it shapes the next piece.</t>
+        </is>
+      </c>
+      <c r="U49" s="3" t="inlineStr">
+        <is>
+          <t>python3 03-composicion/compositor.py --minutos 180 --raiz 432 --modo kumoi --semilla 762820 --caracter sin-cuenco --registro grave</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>python3 03-composicion/capas.py zen 10840 audio/OBRA-048_capa.wav --semilla 762820 --raiz 432 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-048_432_kumoi.wav audio/OBRA-048_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-048_capa.wav</t>
+        </is>
+      </c>
+      <c r="W49" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="X49" s="4" t="inlineStr"/>
+      <c r="Y49" s="4" t="inlineStr"/>
+      <c r="Z49" s="4" t="inlineStr"/>
+      <c r="AA49" s="5">
+        <f>IFERROR(Z49/Y49*1000,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" ht="58" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-049</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Stop Overthinking in 10 Minutes 🌿 Birdsong &amp; Temple Bells · Calming Music · 432 Hz</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Música para momentos de ansiedad · Pájaros y campanas del templo · 432 Hz · Dejar de pensar en diez · 10 minutos</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Ansiedad</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>jardin</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Ten minutes to stop overthinking: birdsong, soft temple bells and a slower breath.
+You don't have to solve it now. Breathe out longer than you breathe in, and just listen to the birds.
+🌿 Headphones on, eyes closed if you can.
+🌿 Subscribe for a new calm piece every week: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+Original composition by Rin, synthesized from scratch in just intonation around 432 Hz, hirajoshi mode. No samples.
+#stopoverthinking #calmingmusic #432hz</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Dejar de pensar en diez · 10 minutos
+Para acompañar un momento de pausa cuando la cabeza no para.
+Ambiente: pájaros y campanas del templo.
+Compuesta con raíz en 432 Hz, en entonación justa, modo hirajoshi.
+Ciclo respiratorio: de 6.0 a 4.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#relaxingmusic #meditation #432hz</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>10 MIN</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>#stopoverthinking #calmingmusic #432hz</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>stop overthinking, stop overthinking music, 10 minute meditation, calming music, music for anxiety, birdsong, temple bells, anxiety relief, calm your mind, 432 hz, rin, música para la ansiedad</t>
+        </is>
+      </c>
+      <c r="K50" s="4" t="inlineStr"/>
+      <c r="L50" s="4" t="inlineStr"/>
+      <c r="M50" s="2" t="n">
+        <v>432</v>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>hirajoshi</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="n">
+        <v>341227</v>
+      </c>
+      <c r="Q50" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="R50" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="S50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t>What's the thought that won't leave you alone today? 🌿 Write one word. Then let it go.</t>
+        </is>
+      </c>
+      <c r="U50" s="3" t="inlineStr">
+        <is>
+          <t>python3 03-composicion/compositor.py --minutos 10 --raiz 432 --modo hirajoshi --semilla 341227 --caracter sin-cuenco</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>python3 03-composicion/capas.py jardin 640 audio/OBRA-049_capa.wav --semilla 341227 --raiz 432 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-049_432_hirajoshi.wav audio/OBRA-049_final.wav --fondo mar --nivel-fondo -8 --nivel-capa 0 --capa audio/OBRA-049_capa.wav</t>
+        </is>
+      </c>
+      <c r="W50" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="X50" s="4" t="inlineStr"/>
+      <c r="Y50" s="4" t="inlineStr"/>
+      <c r="Z50" s="4" t="inlineStr"/>
+      <c r="AA50" s="5">
+        <f>IFERROR(Z50/Y50*1000,"")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AA46"/>
+  <autoFilter ref="A1:AA50"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6202,7 +6678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S304"/>
+  <dimension ref="A1:S316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -28364,8 +28840,872 @@
       <c r="R304" s="4" t="inlineStr"/>
       <c r="S304" s="4" t="inlineStr"/>
     </row>
+    <row r="305" ht="58" customHeight="1">
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-046-S1</t>
+        </is>
+      </c>
+      <c r="B305" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-046</t>
+        </is>
+      </c>
+      <c r="C305" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D305" s="2" t="inlineStr">
+        <is>
+          <t>short-1.mp4</t>
+        </is>
+      </c>
+      <c r="E305" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="F305" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G305" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H305" s="2" t="inlineStr">
+        <is>
+          <t>Breathe out longer than you breathe in</t>
+        </is>
+      </c>
+      <c r="I305" s="3" t="inlineStr">
+        <is>
+          <t>Breathe out longer than you breathe in · 432 Hz · Guqin and Rain</t>
+        </is>
+      </c>
+      <c r="J305" s="3" t="inlineStr">
+        <is>
+          <t>Save this for tonight.
+Full piece (10 min): 3 AM Reset 🌙 10 Minutes of Guqin &amp; Rain to Fall Back Asleep · Chinese Sleep Music
+#sleepmusic #sleep #relaxingmusic #432hz #shorts</t>
+        </is>
+      </c>
+      <c r="K305" s="2" t="inlineStr">
+        <is>
+          <t>sleep music, deep sleep, 432 hz, guqin and rain, Rin</t>
+        </is>
+      </c>
+      <c r="L305" s="2" t="inlineStr"/>
+      <c r="M305" s="2" t="inlineStr">
+        <is>
+          <t>432 Hz · sleep</t>
+        </is>
+      </c>
+      <c r="N305" s="3" t="inlineStr">
+        <is>
+          <t>Save this for tonight. Full 10 min piece on YouTube: Rin.
+#sleepmusic #sleep #relaxingmusic #432hz #meditation</t>
+        </is>
+      </c>
+      <c r="O305" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="P305" s="4" t="inlineStr"/>
+      <c r="Q305" s="4" t="inlineStr"/>
+      <c r="R305" s="4" t="inlineStr"/>
+      <c r="S305" s="4" t="inlineStr"/>
+    </row>
+    <row r="306" ht="58" customHeight="1">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-046-S2</t>
+        </is>
+      </c>
+      <c r="B306" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-046</t>
+        </is>
+      </c>
+      <c r="C306" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D306" s="2" t="inlineStr">
+        <is>
+          <t>short-2.mp4</t>
+        </is>
+      </c>
+      <c r="E306" s="2" t="n">
+        <v>332</v>
+      </c>
+      <c r="F306" s="2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="G306" s="2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H306" s="2" t="inlineStr">
+        <is>
+          <t>Unclench your jaw. Let the pillow hold you</t>
+        </is>
+      </c>
+      <c r="I306" s="3" t="inlineStr">
+        <is>
+          <t>Unclench your jaw. Let the pillow hold you · 432 Hz · Guqin and Rain</t>
+        </is>
+      </c>
+      <c r="J306" s="3" t="inlineStr">
+        <is>
+          <t>Lights off, volume low.
+Full piece (10 min): 3 AM Reset 🌙 10 Minutes of Guqin &amp; Rain to Fall Back Asleep · Chinese Sleep Music
+#sleepmusic #sleep #relaxingmusic #432hz #shorts</t>
+        </is>
+      </c>
+      <c r="K306" s="2" t="inlineStr">
+        <is>
+          <t>sleep music, deep sleep, 432 hz, guqin and rain, Rin</t>
+        </is>
+      </c>
+      <c r="L306" s="2" t="inlineStr"/>
+      <c r="M306" s="2" t="inlineStr">
+        <is>
+          <t>432 Hz · night</t>
+        </is>
+      </c>
+      <c r="N306" s="3" t="inlineStr">
+        <is>
+          <t>Lights off, volume low. Full 10 min piece on YouTube: Rin.
+#sleepmusic #sleep #relaxingmusic #432hz #meditation</t>
+        </is>
+      </c>
+      <c r="O306" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="P306" s="4" t="inlineStr"/>
+      <c r="Q306" s="4" t="inlineStr"/>
+      <c r="R306" s="4" t="inlineStr"/>
+      <c r="S306" s="4" t="inlineStr"/>
+    </row>
+    <row r="307" ht="58" customHeight="1">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-046-S3</t>
+        </is>
+      </c>
+      <c r="B307" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-046</t>
+        </is>
+      </c>
+      <c r="C307" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D307" s="2" t="inlineStr">
+        <is>
+          <t>short-3.mp4</t>
+        </is>
+      </c>
+      <c r="E307" s="2" t="n">
+        <v>575</v>
+      </c>
+      <c r="F307" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G307" s="2" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="H307" s="2" t="inlineStr">
+        <is>
+          <t>Close your eyes. Just listen</t>
+        </is>
+      </c>
+      <c r="I307" s="3" t="inlineStr">
+        <is>
+          <t>Close your eyes. Just listen · 432 Hz · Guqin and Rain</t>
+        </is>
+      </c>
+      <c r="J307" s="3" t="inlineStr">
+        <is>
+          <t>Stay until your breathing slows.
+Full piece (10 min): 3 AM Reset 🌙 10 Minutes of Guqin &amp; Rain to Fall Back Asleep · Chinese Sleep Music
+#sleepmusic #sleep #relaxingmusic #432hz #shorts</t>
+        </is>
+      </c>
+      <c r="K307" s="2" t="inlineStr">
+        <is>
+          <t>sleep music, deep sleep, 432 hz, guqin and rain, Rin</t>
+        </is>
+      </c>
+      <c r="L307" s="2" t="inlineStr"/>
+      <c r="M307" s="2" t="inlineStr">
+        <is>
+          <t>432 Hz · rest</t>
+        </is>
+      </c>
+      <c r="N307" s="3" t="inlineStr">
+        <is>
+          <t>Stay until your breathing slows. Full 10 min piece on YouTube: Rin.
+#sleepmusic #sleep #relaxingmusic #432hz #meditation</t>
+        </is>
+      </c>
+      <c r="O307" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="P307" s="4" t="inlineStr"/>
+      <c r="Q307" s="4" t="inlineStr"/>
+      <c r="R307" s="4" t="inlineStr"/>
+      <c r="S307" s="4" t="inlineStr"/>
+    </row>
+    <row r="308" ht="58" customHeight="1">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-047-S1</t>
+        </is>
+      </c>
+      <c r="B308" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-047</t>
+        </is>
+      </c>
+      <c r="C308" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D308" s="2" t="inlineStr">
+        <is>
+          <t>short-1.mp4</t>
+        </is>
+      </c>
+      <c r="E308" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="F308" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G308" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H308" s="2" t="inlineStr">
+        <is>
+          <t>Breathe out longer than you breathe in</t>
+        </is>
+      </c>
+      <c r="I308" s="3" t="inlineStr">
+        <is>
+          <t>Breathe out longer than you breathe in · 528 Hz · Zen Temple</t>
+        </is>
+      </c>
+      <c r="J308" s="3" t="inlineStr">
+        <is>
+          <t>Save this for the next hard moment.
+Full piece (5 min): 5-Minute Nervous System Reset 🔔 Zen Temple Bells to Calm Anxiety Fast · 528 Hz
+#anxietyrelief #calm #relaxingmusic #528hz #shorts</t>
+        </is>
+      </c>
+      <c r="K308" s="2" t="inlineStr">
+        <is>
+          <t>anxiety relief, calming music, 528 hz, zen temple, Rin</t>
+        </is>
+      </c>
+      <c r="L308" s="2" t="inlineStr"/>
+      <c r="M308" s="2" t="inlineStr">
+        <is>
+          <t>528 Hz · calm</t>
+        </is>
+      </c>
+      <c r="N308" s="3" t="inlineStr">
+        <is>
+          <t>Save this for the next hard moment. Full 5 min piece on YouTube: Rin.
+#anxietyrelief #calm #relaxingmusic #528hz #meditation</t>
+        </is>
+      </c>
+      <c r="O308" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="P308" s="4" t="inlineStr"/>
+      <c r="Q308" s="4" t="inlineStr"/>
+      <c r="R308" s="4" t="inlineStr"/>
+      <c r="S308" s="4" t="inlineStr"/>
+    </row>
+    <row r="309" ht="58" customHeight="1">
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-047-S2</t>
+        </is>
+      </c>
+      <c r="B309" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-047</t>
+        </is>
+      </c>
+      <c r="C309" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D309" s="2" t="inlineStr">
+        <is>
+          <t>short-2.mp4</t>
+        </is>
+      </c>
+      <c r="E309" s="2" t="n">
+        <v>182</v>
+      </c>
+      <c r="F309" s="2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="G309" s="2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H309" s="2" t="inlineStr">
+        <is>
+          <t>Drop your shoulders. Unclench your jaw</t>
+        </is>
+      </c>
+      <c r="I309" s="3" t="inlineStr">
+        <is>
+          <t>Drop your shoulders. Unclench your jaw · 528 Hz · Zen Temple</t>
+        </is>
+      </c>
+      <c r="J309" s="3" t="inlineStr">
+        <is>
+          <t>Headphones on. Exhale slowly.
+Full piece (5 min): 5-Minute Nervous System Reset 🔔 Zen Temple Bells to Calm Anxiety Fast · 528 Hz
+#anxietyrelief #calm #relaxingmusic #528hz #shorts</t>
+        </is>
+      </c>
+      <c r="K309" s="2" t="inlineStr">
+        <is>
+          <t>anxiety relief, calming music, 528 hz, zen temple, Rin</t>
+        </is>
+      </c>
+      <c r="L309" s="2" t="inlineStr"/>
+      <c r="M309" s="2" t="inlineStr">
+        <is>
+          <t>528 Hz · exhale</t>
+        </is>
+      </c>
+      <c r="N309" s="3" t="inlineStr">
+        <is>
+          <t>Headphones on. Exhale slowly. Full 5 min piece on YouTube: Rin.
+#anxietyrelief #calm #relaxingmusic #528hz #meditation</t>
+        </is>
+      </c>
+      <c r="O309" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="P309" s="4" t="inlineStr"/>
+      <c r="Q309" s="4" t="inlineStr"/>
+      <c r="R309" s="4" t="inlineStr"/>
+      <c r="S309" s="4" t="inlineStr"/>
+    </row>
+    <row r="310" ht="58" customHeight="1">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-047-S3</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-047</t>
+        </is>
+      </c>
+      <c r="C310" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D310" s="2" t="inlineStr">
+        <is>
+          <t>short-3.mp4</t>
+        </is>
+      </c>
+      <c r="E310" s="2" t="n">
+        <v>275</v>
+      </c>
+      <c r="F310" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G310" s="2" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="H310" s="2" t="inlineStr">
+        <is>
+          <t>Hand on your chest. Breathe slower</t>
+        </is>
+      </c>
+      <c r="I310" s="3" t="inlineStr">
+        <is>
+          <t>Hand on your chest. Breathe slower · 528 Hz · Zen Temple</t>
+        </is>
+      </c>
+      <c r="J310" s="3" t="inlineStr">
+        <is>
+          <t>Stay for one full breath.
+Full piece (5 min): 5-Minute Nervous System Reset 🔔 Zen Temple Bells to Calm Anxiety Fast · 528 Hz
+#anxietyrelief #calm #relaxingmusic #528hz #shorts</t>
+        </is>
+      </c>
+      <c r="K310" s="2" t="inlineStr">
+        <is>
+          <t>anxiety relief, calming music, 528 hz, zen temple, Rin</t>
+        </is>
+      </c>
+      <c r="L310" s="2" t="inlineStr"/>
+      <c r="M310" s="2" t="inlineStr">
+        <is>
+          <t>528 Hz · pause</t>
+        </is>
+      </c>
+      <c r="N310" s="3" t="inlineStr">
+        <is>
+          <t>Stay for one full breath. Full 5 min piece on YouTube: Rin.
+#anxietyrelief #calm #relaxingmusic #528hz #meditation</t>
+        </is>
+      </c>
+      <c r="O310" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="P310" s="4" t="inlineStr"/>
+      <c r="Q310" s="4" t="inlineStr"/>
+      <c r="R310" s="4" t="inlineStr"/>
+      <c r="S310" s="4" t="inlineStr"/>
+    </row>
+    <row r="311" ht="58" customHeight="1">
+      <c r="A311" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-048-S1</t>
+        </is>
+      </c>
+      <c r="B311" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-048</t>
+        </is>
+      </c>
+      <c r="C311" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D311" s="2" t="inlineStr">
+        <is>
+          <t>short-1.mp4</t>
+        </is>
+      </c>
+      <c r="E311" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="F311" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G311" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H311" s="2" t="inlineStr">
+        <is>
+          <t>Breathe out longer than you breathe in</t>
+        </is>
+      </c>
+      <c r="I311" s="3" t="inlineStr">
+        <is>
+          <t>Breathe out longer than you breathe in · 432 Hz · Zen Temple</t>
+        </is>
+      </c>
+      <c r="J311" s="3" t="inlineStr">
+        <is>
+          <t>Save this for tonight.
+Full piece (3 h): Zen Temple Bells for Deep Sleep 🌙 Dark Screen · Calm Your Mind · 432 Hz · 3 Hours
+#sleepmusic #sleep #relaxingmusic #432hz #shorts</t>
+        </is>
+      </c>
+      <c r="K311" s="2" t="inlineStr">
+        <is>
+          <t>sleep music, deep sleep, 432 hz, zen temple, Rin</t>
+        </is>
+      </c>
+      <c r="L311" s="2" t="inlineStr"/>
+      <c r="M311" s="2" t="inlineStr">
+        <is>
+          <t>432 Hz · sleep</t>
+        </is>
+      </c>
+      <c r="N311" s="3" t="inlineStr">
+        <is>
+          <t>Save this for tonight. Full 3 h piece on YouTube: Rin.
+#sleepmusic #sleep #relaxingmusic #432hz #meditation</t>
+        </is>
+      </c>
+      <c r="O311" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="P311" s="4" t="inlineStr"/>
+      <c r="Q311" s="4" t="inlineStr"/>
+      <c r="R311" s="4" t="inlineStr"/>
+      <c r="S311" s="4" t="inlineStr"/>
+    </row>
+    <row r="312" ht="58" customHeight="1">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-048-S2</t>
+        </is>
+      </c>
+      <c r="B312" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-048</t>
+        </is>
+      </c>
+      <c r="C312" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D312" s="2" t="inlineStr">
+        <is>
+          <t>short-2.mp4</t>
+        </is>
+      </c>
+      <c r="E312" s="2" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F312" s="2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="G312" s="2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H312" s="2" t="inlineStr">
+        <is>
+          <t>Unclench your jaw. Let the pillow hold you</t>
+        </is>
+      </c>
+      <c r="I312" s="3" t="inlineStr">
+        <is>
+          <t>Unclench your jaw. Let the pillow hold you · 432 Hz · Zen Temple</t>
+        </is>
+      </c>
+      <c r="J312" s="3" t="inlineStr">
+        <is>
+          <t>Lights off, volume low.
+Full piece (3 h): Zen Temple Bells for Deep Sleep 🌙 Dark Screen · Calm Your Mind · 432 Hz · 3 Hours
+#sleepmusic #sleep #relaxingmusic #432hz #shorts</t>
+        </is>
+      </c>
+      <c r="K312" s="2" t="inlineStr">
+        <is>
+          <t>sleep music, deep sleep, 432 hz, zen temple, Rin</t>
+        </is>
+      </c>
+      <c r="L312" s="2" t="inlineStr"/>
+      <c r="M312" s="2" t="inlineStr">
+        <is>
+          <t>432 Hz · night</t>
+        </is>
+      </c>
+      <c r="N312" s="3" t="inlineStr">
+        <is>
+          <t>Lights off, volume low. Full 3 h piece on YouTube: Rin.
+#sleepmusic #sleep #relaxingmusic #432hz #meditation</t>
+        </is>
+      </c>
+      <c r="O312" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="P312" s="4" t="inlineStr"/>
+      <c r="Q312" s="4" t="inlineStr"/>
+      <c r="R312" s="4" t="inlineStr"/>
+      <c r="S312" s="4" t="inlineStr"/>
+    </row>
+    <row r="313" ht="58" customHeight="1">
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-048-S3</t>
+        </is>
+      </c>
+      <c r="B313" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-048</t>
+        </is>
+      </c>
+      <c r="C313" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D313" s="2" t="inlineStr">
+        <is>
+          <t>short-3.mp4</t>
+        </is>
+      </c>
+      <c r="E313" s="2" t="n">
+        <v>10775</v>
+      </c>
+      <c r="F313" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G313" s="2" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="H313" s="2" t="inlineStr">
+        <is>
+          <t>Close your eyes. Just listen</t>
+        </is>
+      </c>
+      <c r="I313" s="3" t="inlineStr">
+        <is>
+          <t>Close your eyes. Just listen · 432 Hz · Zen Temple</t>
+        </is>
+      </c>
+      <c r="J313" s="3" t="inlineStr">
+        <is>
+          <t>Stay until your breathing slows.
+Full piece (3 h): Zen Temple Bells for Deep Sleep 🌙 Dark Screen · Calm Your Mind · 432 Hz · 3 Hours
+#sleepmusic #sleep #relaxingmusic #432hz #shorts</t>
+        </is>
+      </c>
+      <c r="K313" s="2" t="inlineStr">
+        <is>
+          <t>sleep music, deep sleep, 432 hz, zen temple, Rin</t>
+        </is>
+      </c>
+      <c r="L313" s="2" t="inlineStr"/>
+      <c r="M313" s="2" t="inlineStr">
+        <is>
+          <t>432 Hz · rest</t>
+        </is>
+      </c>
+      <c r="N313" s="3" t="inlineStr">
+        <is>
+          <t>Stay until your breathing slows. Full 3 h piece on YouTube: Rin.
+#sleepmusic #sleep #relaxingmusic #432hz #meditation</t>
+        </is>
+      </c>
+      <c r="O313" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="P313" s="4" t="inlineStr"/>
+      <c r="Q313" s="4" t="inlineStr"/>
+      <c r="R313" s="4" t="inlineStr"/>
+      <c r="S313" s="4" t="inlineStr"/>
+    </row>
+    <row r="314" ht="58" customHeight="1">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-049-S1</t>
+        </is>
+      </c>
+      <c r="B314" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-049</t>
+        </is>
+      </c>
+      <c r="C314" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D314" s="2" t="inlineStr">
+        <is>
+          <t>short-1.mp4</t>
+        </is>
+      </c>
+      <c r="E314" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="F314" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G314" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H314" s="2" t="inlineStr">
+        <is>
+          <t>Breathe out longer than you breathe in</t>
+        </is>
+      </c>
+      <c r="I314" s="3" t="inlineStr">
+        <is>
+          <t>Breathe out longer than you breathe in · 432 Hz · Birds and Temple Bells</t>
+        </is>
+      </c>
+      <c r="J314" s="3" t="inlineStr">
+        <is>
+          <t>Save this for the next hard moment.
+Full piece (10 min): Stop Overthinking in 10 Minutes 🌿 Birdsong &amp; Temple Bells · Calming Music · 432 Hz
+#anxietyrelief #calm #relaxingmusic #432hz #shorts</t>
+        </is>
+      </c>
+      <c r="K314" s="2" t="inlineStr">
+        <is>
+          <t>anxiety relief, calming music, 432 hz, birds and temple bells, Rin</t>
+        </is>
+      </c>
+      <c r="L314" s="2" t="inlineStr"/>
+      <c r="M314" s="2" t="inlineStr">
+        <is>
+          <t>432 Hz · calm</t>
+        </is>
+      </c>
+      <c r="N314" s="3" t="inlineStr">
+        <is>
+          <t>Save this for the next hard moment. Full 10 min piece on YouTube: Rin.
+#anxietyrelief #calm #relaxingmusic #432hz #meditation</t>
+        </is>
+      </c>
+      <c r="O314" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="P314" s="4" t="inlineStr"/>
+      <c r="Q314" s="4" t="inlineStr"/>
+      <c r="R314" s="4" t="inlineStr"/>
+      <c r="S314" s="4" t="inlineStr"/>
+    </row>
+    <row r="315" ht="58" customHeight="1">
+      <c r="A315" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-049-S2</t>
+        </is>
+      </c>
+      <c r="B315" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-049</t>
+        </is>
+      </c>
+      <c r="C315" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D315" s="2" t="inlineStr">
+        <is>
+          <t>short-2.mp4</t>
+        </is>
+      </c>
+      <c r="E315" s="2" t="n">
+        <v>332</v>
+      </c>
+      <c r="F315" s="2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="G315" s="2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H315" s="2" t="inlineStr">
+        <is>
+          <t>Drop your shoulders. Unclench your jaw</t>
+        </is>
+      </c>
+      <c r="I315" s="3" t="inlineStr">
+        <is>
+          <t>Drop your shoulders. Unclench your jaw · 432 Hz · Birds and Temple Bells</t>
+        </is>
+      </c>
+      <c r="J315" s="3" t="inlineStr">
+        <is>
+          <t>Headphones on. Exhale slowly.
+Full piece (10 min): Stop Overthinking in 10 Minutes 🌿 Birdsong &amp; Temple Bells · Calming Music · 432 Hz
+#anxietyrelief #calm #relaxingmusic #432hz #shorts</t>
+        </is>
+      </c>
+      <c r="K315" s="2" t="inlineStr">
+        <is>
+          <t>anxiety relief, calming music, 432 hz, birds and temple bells, Rin</t>
+        </is>
+      </c>
+      <c r="L315" s="2" t="inlineStr"/>
+      <c r="M315" s="2" t="inlineStr">
+        <is>
+          <t>432 Hz · exhale</t>
+        </is>
+      </c>
+      <c r="N315" s="3" t="inlineStr">
+        <is>
+          <t>Headphones on. Exhale slowly. Full 10 min piece on YouTube: Rin.
+#anxietyrelief #calm #relaxingmusic #432hz #meditation</t>
+        </is>
+      </c>
+      <c r="O315" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="P315" s="4" t="inlineStr"/>
+      <c r="Q315" s="4" t="inlineStr"/>
+      <c r="R315" s="4" t="inlineStr"/>
+      <c r="S315" s="4" t="inlineStr"/>
+    </row>
+    <row r="316" ht="58" customHeight="1">
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-049-S3</t>
+        </is>
+      </c>
+      <c r="B316" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-049</t>
+        </is>
+      </c>
+      <c r="C316" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D316" s="2" t="inlineStr">
+        <is>
+          <t>short-3.mp4</t>
+        </is>
+      </c>
+      <c r="E316" s="2" t="n">
+        <v>575</v>
+      </c>
+      <c r="F316" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G316" s="2" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="H316" s="2" t="inlineStr">
+        <is>
+          <t>Hand on your chest. Breathe slower</t>
+        </is>
+      </c>
+      <c r="I316" s="3" t="inlineStr">
+        <is>
+          <t>Hand on your chest. Breathe slower · 432 Hz · Birds and Temple Bells</t>
+        </is>
+      </c>
+      <c r="J316" s="3" t="inlineStr">
+        <is>
+          <t>Stay for one full breath.
+Full piece (10 min): Stop Overthinking in 10 Minutes 🌿 Birdsong &amp; Temple Bells · Calming Music · 432 Hz
+#anxietyrelief #calm #relaxingmusic #432hz #shorts</t>
+        </is>
+      </c>
+      <c r="K316" s="2" t="inlineStr">
+        <is>
+          <t>anxiety relief, calming music, 432 hz, birds and temple bells, Rin</t>
+        </is>
+      </c>
+      <c r="L316" s="2" t="inlineStr"/>
+      <c r="M316" s="2" t="inlineStr">
+        <is>
+          <t>432 Hz · pause</t>
+        </is>
+      </c>
+      <c r="N316" s="3" t="inlineStr">
+        <is>
+          <t>Stay for one full breath. Full 10 min piece on YouTube: Rin.
+#anxietyrelief #calm #relaxingmusic #432hz #meditation</t>
+        </is>
+      </c>
+      <c r="O316" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="P316" s="4" t="inlineStr"/>
+      <c r="Q316" s="4" t="inlineStr"/>
+      <c r="R316" s="4" t="inlineStr"/>
+      <c r="S316" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S304"/>
+  <autoFilter ref="A1:S316"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -28400,7 +29740,7 @@
         </is>
       </c>
       <c r="B2" s="7">
-        <f>COUNTA(Catálogo!A2:A46)</f>
+        <f>COUNTA(Catálogo!A2:A50)</f>
         <v/>
       </c>
     </row>
@@ -28411,7 +29751,7 @@
         </is>
       </c>
       <c r="B3" s="7">
-        <f>COUNTIF(Catálogo!W2:W46,"pendiente")</f>
+        <f>COUNTIF(Catálogo!W2:W50,"pendiente")</f>
         <v/>
       </c>
     </row>
@@ -28422,7 +29762,7 @@
         </is>
       </c>
       <c r="B4" s="7">
-        <f>COUNTIF(Catálogo!W2:W46,"compuesta")</f>
+        <f>COUNTIF(Catálogo!W2:W50,"compuesta")</f>
         <v/>
       </c>
     </row>
@@ -28433,7 +29773,7 @@
         </is>
       </c>
       <c r="B5" s="7">
-        <f>COUNTIF(Catálogo!W2:W46,"montada")</f>
+        <f>COUNTIF(Catálogo!W2:W50,"montada")</f>
         <v/>
       </c>
     </row>
@@ -28444,7 +29784,7 @@
         </is>
       </c>
       <c r="B6" s="7">
-        <f>COUNTIF(Catálogo!W2:W46,"publicada")</f>
+        <f>COUNTIF(Catálogo!W2:W50,"publicada")</f>
         <v/>
       </c>
     </row>
@@ -28484,15 +29824,15 @@
         </is>
       </c>
       <c r="B10" s="7">
-        <f>COUNTIF(Catálogo!D2:D46,A10)</f>
+        <f>COUNTIF(Catálogo!D2:D50,A10)</f>
         <v/>
       </c>
       <c r="C10" s="7">
-        <f>COUNTIFS(Catálogo!D2:D46,A10,Catálogo!W2:W46,"publicada")</f>
+        <f>COUNTIFS(Catálogo!D2:D50,A10,Catálogo!W2:W50,"publicada")</f>
         <v/>
       </c>
       <c r="D10" s="7">
-        <f>SUMIF(Catálogo!D2:D46,A10,Catálogo!R2:R46)</f>
+        <f>SUMIF(Catálogo!D2:D50,A10,Catálogo!R2:R50)</f>
         <v/>
       </c>
     </row>
@@ -28503,15 +29843,15 @@
         </is>
       </c>
       <c r="B11" s="7">
-        <f>COUNTIF(Catálogo!D2:D46,A11)</f>
+        <f>COUNTIF(Catálogo!D2:D50,A11)</f>
         <v/>
       </c>
       <c r="C11" s="7">
-        <f>COUNTIFS(Catálogo!D2:D46,A11,Catálogo!W2:W46,"publicada")</f>
+        <f>COUNTIFS(Catálogo!D2:D50,A11,Catálogo!W2:W50,"publicada")</f>
         <v/>
       </c>
       <c r="D11" s="7">
-        <f>SUMIF(Catálogo!D2:D46,A11,Catálogo!R2:R46)</f>
+        <f>SUMIF(Catálogo!D2:D50,A11,Catálogo!R2:R50)</f>
         <v/>
       </c>
     </row>
@@ -28522,15 +29862,15 @@
         </is>
       </c>
       <c r="B12" s="7">
-        <f>COUNTIF(Catálogo!D2:D46,A12)</f>
+        <f>COUNTIF(Catálogo!D2:D50,A12)</f>
         <v/>
       </c>
       <c r="C12" s="7">
-        <f>COUNTIFS(Catálogo!D2:D46,A12,Catálogo!W2:W46,"publicada")</f>
+        <f>COUNTIFS(Catálogo!D2:D50,A12,Catálogo!W2:W50,"publicada")</f>
         <v/>
       </c>
       <c r="D12" s="7">
-        <f>SUMIF(Catálogo!D2:D46,A12,Catálogo!R2:R46)</f>
+        <f>SUMIF(Catálogo!D2:D50,A12,Catálogo!R2:R50)</f>
         <v/>
       </c>
     </row>
@@ -28541,15 +29881,15 @@
         </is>
       </c>
       <c r="B13" s="7">
-        <f>COUNTIF(Catálogo!D2:D46,A13)</f>
+        <f>COUNTIF(Catálogo!D2:D50,A13)</f>
         <v/>
       </c>
       <c r="C13" s="7">
-        <f>COUNTIFS(Catálogo!D2:D46,A13,Catálogo!W2:W46,"publicada")</f>
+        <f>COUNTIFS(Catálogo!D2:D50,A13,Catálogo!W2:W50,"publicada")</f>
         <v/>
       </c>
       <c r="D13" s="7">
-        <f>SUMIF(Catálogo!D2:D46,A13,Catálogo!R2:R46)</f>
+        <f>SUMIF(Catálogo!D2:D50,A13,Catálogo!R2:R50)</f>
         <v/>
       </c>
     </row>
@@ -28560,15 +29900,15 @@
         </is>
       </c>
       <c r="B14" s="7">
-        <f>COUNTIF(Catálogo!D2:D46,A14)</f>
+        <f>COUNTIF(Catálogo!D2:D50,A14)</f>
         <v/>
       </c>
       <c r="C14" s="7">
-        <f>COUNTIFS(Catálogo!D2:D46,A14,Catálogo!W2:W46,"publicada")</f>
+        <f>COUNTIFS(Catálogo!D2:D50,A14,Catálogo!W2:W50,"publicada")</f>
         <v/>
       </c>
       <c r="D14" s="7">
-        <f>SUMIF(Catálogo!D2:D46,A14,Catálogo!R2:R46)</f>
+        <f>SUMIF(Catálogo!D2:D50,A14,Catálogo!R2:R50)</f>
         <v/>
       </c>
     </row>
@@ -28605,7 +29945,7 @@
         </is>
       </c>
       <c r="B18" s="7">
-        <f>SUM(Catálogo!Y2:Y46)</f>
+        <f>SUM(Catálogo!Y2:Y50)</f>
         <v/>
       </c>
     </row>
@@ -28616,7 +29956,7 @@
         </is>
       </c>
       <c r="B19" s="7">
-        <f>SUM(Catálogo!Z2:Z46)</f>
+        <f>SUM(Catálogo!Z2:Z50)</f>
         <v/>
       </c>
     </row>

--- a/08-catalogo/catalogo_canal.xlsx
+++ b/08-catalogo/catalogo_canal.xlsx
@@ -13,8 +13,8 @@
     <sheet name="Leyenda" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$AA$50</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Shorts'!$A$1:$S$316</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$AA$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Shorts'!$A$1:$S$322</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA50"/>
+  <dimension ref="A1:AA52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -6017,7 +6017,11 @@
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr"/>
-      <c r="L45" s="4" t="inlineStr"/>
+      <c r="L45" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/BeFuK1CnmII</t>
+        </is>
+      </c>
       <c r="M45" s="2" t="n">
         <v>432</v>
       </c>
@@ -6060,10 +6064,14 @@
       </c>
       <c r="W45" s="4" t="inlineStr">
         <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="X45" s="4" t="inlineStr"/>
+          <t>publicada</t>
+        </is>
+      </c>
+      <c r="X45" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
       <c r="Y45" s="4" t="inlineStr"/>
       <c r="Z45" s="4" t="inlineStr"/>
       <c r="AA45" s="5">
@@ -6666,8 +6674,246 @@
         <v/>
       </c>
     </row>
+    <row r="51" ht="58" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-050</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Brown Noise for Deep Sleep 🌙 Distant Temple Bells · Black Screen · Fall Asleep Fast · 3 Hours</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Música para dormir · Ruido marrón y campanas lejanas · 432 Hz · Ruido marrón · 3 horas</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Dormir</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>marron</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Brown noise and pink noise are the most searched sounds for sleep. This is brown noise: low, warm and steady, with distant temple bells.
+Like heavy rain on a faraway roof. No beat, no melody to follow, nothing to listen for. The screen fades to black after 3 minutes.
+🌙 Lights off, phone face down, volume low. Let it cover the noise.
+🌿 Subscribe for a new calm piece every week: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+Original composition by Rin, synthesized from scratch in just intonation around 216 Hz, the low octave of 432 Hz, kumoi mode. No samples.
+#brownnoise #sleepsounds #darkscreen</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Ruido marrón · 3 horas
+Para acompañar el sueño.
+Ambiente: ruido marrón y campanas lejanas.
+Compuesta con raíz en 216 Hz, la octava grave de 432 Hz, en entonación justa, modo kumoi.
+Ciclo respiratorio: de 4.5 a 3.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#sleepmusic #meditation #432hz</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>3 HOURS</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>#brownnoise #sleepsounds #darkscreen</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>brown noise, brown noise for sleeping, brown noise sleep, brown noise black screen, brown noise 3 hours, deep sleep, sleep sounds, black screen sleep, dark screen sleep music, fall asleep fast, temple bells, noise for sleeping, rin, ruido marrón para dormir</t>
+        </is>
+      </c>
+      <c r="K51" s="4" t="inlineStr"/>
+      <c r="L51" s="4" t="inlineStr"/>
+      <c r="M51" s="2" t="n">
+        <v>432</v>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>kumoi</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>grave</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="n">
+        <v>36529</v>
+      </c>
+      <c r="Q51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="S51" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T51" s="2" t="inlineStr">
+        <is>
+          <t>Brown noise or rain: which one puts you to sleep faster? 🌙 Tell us.</t>
+        </is>
+      </c>
+      <c r="U51" s="3" t="inlineStr">
+        <is>
+          <t>python3 03-composicion/compositor.py --minutos 180 --raiz 432 --modo kumoi --semilla 36529 --caracter sin-cuenco --registro grave</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>python3 03-composicion/capas.py zen 10840 audio/OBRA-050_capa.wav --semilla 36529 --raiz 432 --densidad 0.6 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-050_432_kumoi.wav audio/OBRA-050_final.wav --fondo marron --nivel-obra -24 --nivel-capa -9 --entrada-obra 4 --capa audio/OBRA-050_capa.wav</t>
+        </is>
+      </c>
+      <c r="W51" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="X51" s="4" t="inlineStr"/>
+      <c r="Y51" s="4" t="inlineStr"/>
+      <c r="Z51" s="4" t="inlineStr"/>
+      <c r="AA51" s="5">
+        <f>IFERROR(Z51/Y51*1000,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" ht="58" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-051</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Pink Noise + Delta Waves for Deep Sleep 🌙 Binaural Beats · Black Screen · 3 Hours</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Música para dormir · Ruido rosa y ondas delta · 432 Hz · Ruido rosa y delta · 3 horas</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Dormir</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>delta</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Pink noise and brown noise are the most searched sounds for sleep, and pink noise with delta waves is the pairing sleep apps use in their sleep category. 🎧 Use headphones for the best experience.
+Pink noise is soft and even, like steady rain. Underneath, each ear hears a slightly different tone: the difference starts at 3 Hz and slows to 1.5 Hz, the rhythm of deep sleep. The screen fades to black after 3 minutes.
+🌙 Headphones on, lights off, volume low.
+🌿 Subscribe for a new calm piece every week: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+Original composition by Rin, synthesized from scratch in just intonation around 216 Hz, the low octave of 432 Hz, shin mode. No samples. Delta waves are the brain's slowest rhythm, the one of deep sleep. Not medical advice.
+#pinknoise #deltawaves #deepsleep</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Ruido rosa y delta · 3 horas
+Para acompañar el sueño.
+Ambiente: ruido rosa y ondas delta.
+Compuesta con raíz en 216 Hz, la octava grave de 432 Hz, en entonación justa, modo shin.
+Ciclo respiratorio: de 4.5 a 3.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
+Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
+Mejor a volumen bajo.
+Suscríbete para las próximas obras: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
+#sleepmusic #meditation #432hz</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>3 HOURS</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>#pinknoise #deltawaves #deepsleep</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>pink noise, pink noise for sleeping, delta waves, delta waves sleep, pink noise delta waves, binaural beats, binaural beats for sleep, deep sleep, black screen sleep, sleep sounds, fall asleep fast, 3 hours, rin, ruido rosa para dormir</t>
+        </is>
+      </c>
+      <c r="K52" s="4" t="inlineStr"/>
+      <c r="L52" s="4" t="inlineStr"/>
+      <c r="M52" s="2" t="n">
+        <v>432</v>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>shin</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>grave</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="n">
+        <v>127804</v>
+      </c>
+      <c r="Q52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="S52" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T52" s="2" t="inlineStr">
+        <is>
+          <t>Headphones or speaker? 🎧 Tell us how far you got before falling asleep.</t>
+        </is>
+      </c>
+      <c r="U52" s="3" t="inlineStr">
+        <is>
+          <t>python3 03-composicion/compositor.py --minutos 180 --raiz 432 --modo shin --semilla 127804 --caracter sin-cuenco --registro grave</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>python3 03-composicion/capas.py delta 10840 audio/OBRA-051_capa.wav --semilla 127804 --raiz 432 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-051_432_shin.wav audio/OBRA-051_final.wav --fondo rosa --nivel-fondo -1 --nivel-obra -22 --nivel-capa -13 --entrada-obra 4 --capa audio/OBRA-051_capa.wav</t>
+        </is>
+      </c>
+      <c r="W52" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="X52" s="4" t="inlineStr"/>
+      <c r="Y52" s="4" t="inlineStr"/>
+      <c r="Z52" s="4" t="inlineStr"/>
+      <c r="AA52" s="5">
+        <f>IFERROR(Z52/Y52*1000,"")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AA50"/>
+  <autoFilter ref="A1:AA52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6678,7 +6924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S316"/>
+  <dimension ref="A1:S322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -28450,6 +28696,7 @@
         <is>
           <t>🎧 Use headphones for the best experience. Save this for tonight.
 Full piece (3 h): Deep Sleep Theta Waves 🌙 Turn Off Your Thoughts · Dark Screen · Fall Asleep Fast · 3 Hours
+https://youtu.be/BeFuK1CnmII
 #sleepmusic #sleep #relaxingmusic #432hz #shorts</t>
         </is>
       </c>
@@ -28458,7 +28705,11 @@
           <t>sleep music, deep sleep, 432 hz, theta waves, Rin</t>
         </is>
       </c>
-      <c r="L299" s="2" t="inlineStr"/>
+      <c r="L299" s="2" t="inlineStr">
+        <is>
+          <t>https://youtu.be/BeFuK1CnmII</t>
+        </is>
+      </c>
       <c r="M299" s="2" t="inlineStr">
         <is>
           <t>432 Hz · sleep</t>
@@ -28522,6 +28773,7 @@
         <is>
           <t>🎧 Use headphones for the best experience. Lights off, volume low.
 Full piece (3 h): Deep Sleep Theta Waves 🌙 Turn Off Your Thoughts · Dark Screen · Fall Asleep Fast · 3 Hours
+https://youtu.be/BeFuK1CnmII
 #sleepmusic #sleep #relaxingmusic #432hz #shorts</t>
         </is>
       </c>
@@ -28530,7 +28782,11 @@
           <t>sleep music, deep sleep, 432 hz, theta waves, Rin</t>
         </is>
       </c>
-      <c r="L300" s="2" t="inlineStr"/>
+      <c r="L300" s="2" t="inlineStr">
+        <is>
+          <t>https://youtu.be/BeFuK1CnmII</t>
+        </is>
+      </c>
       <c r="M300" s="2" t="inlineStr">
         <is>
           <t>432 Hz · night</t>
@@ -28594,6 +28850,7 @@
         <is>
           <t>🎧 Use headphones for the best experience. Stay until your breathing slows.
 Full piece (3 h): Deep Sleep Theta Waves 🌙 Turn Off Your Thoughts · Dark Screen · Fall Asleep Fast · 3 Hours
+https://youtu.be/BeFuK1CnmII
 #sleepmusic #sleep #relaxingmusic #432hz #shorts</t>
         </is>
       </c>
@@ -28602,7 +28859,11 @@
           <t>sleep music, deep sleep, 432 hz, theta waves, Rin</t>
         </is>
       </c>
-      <c r="L301" s="2" t="inlineStr"/>
+      <c r="L301" s="2" t="inlineStr">
+        <is>
+          <t>https://youtu.be/BeFuK1CnmII</t>
+        </is>
+      </c>
       <c r="M301" s="2" t="inlineStr">
         <is>
           <t>432 Hz · rest</t>
@@ -29704,8 +29965,440 @@
       <c r="R316" s="4" t="inlineStr"/>
       <c r="S316" s="4" t="inlineStr"/>
     </row>
+    <row r="317" ht="58" customHeight="1">
+      <c r="A317" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-050-S1</t>
+        </is>
+      </c>
+      <c r="B317" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-050</t>
+        </is>
+      </c>
+      <c r="C317" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D317" s="2" t="inlineStr">
+        <is>
+          <t>short-1.mp4</t>
+        </is>
+      </c>
+      <c r="E317" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="F317" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G317" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H317" s="2" t="inlineStr">
+        <is>
+          <t>Breathe out longer than you breathe in</t>
+        </is>
+      </c>
+      <c r="I317" s="3" t="inlineStr">
+        <is>
+          <t>Breathe out longer than you breathe in · 432 Hz · Brown Noise</t>
+        </is>
+      </c>
+      <c r="J317" s="3" t="inlineStr">
+        <is>
+          <t>Save this for tonight.
+Full piece (3 h): Brown Noise for Deep Sleep 🌙 Distant Temple Bells · Black Screen · Fall Asleep Fast · 3 Hours
+#sleepmusic #sleep #relaxingmusic #432hz #shorts</t>
+        </is>
+      </c>
+      <c r="K317" s="2" t="inlineStr">
+        <is>
+          <t>sleep music, deep sleep, 432 hz, brown noise, Rin</t>
+        </is>
+      </c>
+      <c r="L317" s="2" t="inlineStr"/>
+      <c r="M317" s="2" t="inlineStr">
+        <is>
+          <t>432 Hz · sleep</t>
+        </is>
+      </c>
+      <c r="N317" s="3" t="inlineStr">
+        <is>
+          <t>Save this for tonight. Full 3 h piece on YouTube: Rin.
+#sleepmusic #sleep #relaxingmusic #432hz #meditation</t>
+        </is>
+      </c>
+      <c r="O317" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="P317" s="4" t="inlineStr"/>
+      <c r="Q317" s="4" t="inlineStr"/>
+      <c r="R317" s="4" t="inlineStr"/>
+      <c r="S317" s="4" t="inlineStr"/>
+    </row>
+    <row r="318" ht="58" customHeight="1">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-050-S2</t>
+        </is>
+      </c>
+      <c r="B318" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-050</t>
+        </is>
+      </c>
+      <c r="C318" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D318" s="2" t="inlineStr">
+        <is>
+          <t>short-2.mp4</t>
+        </is>
+      </c>
+      <c r="E318" s="2" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F318" s="2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="G318" s="2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H318" s="2" t="inlineStr">
+        <is>
+          <t>Unclench your jaw. Let the pillow hold you</t>
+        </is>
+      </c>
+      <c r="I318" s="3" t="inlineStr">
+        <is>
+          <t>Unclench your jaw. Let the pillow hold you · 432 Hz · Brown Noise</t>
+        </is>
+      </c>
+      <c r="J318" s="3" t="inlineStr">
+        <is>
+          <t>Lights off, volume low.
+Full piece (3 h): Brown Noise for Deep Sleep 🌙 Distant Temple Bells · Black Screen · Fall Asleep Fast · 3 Hours
+#sleepmusic #sleep #relaxingmusic #432hz #shorts</t>
+        </is>
+      </c>
+      <c r="K318" s="2" t="inlineStr">
+        <is>
+          <t>sleep music, deep sleep, 432 hz, brown noise, Rin</t>
+        </is>
+      </c>
+      <c r="L318" s="2" t="inlineStr"/>
+      <c r="M318" s="2" t="inlineStr">
+        <is>
+          <t>432 Hz · night</t>
+        </is>
+      </c>
+      <c r="N318" s="3" t="inlineStr">
+        <is>
+          <t>Lights off, volume low. Full 3 h piece on YouTube: Rin.
+#sleepmusic #sleep #relaxingmusic #432hz #meditation</t>
+        </is>
+      </c>
+      <c r="O318" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="P318" s="4" t="inlineStr"/>
+      <c r="Q318" s="4" t="inlineStr"/>
+      <c r="R318" s="4" t="inlineStr"/>
+      <c r="S318" s="4" t="inlineStr"/>
+    </row>
+    <row r="319" ht="58" customHeight="1">
+      <c r="A319" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-050-S3</t>
+        </is>
+      </c>
+      <c r="B319" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-050</t>
+        </is>
+      </c>
+      <c r="C319" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D319" s="2" t="inlineStr">
+        <is>
+          <t>short-3.mp4</t>
+        </is>
+      </c>
+      <c r="E319" s="2" t="n">
+        <v>10775</v>
+      </c>
+      <c r="F319" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G319" s="2" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="H319" s="2" t="inlineStr">
+        <is>
+          <t>Close your eyes. Just listen</t>
+        </is>
+      </c>
+      <c r="I319" s="3" t="inlineStr">
+        <is>
+          <t>Close your eyes. Just listen · 432 Hz · Brown Noise</t>
+        </is>
+      </c>
+      <c r="J319" s="3" t="inlineStr">
+        <is>
+          <t>Stay until your breathing slows.
+Full piece (3 h): Brown Noise for Deep Sleep 🌙 Distant Temple Bells · Black Screen · Fall Asleep Fast · 3 Hours
+#sleepmusic #sleep #relaxingmusic #432hz #shorts</t>
+        </is>
+      </c>
+      <c r="K319" s="2" t="inlineStr">
+        <is>
+          <t>sleep music, deep sleep, 432 hz, brown noise, Rin</t>
+        </is>
+      </c>
+      <c r="L319" s="2" t="inlineStr"/>
+      <c r="M319" s="2" t="inlineStr">
+        <is>
+          <t>432 Hz · rest</t>
+        </is>
+      </c>
+      <c r="N319" s="3" t="inlineStr">
+        <is>
+          <t>Stay until your breathing slows. Full 3 h piece on YouTube: Rin.
+#sleepmusic #sleep #relaxingmusic #432hz #meditation</t>
+        </is>
+      </c>
+      <c r="O319" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="P319" s="4" t="inlineStr"/>
+      <c r="Q319" s="4" t="inlineStr"/>
+      <c r="R319" s="4" t="inlineStr"/>
+      <c r="S319" s="4" t="inlineStr"/>
+    </row>
+    <row r="320" ht="58" customHeight="1">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-051-S1</t>
+        </is>
+      </c>
+      <c r="B320" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-051</t>
+        </is>
+      </c>
+      <c r="C320" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D320" s="2" t="inlineStr">
+        <is>
+          <t>short-1.mp4</t>
+        </is>
+      </c>
+      <c r="E320" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="F320" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G320" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H320" s="2" t="inlineStr">
+        <is>
+          <t>Breathe out longer than you breathe in</t>
+        </is>
+      </c>
+      <c r="I320" s="3" t="inlineStr">
+        <is>
+          <t>Breathe out longer than you breathe in · 432 Hz · Pink Noise and Delta Waves</t>
+        </is>
+      </c>
+      <c r="J320" s="3" t="inlineStr">
+        <is>
+          <t>Save this for tonight.
+Full piece (3 h): Pink Noise + Delta Waves for Deep Sleep 🌙 Binaural Beats · Black Screen · 3 Hours
+#sleepmusic #sleep #relaxingmusic #432hz #shorts</t>
+        </is>
+      </c>
+      <c r="K320" s="2" t="inlineStr">
+        <is>
+          <t>sleep music, deep sleep, 432 hz, pink noise and delta waves, Rin</t>
+        </is>
+      </c>
+      <c r="L320" s="2" t="inlineStr"/>
+      <c r="M320" s="2" t="inlineStr">
+        <is>
+          <t>432 Hz · sleep</t>
+        </is>
+      </c>
+      <c r="N320" s="3" t="inlineStr">
+        <is>
+          <t>Save this for tonight. Full 3 h piece on YouTube: Rin.
+#sleepmusic #sleep #relaxingmusic #432hz #meditation</t>
+        </is>
+      </c>
+      <c r="O320" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="P320" s="4" t="inlineStr"/>
+      <c r="Q320" s="4" t="inlineStr"/>
+      <c r="R320" s="4" t="inlineStr"/>
+      <c r="S320" s="4" t="inlineStr"/>
+    </row>
+    <row r="321" ht="58" customHeight="1">
+      <c r="A321" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-051-S2</t>
+        </is>
+      </c>
+      <c r="B321" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-051</t>
+        </is>
+      </c>
+      <c r="C321" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D321" s="2" t="inlineStr">
+        <is>
+          <t>short-2.mp4</t>
+        </is>
+      </c>
+      <c r="E321" s="2" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F321" s="2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="G321" s="2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H321" s="2" t="inlineStr">
+        <is>
+          <t>Unclench your jaw. Let the pillow hold you</t>
+        </is>
+      </c>
+      <c r="I321" s="3" t="inlineStr">
+        <is>
+          <t>Unclench your jaw. Let the pillow hold you · 432 Hz · Pink Noise and Delta Waves</t>
+        </is>
+      </c>
+      <c r="J321" s="3" t="inlineStr">
+        <is>
+          <t>Lights off, volume low.
+Full piece (3 h): Pink Noise + Delta Waves for Deep Sleep 🌙 Binaural Beats · Black Screen · 3 Hours
+#sleepmusic #sleep #relaxingmusic #432hz #shorts</t>
+        </is>
+      </c>
+      <c r="K321" s="2" t="inlineStr">
+        <is>
+          <t>sleep music, deep sleep, 432 hz, pink noise and delta waves, Rin</t>
+        </is>
+      </c>
+      <c r="L321" s="2" t="inlineStr"/>
+      <c r="M321" s="2" t="inlineStr">
+        <is>
+          <t>432 Hz · night</t>
+        </is>
+      </c>
+      <c r="N321" s="3" t="inlineStr">
+        <is>
+          <t>Lights off, volume low. Full 3 h piece on YouTube: Rin.
+#sleepmusic #sleep #relaxingmusic #432hz #meditation</t>
+        </is>
+      </c>
+      <c r="O321" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="P321" s="4" t="inlineStr"/>
+      <c r="Q321" s="4" t="inlineStr"/>
+      <c r="R321" s="4" t="inlineStr"/>
+      <c r="S321" s="4" t="inlineStr"/>
+    </row>
+    <row r="322" ht="58" customHeight="1">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-051-S3</t>
+        </is>
+      </c>
+      <c r="B322" s="2" t="inlineStr">
+        <is>
+          <t>OBRA-051</t>
+        </is>
+      </c>
+      <c r="C322" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D322" s="2" t="inlineStr">
+        <is>
+          <t>short-3.mp4</t>
+        </is>
+      </c>
+      <c r="E322" s="2" t="n">
+        <v>10775</v>
+      </c>
+      <c r="F322" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G322" s="2" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="H322" s="2" t="inlineStr">
+        <is>
+          <t>Close your eyes. Just listen</t>
+        </is>
+      </c>
+      <c r="I322" s="3" t="inlineStr">
+        <is>
+          <t>Close your eyes. Just listen · 432 Hz · Pink Noise and Delta Waves</t>
+        </is>
+      </c>
+      <c r="J322" s="3" t="inlineStr">
+        <is>
+          <t>Stay until your breathing slows.
+Full piece (3 h): Pink Noise + Delta Waves for Deep Sleep 🌙 Binaural Beats · Black Screen · 3 Hours
+#sleepmusic #sleep #relaxingmusic #432hz #shorts</t>
+        </is>
+      </c>
+      <c r="K322" s="2" t="inlineStr">
+        <is>
+          <t>sleep music, deep sleep, 432 hz, pink noise and delta waves, Rin</t>
+        </is>
+      </c>
+      <c r="L322" s="2" t="inlineStr"/>
+      <c r="M322" s="2" t="inlineStr">
+        <is>
+          <t>432 Hz · rest</t>
+        </is>
+      </c>
+      <c r="N322" s="3" t="inlineStr">
+        <is>
+          <t>Stay until your breathing slows. Full 3 h piece on YouTube: Rin.
+#sleepmusic #sleep #relaxingmusic #432hz #meditation</t>
+        </is>
+      </c>
+      <c r="O322" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="P322" s="4" t="inlineStr"/>
+      <c r="Q322" s="4" t="inlineStr"/>
+      <c r="R322" s="4" t="inlineStr"/>
+      <c r="S322" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S316"/>
+  <autoFilter ref="A1:S322"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -29740,7 +30433,7 @@
         </is>
       </c>
       <c r="B2" s="7">
-        <f>COUNTA(Catálogo!A2:A50)</f>
+        <f>COUNTA(Catálogo!A2:A52)</f>
         <v/>
       </c>
     </row>
@@ -29751,7 +30444,7 @@
         </is>
       </c>
       <c r="B3" s="7">
-        <f>COUNTIF(Catálogo!W2:W50,"pendiente")</f>
+        <f>COUNTIF(Catálogo!W2:W52,"pendiente")</f>
         <v/>
       </c>
     </row>
@@ -29762,7 +30455,7 @@
         </is>
       </c>
       <c r="B4" s="7">
-        <f>COUNTIF(Catálogo!W2:W50,"compuesta")</f>
+        <f>COUNTIF(Catálogo!W2:W52,"compuesta")</f>
         <v/>
       </c>
     </row>
@@ -29773,7 +30466,7 @@
         </is>
       </c>
       <c r="B5" s="7">
-        <f>COUNTIF(Catálogo!W2:W50,"montada")</f>
+        <f>COUNTIF(Catálogo!W2:W52,"montada")</f>
         <v/>
       </c>
     </row>
@@ -29784,7 +30477,7 @@
         </is>
       </c>
       <c r="B6" s="7">
-        <f>COUNTIF(Catálogo!W2:W50,"publicada")</f>
+        <f>COUNTIF(Catálogo!W2:W52,"publicada")</f>
         <v/>
       </c>
     </row>
@@ -29824,15 +30517,15 @@
         </is>
       </c>
       <c r="B10" s="7">
-        <f>COUNTIF(Catálogo!D2:D50,A10)</f>
+        <f>COUNTIF(Catálogo!D2:D52,A10)</f>
         <v/>
       </c>
       <c r="C10" s="7">
-        <f>COUNTIFS(Catálogo!D2:D50,A10,Catálogo!W2:W50,"publicada")</f>
+        <f>COUNTIFS(Catálogo!D2:D52,A10,Catálogo!W2:W52,"publicada")</f>
         <v/>
       </c>
       <c r="D10" s="7">
-        <f>SUMIF(Catálogo!D2:D50,A10,Catálogo!R2:R50)</f>
+        <f>SUMIF(Catálogo!D2:D52,A10,Catálogo!R2:R52)</f>
         <v/>
       </c>
     </row>
@@ -29843,15 +30536,15 @@
         </is>
       </c>
       <c r="B11" s="7">
-        <f>COUNTIF(Catálogo!D2:D50,A11)</f>
+        <f>COUNTIF(Catálogo!D2:D52,A11)</f>
         <v/>
       </c>
       <c r="C11" s="7">
-        <f>COUNTIFS(Catálogo!D2:D50,A11,Catálogo!W2:W50,"publicada")</f>
+        <f>COUNTIFS(Catálogo!D2:D52,A11,Catálogo!W2:W52,"publicada")</f>
         <v/>
       </c>
       <c r="D11" s="7">
-        <f>SUMIF(Catálogo!D2:D50,A11,Catálogo!R2:R50)</f>
+        <f>SUMIF(Catálogo!D2:D52,A11,Catálogo!R2:R52)</f>
         <v/>
       </c>
     </row>
@@ -29862,15 +30555,15 @@
         </is>
       </c>
       <c r="B12" s="7">
-        <f>COUNTIF(Catálogo!D2:D50,A12)</f>
+        <f>COUNTIF(Catálogo!D2:D52,A12)</f>
         <v/>
       </c>
       <c r="C12" s="7">
-        <f>COUNTIFS(Catálogo!D2:D50,A12,Catálogo!W2:W50,"publicada")</f>
+        <f>COUNTIFS(Catálogo!D2:D52,A12,Catálogo!W2:W52,"publicada")</f>
         <v/>
       </c>
       <c r="D12" s="7">
-        <f>SUMIF(Catálogo!D2:D50,A12,Catálogo!R2:R50)</f>
+        <f>SUMIF(Catálogo!D2:D52,A12,Catálogo!R2:R52)</f>
         <v/>
       </c>
     </row>
@@ -29881,15 +30574,15 @@
         </is>
       </c>
       <c r="B13" s="7">
-        <f>COUNTIF(Catálogo!D2:D50,A13)</f>
+        <f>COUNTIF(Catálogo!D2:D52,A13)</f>
         <v/>
       </c>
       <c r="C13" s="7">
-        <f>COUNTIFS(Catálogo!D2:D50,A13,Catálogo!W2:W50,"publicada")</f>
+        <f>COUNTIFS(Catálogo!D2:D52,A13,Catálogo!W2:W52,"publicada")</f>
         <v/>
       </c>
       <c r="D13" s="7">
-        <f>SUMIF(Catálogo!D2:D50,A13,Catálogo!R2:R50)</f>
+        <f>SUMIF(Catálogo!D2:D52,A13,Catálogo!R2:R52)</f>
         <v/>
       </c>
     </row>
@@ -29900,15 +30593,15 @@
         </is>
       </c>
       <c r="B14" s="7">
-        <f>COUNTIF(Catálogo!D2:D50,A14)</f>
+        <f>COUNTIF(Catálogo!D2:D52,A14)</f>
         <v/>
       </c>
       <c r="C14" s="7">
-        <f>COUNTIFS(Catálogo!D2:D50,A14,Catálogo!W2:W50,"publicada")</f>
+        <f>COUNTIFS(Catálogo!D2:D52,A14,Catálogo!W2:W52,"publicada")</f>
         <v/>
       </c>
       <c r="D14" s="7">
-        <f>SUMIF(Catálogo!D2:D50,A14,Catálogo!R2:R50)</f>
+        <f>SUMIF(Catálogo!D2:D52,A14,Catálogo!R2:R52)</f>
         <v/>
       </c>
     </row>
@@ -29945,7 +30638,7 @@
         </is>
       </c>
       <c r="B18" s="7">
-        <f>SUM(Catálogo!Y2:Y50)</f>
+        <f>SUM(Catálogo!Y2:Y52)</f>
         <v/>
       </c>
     </row>
@@ -29956,7 +30649,7 @@
         </is>
       </c>
       <c r="B19" s="7">
-        <f>SUM(Catálogo!Z2:Z50)</f>
+        <f>SUM(Catálogo!Z2:Z52)</f>
         <v/>
       </c>
     </row>
@@ -30099,7 +30792,7 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Ambiente aprobado en escucha: mar, mar-aves, zen, selva, lluvia-tambor, jardin, lluvia, theta o guqin.</t>
+          <t>Ambiente aprobado en escucha: mar, mar-aves, zen, selva, lluvia-tambor, jardin, lluvia, theta, guqin, marron o delta.</t>
         </is>
       </c>
     </row>

--- a/08-catalogo/catalogo_canal.xlsx
+++ b/08-catalogo/catalogo_canal.xlsx
@@ -6702,7 +6702,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>Brown noise and pink noise are the most searched sounds for sleep. This is brown noise: low, warm and steady, with distant temple bells.
+          <t>Brown noise for deep sleep: low, warm and steady, with distant temple bells.
 Like heavy rain on a faraway roof. No beat, no melody to follow, nothing to listen for. The screen fades to black after 3 minutes.
 🌙 Lights off, phone face down, volume low. Let it cover the noise.
 🌿 Subscribe for a new calm piece every week: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
@@ -6821,7 +6821,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Pink noise and brown noise are the most searched sounds for sleep, and pink noise with delta waves is the pairing sleep apps use in their sleep category. 🎧 Use headphones for the best experience.
+          <t>Pink noise with delta waves for deep sleep. 🎧 Use headphones for the best experience.
 Pink noise is soft and even, like steady rain. Underneath, each ear hears a slightly different tone: the difference starts at 3 Hz and slows to 1.5 Hz, the rhythm of deep sleep. The screen fades to black after 3 minutes.
 🌙 Headphones on, lights off, volume low.
 🌿 Subscribe for a new calm piece every week: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1

--- a/08-catalogo/catalogo_canal.xlsx
+++ b/08-catalogo/catalogo_canal.xlsx
@@ -6182,7 +6182,7 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/ambiente.py audio/OBRA-045_432_yu.wav audio/OBRA-045_final.wav --fondo lluvia --nivel-obra 0 --nivel-fondo -6 --entrada-obra 6</t>
+          <t>python3 03-composicion/ambiente.py audio/OBRA-045_432_yu.wav audio/OBRA-045_final.wav --fondo lluvia --nivel-obra 0 --nivel-fondo -6 --entrada-obra 6 --corte-obra 70</t>
         </is>
       </c>
       <c r="W46" s="4" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/ambiente.py audio/OBRA-046_432_yu.wav audio/OBRA-046_final.wav --fondo lluvia --nivel-obra 0 --nivel-fondo -6 --entrada-obra 6</t>
+          <t>python3 03-composicion/ambiente.py audio/OBRA-046_432_yu.wav audio/OBRA-046_final.wav --fondo lluvia --nivel-obra 0 --nivel-fondo -6 --entrada-obra 6 --corte-obra 70</t>
         </is>
       </c>
       <c r="W47" s="4" t="inlineStr">

--- a/08-catalogo/catalogo_canal.xlsx
+++ b/08-catalogo/catalogo_canal.xlsx
@@ -1870,7 +1870,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py zen 1840 audio/OBRA-010_capa.wav --semilla 739461 --raiz 432 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-010_432_hirajoshi.wav audio/OBRA-010_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-010_capa.wav</t>
+          <t>python3 03-composicion/capas.py zen 1840 audio/OBRA-010_capa.wav --semilla 739461 --raiz 432 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-010_432_hirajoshi.wav audio/OBRA-010_final.wav --fondo mar --nivel-fondo -12 --nivel-capa 2 --capa audio/OBRA-010_capa.wav</t>
         </is>
       </c>
       <c r="W11" s="4" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py zen 640 audio/OBRA-012_capa.wav --semilla 43734 --raiz 528 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-012_528_shin.wav audio/OBRA-012_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-012_capa.wav</t>
+          <t>python3 03-composicion/capas.py zen 640 audio/OBRA-012_capa.wav --semilla 43734 --raiz 528 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-012_528_shin.wav audio/OBRA-012_final.wav --fondo mar --nivel-fondo -12 --nivel-capa 2 --capa audio/OBRA-012_capa.wav</t>
         </is>
       </c>
       <c r="W13" s="4" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py zen 1240 audio/OBRA-014_capa.wav --semilla 310137 --raiz 528 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-014_528_yo.wav audio/OBRA-014_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-014_capa.wav</t>
+          <t>python3 03-composicion/capas.py zen 1240 audio/OBRA-014_capa.wav --semilla 310137 --raiz 528 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-014_528_yo.wav audio/OBRA-014_final.wav --fondo mar --nivel-fondo -12 --nivel-capa 2 --capa audio/OBRA-014_capa.wav</t>
         </is>
       </c>
       <c r="W15" s="4" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py zen 2740 audio/OBRA-017_capa.wav --semilla 714152 --raiz 417 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-017_417_hirajoshi.wav audio/OBRA-017_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-017_capa.wav</t>
+          <t>python3 03-composicion/capas.py zen 2740 audio/OBRA-017_capa.wav --semilla 714152 --raiz 417 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-017_417_hirajoshi.wav audio/OBRA-017_final.wav --fondo mar --nivel-fondo -12 --nivel-capa 2 --capa audio/OBRA-017_capa.wav</t>
         </is>
       </c>
       <c r="W18" s="4" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py zen 2740 audio/OBRA-018_capa.wav --semilla 735455 --raiz 528 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-018_528_hirajoshi.wav audio/OBRA-018_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-018_capa.wav</t>
+          <t>python3 03-composicion/capas.py zen 2740 audio/OBRA-018_capa.wav --semilla 735455 --raiz 528 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-018_528_hirajoshi.wav audio/OBRA-018_final.wav --fondo mar --nivel-fondo -12 --nivel-capa 2 --capa audio/OBRA-018_capa.wav</t>
         </is>
       </c>
       <c r="W19" s="4" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py zen 3640 audio/OBRA-019_capa.wav --semilla 627577 --raiz 432 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-019_432_shin.wav audio/OBRA-019_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-019_capa.wav</t>
+          <t>python3 03-composicion/capas.py zen 3640 audio/OBRA-019_capa.wav --semilla 627577 --raiz 432 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-019_432_shin.wav audio/OBRA-019_final.wav --fondo mar --nivel-fondo -12 --nivel-capa 2 --capa audio/OBRA-019_capa.wav</t>
         </is>
       </c>
       <c r="W20" s="4" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py zen 2740 audio/OBRA-021_capa.wav --semilla 864630 --raiz 396 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-021_396_kumoi.wav audio/OBRA-021_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-021_capa.wav</t>
+          <t>python3 03-composicion/capas.py zen 2740 audio/OBRA-021_capa.wav --semilla 864630 --raiz 396 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-021_396_kumoi.wav audio/OBRA-021_final.wav --fondo mar --nivel-fondo -12 --nivel-capa 2 --capa audio/OBRA-021_capa.wav</t>
         </is>
       </c>
       <c r="W22" s="4" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py zen 3640 audio/OBRA-022_capa.wav --semilla 335798 --raiz 639 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-022_639_yo.wav audio/OBRA-022_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-022_capa.wav</t>
+          <t>python3 03-composicion/capas.py zen 3640 audio/OBRA-022_capa.wav --semilla 335798 --raiz 639 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-022_639_yo.wav audio/OBRA-022_final.wav --fondo mar --nivel-fondo -12 --nivel-capa 2 --capa audio/OBRA-022_capa.wav</t>
         </is>
       </c>
       <c r="W23" s="4" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py zen 1240 audio/OBRA-023_capa.wav --semilla 299306 --raiz 528 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-023_528_shin.wav audio/OBRA-023_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-023_capa.wav</t>
+          <t>python3 03-composicion/capas.py zen 1240 audio/OBRA-023_capa.wav --semilla 299306 --raiz 528 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-023_528_shin.wav audio/OBRA-023_final.wav --fondo mar --nivel-fondo -12 --nivel-capa 2 --capa audio/OBRA-023_capa.wav</t>
         </is>
       </c>
       <c r="W24" s="4" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py zen 2740 audio/OBRA-028_capa.wav --semilla 409966 --raiz 417 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-028_417_hirajoshi.wav audio/OBRA-028_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-028_capa.wav</t>
+          <t>python3 03-composicion/capas.py zen 2740 audio/OBRA-028_capa.wav --semilla 409966 --raiz 417 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-028_417_hirajoshi.wav audio/OBRA-028_final.wav --fondo mar --nivel-fondo -12 --nivel-capa 2 --capa audio/OBRA-028_capa.wav</t>
         </is>
       </c>
       <c r="W29" s="4" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py zen 2740 audio/OBRA-031_capa.wav --semilla 288169 --raiz 852 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-031_852_hirajoshi.wav audio/OBRA-031_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-031_capa.wav</t>
+          <t>python3 03-composicion/capas.py zen 2740 audio/OBRA-031_capa.wav --semilla 288169 --raiz 852 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-031_852_hirajoshi.wav audio/OBRA-031_final.wav --fondo mar --nivel-fondo -12 --nivel-capa 2 --capa audio/OBRA-031_capa.wav</t>
         </is>
       </c>
       <c r="W32" s="4" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py jardin 3640 audio/OBRA-041_capa.wav --semilla 304617 --raiz 432 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-041_432_hirajoshi.wav audio/OBRA-041_final.wav --fondo mar --nivel-fondo -8 --nivel-capa 0 --capa audio/OBRA-041_capa.wav</t>
+          <t>python3 03-composicion/capas.py jardin 3640 audio/OBRA-041_capa.wav --semilla 304617 --raiz 432 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-041_432_hirajoshi.wav audio/OBRA-041_final.wav --fondo mar --nivel-fondo -13 --nivel-capa 0 --capa audio/OBRA-041_capa.wav</t>
         </is>
       </c>
       <c r="W42" s="4" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py zen 10840 audio/OBRA-042_capa.wav --semilla 266691 --raiz 528 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-042_528_shin.wav audio/OBRA-042_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-042_capa.wav</t>
+          <t>python3 03-composicion/capas.py zen 10840 audio/OBRA-042_capa.wav --semilla 266691 --raiz 528 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-042_528_shin.wav audio/OBRA-042_final.wav --fondo mar --nivel-fondo -12 --nivel-capa 2 --capa audio/OBRA-042_capa.wav</t>
         </is>
       </c>
       <c r="W43" s="4" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Woke Up at 3 AM? 🌙 Chinese Guqin &amp; Rain to Fall Back Asleep · Dark Screen · 3 Hours</t>
+          <t>Woke Up at 3 AM? 🌙 Chinese Guqin &amp; Xiao Flute to Fall Back Asleep · Dark Screen · 3 Hours</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Música para dormir · Guqin y lluvia · 432 Hz · Las tres de la mañana · 3 horas</t>
+          <t>Música para dormir · Guqin y flauta xiao · 432 Hz · Las tres de la mañana · 3 horas</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -6107,9 +6107,9 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Woke up at 3 AM again? Three hours of guqin, xiao flute and gentle rain to fall back asleep.
+          <t>Woke up at 3 AM again? Three hours of Chinese guqin and xiao flute to fall back asleep.
 In the Chinese body clock, 1 to 3 AM is the liver's hour: the hour of what you couldn't let go of. Don't check the time. Breathe out slowly through your lips, "shhh" (xū), six times, and let the strings take it from there. The screen fades to black after 3 minutes.
-🌙 Phone face down, volume low. The music thins out over the hours, until only the rain is left.
+🌙 Phone face down, volume low. The music thins out over the hours, until only soft harmonics are left.
 🌿 Subscribe for a new calm piece every week: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
 Original composition by Rin, synthesized from scratch in just intonation around 432 Hz, yu mode. No samples. The yu scale is the one Chinese five-element music keeps for the night. A 2,000-year-old tradition, not medical advice.
 #sleepmusic #guqin #chinesemusic</t>
@@ -6119,7 +6119,7 @@
         <is>
           <t>Las tres de la mañana · 3 horas
 Para acompañar el sueño.
-Ambiente: guqin y lluvia.
+Ambiente: guqin y flauta xiao.
 Compuesta con raíz en 432 Hz, en entonación justa, modo yu.
 Ciclo respiratorio: de 4.5 a 3.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
@@ -6140,7 +6140,7 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>woke up at 3am, fall back asleep, music to fall back asleep, chinese sleep music, guqin, guqin music, chinese meditation music, chinese music for sleep, rain sounds for sleeping, dark screen sleep music, black screen sleep music, deep sleep music, sleep music, traditional chinese medicine, chinamaxxing, 3 hours, rin, música para dormir</t>
+          <t>woke up at 3am, fall back asleep, music to fall back asleep, chinese sleep music, guqin, guqin music, chinese meditation music, chinese music for sleep, chinese flute music, dark screen sleep music, black screen sleep music, deep sleep music, sleep music, traditional chinese medicine, chinamaxxing, 3 hours, rin, música para dormir</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr"/>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/ambiente.py audio/OBRA-045_432_yu.wav audio/OBRA-045_final.wav --fondo lluvia --nivel-obra 0 --nivel-fondo -6 --entrada-obra 6 --corte-obra 70</t>
+          <t>python3 03-composicion/ambiente.py audio/OBRA-045_432_yu.wav audio/OBRA-045_final.wav --fondo nada --nivel-obra 0 --entrada-obra 6 --corte-obra 70</t>
         </is>
       </c>
       <c r="W46" s="4" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>3 AM Reset 🌙 10 Minutes of Guqin &amp; Rain to Fall Back Asleep · Chinese Sleep Music</t>
+          <t>3 AM Reset 🌙 10 Minutes of Chinese Guqin to Fall Back Asleep · Sleep Music</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Música para dormir · Guqin y lluvia · 432 Hz · Volver a dormir · 10 minutos</t>
+          <t>Música para dormir · Guqin y flauta xiao · 432 Hz · Volver a dormir · 10 minutos</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>Woke up at 3 AM? Ten minutes of guqin, xiao flute and gentle rain to fall back asleep.
+          <t>Woke up at 3 AM? Ten minutes of Chinese guqin and xiao flute to fall back asleep.
 Don't check the time. Breathe out slowly through your lips, "shhh", six times, and let the strings take it from there.
 🌙 Phone face down, volume low. If you're still awake at the end, the full 3 hours are on the channel.
 🌿 Subscribe for a new calm piece every week: https://www.youtube.com/@rinchanneloficial?sub_confirmation=1
@@ -6238,7 +6238,7 @@
         <is>
           <t>Volver a dormir · 10 minutos
 Para acompañar el sueño.
-Ambiente: guqin y lluvia.
+Ambiente: guqin y flauta xiao.
 Compuesta con raíz en 432 Hz, en entonación justa, modo yu.
 Ciclo respiratorio: de 4.5 a 3.5 respiraciones por minuto, inhalar 40 % / exhalar 60 %.
 Composición original, sintetizada desde cero: el ambiente también. Ninguna muestra procede de terceros.
@@ -6259,7 +6259,7 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>3am reset, fall back asleep, woke up at 3am, music to fall back asleep, guqin, chinese sleep music, 10 minute sleep music, rain sounds for sleeping, sleep music, chinese meditation music, rin, música para dormir</t>
+          <t>3am reset, fall back asleep, woke up at 3am, music to fall back asleep, guqin, chinese sleep music, 10 minute sleep music, chinese flute music, sleep music, chinese meditation music, rin, música para dormir</t>
         </is>
       </c>
       <c r="K47" s="4" t="inlineStr"/>
@@ -6301,7 +6301,7 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/ambiente.py audio/OBRA-046_432_yu.wav audio/OBRA-046_final.wav --fondo lluvia --nivel-obra 0 --nivel-fondo -6 --entrada-obra 6 --corte-obra 70</t>
+          <t>python3 03-composicion/ambiente.py audio/OBRA-046_432_yu.wav audio/OBRA-046_final.wav --fondo nada --nivel-obra 0 --entrada-obra 6 --corte-obra 70</t>
         </is>
       </c>
       <c r="W47" s="4" t="inlineStr">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py zen 340 audio/OBRA-047_capa.wav --semilla 756077 --raiz 528 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-047_528_shin.wav audio/OBRA-047_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-047_capa.wav</t>
+          <t>python3 03-composicion/capas.py zen 340 audio/OBRA-047_capa.wav --semilla 756077 --raiz 528 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-047_528_shin.wav audio/OBRA-047_final.wav --fondo mar --nivel-fondo -12 --nivel-capa 2 --capa audio/OBRA-047_capa.wav</t>
         </is>
       </c>
       <c r="W48" s="4" t="inlineStr">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>Do bells help you sleep, or do you prefer rain? 🔔🌧️ Tell us, it shapes the next piece.</t>
+          <t>Do bells help you sleep? 🔔 Tell us what sound you want next, it shapes the next piece.</t>
         </is>
       </c>
       <c r="U49" s="3" t="inlineStr">
@@ -6539,7 +6539,7 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py zen 10840 audio/OBRA-048_capa.wav --semilla 762820 --raiz 432 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-048_432_kumoi.wav audio/OBRA-048_final.wav --fondo mar --nivel-fondo -7 --nivel-capa 2 --capa audio/OBRA-048_capa.wav</t>
+          <t>python3 03-composicion/capas.py zen 10840 audio/OBRA-048_capa.wav --semilla 762820 --raiz 432 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-048_432_kumoi.wav audio/OBRA-048_final.wav --fondo mar --nivel-fondo -12 --nivel-capa 2 --capa audio/OBRA-048_capa.wav</t>
         </is>
       </c>
       <c r="W49" s="4" t="inlineStr">
@@ -6658,7 +6658,7 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py jardin 640 audio/OBRA-049_capa.wav --semilla 341227 --raiz 432 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-049_432_hirajoshi.wav audio/OBRA-049_final.wav --fondo mar --nivel-fondo -8 --nivel-capa 0 --capa audio/OBRA-049_capa.wav</t>
+          <t>python3 03-composicion/capas.py jardin 640 audio/OBRA-049_capa.wav --semilla 341227 --raiz 432 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-049_432_hirajoshi.wav audio/OBRA-049_final.wav --fondo mar --nivel-fondo -13 --nivel-capa 0 --capa audio/OBRA-049_capa.wav</t>
         </is>
       </c>
       <c r="W50" s="4" t="inlineStr">
@@ -28920,19 +28920,19 @@
       </c>
       <c r="I302" s="3" t="inlineStr">
         <is>
-          <t>Breathe out longer than you breathe in · 432 Hz · Guqin and Rain</t>
+          <t>Breathe out longer than you breathe in · 432 Hz · Guqin and Xiao Flute</t>
         </is>
       </c>
       <c r="J302" s="3" t="inlineStr">
         <is>
           <t>Save this for tonight.
-Full piece (3 h): Woke Up at 3 AM? 🌙 Chinese Guqin &amp; Rain to Fall Back Asleep · Dark Screen · 3 Hours
+Full piece (3 h): Woke Up at 3 AM? 🌙 Chinese Guqin &amp; Xiao Flute to Fall Back Asleep · Dark Screen · 3 Hours
 #sleepmusic #sleep #relaxingmusic #432hz #shorts</t>
         </is>
       </c>
       <c r="K302" s="2" t="inlineStr">
         <is>
-          <t>sleep music, deep sleep, 432 hz, guqin and rain, Rin</t>
+          <t>sleep music, deep sleep, 432 hz, guqin and xiao flute, Rin</t>
         </is>
       </c>
       <c r="L302" s="2" t="inlineStr"/>
@@ -28992,19 +28992,19 @@
       </c>
       <c r="I303" s="3" t="inlineStr">
         <is>
-          <t>Unclench your jaw. Let the pillow hold you · 432 Hz · Guqin and Rain</t>
+          <t>Unclench your jaw. Let the pillow hold you · 432 Hz · Guqin and Xiao Flute</t>
         </is>
       </c>
       <c r="J303" s="3" t="inlineStr">
         <is>
           <t>Lights off, volume low.
-Full piece (3 h): Woke Up at 3 AM? 🌙 Chinese Guqin &amp; Rain to Fall Back Asleep · Dark Screen · 3 Hours
+Full piece (3 h): Woke Up at 3 AM? 🌙 Chinese Guqin &amp; Xiao Flute to Fall Back Asleep · Dark Screen · 3 Hours
 #sleepmusic #sleep #relaxingmusic #432hz #shorts</t>
         </is>
       </c>
       <c r="K303" s="2" t="inlineStr">
         <is>
-          <t>sleep music, deep sleep, 432 hz, guqin and rain, Rin</t>
+          <t>sleep music, deep sleep, 432 hz, guqin and xiao flute, Rin</t>
         </is>
       </c>
       <c r="L303" s="2" t="inlineStr"/>
@@ -29064,19 +29064,19 @@
       </c>
       <c r="I304" s="3" t="inlineStr">
         <is>
-          <t>Close your eyes. Just listen · 432 Hz · Guqin and Rain</t>
+          <t>Close your eyes. Just listen · 432 Hz · Guqin and Xiao Flute</t>
         </is>
       </c>
       <c r="J304" s="3" t="inlineStr">
         <is>
           <t>Stay until your breathing slows.
-Full piece (3 h): Woke Up at 3 AM? 🌙 Chinese Guqin &amp; Rain to Fall Back Asleep · Dark Screen · 3 Hours
+Full piece (3 h): Woke Up at 3 AM? 🌙 Chinese Guqin &amp; Xiao Flute to Fall Back Asleep · Dark Screen · 3 Hours
 #sleepmusic #sleep #relaxingmusic #432hz #shorts</t>
         </is>
       </c>
       <c r="K304" s="2" t="inlineStr">
         <is>
-          <t>sleep music, deep sleep, 432 hz, guqin and rain, Rin</t>
+          <t>sleep music, deep sleep, 432 hz, guqin and xiao flute, Rin</t>
         </is>
       </c>
       <c r="L304" s="2" t="inlineStr"/>
@@ -29136,19 +29136,19 @@
       </c>
       <c r="I305" s="3" t="inlineStr">
         <is>
-          <t>Breathe out longer than you breathe in · 432 Hz · Guqin and Rain</t>
+          <t>Breathe out longer than you breathe in · 432 Hz · Guqin and Xiao Flute</t>
         </is>
       </c>
       <c r="J305" s="3" t="inlineStr">
         <is>
           <t>Save this for tonight.
-Full piece (10 min): 3 AM Reset 🌙 10 Minutes of Guqin &amp; Rain to Fall Back Asleep · Chinese Sleep Music
+Full piece (10 min): 3 AM Reset 🌙 10 Minutes of Chinese Guqin to Fall Back Asleep · Sleep Music
 #sleepmusic #sleep #relaxingmusic #432hz #shorts</t>
         </is>
       </c>
       <c r="K305" s="2" t="inlineStr">
         <is>
-          <t>sleep music, deep sleep, 432 hz, guqin and rain, Rin</t>
+          <t>sleep music, deep sleep, 432 hz, guqin and xiao flute, Rin</t>
         </is>
       </c>
       <c r="L305" s="2" t="inlineStr"/>
@@ -29208,19 +29208,19 @@
       </c>
       <c r="I306" s="3" t="inlineStr">
         <is>
-          <t>Unclench your jaw. Let the pillow hold you · 432 Hz · Guqin and Rain</t>
+          <t>Unclench your jaw. Let the pillow hold you · 432 Hz · Guqin and Xiao Flute</t>
         </is>
       </c>
       <c r="J306" s="3" t="inlineStr">
         <is>
           <t>Lights off, volume low.
-Full piece (10 min): 3 AM Reset 🌙 10 Minutes of Guqin &amp; Rain to Fall Back Asleep · Chinese Sleep Music
+Full piece (10 min): 3 AM Reset 🌙 10 Minutes of Chinese Guqin to Fall Back Asleep · Sleep Music
 #sleepmusic #sleep #relaxingmusic #432hz #shorts</t>
         </is>
       </c>
       <c r="K306" s="2" t="inlineStr">
         <is>
-          <t>sleep music, deep sleep, 432 hz, guqin and rain, Rin</t>
+          <t>sleep music, deep sleep, 432 hz, guqin and xiao flute, Rin</t>
         </is>
       </c>
       <c r="L306" s="2" t="inlineStr"/>
@@ -29280,19 +29280,19 @@
       </c>
       <c r="I307" s="3" t="inlineStr">
         <is>
-          <t>Close your eyes. Just listen · 432 Hz · Guqin and Rain</t>
+          <t>Close your eyes. Just listen · 432 Hz · Guqin and Xiao Flute</t>
         </is>
       </c>
       <c r="J307" s="3" t="inlineStr">
         <is>
           <t>Stay until your breathing slows.
-Full piece (10 min): 3 AM Reset 🌙 10 Minutes of Guqin &amp; Rain to Fall Back Asleep · Chinese Sleep Music
+Full piece (10 min): 3 AM Reset 🌙 10 Minutes of Chinese Guqin to Fall Back Asleep · Sleep Music
 #sleepmusic #sleep #relaxingmusic #432hz #shorts</t>
         </is>
       </c>
       <c r="K307" s="2" t="inlineStr">
         <is>
-          <t>sleep music, deep sleep, 432 hz, guqin and rain, Rin</t>
+          <t>sleep music, deep sleep, 432 hz, guqin and xiao flute, Rin</t>
         </is>
       </c>
       <c r="L307" s="2" t="inlineStr"/>

--- a/08-catalogo/catalogo_canal.xlsx
+++ b/08-catalogo/catalogo_canal.xlsx
@@ -6182,7 +6182,7 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/ambiente.py audio/OBRA-045_432_yu.wav audio/OBRA-045_final.wav --fondo nada --nivel-obra 0 --entrada-obra 6 --corte-obra 70</t>
+          <t>python3 03-composicion/ambiente.py audio/OBRA-045_432_yu.wav audio/OBRA-045_final.wav --fondo nada --nivel-obra 0 --entrada-obra 1.5 --corte-obra 70</t>
         </is>
       </c>
       <c r="W46" s="4" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/ambiente.py audio/OBRA-046_432_yu.wav audio/OBRA-046_final.wav --fondo nada --nivel-obra 0 --entrada-obra 6 --corte-obra 70</t>
+          <t>python3 03-composicion/ambiente.py audio/OBRA-046_432_yu.wav audio/OBRA-046_final.wav --fondo nada --nivel-obra 0 --entrada-obra 1.5 --corte-obra 70</t>
         </is>
       </c>
       <c r="W47" s="4" t="inlineStr">

--- a/08-catalogo/catalogo_canal.xlsx
+++ b/08-catalogo/catalogo_canal.xlsx
@@ -1870,7 +1870,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py zen 1840 audio/OBRA-010_capa.wav --semilla 739461 --raiz 432 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-010_432_hirajoshi.wav audio/OBRA-010_final.wav --fondo mar --nivel-fondo -12 --nivel-capa 2 --capa audio/OBRA-010_capa.wav</t>
+          <t>python3 03-composicion/capas.py zen 1840 audio/OBRA-010_capa.wav --semilla 739461 --raiz 432 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-010_432_hirajoshi.wav audio/OBRA-010_final.wav --fondo mar --nivel-fondo -12 --nivel-capa 2 --nivel-obra -23 --capa audio/OBRA-010_capa.wav</t>
         </is>
       </c>
       <c r="W11" s="4" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py zen 640 audio/OBRA-012_capa.wav --semilla 43734 --raiz 528 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-012_528_shin.wav audio/OBRA-012_final.wav --fondo mar --nivel-fondo -12 --nivel-capa 2 --capa audio/OBRA-012_capa.wav</t>
+          <t>python3 03-composicion/capas.py zen 640 audio/OBRA-012_capa.wav --semilla 43734 --raiz 528 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-012_528_shin.wav audio/OBRA-012_final.wav --fondo mar --nivel-fondo -12 --nivel-capa 2 --nivel-obra -23 --capa audio/OBRA-012_capa.wav</t>
         </is>
       </c>
       <c r="W13" s="4" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py zen 1240 audio/OBRA-014_capa.wav --semilla 310137 --raiz 528 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-014_528_yo.wav audio/OBRA-014_final.wav --fondo mar --nivel-fondo -12 --nivel-capa 2 --capa audio/OBRA-014_capa.wav</t>
+          <t>python3 03-composicion/capas.py zen 1240 audio/OBRA-014_capa.wav --semilla 310137 --raiz 528 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-014_528_yo.wav audio/OBRA-014_final.wav --fondo mar --nivel-fondo -12 --nivel-capa 2 --nivel-obra -23 --capa audio/OBRA-014_capa.wav</t>
         </is>
       </c>
       <c r="W15" s="4" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py zen 2740 audio/OBRA-017_capa.wav --semilla 714152 --raiz 417 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-017_417_hirajoshi.wav audio/OBRA-017_final.wav --fondo mar --nivel-fondo -12 --nivel-capa 2 --capa audio/OBRA-017_capa.wav</t>
+          <t>python3 03-composicion/capas.py zen 2740 audio/OBRA-017_capa.wav --semilla 714152 --raiz 417 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-017_417_hirajoshi.wav audio/OBRA-017_final.wav --fondo mar --nivel-fondo -12 --nivel-capa 2 --nivel-obra -23 --capa audio/OBRA-017_capa.wav</t>
         </is>
       </c>
       <c r="W18" s="4" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py zen 2740 audio/OBRA-018_capa.wav --semilla 735455 --raiz 528 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-018_528_hirajoshi.wav audio/OBRA-018_final.wav --fondo mar --nivel-fondo -12 --nivel-capa 2 --capa audio/OBRA-018_capa.wav</t>
+          <t>python3 03-composicion/capas.py zen 2740 audio/OBRA-018_capa.wav --semilla 735455 --raiz 528 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-018_528_hirajoshi.wav audio/OBRA-018_final.wav --fondo mar --nivel-fondo -12 --nivel-capa 2 --nivel-obra -23 --capa audio/OBRA-018_capa.wav</t>
         </is>
       </c>
       <c r="W19" s="4" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py zen 3640 audio/OBRA-019_capa.wav --semilla 627577 --raiz 432 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-019_432_shin.wav audio/OBRA-019_final.wav --fondo mar --nivel-fondo -12 --nivel-capa 2 --capa audio/OBRA-019_capa.wav</t>
+          <t>python3 03-composicion/capas.py zen 3640 audio/OBRA-019_capa.wav --semilla 627577 --raiz 432 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-019_432_shin.wav audio/OBRA-019_final.wav --fondo mar --nivel-fondo -12 --nivel-capa 2 --nivel-obra -23 --capa audio/OBRA-019_capa.wav</t>
         </is>
       </c>
       <c r="W20" s="4" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py zen 2740 audio/OBRA-021_capa.wav --semilla 864630 --raiz 396 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-021_396_kumoi.wav audio/OBRA-021_final.wav --fondo mar --nivel-fondo -12 --nivel-capa 2 --capa audio/OBRA-021_capa.wav</t>
+          <t>python3 03-composicion/capas.py zen 2740 audio/OBRA-021_capa.wav --semilla 864630 --raiz 396 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-021_396_kumoi.wav audio/OBRA-021_final.wav --fondo mar --nivel-fondo -12 --nivel-capa 2 --nivel-obra -23 --capa audio/OBRA-021_capa.wav</t>
         </is>
       </c>
       <c r="W22" s="4" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py zen 3640 audio/OBRA-022_capa.wav --semilla 335798 --raiz 639 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-022_639_yo.wav audio/OBRA-022_final.wav --fondo mar --nivel-fondo -12 --nivel-capa 2 --capa audio/OBRA-022_capa.wav</t>
+          <t>python3 03-composicion/capas.py zen 3640 audio/OBRA-022_capa.wav --semilla 335798 --raiz 639 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-022_639_yo.wav audio/OBRA-022_final.wav --fondo mar --nivel-fondo -12 --nivel-capa 2 --nivel-obra -23 --capa audio/OBRA-022_capa.wav</t>
         </is>
       </c>
       <c r="W23" s="4" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py zen 1240 audio/OBRA-023_capa.wav --semilla 299306 --raiz 528 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-023_528_shin.wav audio/OBRA-023_final.wav --fondo mar --nivel-fondo -12 --nivel-capa 2 --capa audio/OBRA-023_capa.wav</t>
+          <t>python3 03-composicion/capas.py zen 1240 audio/OBRA-023_capa.wav --semilla 299306 --raiz 528 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-023_528_shin.wav audio/OBRA-023_final.wav --fondo mar --nivel-fondo -12 --nivel-capa 2 --nivel-obra -23 --capa audio/OBRA-023_capa.wav</t>
         </is>
       </c>
       <c r="W24" s="4" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py zen 2740 audio/OBRA-028_capa.wav --semilla 409966 --raiz 417 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-028_417_hirajoshi.wav audio/OBRA-028_final.wav --fondo mar --nivel-fondo -12 --nivel-capa 2 --capa audio/OBRA-028_capa.wav</t>
+          <t>python3 03-composicion/capas.py zen 2740 audio/OBRA-028_capa.wav --semilla 409966 --raiz 417 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-028_417_hirajoshi.wav audio/OBRA-028_final.wav --fondo mar --nivel-fondo -12 --nivel-capa 2 --nivel-obra -23 --capa audio/OBRA-028_capa.wav</t>
         </is>
       </c>
       <c r="W29" s="4" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py zen 2740 audio/OBRA-031_capa.wav --semilla 288169 --raiz 852 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-031_852_hirajoshi.wav audio/OBRA-031_final.wav --fondo mar --nivel-fondo -12 --nivel-capa 2 --capa audio/OBRA-031_capa.wav</t>
+          <t>python3 03-composicion/capas.py zen 2740 audio/OBRA-031_capa.wav --semilla 288169 --raiz 852 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-031_852_hirajoshi.wav audio/OBRA-031_final.wav --fondo mar --nivel-fondo -12 --nivel-capa 2 --nivel-obra -23 --capa audio/OBRA-031_capa.wav</t>
         </is>
       </c>
       <c r="W32" s="4" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py jardin 3640 audio/OBRA-041_capa.wav --semilla 304617 --raiz 432 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-041_432_hirajoshi.wav audio/OBRA-041_final.wav --fondo mar --nivel-fondo -13 --nivel-capa 0 --capa audio/OBRA-041_capa.wav</t>
+          <t>python3 03-composicion/capas.py jardin 3640 audio/OBRA-041_capa.wav --semilla 304617 --raiz 432 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-041_432_hirajoshi.wav audio/OBRA-041_final.wav --fondo mar --nivel-fondo -13 --nivel-capa 0 --nivel-obra -23 --capa audio/OBRA-041_capa.wav</t>
         </is>
       </c>
       <c r="W42" s="4" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py zen 10840 audio/OBRA-042_capa.wav --semilla 266691 --raiz 528 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-042_528_shin.wav audio/OBRA-042_final.wav --fondo mar --nivel-fondo -12 --nivel-capa 2 --capa audio/OBRA-042_capa.wav</t>
+          <t>python3 03-composicion/capas.py zen 10840 audio/OBRA-042_capa.wav --semilla 266691 --raiz 528 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-042_528_shin.wav audio/OBRA-042_final.wav --fondo mar --nivel-fondo -12 --nivel-capa 2 --nivel-obra -23 --capa audio/OBRA-042_capa.wav</t>
         </is>
       </c>
       <c r="W43" s="4" t="inlineStr">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/ambiente.py audio/OBRA-045_432_yu.wav audio/OBRA-045_final.wav --fondo nada --nivel-obra 0 --entrada-obra 1.5 --corte-obra 70</t>
+          <t>python3 03-composicion/ambiente.py audio/OBRA-045_432_yu.wav audio/OBRA-045_final.wav --fondo nada --nivel-obra 0 --entrada-obra 1.5 --corte-obra 70 --intro 0.3 --cola 3</t>
         </is>
       </c>
       <c r="W46" s="4" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/ambiente.py audio/OBRA-046_432_yu.wav audio/OBRA-046_final.wav --fondo nada --nivel-obra 0 --entrada-obra 1.5 --corte-obra 70</t>
+          <t>python3 03-composicion/ambiente.py audio/OBRA-046_432_yu.wav audio/OBRA-046_final.wav --fondo nada --nivel-obra 0 --entrada-obra 1.5 --corte-obra 70 --intro 0.3 --cola 3</t>
         </is>
       </c>
       <c r="W47" s="4" t="inlineStr">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py zen 340 audio/OBRA-047_capa.wav --semilla 756077 --raiz 528 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-047_528_shin.wav audio/OBRA-047_final.wav --fondo mar --nivel-fondo -12 --nivel-capa 2 --capa audio/OBRA-047_capa.wav</t>
+          <t>python3 03-composicion/capas.py zen 340 audio/OBRA-047_capa.wav --semilla 756077 --raiz 528 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-047_528_shin.wav audio/OBRA-047_final.wav --fondo mar --nivel-fondo -12 --nivel-capa 2 --nivel-obra -23 --capa audio/OBRA-047_capa.wav</t>
         </is>
       </c>
       <c r="W48" s="4" t="inlineStr">
@@ -6539,7 +6539,7 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py zen 10840 audio/OBRA-048_capa.wav --semilla 762820 --raiz 432 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-048_432_kumoi.wav audio/OBRA-048_final.wav --fondo mar --nivel-fondo -12 --nivel-capa 2 --capa audio/OBRA-048_capa.wav</t>
+          <t>python3 03-composicion/capas.py zen 10840 audio/OBRA-048_capa.wav --semilla 762820 --raiz 432 --densidad 1.4 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-048_432_kumoi.wav audio/OBRA-048_final.wav --fondo mar --nivel-fondo -12 --nivel-capa 2 --nivel-obra -23 --capa audio/OBRA-048_capa.wav</t>
         </is>
       </c>
       <c r="W49" s="4" t="inlineStr">
@@ -6658,7 +6658,7 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/capas.py jardin 640 audio/OBRA-049_capa.wav --semilla 341227 --raiz 432 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-049_432_hirajoshi.wav audio/OBRA-049_final.wav --fondo mar --nivel-fondo -13 --nivel-capa 0 --capa audio/OBRA-049_capa.wav</t>
+          <t>python3 03-composicion/capas.py jardin 640 audio/OBRA-049_capa.wav --semilla 341227 --raiz 432 &amp;&amp; python3 03-composicion/ambiente.py audio/OBRA-049_432_hirajoshi.wav audio/OBRA-049_final.wav --fondo mar --nivel-fondo -13 --nivel-capa 0 --nivel-obra -23 --capa audio/OBRA-049_capa.wav</t>
         </is>
       </c>
       <c r="W50" s="4" t="inlineStr">

--- a/08-catalogo/catalogo_canal.xlsx
+++ b/08-catalogo/catalogo_canal.xlsx
@@ -6182,7 +6182,7 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/ambiente.py audio/OBRA-045_432_yu.wav audio/OBRA-045_final.wav --fondo nada --nivel-obra 0 --entrada-obra 1.5 --corte-obra 70 --intro 0.3 --cola 3</t>
+          <t>python3 03-composicion/ambiente.py audio/OBRA-045_432_yu.wav audio/OBRA-045_final.wav --fondo nada --nivel-obra 0 --entrada-obra 1.5 --corte-obra 70 --intro 0.3 --cola 1</t>
         </is>
       </c>
       <c r="W46" s="4" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>python3 03-composicion/ambiente.py audio/OBRA-046_432_yu.wav audio/OBRA-046_final.wav --fondo nada --nivel-obra 0 --entrada-obra 1.5 --corte-obra 70 --intro 0.3 --cola 3</t>
+          <t>python3 03-composicion/ambiente.py audio/OBRA-046_432_yu.wav audio/OBRA-046_final.wav --fondo nada --nivel-obra 0 --entrada-obra 1.5 --corte-obra 70 --intro 0.3 --cola 1</t>
         </is>
       </c>
       <c r="W47" s="4" t="inlineStr">
